--- a/audit_report_ALL_TEAM_10_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_10_Oct_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -851,10 +851,8 @@
           <t>Ravi Shahi</t>
         </is>
       </c>
-      <c r="O2" s="3" t="inlineStr">
-        <is>
-          <t>9851071622</t>
-        </is>
+      <c r="O2" s="3" t="n">
+        <v>9851071622</v>
       </c>
       <c r="P2" s="3" t="inlineStr">
         <is>
@@ -944,25 +942,21 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN2" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN2" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO2" s="3" t="inlineStr">
         <is>
           <t>3,2</t>
         </is>
       </c>
-      <c r="AP2" s="3" t="inlineStr">
-        <is>
-          <t>85.30718</t>
-        </is>
+      <c r="AP2" s="3" t="n">
+        <v>85.30718</v>
       </c>
       <c r="AQ2" s="3" t="inlineStr"/>
       <c r="AR2" s="3" t="inlineStr">
         <is>
-          <t>Case : For upgradation to wifi6   has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS2" s="3" t="inlineStr">
@@ -1058,10 +1052,8 @@
           <t>Roshan Shrestha</t>
         </is>
       </c>
-      <c r="O3" s="3" t="inlineStr">
-        <is>
-          <t>9700971170</t>
-        </is>
+      <c r="O3" s="3" t="n">
+        <v>9700971170</v>
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
@@ -1151,25 +1143,21 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN3" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN3" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO3" s="3" t="inlineStr">
         <is>
           <t>1,15</t>
         </is>
       </c>
-      <c r="AP3" s="3" t="inlineStr">
-        <is>
-          <t>85.33794</t>
-        </is>
+      <c r="AP3" s="3" t="n">
+        <v>85.33794</v>
       </c>
       <c r="AQ3" s="3" t="inlineStr"/>
       <c r="AR3" s="3" t="inlineStr">
         <is>
-          <t>Case : worst internet service   has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS3" s="3" t="inlineStr">

--- a/audit_report_ALL_TEAM_10_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_10_Oct_2026.xlsx
@@ -483,11 +483,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW3"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
     <col width="35" customWidth="1" min="3" max="3"/>
     <col width="21" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
@@ -496,40 +496,40 @@
     <col width="40" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
-    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="22" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="27" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
     <col width="26" customWidth="1" min="18" max="18"/>
     <col width="37" customWidth="1" min="19" max="19"/>
     <col width="37" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="16" customWidth="1" min="21" max="21"/>
     <col width="26" customWidth="1" min="22" max="22"/>
     <col width="26" customWidth="1" min="23" max="23"/>
     <col width="29" customWidth="1" min="24" max="24"/>
     <col width="12" customWidth="1" min="25" max="25"/>
     <col width="27" customWidth="1" min="26" max="26"/>
-    <col width="15" customWidth="1" min="27" max="27"/>
+    <col width="19" customWidth="1" min="27" max="27"/>
     <col width="14" customWidth="1" min="28" max="28"/>
     <col width="11" customWidth="1" min="29" max="29"/>
     <col width="10" customWidth="1" min="30" max="30"/>
     <col width="40" customWidth="1" min="31" max="31"/>
     <col width="25" customWidth="1" min="32" max="32"/>
-    <col width="29" customWidth="1" min="33" max="33"/>
+    <col width="38" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
-    <col width="10" customWidth="1" min="35" max="35"/>
+    <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
     <col width="17" customWidth="1" min="37" max="37"/>
-    <col width="16" customWidth="1" min="38" max="38"/>
+    <col width="17" customWidth="1" min="38" max="38"/>
     <col width="20" customWidth="1" min="39" max="39"/>
     <col width="28" customWidth="1" min="40" max="40"/>
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -1183,6 +1183,627 @@
       <c r="AW3" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 10:41 AM</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr"/>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>Case : upgrade wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>upgrade wifi 6</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>TKT1364446</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>Jeet Bahadur Basnet</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
+          <t>Jeet Bahadur Basnet</t>
+        </is>
+      </c>
+      <c r="O4" s="3" t="inlineStr">
+        <is>
+          <t>9823773885</t>
+        </is>
+      </c>
+      <c r="P4" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q4" s="3" t="inlineStr"/>
+      <c r="R4" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 10:40:59 AM</t>
+        </is>
+      </c>
+      <c r="S4" s="3" t="inlineStr"/>
+      <c r="T4" s="3" t="inlineStr"/>
+      <c r="U4" s="3" t="inlineStr">
+        <is>
+          <t>9840938326</t>
+        </is>
+      </c>
+      <c r="V4" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 12:30:31 PM</t>
+        </is>
+      </c>
+      <c r="W4" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 10:40:59 AM</t>
+        </is>
+      </c>
+      <c r="X4" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y4" s="3" t="inlineStr">
+        <is>
+          <t>27.701075</t>
+        </is>
+      </c>
+      <c r="Z4" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA4" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB4" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC4" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD4" s="3" t="inlineStr"/>
+      <c r="AE4" s="3" t="inlineStr">
+        <is>
+          <t>Pepsicola,forcepark buspark	, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF4" s="3" t="inlineStr"/>
+      <c r="AG4" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH4" s="3" t="inlineStr"/>
+      <c r="AI4" s="3" t="inlineStr">
+        <is>
+          <t>08:11 hour</t>
+        </is>
+      </c>
+      <c r="AJ4" s="3" t="inlineStr"/>
+      <c r="AK4" s="3" t="inlineStr"/>
+      <c r="AL4" s="3" t="inlineStr">
+        <is>
+          <t>Asmita Sunar</t>
+        </is>
+      </c>
+      <c r="AM4" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN4" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO4" s="3" t="inlineStr">
+        <is>
+          <t>L56-4</t>
+        </is>
+      </c>
+      <c r="AP4" s="3" t="inlineStr">
+        <is>
+          <t>85.379044</t>
+        </is>
+      </c>
+      <c r="AQ4" s="3" t="inlineStr"/>
+      <c r="AR4" s="3" t="inlineStr">
+        <is>
+          <t>Case : upgrade wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS4" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT4" s="3" t="inlineStr">
+        <is>
+          <t>22h 10m</t>
+        </is>
+      </c>
+      <c r="AU4" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV4" s="3" t="inlineStr">
+        <is>
+          <t>Case : upgrade wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW4" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 10:40 AM</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr"/>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6 upgrade</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>TKT1364411</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>Bijya Lama</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t>Bijya Lama</t>
+        </is>
+      </c>
+      <c r="O5" s="3" t="inlineStr">
+        <is>
+          <t>9843955238</t>
+        </is>
+      </c>
+      <c r="P5" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q5" s="3" t="inlineStr"/>
+      <c r="R5" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 10:40:30 AM</t>
+        </is>
+      </c>
+      <c r="S5" s="3" t="inlineStr"/>
+      <c r="T5" s="3" t="inlineStr"/>
+      <c r="U5" s="3" t="inlineStr">
+        <is>
+          <t>9843955238</t>
+        </is>
+      </c>
+      <c r="V5" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 12:06:35 PM</t>
+        </is>
+      </c>
+      <c r="W5" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 10:40:30 AM</t>
+        </is>
+      </c>
+      <c r="X5" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y5" s="3" t="inlineStr">
+        <is>
+          <t>27.68945</t>
+        </is>
+      </c>
+      <c r="Z5" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA5" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB5" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC5" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD5" s="3" t="inlineStr"/>
+      <c r="AE5" s="3" t="inlineStr">
+        <is>
+          <t>pepsicola Punchmukhi chowk . ward -35,kageshwori  municipality kathmandu Baghmati Nepal , Bagmati,</t>
+        </is>
+      </c>
+      <c r="AF5" s="3" t="inlineStr">
+        <is>
+          <t>bj.lama987@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG5" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH5" s="3" t="inlineStr"/>
+      <c r="AI5" s="3" t="inlineStr">
+        <is>
+          <t>08:34 hour</t>
+        </is>
+      </c>
+      <c r="AJ5" s="3" t="inlineStr"/>
+      <c r="AK5" s="3" t="inlineStr"/>
+      <c r="AL5" s="3" t="inlineStr">
+        <is>
+          <t>Merika Silwal</t>
+        </is>
+      </c>
+      <c r="AM5" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN5" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO5" s="3" t="inlineStr">
+        <is>
+          <t>L11-3</t>
+        </is>
+      </c>
+      <c r="AP5" s="3" t="inlineStr">
+        <is>
+          <t>85.36467</t>
+        </is>
+      </c>
+      <c r="AQ5" s="3" t="inlineStr"/>
+      <c r="AR5" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS5" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT5" s="3" t="inlineStr">
+        <is>
+          <t>22h 33m</t>
+        </is>
+      </c>
+      <c r="AU5" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV5" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW5" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 10:46 AM</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr"/>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>Case : sbt connection   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>sbt connection</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>TKT1363024</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>Sundar Regmi</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
+          <t>Sundar Regmi</t>
+        </is>
+      </c>
+      <c r="O6" s="3" t="inlineStr">
+        <is>
+          <t>9803357149</t>
+        </is>
+      </c>
+      <c r="P6" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="Q6" s="3" t="inlineStr"/>
+      <c r="R6" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 10:46:50 AM</t>
+        </is>
+      </c>
+      <c r="S6" s="3" t="inlineStr"/>
+      <c r="T6" s="3" t="inlineStr"/>
+      <c r="U6" s="3" t="inlineStr">
+        <is>
+          <t>KLK9803357149</t>
+        </is>
+      </c>
+      <c r="V6" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 10:22:13 AM</t>
+        </is>
+      </c>
+      <c r="W6" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 10:46:50 AM</t>
+        </is>
+      </c>
+      <c r="X6" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y6" s="3" t="inlineStr"/>
+      <c r="Z6" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="AA6" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB6" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC6" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD6" s="3" t="inlineStr"/>
+      <c r="AE6" s="3" t="inlineStr">
+        <is>
+          <t>ktm tokha chowk, Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF6" s="3" t="inlineStr">
+        <is>
+          <t>regmi8@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG6" s="3" t="inlineStr">
+        <is>
+          <t>NETTV-No internet connection in STB</t>
+        </is>
+      </c>
+      <c r="AH6" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI6" s="3" t="inlineStr"/>
+      <c r="AJ6" s="3" t="inlineStr"/>
+      <c r="AK6" s="3" t="inlineStr"/>
+      <c r="AL6" s="3" t="inlineStr">
+        <is>
+          <t>Manisha kunwar</t>
+        </is>
+      </c>
+      <c r="AM6" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN6" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO6" s="3" t="inlineStr">
+        <is>
+          <t>L14-8</t>
+        </is>
+      </c>
+      <c r="AP6" s="3" t="inlineStr"/>
+      <c r="AQ6" s="3" t="inlineStr"/>
+      <c r="AR6" s="3" t="inlineStr">
+        <is>
+          <t>Case : sbt connection   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS6" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT6" s="3" t="inlineStr">
+        <is>
+          <t>2d 24m</t>
+        </is>
+      </c>
+      <c r="AU6" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV6" s="3" t="inlineStr">
+        <is>
+          <t>Case : sbt connection   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW6" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
         </is>
       </c>
     </row>
@@ -1197,20 +1818,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M19"/>
+  <dimension ref="A1:M23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="39" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
     <col width="28" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
-    <col width="19" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
-    <col width="28" customWidth="1" min="8" max="8"/>
-    <col width="17" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="8" max="8"/>
+    <col width="27" customWidth="1" min="9" max="9"/>
+    <col width="27" customWidth="1" min="10" max="10"/>
+    <col width="27" customWidth="1" min="11" max="11"/>
     <col width="35" customWidth="1" min="12" max="12"/>
     <col width="34" customWidth="1" min="13" max="13"/>
   </cols>
@@ -1234,7 +1855,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
@@ -1244,7 +1865,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -1255,7 +1876,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
     </row>
@@ -1267,7 +1888,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0m</t>
         </is>
       </c>
     </row>
@@ -1279,7 +1900,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>22h 22m</t>
         </is>
       </c>
     </row>
@@ -1320,21 +1941,21 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>Slow Internet Connection</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="B11" s="5" t="n">
@@ -1349,159 +1970,334 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>Total Tickets Breakdown by Category &amp; Sub Category</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>Sub Category</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>Total Scraped Tickets</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr">
         <is>
           <t>Solved / Handled Count</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr">
+      <c r="E15" s="4" t="inlineStr">
         <is>
           <t>Solution Rate %</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D15" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>NETTV-No internet connection in STB</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
           <t>Slow Internet Connection</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>Video content is Buffering</t>
         </is>
       </c>
-      <c r="C16" s="3" t="n">
+      <c r="C18" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="3" t="n">
+      <c r="D18" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E16" s="3" t="inlineStr">
+      <c r="E18" s="3" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
     </row>
-    <row r="17"/>
-    <row r="18">
-      <c r="A18" s="6" t="inlineStr">
+    <row r="19"/>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t>Ticket Number</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>Account Name</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C21" s="4" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="D21" s="4" t="inlineStr">
         <is>
           <t>Sub Category</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr">
+      <c r="E21" s="4" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="F19" s="4" t="inlineStr">
+      <c r="F21" s="4" t="inlineStr">
         <is>
           <t>Resolution Type</t>
         </is>
       </c>
-      <c r="G19" s="4" t="inlineStr">
+      <c r="G21" s="4" t="inlineStr">
         <is>
           <t>Employee Remark / Solution Note</t>
         </is>
       </c>
-      <c r="H19" s="4" t="inlineStr">
+      <c r="H21" s="4" t="inlineStr">
         <is>
           <t>Action / Transfer Remark</t>
         </is>
       </c>
-      <c r="I19" s="4" t="inlineStr">
+      <c r="I21" s="4" t="inlineStr">
         <is>
           <t>Assigned Date</t>
         </is>
       </c>
-      <c r="J19" s="4" t="inlineStr">
+      <c r="J21" s="4" t="inlineStr">
         <is>
           <t>Created Date</t>
         </is>
       </c>
-      <c r="K19" s="4" t="inlineStr">
+      <c r="K21" s="4" t="inlineStr">
         <is>
           <t>Last Modified Date</t>
         </is>
       </c>
-      <c r="L19" s="4" t="inlineStr">
+      <c r="L21" s="4" t="inlineStr">
         <is>
           <t>Resolution Time (From Assigned)</t>
         </is>
       </c>
-      <c r="M19" s="4" t="inlineStr">
+      <c r="M21" s="4" t="inlineStr">
         <is>
           <t>Resolution Time (From Created)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>TKT1364446</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Jeet Bahadur Basnet</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>Case : upgrade wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>Case : upgrade wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 10:40:59 AM</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 12:30:31 PM</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 10:40:59 AM</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>22h 10m</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>TKT1364411</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>Bijya Lama</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="H23" s="5" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I23" s="5" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 10:40:30 AM</t>
+        </is>
+      </c>
+      <c r="J23" s="5" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 12:06:35 PM</t>
+        </is>
+      </c>
+      <c r="K23" s="5" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 10:40:30 AM</t>
+        </is>
+      </c>
+      <c r="L23" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M23" s="5" t="inlineStr">
+        <is>
+          <t>22h 33m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_10_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_10_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AW7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1253,10 +1253,8 @@
           <t>Jeet Bahadur Basnet</t>
         </is>
       </c>
-      <c r="O4" s="3" t="inlineStr">
-        <is>
-          <t>9823773885</t>
-        </is>
+      <c r="O4" s="3" t="n">
+        <v>9823773885</v>
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
@@ -1346,25 +1344,21 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN4" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN4" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO4" s="3" t="inlineStr">
         <is>
           <t>L56-4</t>
         </is>
       </c>
-      <c r="AP4" s="3" t="inlineStr">
-        <is>
-          <t>85.379044</t>
-        </is>
+      <c r="AP4" s="3" t="n">
+        <v>85.37904399999999</v>
       </c>
       <c r="AQ4" s="3" t="inlineStr"/>
       <c r="AR4" s="3" t="inlineStr">
         <is>
-          <t>Case : upgrade wifi 6  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS4" s="3" t="inlineStr">
@@ -1460,10 +1454,8 @@
           <t>Bijya Lama</t>
         </is>
       </c>
-      <c r="O5" s="3" t="inlineStr">
-        <is>
-          <t>9843955238</t>
-        </is>
+      <c r="O5" s="3" t="n">
+        <v>9843955238</v>
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
@@ -1557,25 +1549,21 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN5" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN5" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO5" s="3" t="inlineStr">
         <is>
           <t>L11-3</t>
         </is>
       </c>
-      <c r="AP5" s="3" t="inlineStr">
-        <is>
-          <t>85.36467</t>
-        </is>
+      <c r="AP5" s="3" t="n">
+        <v>85.36467</v>
       </c>
       <c r="AQ5" s="3" t="inlineStr"/>
       <c r="AR5" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 upgrade   has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS5" s="3" t="inlineStr">
@@ -1671,10 +1659,8 @@
           <t>Sundar Regmi</t>
         </is>
       </c>
-      <c r="O6" s="3" t="inlineStr">
-        <is>
-          <t>9803357149</t>
-        </is>
+      <c r="O6" s="3" t="n">
+        <v>9803357149</v>
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
@@ -1746,10 +1732,8 @@
           <t>NETTV-No internet connection in STB</t>
         </is>
       </c>
-      <c r="AH6" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH6" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI6" s="3" t="inlineStr"/>
       <c r="AJ6" s="3" t="inlineStr"/>
@@ -1764,10 +1748,8 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN6" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN6" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO6" s="3" t="inlineStr">
         <is>
@@ -1778,32 +1760,231 @@
       <c r="AQ6" s="3" t="inlineStr"/>
       <c r="AR6" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS6" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT6" s="3" t="inlineStr">
+        <is>
+          <t>2d 24m</t>
+        </is>
+      </c>
+      <c r="AU6" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV6" s="3" t="inlineStr">
+        <is>
           <t>Case : sbt connection   has been updated by Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AS6" s="3" t="inlineStr">
+      <c r="AW6" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 10:49 AM</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr"/>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6 upgrade</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>TKT1357376</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>Goma Adhikari</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
+          <t>Goma Adhikari</t>
+        </is>
+      </c>
+      <c r="O7" s="3" t="inlineStr">
+        <is>
+          <t>9813097646</t>
+        </is>
+      </c>
+      <c r="P7" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q7" s="3" t="inlineStr"/>
+      <c r="R7" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 10:49:43 AM</t>
+        </is>
+      </c>
+      <c r="S7" s="3" t="inlineStr"/>
+      <c r="T7" s="3" t="inlineStr"/>
+      <c r="U7" s="3" t="inlineStr">
+        <is>
+          <t>9813097646</t>
+        </is>
+      </c>
+      <c r="V7" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 08:51:00 AM</t>
+        </is>
+      </c>
+      <c r="W7" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 10:49:43 AM</t>
+        </is>
+      </c>
+      <c r="X7" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y7" s="3" t="inlineStr"/>
+      <c r="Z7" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA7" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB7" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC7" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD7" s="3" t="inlineStr"/>
+      <c r="AE7" s="3" t="inlineStr">
+        <is>
+          <t>Near lkapuri Colony - Housing society P8Q9+WVH Prayas marg Tokha 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF7" s="3" t="inlineStr"/>
+      <c r="AG7" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH7" s="3" t="inlineStr"/>
+      <c r="AI7" s="3" t="inlineStr">
+        <is>
+          <t>02:49 hour</t>
+        </is>
+      </c>
+      <c r="AJ7" s="3" t="inlineStr"/>
+      <c r="AK7" s="3" t="inlineStr"/>
+      <c r="AL7" s="3" t="inlineStr">
+        <is>
+          <t>Merika Silwal</t>
+        </is>
+      </c>
+      <c r="AM7" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN7" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO7" s="3" t="inlineStr">
+        <is>
+          <t>L27-7</t>
+        </is>
+      </c>
+      <c r="AP7" s="3" t="inlineStr"/>
+      <c r="AQ7" s="3" t="inlineStr"/>
+      <c r="AR7" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS7" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT6" s="3" t="inlineStr">
-        <is>
-          <t>2d 24m</t>
-        </is>
-      </c>
-      <c r="AU6" s="3" t="inlineStr">
-        <is>
-          <t>Other / In Progress (On Hold)</t>
-        </is>
-      </c>
-      <c r="AV6" s="3" t="inlineStr">
-        <is>
-          <t>Case : sbt connection   has been updated by Sanjeev Giri</t>
-        </is>
-      </c>
-      <c r="AW6" s="3" t="inlineStr">
-        <is>
-          <t>IPTV Issue</t>
+      <c r="AT7" s="3" t="inlineStr">
+        <is>
+          <t>6d 1h 58m</t>
+        </is>
+      </c>
+      <c r="AU7" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV7" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW7" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
         </is>
       </c>
     </row>
@@ -1818,7 +1999,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M23"/>
+  <dimension ref="A1:M24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -1855,7 +2036,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
@@ -1865,7 +2046,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -1876,7 +2057,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -1900,7 +2081,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>22h 22m</t>
+          <t>2d 15h 34m</t>
         </is>
       </c>
     </row>
@@ -1941,14 +2122,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C10" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="C10" s="3" t="n">
-        <v>2</v>
-      </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -2035,14 +2216,14 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D16" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="D16" s="3" t="n">
-        <v>2</v>
-      </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -2200,7 +2381,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>Case : upgrade wifi 6  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
@@ -2267,14 +2448,14 @@
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H23" s="5" t="inlineStr">
+        <is>
           <t>Case : Wifi 6 upgrade   has been updated by Sabin Giri</t>
         </is>
       </c>
-      <c r="H23" s="5" t="inlineStr">
-        <is>
-          <t>Case : Wifi 6 upgrade   has been updated by Sabin Giri</t>
-        </is>
-      </c>
       <c r="I23" s="5" t="inlineStr">
         <is>
           <t>10 Oct 2026 10:40:30 AM</t>
@@ -2298,6 +2479,73 @@
       <c r="M23" s="5" t="inlineStr">
         <is>
           <t>22h 33m</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>TKT1357376</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>Goma Adhikari</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 10:49:43 AM</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 08:51:00 AM</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 10:49:43 AM</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>6d 1h 58m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_10_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_10_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW7"/>
+  <dimension ref="A1:AW11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -513,11 +513,11 @@
     <col width="12" customWidth="1" min="25" max="25"/>
     <col width="27" customWidth="1" min="26" max="26"/>
     <col width="19" customWidth="1" min="27" max="27"/>
-    <col width="14" customWidth="1" min="28" max="28"/>
+    <col width="17" customWidth="1" min="28" max="28"/>
     <col width="11" customWidth="1" min="29" max="29"/>
     <col width="10" customWidth="1" min="30" max="30"/>
     <col width="40" customWidth="1" min="31" max="31"/>
-    <col width="25" customWidth="1" min="32" max="32"/>
+    <col width="30" customWidth="1" min="32" max="32"/>
     <col width="38" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
@@ -1856,10 +1856,8 @@
           <t>Goma Adhikari</t>
         </is>
       </c>
-      <c r="O7" s="3" t="inlineStr">
-        <is>
-          <t>9813097646</t>
-        </is>
+      <c r="O7" s="3" t="n">
+        <v>9813097646</v>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
@@ -1945,10 +1943,8 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN7" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN7" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO7" s="3" t="inlineStr">
         <is>
@@ -1959,30 +1955,870 @@
       <c r="AQ7" s="3" t="inlineStr"/>
       <c r="AR7" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS7" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT7" s="3" t="inlineStr">
+        <is>
+          <t>6d 1h 58m</t>
+        </is>
+      </c>
+      <c r="AU7" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV7" s="3" t="inlineStr">
+        <is>
           <t>Case : Wifi 6 upgrade   has been updated by Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AS7" s="3" t="inlineStr">
+      <c r="AW7" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 11:04 AM</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr"/>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>TKT1358035</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>Saurav Lamsal</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
+          <t>Saurav Lamsal</t>
+        </is>
+      </c>
+      <c r="O8" s="3" t="inlineStr">
+        <is>
+          <t>9840527775</t>
+        </is>
+      </c>
+      <c r="P8" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q8" s="3" t="inlineStr"/>
+      <c r="R8" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 02:07:16 PM</t>
+        </is>
+      </c>
+      <c r="S8" s="3" t="inlineStr"/>
+      <c r="T8" s="3" t="inlineStr"/>
+      <c r="U8" s="3" t="inlineStr">
+        <is>
+          <t>9851328488</t>
+        </is>
+      </c>
+      <c r="V8" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 02:07:16 PM</t>
+        </is>
+      </c>
+      <c r="W8" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 11:04:09 AM</t>
+        </is>
+      </c>
+      <c r="X8" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y8" s="3" t="inlineStr">
+        <is>
+          <t>27.699563</t>
+        </is>
+      </c>
+      <c r="Z8" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA8" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB8" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC8" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD8" s="3" t="inlineStr"/>
+      <c r="AE8" s="3" t="inlineStr">
+        <is>
+          <t>Syuchatar, Kathmandu 44600 near by Syuchatar Pati Chowk ????????? ???? ???, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF8" s="3" t="inlineStr">
+        <is>
+          <t>lamsalsaurav555@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG8" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH8" s="3" t="inlineStr"/>
+      <c r="AI8" s="3" t="inlineStr">
+        <is>
+          <t>03:03 hour</t>
+        </is>
+      </c>
+      <c r="AJ8" s="3" t="inlineStr"/>
+      <c r="AK8" s="3" t="inlineStr"/>
+      <c r="AL8" s="3" t="inlineStr">
+        <is>
+          <t>Monali Lohani</t>
+        </is>
+      </c>
+      <c r="AM8" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN8" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO8" s="3" t="inlineStr">
+        <is>
+          <t>2,7</t>
+        </is>
+      </c>
+      <c r="AP8" s="3" t="inlineStr">
+        <is>
+          <t>85.274141</t>
+        </is>
+      </c>
+      <c r="AQ8" s="3" t="inlineStr"/>
+      <c r="AR8" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS8" s="3" t="inlineStr">
+        <is>
+          <t>5d 20h 56m</t>
+        </is>
+      </c>
+      <c r="AT8" s="3" t="inlineStr">
+        <is>
+          <t>5d 20h 56m</t>
+        </is>
+      </c>
+      <c r="AU8" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV8" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW8" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 11:03 AM</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr"/>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>TKT1358035</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>Saurav Lamsal</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
+          <t>Saurav Lamsal</t>
+        </is>
+      </c>
+      <c r="O9" s="3" t="inlineStr">
+        <is>
+          <t>9840527775</t>
+        </is>
+      </c>
+      <c r="P9" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q9" s="3" t="inlineStr"/>
+      <c r="R9" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 02:07:16 PM</t>
+        </is>
+      </c>
+      <c r="S9" s="3" t="inlineStr"/>
+      <c r="T9" s="3" t="inlineStr"/>
+      <c r="U9" s="3" t="inlineStr">
+        <is>
+          <t>9851328488</t>
+        </is>
+      </c>
+      <c r="V9" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 02:07:16 PM</t>
+        </is>
+      </c>
+      <c r="W9" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 11:04:09 AM</t>
+        </is>
+      </c>
+      <c r="X9" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y9" s="3" t="inlineStr">
+        <is>
+          <t>27.699563</t>
+        </is>
+      </c>
+      <c r="Z9" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA9" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB9" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC9" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD9" s="3" t="inlineStr"/>
+      <c r="AE9" s="3" t="inlineStr">
+        <is>
+          <t>Syuchatar, Kathmandu 44600 near by Syuchatar Pati Chowk ????????? ???? ???, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF9" s="3" t="inlineStr">
+        <is>
+          <t>lamsalsaurav555@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG9" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH9" s="3" t="inlineStr"/>
+      <c r="AI9" s="3" t="inlineStr">
+        <is>
+          <t>03:03 hour</t>
+        </is>
+      </c>
+      <c r="AJ9" s="3" t="inlineStr"/>
+      <c r="AK9" s="3" t="inlineStr"/>
+      <c r="AL9" s="3" t="inlineStr">
+        <is>
+          <t>Monali Lohani</t>
+        </is>
+      </c>
+      <c r="AM9" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN9" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO9" s="3" t="inlineStr">
+        <is>
+          <t>2,7</t>
+        </is>
+      </c>
+      <c r="AP9" s="3" t="inlineStr">
+        <is>
+          <t>85.274141</t>
+        </is>
+      </c>
+      <c r="AQ9" s="3" t="inlineStr"/>
+      <c r="AR9" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS9" s="3" t="inlineStr">
+        <is>
+          <t>5d 20h 56m</t>
+        </is>
+      </c>
+      <c r="AT9" s="3" t="inlineStr">
+        <is>
+          <t>5d 20h 56m</t>
+        </is>
+      </c>
+      <c r="AU9" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV9" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW9" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 11:15 AM</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr"/>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>wifi6</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>TKT1364756</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>New Assist Traders</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
+          <t>New Assist Traders</t>
+        </is>
+      </c>
+      <c r="O10" s="3" t="inlineStr">
+        <is>
+          <t>9841756485</t>
+        </is>
+      </c>
+      <c r="P10" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q10" s="3" t="inlineStr"/>
+      <c r="R10" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 11:15:36 AM</t>
+        </is>
+      </c>
+      <c r="S10" s="3" t="inlineStr"/>
+      <c r="T10" s="3" t="inlineStr"/>
+      <c r="U10" s="3" t="inlineStr">
+        <is>
+          <t>9841756485</t>
+        </is>
+      </c>
+      <c r="V10" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 04:33:35 PM</t>
+        </is>
+      </c>
+      <c r="W10" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 11:15:36 AM</t>
+        </is>
+      </c>
+      <c r="X10" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y10" s="3" t="inlineStr">
+        <is>
+          <t>27.68162</t>
+        </is>
+      </c>
+      <c r="Z10" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA10" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB10" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC10" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD10" s="3" t="inlineStr"/>
+      <c r="AE10" s="3" t="inlineStr">
+        <is>
+          <t>Near Big Mart Warehouse, Sankhamul - Balkumari Rd 11, Lalitpur - Near Big Mart Warehouse, Sankhamul</t>
+        </is>
+      </c>
+      <c r="AF10" s="3" t="inlineStr">
+        <is>
+          <t>bhattaraidipesh96@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG10" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH10" s="3" t="inlineStr"/>
+      <c r="AI10" s="3" t="inlineStr">
+        <is>
+          <t>04:42 hour</t>
+        </is>
+      </c>
+      <c r="AJ10" s="3" t="inlineStr"/>
+      <c r="AK10" s="3" t="inlineStr"/>
+      <c r="AL10" s="3" t="inlineStr">
+        <is>
+          <t>Ishlok Shahi</t>
+        </is>
+      </c>
+      <c r="AM10" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN10" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO10" s="3" t="inlineStr">
+        <is>
+          <t>3,16</t>
+        </is>
+      </c>
+      <c r="AP10" s="3" t="inlineStr">
+        <is>
+          <t>85.32741</t>
+        </is>
+      </c>
+      <c r="AQ10" s="3" t="inlineStr"/>
+      <c r="AR10" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS10" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT7" s="3" t="inlineStr">
-        <is>
-          <t>6d 1h 58m</t>
-        </is>
-      </c>
-      <c r="AU7" s="3" t="inlineStr">
+      <c r="AT10" s="3" t="inlineStr">
+        <is>
+          <t>18h 42m</t>
+        </is>
+      </c>
+      <c r="AU10" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV7" s="3" t="inlineStr">
-        <is>
-          <t>Case : Wifi 6 upgrade   has been updated by Sanjeev Giri</t>
-        </is>
-      </c>
-      <c r="AW7" s="3" t="inlineStr">
+      <c r="AV10" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW10" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 11:13 AM</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr"/>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>wifi6</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>TKT1358080</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>Baburaja Maharjan</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
+          <t>Baburaja Maharjan</t>
+        </is>
+      </c>
+      <c r="O11" s="3" t="inlineStr">
+        <is>
+          <t>9841479122</t>
+        </is>
+      </c>
+      <c r="P11" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q11" s="3" t="inlineStr"/>
+      <c r="R11" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 11:13:31 AM</t>
+        </is>
+      </c>
+      <c r="S11" s="3" t="inlineStr"/>
+      <c r="T11" s="3" t="inlineStr"/>
+      <c r="U11" s="3" t="inlineStr">
+        <is>
+          <t>9841479122</t>
+        </is>
+      </c>
+      <c r="V11" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 02:29:39 PM</t>
+        </is>
+      </c>
+      <c r="W11" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 11:13:31 AM</t>
+        </is>
+      </c>
+      <c r="X11" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y11" s="3" t="inlineStr">
+        <is>
+          <t>27.65564</t>
+        </is>
+      </c>
+      <c r="Z11" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA11" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB11" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC11" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD11" s="3" t="inlineStr"/>
+      <c r="AE11" s="3" t="inlineStr">
+        <is>
+          <t>27.65564, 85.3402, New Ganesh Temple Naya Basti, M84Q+9V5, Mahalaxmi 44700, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF11" s="3" t="inlineStr"/>
+      <c r="AG11" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH11" s="3" t="inlineStr"/>
+      <c r="AI11" s="3" t="inlineStr">
+        <is>
+          <t>03:13 hour</t>
+        </is>
+      </c>
+      <c r="AJ11" s="3" t="inlineStr"/>
+      <c r="AK11" s="3" t="inlineStr"/>
+      <c r="AL11" s="3" t="inlineStr">
+        <is>
+          <t>Sunita Yonjan</t>
+        </is>
+      </c>
+      <c r="AM11" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN11" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO11" s="3" t="inlineStr">
+        <is>
+          <t>1,2</t>
+        </is>
+      </c>
+      <c r="AP11" s="3" t="inlineStr">
+        <is>
+          <t>85.3402</t>
+        </is>
+      </c>
+      <c r="AQ11" s="3" t="inlineStr"/>
+      <c r="AR11" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS11" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT11" s="3" t="inlineStr">
+        <is>
+          <t>5d 20h 43m</t>
+        </is>
+      </c>
+      <c r="AU11" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV11" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW11" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
@@ -1999,7 +2835,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M24"/>
+  <dimension ref="A1:M28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -2036,7 +2872,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3">
@@ -2046,7 +2882,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4">
@@ -2057,7 +2893,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>70.0%</t>
         </is>
       </c>
     </row>
@@ -2069,7 +2905,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>1d 16h 16m</t>
         </is>
       </c>
     </row>
@@ -2081,7 +2917,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>2d 15h 34m</t>
+          <t>3d 18h 17m</t>
         </is>
       </c>
     </row>
@@ -2122,14 +2958,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>87.5%</t>
         </is>
       </c>
     </row>
@@ -2216,14 +3052,14 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>87.5%</t>
         </is>
       </c>
     </row>
@@ -2515,14 +3351,14 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
           <t>Case : Wifi 6 upgrade   has been updated by Sanjeev Giri</t>
         </is>
       </c>
-      <c r="H24" s="3" t="inlineStr">
-        <is>
-          <t>Case : Wifi 6 upgrade   has been updated by Sanjeev Giri</t>
-        </is>
-      </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
           <t>10 Oct 2026 10:49:43 AM</t>
@@ -2546,6 +3382,274 @@
       <c r="M24" s="3" t="inlineStr">
         <is>
           <t>6d 1h 58m</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>TKT1358035</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>Saurav Lamsal</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="H25" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I25" s="5" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 02:07:16 PM</t>
+        </is>
+      </c>
+      <c r="J25" s="5" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 02:07:16 PM</t>
+        </is>
+      </c>
+      <c r="K25" s="5" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 11:04:09 AM</t>
+        </is>
+      </c>
+      <c r="L25" s="5" t="inlineStr">
+        <is>
+          <t>5d 20h 56m</t>
+        </is>
+      </c>
+      <c r="M25" s="5" t="inlineStr">
+        <is>
+          <t>5d 20h 56m</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>TKT1358035</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>Saurav Lamsal</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 02:07:16 PM</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 02:07:16 PM</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 11:04:09 AM</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>5d 20h 56m</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>5d 20h 56m</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>TKT1364756</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>New Assist Traders</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="H27" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I27" s="5" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 11:15:36 AM</t>
+        </is>
+      </c>
+      <c r="J27" s="5" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 04:33:35 PM</t>
+        </is>
+      </c>
+      <c r="K27" s="5" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 11:15:36 AM</t>
+        </is>
+      </c>
+      <c r="L27" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M27" s="5" t="inlineStr">
+        <is>
+          <t>18h 42m</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>TKT1358080</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>Baburaja Maharjan</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 11:13:31 AM</t>
+        </is>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 02:29:39 PM</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 11:13:31 AM</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>5d 20h 43m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_10_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_10_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW11"/>
+  <dimension ref="A1:AW12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -523,7 +523,7 @@
     <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
     <col width="17" customWidth="1" min="37" max="37"/>
-    <col width="17" customWidth="1" min="38" max="38"/>
+    <col width="18" customWidth="1" min="38" max="38"/>
     <col width="20" customWidth="1" min="39" max="39"/>
     <col width="28" customWidth="1" min="40" max="40"/>
     <col width="27" customWidth="1" min="41" max="41"/>
@@ -2051,10 +2051,8 @@
           <t>Saurav Lamsal</t>
         </is>
       </c>
-      <c r="O8" s="3" t="inlineStr">
-        <is>
-          <t>9840527775</t>
-        </is>
+      <c r="O8" s="3" t="n">
+        <v>9840527775</v>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
@@ -2148,25 +2146,21 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN8" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN8" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO8" s="3" t="inlineStr">
         <is>
           <t>2,7</t>
         </is>
       </c>
-      <c r="AP8" s="3" t="inlineStr">
-        <is>
-          <t>85.274141</t>
-        </is>
+      <c r="AP8" s="3" t="n">
+        <v>85.274141</v>
       </c>
       <c r="AQ8" s="3" t="inlineStr"/>
       <c r="AR8" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS8" s="3" t="inlineStr">
@@ -2262,10 +2256,8 @@
           <t>Saurav Lamsal</t>
         </is>
       </c>
-      <c r="O9" s="3" t="inlineStr">
-        <is>
-          <t>9840527775</t>
-        </is>
+      <c r="O9" s="3" t="n">
+        <v>9840527775</v>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
@@ -2359,25 +2351,21 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN9" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN9" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO9" s="3" t="inlineStr">
         <is>
           <t>2,7</t>
         </is>
       </c>
-      <c r="AP9" s="3" t="inlineStr">
-        <is>
-          <t>85.274141</t>
-        </is>
+      <c r="AP9" s="3" t="n">
+        <v>85.274141</v>
       </c>
       <c r="AQ9" s="3" t="inlineStr"/>
       <c r="AR9" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS9" s="3" t="inlineStr">
@@ -2463,20 +2451,14 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="M10" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="M10" s="3" t="inlineStr"/>
       <c r="N10" s="3" t="inlineStr">
         <is>
           <t>New Assist Traders</t>
         </is>
       </c>
-      <c r="O10" s="3" t="inlineStr">
-        <is>
-          <t>9841756485</t>
-        </is>
+      <c r="O10" s="3" t="n">
+        <v>9841756485</v>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
@@ -2570,25 +2552,21 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN10" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN10" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO10" s="3" t="inlineStr">
         <is>
           <t>3,16</t>
         </is>
       </c>
-      <c r="AP10" s="3" t="inlineStr">
-        <is>
-          <t>85.32741</t>
-        </is>
+      <c r="AP10" s="3" t="n">
+        <v>85.32741</v>
       </c>
       <c r="AQ10" s="3" t="inlineStr"/>
       <c r="AR10" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS10" s="3" t="inlineStr">
@@ -2684,10 +2662,8 @@
           <t>Baburaja Maharjan</t>
         </is>
       </c>
-      <c r="O11" s="3" t="inlineStr">
-        <is>
-          <t>9841479122</t>
-        </is>
+      <c r="O11" s="3" t="n">
+        <v>9841479122</v>
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
@@ -2777,50 +2753,253 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN11" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN11" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO11" s="3" t="inlineStr">
         <is>
           <t>1,2</t>
         </is>
       </c>
-      <c r="AP11" s="3" t="inlineStr">
-        <is>
-          <t>85.3402</t>
-        </is>
+      <c r="AP11" s="3" t="n">
+        <v>85.3402</v>
       </c>
       <c r="AQ11" s="3" t="inlineStr"/>
       <c r="AR11" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS11" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT11" s="3" t="inlineStr">
+        <is>
+          <t>5d 20h 43m</t>
+        </is>
+      </c>
+      <c r="AU11" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV11" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi6  has been updated by Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AS11" s="3" t="inlineStr">
+      <c r="AW11" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 11:23 AM</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr"/>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrade  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>router upgrade</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>TKT1359556</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>Puspa KC</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
+          <t>Puspa KC</t>
+        </is>
+      </c>
+      <c r="O12" s="3" t="inlineStr">
+        <is>
+          <t>9849750351</t>
+        </is>
+      </c>
+      <c r="P12" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q12" s="3" t="inlineStr"/>
+      <c r="R12" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 11:23:36 AM</t>
+        </is>
+      </c>
+      <c r="S12" s="3" t="inlineStr"/>
+      <c r="T12" s="3" t="inlineStr"/>
+      <c r="U12" s="3" t="inlineStr">
+        <is>
+          <t>9849750351</t>
+        </is>
+      </c>
+      <c r="V12" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 03:34:34 PM</t>
+        </is>
+      </c>
+      <c r="W12" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 11:23:36 AM</t>
+        </is>
+      </c>
+      <c r="X12" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y12" s="3" t="inlineStr">
+        <is>
+          <t>27.67713</t>
+        </is>
+      </c>
+      <c r="Z12" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA12" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB12" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC12" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD12" s="3" t="inlineStr"/>
+      <c r="AE12" s="3" t="inlineStr">
+        <is>
+          <t>Near by radhe radhe Vatbhatini, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF12" s="3" t="inlineStr"/>
+      <c r="AG12" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH12" s="3" t="inlineStr"/>
+      <c r="AI12" s="3" t="inlineStr">
+        <is>
+          <t>21:49 hour</t>
+        </is>
+      </c>
+      <c r="AJ12" s="3" t="inlineStr"/>
+      <c r="AK12" s="3" t="inlineStr"/>
+      <c r="AL12" s="3" t="inlineStr">
+        <is>
+          <t>Rejina Shrestha</t>
+        </is>
+      </c>
+      <c r="AM12" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN12" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO12" s="3" t="inlineStr">
+        <is>
+          <t>L64-1</t>
+        </is>
+      </c>
+      <c r="AP12" s="3" t="inlineStr">
+        <is>
+          <t>85.395276</t>
+        </is>
+      </c>
+      <c r="AQ12" s="3" t="inlineStr"/>
+      <c r="AR12" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrade  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS12" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT11" s="3" t="inlineStr">
-        <is>
-          <t>5d 20h 43m</t>
-        </is>
-      </c>
-      <c r="AU11" s="3" t="inlineStr">
+      <c r="AT12" s="3" t="inlineStr">
+        <is>
+          <t>4d 19h 49m</t>
+        </is>
+      </c>
+      <c r="AU12" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV11" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi6  has been updated by Chandramani Tharu</t>
-        </is>
-      </c>
-      <c r="AW11" s="3" t="inlineStr">
-        <is>
-          <t>WiFi 6 Upgrade</t>
+      <c r="AV12" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrade  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW12" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
         </is>
       </c>
     </row>
@@ -2835,7 +3014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M28"/>
+  <dimension ref="A1:M29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -2872,7 +3051,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3">
@@ -2882,7 +3061,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4">
@@ -2893,7 +3072,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>70.0%</t>
+          <t>72.7%</t>
         </is>
       </c>
     </row>
@@ -2905,7 +3084,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>1d 16h 16m</t>
+          <t>1d 11h 14m</t>
         </is>
       </c>
     </row>
@@ -2917,7 +3096,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>3d 18h 17m</t>
+          <t>3d 21h 28m</t>
         </is>
       </c>
     </row>
@@ -2958,14 +3137,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="C10" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="C10" s="3" t="n">
-        <v>7</v>
-      </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>87.5%</t>
+          <t>88.9%</t>
         </is>
       </c>
     </row>
@@ -3052,14 +3231,14 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="D16" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="D16" s="3" t="n">
-        <v>7</v>
-      </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>87.5%</t>
+          <t>88.9%</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3597,7 @@
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H25" s="5" t="inlineStr">
@@ -3485,7 +3664,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
@@ -3552,7 +3731,7 @@
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H27" s="5" t="inlineStr">
@@ -3619,14 +3798,14 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi6  has been updated by Chandramani Tharu</t>
         </is>
       </c>
-      <c r="H28" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi6  has been updated by Chandramani Tharu</t>
-        </is>
-      </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
           <t>10 Oct 2026 11:13:31 AM</t>
@@ -3650,6 +3829,73 @@
       <c r="M28" s="3" t="inlineStr">
         <is>
           <t>5d 20h 43m</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>TKT1359556</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>Puspa KC</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="inlineStr">
+        <is>
+          <t>Case : router upgrade  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="H29" s="5" t="inlineStr">
+        <is>
+          <t>Case : router upgrade  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I29" s="5" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 11:23:36 AM</t>
+        </is>
+      </c>
+      <c r="J29" s="5" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 03:34:34 PM</t>
+        </is>
+      </c>
+      <c r="K29" s="5" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 11:23:36 AM</t>
+        </is>
+      </c>
+      <c r="L29" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M29" s="5" t="inlineStr">
+        <is>
+          <t>4d 19h 49m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_10_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_10_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW12"/>
+  <dimension ref="A1:AW15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -2853,20 +2853,14 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="M12" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="M12" s="3" t="inlineStr"/>
       <c r="N12" s="3" t="inlineStr">
         <is>
           <t>Puspa KC</t>
         </is>
       </c>
-      <c r="O12" s="3" t="inlineStr">
-        <is>
-          <t>9849750351</t>
-        </is>
+      <c r="O12" s="3" t="n">
+        <v>9849750351</v>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
@@ -2956,50 +2950,675 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN12" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN12" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO12" s="3" t="inlineStr">
         <is>
           <t>L64-1</t>
         </is>
       </c>
-      <c r="AP12" s="3" t="inlineStr">
-        <is>
-          <t>85.395276</t>
-        </is>
+      <c r="AP12" s="3" t="n">
+        <v>85.395276</v>
       </c>
       <c r="AQ12" s="3" t="inlineStr"/>
       <c r="AR12" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS12" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT12" s="3" t="inlineStr">
+        <is>
+          <t>4d 19h 49m</t>
+        </is>
+      </c>
+      <c r="AU12" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV12" s="3" t="inlineStr">
+        <is>
           <t>Case : router upgrade  has been updated by Sabin Giri</t>
         </is>
       </c>
-      <c r="AS12" s="3" t="inlineStr">
+      <c r="AW12" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 11:41 AM</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr"/>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>TKT1365031</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>Prem Kumar Shrestha</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
+          <t>Prem Kumar Shrestha</t>
+        </is>
+      </c>
+      <c r="O13" s="3" t="inlineStr">
+        <is>
+          <t>9840755152</t>
+        </is>
+      </c>
+      <c r="P13" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q13" s="3" t="inlineStr"/>
+      <c r="R13" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 11:41:30 AM</t>
+        </is>
+      </c>
+      <c r="S13" s="3" t="inlineStr"/>
+      <c r="T13" s="3" t="inlineStr"/>
+      <c r="U13" s="3" t="inlineStr">
+        <is>
+          <t>9840755152</t>
+        </is>
+      </c>
+      <c r="V13" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 09:56:52 PM</t>
+        </is>
+      </c>
+      <c r="W13" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 11:41:30 AM</t>
+        </is>
+      </c>
+      <c r="X13" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y13" s="3" t="inlineStr">
+        <is>
+          <t>27.7483</t>
+        </is>
+      </c>
+      <c r="Z13" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA13" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB13" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC13" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD13" s="3" t="inlineStr"/>
+      <c r="AE13" s="3" t="inlineStr">
+        <is>
+          <t>Baniyatar Road,Jalpa Chowk, Opposite Himalayan Valley English Boarding School, Kathmandu, Bagmati, C</t>
+        </is>
+      </c>
+      <c r="AF13" s="3" t="inlineStr"/>
+      <c r="AG13" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH13" s="3" t="inlineStr"/>
+      <c r="AI13" s="3" t="inlineStr">
+        <is>
+          <t>01:41 hour</t>
+        </is>
+      </c>
+      <c r="AJ13" s="3" t="inlineStr"/>
+      <c r="AK13" s="3" t="inlineStr"/>
+      <c r="AL13" s="3" t="inlineStr">
+        <is>
+          <t>Nirajan Dhamala</t>
+        </is>
+      </c>
+      <c r="AM13" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN13" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO13" s="3" t="inlineStr">
+        <is>
+          <t>L39-1</t>
+        </is>
+      </c>
+      <c r="AP13" s="3" t="inlineStr">
+        <is>
+          <t>85.31749</t>
+        </is>
+      </c>
+      <c r="AQ13" s="3" t="inlineStr"/>
+      <c r="AR13" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS13" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT12" s="3" t="inlineStr">
-        <is>
-          <t>4d 19h 49m</t>
-        </is>
-      </c>
-      <c r="AU12" s="3" t="inlineStr">
+      <c r="AT13" s="3" t="inlineStr">
+        <is>
+          <t>13h 44m</t>
+        </is>
+      </c>
+      <c r="AU13" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV12" s="3" t="inlineStr">
-        <is>
-          <t>Case : router upgrade  has been updated by Sabin Giri</t>
-        </is>
-      </c>
-      <c r="AW12" s="3" t="inlineStr">
+      <c r="AV13" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW13" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 11:36 AM</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr"/>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>Case : For upgradation to wifi6   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>For upgradation to wifi6</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>TKT1362058</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>Gyan Chiraniya</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
+          <t>Gyan Chiraniya</t>
+        </is>
+      </c>
+      <c r="O14" s="3" t="inlineStr">
+        <is>
+          <t>9803334769</t>
+        </is>
+      </c>
+      <c r="P14" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q14" s="3" t="inlineStr"/>
+      <c r="R14" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 02:43:23 PM</t>
+        </is>
+      </c>
+      <c r="S14" s="3" t="inlineStr"/>
+      <c r="T14" s="3" t="inlineStr"/>
+      <c r="U14" s="3" t="inlineStr">
+        <is>
+          <t>9861500589</t>
+        </is>
+      </c>
+      <c r="V14" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 02:43:23 PM</t>
+        </is>
+      </c>
+      <c r="W14" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 11:36:00 AM</t>
+        </is>
+      </c>
+      <c r="X14" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y14" s="3" t="inlineStr">
+        <is>
+          <t>27.69044</t>
+        </is>
+      </c>
+      <c r="Z14" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA14" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB14" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC14" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD14" s="3" t="inlineStr"/>
+      <c r="AE14" s="3" t="inlineStr">
+        <is>
+          <t>Naya Basti, Kuleshwor Height Pani Tanki, Kathmandu, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF14" s="3" t="inlineStr">
+        <is>
+          <t>chiraniyagyan@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG14" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH14" s="3" t="inlineStr"/>
+      <c r="AI14" s="3" t="inlineStr">
+        <is>
+          <t>02:52 hour</t>
+        </is>
+      </c>
+      <c r="AJ14" s="3" t="inlineStr"/>
+      <c r="AK14" s="3" t="inlineStr"/>
+      <c r="AL14" s="3" t="inlineStr">
+        <is>
+          <t>Pradeep Yadav</t>
+        </is>
+      </c>
+      <c r="AM14" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN14" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO14" s="3" t="inlineStr">
+        <is>
+          <t>CDB297</t>
+        </is>
+      </c>
+      <c r="AP14" s="3" t="inlineStr">
+        <is>
+          <t>85.29494</t>
+        </is>
+      </c>
+      <c r="AQ14" s="3" t="inlineStr"/>
+      <c r="AR14" s="3" t="inlineStr">
+        <is>
+          <t>Case : For upgradation to wifi6   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS14" s="3" t="inlineStr">
+        <is>
+          <t>2d 20h 52m</t>
+        </is>
+      </c>
+      <c r="AT14" s="3" t="inlineStr">
+        <is>
+          <t>2d 20h 52m</t>
+        </is>
+      </c>
+      <c r="AU14" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV14" s="3" t="inlineStr">
+        <is>
+          <t>Case : For upgradation to wifi6   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW14" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 11:35 AM</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr"/>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>Case : For upgradation to wifi6   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>For upgradation to wifi6</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>TKT1362058</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>Gyan Chiraniya</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
+          <t>Gyan Chiraniya</t>
+        </is>
+      </c>
+      <c r="O15" s="3" t="inlineStr">
+        <is>
+          <t>9803334769</t>
+        </is>
+      </c>
+      <c r="P15" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q15" s="3" t="inlineStr"/>
+      <c r="R15" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 02:43:23 PM</t>
+        </is>
+      </c>
+      <c r="S15" s="3" t="inlineStr"/>
+      <c r="T15" s="3" t="inlineStr"/>
+      <c r="U15" s="3" t="inlineStr">
+        <is>
+          <t>9861500589</t>
+        </is>
+      </c>
+      <c r="V15" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 02:43:23 PM</t>
+        </is>
+      </c>
+      <c r="W15" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 11:36:00 AM</t>
+        </is>
+      </c>
+      <c r="X15" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y15" s="3" t="inlineStr">
+        <is>
+          <t>27.69044</t>
+        </is>
+      </c>
+      <c r="Z15" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA15" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB15" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC15" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD15" s="3" t="inlineStr"/>
+      <c r="AE15" s="3" t="inlineStr">
+        <is>
+          <t>Naya Basti, Kuleshwor Height Pani Tanki, Kathmandu, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF15" s="3" t="inlineStr">
+        <is>
+          <t>chiraniyagyan@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG15" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH15" s="3" t="inlineStr"/>
+      <c r="AI15" s="3" t="inlineStr">
+        <is>
+          <t>02:52 hour</t>
+        </is>
+      </c>
+      <c r="AJ15" s="3" t="inlineStr"/>
+      <c r="AK15" s="3" t="inlineStr"/>
+      <c r="AL15" s="3" t="inlineStr">
+        <is>
+          <t>Pradeep Yadav</t>
+        </is>
+      </c>
+      <c r="AM15" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN15" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO15" s="3" t="inlineStr">
+        <is>
+          <t>CDB297</t>
+        </is>
+      </c>
+      <c r="AP15" s="3" t="inlineStr">
+        <is>
+          <t>85.29494</t>
+        </is>
+      </c>
+      <c r="AQ15" s="3" t="inlineStr"/>
+      <c r="AR15" s="3" t="inlineStr">
+        <is>
+          <t>Case : For upgradation to wifi6   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS15" s="3" t="inlineStr">
+        <is>
+          <t>2d 20h 52m</t>
+        </is>
+      </c>
+      <c r="AT15" s="3" t="inlineStr">
+        <is>
+          <t>2d 20h 52m</t>
+        </is>
+      </c>
+      <c r="AU15" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV15" s="3" t="inlineStr">
+        <is>
+          <t>Case : For upgradation to wifi6   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW15" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
         </is>
       </c>
     </row>
@@ -3014,7 +3633,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M29"/>
+  <dimension ref="A1:M32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -3051,7 +3670,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3">
@@ -3061,7 +3680,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4">
@@ -3072,7 +3691,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>72.7%</t>
+          <t>78.6%</t>
         </is>
       </c>
     </row>
@@ -3084,7 +3703,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>1d 11h 14m</t>
+          <t>1d 14h 9m</t>
         </is>
       </c>
     </row>
@@ -3096,7 +3715,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>3d 21h 28m</t>
+          <t>3d 9h 45m</t>
         </is>
       </c>
     </row>
@@ -3137,14 +3756,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>88.9%</t>
+          <t>91.7%</t>
         </is>
       </c>
     </row>
@@ -3231,14 +3850,14 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>88.9%</t>
+          <t>91.7%</t>
         </is>
       </c>
     </row>
@@ -3865,14 +4484,14 @@
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H29" s="5" t="inlineStr">
+        <is>
           <t>Case : router upgrade  has been updated by Sabin Giri</t>
         </is>
       </c>
-      <c r="H29" s="5" t="inlineStr">
-        <is>
-          <t>Case : router upgrade  has been updated by Sabin Giri</t>
-        </is>
-      </c>
       <c r="I29" s="5" t="inlineStr">
         <is>
           <t>10 Oct 2026 11:23:36 AM</t>
@@ -3896,6 +4515,207 @@
       <c r="M29" s="5" t="inlineStr">
         <is>
           <t>4d 19h 49m</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>TKT1365031</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>Prem Kumar Shrestha</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 11:41:30 AM</t>
+        </is>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 09:56:52 PM</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 11:41:30 AM</t>
+        </is>
+      </c>
+      <c r="L30" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t>13h 44m</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>TKT1362058</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>Gyan Chiraniya</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G31" s="5" t="inlineStr">
+        <is>
+          <t>Case : For upgradation to wifi6   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="H31" s="5" t="inlineStr">
+        <is>
+          <t>Case : For upgradation to wifi6   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I31" s="5" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 02:43:23 PM</t>
+        </is>
+      </c>
+      <c r="J31" s="5" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 02:43:23 PM</t>
+        </is>
+      </c>
+      <c r="K31" s="5" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 11:36:00 AM</t>
+        </is>
+      </c>
+      <c r="L31" s="5" t="inlineStr">
+        <is>
+          <t>2d 20h 52m</t>
+        </is>
+      </c>
+      <c r="M31" s="5" t="inlineStr">
+        <is>
+          <t>2d 20h 52m</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>TKT1362058</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>Gyan Chiraniya</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t>Case : For upgradation to wifi6   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>Case : For upgradation to wifi6   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 02:43:23 PM</t>
+        </is>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 02:43:23 PM</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 11:36:00 AM</t>
+        </is>
+      </c>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t>2d 20h 52m</t>
+        </is>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>2d 20h 52m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_10_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_10_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW15"/>
+  <dimension ref="A1:AW17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -3060,10 +3060,8 @@
           <t>Prem Kumar Shrestha</t>
         </is>
       </c>
-      <c r="O13" s="3" t="inlineStr">
-        <is>
-          <t>9840755152</t>
-        </is>
+      <c r="O13" s="3" t="n">
+        <v>9840755152</v>
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
@@ -3153,25 +3151,21 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN13" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN13" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO13" s="3" t="inlineStr">
         <is>
           <t>L39-1</t>
         </is>
       </c>
-      <c r="AP13" s="3" t="inlineStr">
-        <is>
-          <t>85.31749</t>
-        </is>
+      <c r="AP13" s="3" t="n">
+        <v>85.31749000000001</v>
       </c>
       <c r="AQ13" s="3" t="inlineStr"/>
       <c r="AR13" s="3" t="inlineStr">
         <is>
-          <t>Case : WiFi 6   has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS13" s="3" t="inlineStr">
@@ -3267,10 +3261,8 @@
           <t>Gyan Chiraniya</t>
         </is>
       </c>
-      <c r="O14" s="3" t="inlineStr">
-        <is>
-          <t>9803334769</t>
-        </is>
+      <c r="O14" s="3" t="n">
+        <v>9803334769</v>
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
@@ -3364,25 +3356,21 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN14" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN14" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO14" s="3" t="inlineStr">
         <is>
           <t>CDB297</t>
         </is>
       </c>
-      <c r="AP14" s="3" t="inlineStr">
-        <is>
-          <t>85.29494</t>
-        </is>
+      <c r="AP14" s="3" t="n">
+        <v>85.29494</v>
       </c>
       <c r="AQ14" s="3" t="inlineStr"/>
       <c r="AR14" s="3" t="inlineStr">
         <is>
-          <t>Case : For upgradation to wifi6   has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS14" s="3" t="inlineStr">
@@ -3478,10 +3466,8 @@
           <t>Gyan Chiraniya</t>
         </is>
       </c>
-      <c r="O15" s="3" t="inlineStr">
-        <is>
-          <t>9803334769</t>
-        </is>
+      <c r="O15" s="3" t="n">
+        <v>9803334769</v>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
@@ -3575,50 +3561,460 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN15" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN15" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO15" s="3" t="inlineStr">
         <is>
           <t>CDB297</t>
         </is>
       </c>
-      <c r="AP15" s="3" t="inlineStr">
-        <is>
-          <t>85.29494</t>
-        </is>
+      <c r="AP15" s="3" t="n">
+        <v>85.29494</v>
       </c>
       <c r="AQ15" s="3" t="inlineStr"/>
       <c r="AR15" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS15" s="3" t="inlineStr">
+        <is>
+          <t>2d 20h 52m</t>
+        </is>
+      </c>
+      <c r="AT15" s="3" t="inlineStr">
+        <is>
+          <t>2d 20h 52m</t>
+        </is>
+      </c>
+      <c r="AU15" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV15" s="3" t="inlineStr">
+        <is>
           <t>Case : For upgradation to wifi6   has been updated by Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AS15" s="3" t="inlineStr">
-        <is>
-          <t>2d 20h 52m</t>
-        </is>
-      </c>
-      <c r="AT15" s="3" t="inlineStr">
-        <is>
-          <t>2d 20h 52m</t>
-        </is>
-      </c>
-      <c r="AU15" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Closed)</t>
-        </is>
-      </c>
-      <c r="AV15" s="3" t="inlineStr">
-        <is>
-          <t>Case : For upgradation to wifi6   has been updated by Ajit Shrestha</t>
-        </is>
-      </c>
       <c r="AW15" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 11:53 AM</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr"/>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>Case : For upgradation to wifi6   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>For upgradation to wifi6</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>TKT1362055</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>Ravi Shahi</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
+          <t>Ravi Shahi</t>
+        </is>
+      </c>
+      <c r="O16" s="3" t="inlineStr">
+        <is>
+          <t>9851071622</t>
+        </is>
+      </c>
+      <c r="P16" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q16" s="3" t="inlineStr"/>
+      <c r="R16" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 11:53:17 AM</t>
+        </is>
+      </c>
+      <c r="S16" s="3" t="inlineStr"/>
+      <c r="T16" s="3" t="inlineStr"/>
+      <c r="U16" s="3" t="inlineStr">
+        <is>
+          <t>9851071622</t>
+        </is>
+      </c>
+      <c r="V16" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 02:42:05 PM</t>
+        </is>
+      </c>
+      <c r="W16" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 11:53:17 AM</t>
+        </is>
+      </c>
+      <c r="X16" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y16" s="3" t="inlineStr">
+        <is>
+          <t>27.68556</t>
+        </is>
+      </c>
+      <c r="Z16" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA16" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB16" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC16" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD16" s="3" t="inlineStr"/>
+      <c r="AE16" s="3" t="inlineStr">
+        <is>
+          <t>Near Sanepa Meat Shop Lalitpur, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF16" s="3" t="inlineStr">
+        <is>
+          <t>kapilshahi885@gmai.com</t>
+        </is>
+      </c>
+      <c r="AG16" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH16" s="3" t="inlineStr"/>
+      <c r="AI16" s="3" t="inlineStr">
+        <is>
+          <t>03:11 hour</t>
+        </is>
+      </c>
+      <c r="AJ16" s="3" t="inlineStr"/>
+      <c r="AK16" s="3" t="inlineStr"/>
+      <c r="AL16" s="3" t="inlineStr">
+        <is>
+          <t>Pradeep Yadav</t>
+        </is>
+      </c>
+      <c r="AM16" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN16" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO16" s="3" t="inlineStr">
+        <is>
+          <t>3,2</t>
+        </is>
+      </c>
+      <c r="AP16" s="3" t="inlineStr">
+        <is>
+          <t>85.30718</t>
+        </is>
+      </c>
+      <c r="AQ16" s="3" t="inlineStr"/>
+      <c r="AR16" s="3" t="inlineStr">
+        <is>
+          <t>Case : For upgradation to wifi6   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS16" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT16" s="3" t="inlineStr">
+        <is>
+          <t>2d 21h 11m</t>
+        </is>
+      </c>
+      <c r="AU16" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV16" s="3" t="inlineStr">
+        <is>
+          <t>Case : For upgradation to wifi6   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW16" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 12:00 PM</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr"/>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>Case : NETTV issue  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>NETTV issue</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>TKT1364261</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>Niratna manandhar</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
+          <t>Niratna manandhar</t>
+        </is>
+      </c>
+      <c r="O17" s="3" t="inlineStr">
+        <is>
+          <t>9826039231</t>
+        </is>
+      </c>
+      <c r="P17" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="Q17" s="3" t="inlineStr"/>
+      <c r="R17" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 12:00:52 PM</t>
+        </is>
+      </c>
+      <c r="S17" s="3" t="inlineStr"/>
+      <c r="T17" s="3" t="inlineStr"/>
+      <c r="U17" s="3" t="inlineStr">
+        <is>
+          <t>KLK9826039231</t>
+        </is>
+      </c>
+      <c r="V17" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 10:23:09 AM</t>
+        </is>
+      </c>
+      <c r="W17" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 12:00:52 PM</t>
+        </is>
+      </c>
+      <c r="X17" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y17" s="3" t="inlineStr"/>
+      <c r="Z17" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="AA17" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB17" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC17" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD17" s="3" t="inlineStr"/>
+      <c r="AE17" s="3" t="inlineStr">
+        <is>
+          <t>Dallu, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF17" s="3" t="inlineStr">
+        <is>
+          <t>triratna@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG17" s="3" t="inlineStr">
+        <is>
+          <t>NETTV-Welcome Screen Issue</t>
+        </is>
+      </c>
+      <c r="AH17" s="3" t="inlineStr"/>
+      <c r="AI17" s="3" t="inlineStr">
+        <is>
+          <t>11:37 hour</t>
+        </is>
+      </c>
+      <c r="AJ17" s="3" t="inlineStr"/>
+      <c r="AK17" s="3" t="inlineStr"/>
+      <c r="AL17" s="3" t="inlineStr">
+        <is>
+          <t>Sanish Magar</t>
+        </is>
+      </c>
+      <c r="AM17" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN17" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO17" s="3" t="inlineStr">
+        <is>
+          <t>1,1</t>
+        </is>
+      </c>
+      <c r="AP17" s="3" t="inlineStr"/>
+      <c r="AQ17" s="3" t="inlineStr"/>
+      <c r="AR17" s="3" t="inlineStr">
+        <is>
+          <t>Case : NETTV issue  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS17" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT17" s="3" t="inlineStr">
+        <is>
+          <t>1d 1h 37m</t>
+        </is>
+      </c>
+      <c r="AU17" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV17" s="3" t="inlineStr">
+        <is>
+          <t>Case : NETTV issue  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW17" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
         </is>
       </c>
     </row>
@@ -3633,13 +4029,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M32"/>
+  <dimension ref="A1:M35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
     <col width="39" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
     <col width="45" customWidth="1" min="7" max="7"/>
@@ -3670,7 +4066,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3">
@@ -3680,7 +4076,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4">
@@ -3691,7 +4087,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>78.6%</t>
+          <t>81.2%</t>
         </is>
       </c>
     </row>
@@ -3703,7 +4099,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>1d 14h 9m</t>
+          <t>1d 8h 16m</t>
         </is>
       </c>
     </row>
@@ -3715,7 +4111,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>3d 9h 45m</t>
+          <t>3d 4h 28m</t>
         </is>
       </c>
     </row>
@@ -3756,14 +4152,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="C10" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="C10" s="3" t="n">
-        <v>11</v>
-      </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>91.7%</t>
+          <t>92.3%</t>
         </is>
       </c>
     </row>
@@ -3774,14 +4170,14 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C11" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C11" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -3850,14 +4246,14 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="D16" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="D16" s="3" t="n">
-        <v>11</v>
-      </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>91.7%</t>
+          <t>92.3%</t>
         </is>
       </c>
     </row>
@@ -3887,177 +4283,133 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>Slow Internet Connection</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Video content is Buffering</t>
+          <t>NETTV-Welcome Screen Issue</t>
         </is>
       </c>
       <c r="C18" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D18" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="E18" s="3" t="inlineStr">
+      <c r="E19" s="5" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
     </row>
-    <row r="19"/>
-    <row r="20">
-      <c r="A20" s="6" t="inlineStr">
+    <row r="20"/>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>Ticket Number</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>Account Name</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D21" s="4" t="inlineStr">
-        <is>
-          <t>Sub Category</t>
-        </is>
-      </c>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="F21" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Type</t>
-        </is>
-      </c>
-      <c r="G21" s="4" t="inlineStr">
-        <is>
-          <t>Employee Remark / Solution Note</t>
-        </is>
-      </c>
-      <c r="H21" s="4" t="inlineStr">
-        <is>
-          <t>Action / Transfer Remark</t>
-        </is>
-      </c>
-      <c r="I21" s="4" t="inlineStr">
-        <is>
-          <t>Assigned Date</t>
-        </is>
-      </c>
-      <c r="J21" s="4" t="inlineStr">
-        <is>
-          <t>Created Date</t>
-        </is>
-      </c>
-      <c r="K21" s="4" t="inlineStr">
-        <is>
-          <t>Last Modified Date</t>
-        </is>
-      </c>
-      <c r="L21" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Assigned)</t>
-        </is>
-      </c>
-      <c r="M21" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>TKT1364446</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>Jeet Bahadur Basnet</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F22" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G22" s="3" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H22" s="3" t="inlineStr">
-        <is>
-          <t>Case : upgrade wifi 6  has been updated by Sabin Giri</t>
-        </is>
-      </c>
-      <c r="I22" s="3" t="inlineStr">
-        <is>
-          <t>10 Oct 2026 10:40:59 AM</t>
-        </is>
-      </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>09 Oct 2026 12:30:31 PM</t>
-        </is>
-      </c>
-      <c r="K22" s="3" t="inlineStr">
-        <is>
-          <t>10 Oct 2026 10:40:59 AM</t>
-        </is>
-      </c>
-      <c r="L22" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M22" s="3" t="inlineStr">
-        <is>
-          <t>22h 10m</t>
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Ticket Number</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>Account Name</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>Sub Category</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Type</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t>Employee Remark / Solution Note</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>Action / Transfer Remark</t>
+        </is>
+      </c>
+      <c r="I22" s="4" t="inlineStr">
+        <is>
+          <t>Assigned Date</t>
+        </is>
+      </c>
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>Created Date</t>
+        </is>
+      </c>
+      <c r="K22" s="4" t="inlineStr">
+        <is>
+          <t>Last Modified Date</t>
+        </is>
+      </c>
+      <c r="L22" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Assigned)</t>
+        </is>
+      </c>
+      <c r="M22" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>TKT1364411</t>
+          <t>TKT1364446</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>Bijya Lama</t>
+          <t>Jeet Bahadur Basnet</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
@@ -4087,22 +4439,22 @@
       </c>
       <c r="H23" s="5" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 upgrade   has been updated by Sabin Giri</t>
+          <t>Case : upgrade wifi 6  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I23" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 10:40:30 AM</t>
+          <t>10 Oct 2026 10:40:59 AM</t>
         </is>
       </c>
       <c r="J23" s="5" t="inlineStr">
         <is>
-          <t>09 Oct 2026 12:06:35 PM</t>
+          <t>09 Oct 2026 12:30:31 PM</t>
         </is>
       </c>
       <c r="K23" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 10:40:30 AM</t>
+          <t>10 Oct 2026 10:40:59 AM</t>
         </is>
       </c>
       <c r="L23" s="5" t="inlineStr">
@@ -4112,19 +4464,19 @@
       </c>
       <c r="M23" s="5" t="inlineStr">
         <is>
-          <t>22h 33m</t>
+          <t>22h 10m</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>TKT1357376</t>
+          <t>TKT1364411</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Goma Adhikari</t>
+          <t>Bijya Lama</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -4154,22 +4506,22 @@
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 upgrade   has been updated by Sanjeev Giri</t>
+          <t>Case : Wifi 6 upgrade   has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 10:49:43 AM</t>
+          <t>10 Oct 2026 10:40:30 AM</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>04 Oct 2026 08:51:00 AM</t>
+          <t>09 Oct 2026 12:06:35 PM</t>
         </is>
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 10:49:43 AM</t>
+          <t>10 Oct 2026 10:40:30 AM</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
@@ -4179,19 +4531,19 @@
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t>6d 1h 58m</t>
+          <t>22h 33m</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>TKT1358035</t>
+          <t>TKT1357376</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>Saurav Lamsal</t>
+          <t>Goma Adhikari</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
@@ -4206,12 +4558,12 @@
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
@@ -4221,32 +4573,32 @@
       </c>
       <c r="H25" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+          <t>Case : Wifi 6 upgrade   has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I25" s="5" t="inlineStr">
         <is>
-          <t>04 Oct 2026 02:07:16 PM</t>
+          <t>10 Oct 2026 10:49:43 AM</t>
         </is>
       </c>
       <c r="J25" s="5" t="inlineStr">
         <is>
-          <t>04 Oct 2026 02:07:16 PM</t>
+          <t>04 Oct 2026 08:51:00 AM</t>
         </is>
       </c>
       <c r="K25" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 11:04:09 AM</t>
+          <t>10 Oct 2026 10:49:43 AM</t>
         </is>
       </c>
       <c r="L25" s="5" t="inlineStr">
         <is>
-          <t>5d 20h 56m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M25" s="5" t="inlineStr">
         <is>
-          <t>5d 20h 56m</t>
+          <t>6d 1h 58m</t>
         </is>
       </c>
     </row>
@@ -4320,12 +4672,12 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>TKT1364756</t>
+          <t>TKT1358035</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>New Assist Traders</t>
+          <t>Saurav Lamsal</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
@@ -4340,12 +4692,12 @@
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
@@ -4355,44 +4707,44 @@
       </c>
       <c r="H27" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Chandramani Tharu</t>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I27" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 11:15:36 AM</t>
+          <t>04 Oct 2026 02:07:16 PM</t>
         </is>
       </c>
       <c r="J27" s="5" t="inlineStr">
         <is>
-          <t>09 Oct 2026 04:33:35 PM</t>
+          <t>04 Oct 2026 02:07:16 PM</t>
         </is>
       </c>
       <c r="K27" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 11:15:36 AM</t>
+          <t>10 Oct 2026 11:04:09 AM</t>
         </is>
       </c>
       <c r="L27" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>5d 20h 56m</t>
         </is>
       </c>
       <c r="M27" s="5" t="inlineStr">
         <is>
-          <t>18h 42m</t>
+          <t>5d 20h 56m</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>TKT1358080</t>
+          <t>TKT1364756</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Baburaja Maharjan</t>
+          <t>New Assist Traders</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
@@ -4427,17 +4779,17 @@
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 11:13:31 AM</t>
+          <t>10 Oct 2026 11:15:36 AM</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>04 Oct 2026 02:29:39 PM</t>
+          <t>09 Oct 2026 04:33:35 PM</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 11:13:31 AM</t>
+          <t>10 Oct 2026 11:15:36 AM</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
@@ -4447,19 +4799,19 @@
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>5d 20h 43m</t>
+          <t>18h 42m</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>TKT1359556</t>
+          <t>TKT1358080</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>Puspa KC</t>
+          <t>Baburaja Maharjan</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
@@ -4489,22 +4841,22 @@
       </c>
       <c r="H29" s="5" t="inlineStr">
         <is>
-          <t>Case : router upgrade  has been updated by Sabin Giri</t>
+          <t>Case : wifi6  has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I29" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 11:23:36 AM</t>
+          <t>10 Oct 2026 11:13:31 AM</t>
         </is>
       </c>
       <c r="J29" s="5" t="inlineStr">
         <is>
-          <t>05 Oct 2026 03:34:34 PM</t>
+          <t>04 Oct 2026 02:29:39 PM</t>
         </is>
       </c>
       <c r="K29" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 11:23:36 AM</t>
+          <t>10 Oct 2026 11:13:31 AM</t>
         </is>
       </c>
       <c r="L29" s="5" t="inlineStr">
@@ -4514,19 +4866,19 @@
       </c>
       <c r="M29" s="5" t="inlineStr">
         <is>
-          <t>4d 19h 49m</t>
+          <t>5d 20h 43m</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>TKT1365031</t>
+          <t>TKT1359556</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Prem Kumar Shrestha</t>
+          <t>Puspa KC</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
@@ -4551,27 +4903,27 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>Case : WiFi 6   has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>Case : WiFi 6   has been updated by Sanjeev Giri</t>
+          <t>Case : router upgrade  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 11:41:30 AM</t>
+          <t>10 Oct 2026 11:23:36 AM</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>09 Oct 2026 09:56:52 PM</t>
+          <t>05 Oct 2026 03:34:34 PM</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 11:41:30 AM</t>
+          <t>10 Oct 2026 11:23:36 AM</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
@@ -4581,19 +4933,19 @@
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>13h 44m</t>
+          <t>4d 19h 49m</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>TKT1362058</t>
+          <t>TKT1365031</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>Gyan Chiraniya</t>
+          <t>Prem Kumar Shrestha</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
@@ -4608,47 +4960,47 @@
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>Case : For upgradation to wifi6   has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H31" s="5" t="inlineStr">
         <is>
-          <t>Case : For upgradation to wifi6   has been updated by Ajit Shrestha</t>
+          <t>Case : WiFi 6   has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I31" s="5" t="inlineStr">
         <is>
-          <t>07 Oct 2026 02:43:23 PM</t>
+          <t>10 Oct 2026 11:41:30 AM</t>
         </is>
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>07 Oct 2026 02:43:23 PM</t>
+          <t>09 Oct 2026 09:56:52 PM</t>
         </is>
       </c>
       <c r="K31" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 11:36:00 AM</t>
+          <t>10 Oct 2026 11:41:30 AM</t>
         </is>
       </c>
       <c r="L31" s="5" t="inlineStr">
         <is>
-          <t>2d 20h 52m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M31" s="5" t="inlineStr">
         <is>
-          <t>2d 20h 52m</t>
+          <t>13h 44m</t>
         </is>
       </c>
     </row>
@@ -4685,37 +5037,238 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
           <t>Case : For upgradation to wifi6   has been updated by Ajit Shrestha</t>
         </is>
       </c>
-      <c r="H32" s="3" t="inlineStr">
+      <c r="I32" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 02:43:23 PM</t>
+        </is>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 02:43:23 PM</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 11:36:00 AM</t>
+        </is>
+      </c>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t>2d 20h 52m</t>
+        </is>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>2d 20h 52m</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>TKT1362058</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>Gyan Chiraniya</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F33" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G33" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H33" s="5" t="inlineStr">
         <is>
           <t>Case : For upgradation to wifi6   has been updated by Ajit Shrestha</t>
         </is>
       </c>
-      <c r="I32" s="3" t="inlineStr">
+      <c r="I33" s="5" t="inlineStr">
         <is>
           <t>07 Oct 2026 02:43:23 PM</t>
         </is>
       </c>
-      <c r="J32" s="3" t="inlineStr">
+      <c r="J33" s="5" t="inlineStr">
         <is>
           <t>07 Oct 2026 02:43:23 PM</t>
         </is>
       </c>
-      <c r="K32" s="3" t="inlineStr">
+      <c r="K33" s="5" t="inlineStr">
         <is>
           <t>10 Oct 2026 11:36:00 AM</t>
         </is>
       </c>
-      <c r="L32" s="3" t="inlineStr">
+      <c r="L33" s="5" t="inlineStr">
         <is>
           <t>2d 20h 52m</t>
         </is>
       </c>
-      <c r="M32" s="3" t="inlineStr">
+      <c r="M33" s="5" t="inlineStr">
         <is>
           <t>2d 20h 52m</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>TKT1362055</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>Ravi Shahi</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr">
+        <is>
+          <t>Case : For upgradation to wifi6   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>Case : For upgradation to wifi6   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 11:53:17 AM</t>
+        </is>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 02:42:05 PM</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 11:53:17 AM</t>
+        </is>
+      </c>
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>2d 21h 11m</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>TKT1364261</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>Niratna manandhar</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>NETTV-Welcome Screen Issue</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <t>Case : NETTV issue  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="H35" s="5" t="inlineStr">
+        <is>
+          <t>Case : NETTV issue  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I35" s="5" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 12:00:52 PM</t>
+        </is>
+      </c>
+      <c r="J35" s="5" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 10:23:09 AM</t>
+        </is>
+      </c>
+      <c r="K35" s="5" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 12:00:52 PM</t>
+        </is>
+      </c>
+      <c r="L35" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M35" s="5" t="inlineStr">
+        <is>
+          <t>1d 1h 37m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_10_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_10_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW17"/>
+  <dimension ref="A1:AW19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -3671,10 +3671,8 @@
           <t>Ravi Shahi</t>
         </is>
       </c>
-      <c r="O16" s="3" t="inlineStr">
-        <is>
-          <t>9851071622</t>
-        </is>
+      <c r="O16" s="3" t="n">
+        <v>9851071622</v>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
@@ -3768,25 +3766,21 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN16" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN16" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO16" s="3" t="inlineStr">
         <is>
           <t>3,2</t>
         </is>
       </c>
-      <c r="AP16" s="3" t="inlineStr">
-        <is>
-          <t>85.30718</t>
-        </is>
+      <c r="AP16" s="3" t="n">
+        <v>85.30718</v>
       </c>
       <c r="AQ16" s="3" t="inlineStr"/>
       <c r="AR16" s="3" t="inlineStr">
         <is>
-          <t>Case : For upgradation to wifi6   has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS16" s="3" t="inlineStr">
@@ -3882,10 +3876,8 @@
           <t>Niratna manandhar</t>
         </is>
       </c>
-      <c r="O17" s="3" t="inlineStr">
-        <is>
-          <t>9826039231</t>
-        </is>
+      <c r="O17" s="3" t="n">
+        <v>9826039231</v>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
@@ -3975,10 +3967,8 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN17" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN17" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO17" s="3" t="inlineStr">
         <is>
@@ -3989,32 +3979,438 @@
       <c r="AQ17" s="3" t="inlineStr"/>
       <c r="AR17" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS17" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT17" s="3" t="inlineStr">
+        <is>
+          <t>1d 1h 37m</t>
+        </is>
+      </c>
+      <c r="AU17" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV17" s="3" t="inlineStr">
+        <is>
           <t>Case : NETTV issue  has been updated by Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AS17" s="3" t="inlineStr">
+      <c r="AW17" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 12:04 PM</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr"/>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>Case :   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr"/>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>TKT1360378</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>Maheshwor Maharjan</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
+          <t>Maheshwor Maharjan</t>
+        </is>
+      </c>
+      <c r="O18" s="3" t="inlineStr">
+        <is>
+          <t>9841390735</t>
+        </is>
+      </c>
+      <c r="P18" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q18" s="3" t="inlineStr"/>
+      <c r="R18" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 12:04:10 PM</t>
+        </is>
+      </c>
+      <c r="S18" s="3" t="inlineStr"/>
+      <c r="T18" s="3" t="inlineStr"/>
+      <c r="U18" s="3" t="inlineStr">
+        <is>
+          <t>9841390735</t>
+        </is>
+      </c>
+      <c r="V18" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 10:49:38 AM</t>
+        </is>
+      </c>
+      <c r="W18" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 12:04:10 PM</t>
+        </is>
+      </c>
+      <c r="X18" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y18" s="3" t="inlineStr">
+        <is>
+          <t>27.751766</t>
+        </is>
+      </c>
+      <c r="Z18" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA18" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB18" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC18" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD18" s="3" t="inlineStr"/>
+      <c r="AE18" s="3" t="inlineStr">
+        <is>
+          <t>Manmaiju chowk, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF18" s="3" t="inlineStr"/>
+      <c r="AG18" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH18" s="3" t="inlineStr"/>
+      <c r="AI18" s="3" t="inlineStr">
+        <is>
+          <t>17:15 hour</t>
+        </is>
+      </c>
+      <c r="AJ18" s="3" t="inlineStr"/>
+      <c r="AK18" s="3" t="inlineStr"/>
+      <c r="AL18" s="3" t="inlineStr">
+        <is>
+          <t>Merika Silwal</t>
+        </is>
+      </c>
+      <c r="AM18" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN18" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO18" s="3" t="inlineStr">
+        <is>
+          <t>3,4</t>
+        </is>
+      </c>
+      <c r="AP18" s="3" t="inlineStr">
+        <is>
+          <t>85.308081</t>
+        </is>
+      </c>
+      <c r="AQ18" s="3" t="inlineStr"/>
+      <c r="AR18" s="3" t="inlineStr">
+        <is>
+          <t>Case :   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS18" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT17" s="3" t="inlineStr">
-        <is>
-          <t>1d 1h 37m</t>
-        </is>
-      </c>
-      <c r="AU17" s="3" t="inlineStr">
+      <c r="AT18" s="3" t="inlineStr">
+        <is>
+          <t>4d 1h 14m</t>
+        </is>
+      </c>
+      <c r="AU18" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV17" s="3" t="inlineStr">
-        <is>
-          <t>Case : NETTV issue  has been updated by Ajit Shrestha</t>
-        </is>
-      </c>
-      <c r="AW17" s="3" t="inlineStr">
-        <is>
-          <t>IPTV Issue</t>
+      <c r="AV18" s="3" t="inlineStr">
+        <is>
+          <t>Case :   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW18" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 12:06 PM</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr"/>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>Case : low wifi range issue  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>low wifi range issue</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>TKT1365280</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>Atul Ali</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
+          <t>Atul Ali</t>
+        </is>
+      </c>
+      <c r="O19" s="3" t="inlineStr">
+        <is>
+          <t>9841121934</t>
+        </is>
+      </c>
+      <c r="P19" s="3" t="inlineStr">
+        <is>
+          <t>Wi-Fi Range</t>
+        </is>
+      </c>
+      <c r="Q19" s="3" t="inlineStr"/>
+      <c r="R19" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 12:06:57 PM</t>
+        </is>
+      </c>
+      <c r="S19" s="3" t="inlineStr"/>
+      <c r="T19" s="3" t="inlineStr"/>
+      <c r="U19" s="3" t="inlineStr">
+        <is>
+          <t>9841121934</t>
+        </is>
+      </c>
+      <c r="V19" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 10:00:04 AM</t>
+        </is>
+      </c>
+      <c r="W19" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 12:06:57 PM</t>
+        </is>
+      </c>
+      <c r="X19" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y19" s="3" t="inlineStr"/>
+      <c r="Z19" s="3" t="inlineStr">
+        <is>
+          <t>Wi-Fi Range</t>
+        </is>
+      </c>
+      <c r="AA19" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB19" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC19" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD19" s="3" t="inlineStr"/>
+      <c r="AE19" s="3" t="inlineStr">
+        <is>
+          <t>Srijana Nagar Bus Stop - Bus stop Araniko Highway Bhaktapur 44800, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF19" s="3" t="inlineStr">
+        <is>
+          <t>atul.mansur100@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG19" s="3" t="inlineStr">
+        <is>
+          <t>Low Wi-Fi Range on both band</t>
+        </is>
+      </c>
+      <c r="AH19" s="3" t="inlineStr"/>
+      <c r="AI19" s="3" t="inlineStr">
+        <is>
+          <t>02:06 hour</t>
+        </is>
+      </c>
+      <c r="AJ19" s="3" t="inlineStr"/>
+      <c r="AK19" s="3" t="inlineStr"/>
+      <c r="AL19" s="3" t="inlineStr">
+        <is>
+          <t>Sanish Magar</t>
+        </is>
+      </c>
+      <c r="AM19" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN19" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO19" s="3" t="inlineStr">
+        <is>
+          <t>L20-6</t>
+        </is>
+      </c>
+      <c r="AP19" s="3" t="inlineStr"/>
+      <c r="AQ19" s="3" t="inlineStr"/>
+      <c r="AR19" s="3" t="inlineStr">
+        <is>
+          <t>Case : low wifi range issue  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS19" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT19" s="3" t="inlineStr">
+        <is>
+          <t>2h 6m</t>
+        </is>
+      </c>
+      <c r="AU19" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV19" s="3" t="inlineStr">
+        <is>
+          <t>Case : low wifi range issue  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW19" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
         </is>
       </c>
     </row>
@@ -4029,13 +4425,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M35"/>
+  <dimension ref="A1:M39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
     <col width="39" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
     <col width="45" customWidth="1" min="7" max="7"/>
@@ -4066,7 +4462,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3">
@@ -4076,7 +4472,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4">
@@ -4087,7 +4483,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>81.2%</t>
+          <t>83.3%</t>
         </is>
       </c>
     </row>
@@ -4099,7 +4495,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>1d 8h 16m</t>
+          <t>1d 3h 58m</t>
         </is>
       </c>
     </row>
@@ -4111,7 +4507,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>3d 4h 28m</t>
+          <t>3d 54m</t>
         </is>
       </c>
     </row>
@@ -4152,14 +4548,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="C10" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="C10" s="3" t="n">
-        <v>12</v>
-      </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>92.3%</t>
+          <t>92.9%</t>
         </is>
       </c>
     </row>
@@ -4199,84 +4595,79 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Wi-Fi Range</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>Total Tickets Breakdown by Category &amp; Sub Category</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>Sub Category</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>Total Scraped Tickets</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>Solved / Handled Count</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>Solution Rate %</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="n">
-        <v>13</v>
-      </c>
-      <c r="D16" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="E16" s="3" t="inlineStr">
-        <is>
-          <t>92.3%</t>
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>Sub Category</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>Total Scraped Tickets</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>Solved / Handled Count</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>Solution Rate %</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>NETTV-No internet connection in STB</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>92.9%</t>
         </is>
       </c>
     </row>
@@ -4288,262 +4679,174 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>NETTV-Welcome Screen Issue</t>
+          <t>NETTV-No internet connection in STB</t>
         </is>
       </c>
       <c r="C18" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>Slow Internet Connection</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>Video content is Buffering</t>
+          <t>NETTV-Welcome Screen Issue</t>
         </is>
       </c>
       <c r="C19" s="5" t="n">
         <v>1</v>
       </c>
       <c r="D19" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E19" s="5" t="inlineStr">
+      <c r="E20" s="3" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
     </row>
-    <row r="20"/>
     <row r="21">
-      <c r="A21" s="6" t="inlineStr">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>Wi-Fi Range</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>Low Wi-Fi Range on both band</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="22"/>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>Ticket Number</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>Account Name</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D22" s="4" t="inlineStr">
-        <is>
-          <t>Sub Category</t>
-        </is>
-      </c>
-      <c r="E22" s="4" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="F22" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Type</t>
-        </is>
-      </c>
-      <c r="G22" s="4" t="inlineStr">
-        <is>
-          <t>Employee Remark / Solution Note</t>
-        </is>
-      </c>
-      <c r="H22" s="4" t="inlineStr">
-        <is>
-          <t>Action / Transfer Remark</t>
-        </is>
-      </c>
-      <c r="I22" s="4" t="inlineStr">
-        <is>
-          <t>Assigned Date</t>
-        </is>
-      </c>
-      <c r="J22" s="4" t="inlineStr">
-        <is>
-          <t>Created Date</t>
-        </is>
-      </c>
-      <c r="K22" s="4" t="inlineStr">
-        <is>
-          <t>Last Modified Date</t>
-        </is>
-      </c>
-      <c r="L22" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Assigned)</t>
-        </is>
-      </c>
-      <c r="M22" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Created)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="5" t="inlineStr">
-        <is>
-          <t>TKT1364446</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>Jeet Bahadur Basnet</t>
-        </is>
-      </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D23" s="5" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E23" s="5" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F23" s="5" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G23" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H23" s="5" t="inlineStr">
-        <is>
-          <t>Case : upgrade wifi 6  has been updated by Sabin Giri</t>
-        </is>
-      </c>
-      <c r="I23" s="5" t="inlineStr">
-        <is>
-          <t>10 Oct 2026 10:40:59 AM</t>
-        </is>
-      </c>
-      <c r="J23" s="5" t="inlineStr">
-        <is>
-          <t>09 Oct 2026 12:30:31 PM</t>
-        </is>
-      </c>
-      <c r="K23" s="5" t="inlineStr">
-        <is>
-          <t>10 Oct 2026 10:40:59 AM</t>
-        </is>
-      </c>
-      <c r="L23" s="5" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M23" s="5" t="inlineStr">
-        <is>
-          <t>22h 10m</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t>TKT1364411</t>
-        </is>
-      </c>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>Bijya Lama</t>
-        </is>
-      </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D24" s="3" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E24" s="3" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F24" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G24" s="3" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H24" s="3" t="inlineStr">
-        <is>
-          <t>Case : Wifi 6 upgrade   has been updated by Sabin Giri</t>
-        </is>
-      </c>
-      <c r="I24" s="3" t="inlineStr">
-        <is>
-          <t>10 Oct 2026 10:40:30 AM</t>
-        </is>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t>09 Oct 2026 12:06:35 PM</t>
-        </is>
-      </c>
-      <c r="K24" s="3" t="inlineStr">
-        <is>
-          <t>10 Oct 2026 10:40:30 AM</t>
-        </is>
-      </c>
-      <c r="L24" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M24" s="3" t="inlineStr">
-        <is>
-          <t>22h 33m</t>
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Ticket Number</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>Account Name</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>Sub Category</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Type</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="inlineStr">
+        <is>
+          <t>Employee Remark / Solution Note</t>
+        </is>
+      </c>
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t>Action / Transfer Remark</t>
+        </is>
+      </c>
+      <c r="I24" s="4" t="inlineStr">
+        <is>
+          <t>Assigned Date</t>
+        </is>
+      </c>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>Created Date</t>
+        </is>
+      </c>
+      <c r="K24" s="4" t="inlineStr">
+        <is>
+          <t>Last Modified Date</t>
+        </is>
+      </c>
+      <c r="L24" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Assigned)</t>
+        </is>
+      </c>
+      <c r="M24" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>TKT1357376</t>
+          <t>TKT1364446</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>Goma Adhikari</t>
+          <t>Jeet Bahadur Basnet</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
@@ -4573,22 +4876,22 @@
       </c>
       <c r="H25" s="5" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 upgrade   has been updated by Sanjeev Giri</t>
+          <t>Case : upgrade wifi 6  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I25" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 10:49:43 AM</t>
+          <t>10 Oct 2026 10:40:59 AM</t>
         </is>
       </c>
       <c r="J25" s="5" t="inlineStr">
         <is>
-          <t>04 Oct 2026 08:51:00 AM</t>
+          <t>09 Oct 2026 12:30:31 PM</t>
         </is>
       </c>
       <c r="K25" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 10:49:43 AM</t>
+          <t>10 Oct 2026 10:40:59 AM</t>
         </is>
       </c>
       <c r="L25" s="5" t="inlineStr">
@@ -4598,19 +4901,19 @@
       </c>
       <c r="M25" s="5" t="inlineStr">
         <is>
-          <t>6d 1h 58m</t>
+          <t>22h 10m</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>TKT1358035</t>
+          <t>TKT1364411</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Saurav Lamsal</t>
+          <t>Bijya Lama</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
@@ -4625,12 +4928,12 @@
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
@@ -4640,44 +4943,44 @@
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+          <t>Case : Wifi 6 upgrade   has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>04 Oct 2026 02:07:16 PM</t>
+          <t>10 Oct 2026 10:40:30 AM</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>04 Oct 2026 02:07:16 PM</t>
+          <t>09 Oct 2026 12:06:35 PM</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 11:04:09 AM</t>
+          <t>10 Oct 2026 10:40:30 AM</t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t>5d 20h 56m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>5d 20h 56m</t>
+          <t>22h 33m</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>TKT1358035</t>
+          <t>TKT1357376</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>Saurav Lamsal</t>
+          <t>Goma Adhikari</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
@@ -4692,12 +4995,12 @@
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
@@ -4707,44 +5010,44 @@
       </c>
       <c r="H27" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+          <t>Case : Wifi 6 upgrade   has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I27" s="5" t="inlineStr">
         <is>
-          <t>04 Oct 2026 02:07:16 PM</t>
+          <t>10 Oct 2026 10:49:43 AM</t>
         </is>
       </c>
       <c r="J27" s="5" t="inlineStr">
         <is>
-          <t>04 Oct 2026 02:07:16 PM</t>
+          <t>04 Oct 2026 08:51:00 AM</t>
         </is>
       </c>
       <c r="K27" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 11:04:09 AM</t>
+          <t>10 Oct 2026 10:49:43 AM</t>
         </is>
       </c>
       <c r="L27" s="5" t="inlineStr">
         <is>
-          <t>5d 20h 56m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M27" s="5" t="inlineStr">
         <is>
-          <t>5d 20h 56m</t>
+          <t>6d 1h 58m</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>TKT1364756</t>
+          <t>TKT1358035</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>New Assist Traders</t>
+          <t>Saurav Lamsal</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
@@ -4759,12 +5062,12 @@
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
@@ -4774,44 +5077,44 @@
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Chandramani Tharu</t>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 11:15:36 AM</t>
+          <t>04 Oct 2026 02:07:16 PM</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>09 Oct 2026 04:33:35 PM</t>
+          <t>04 Oct 2026 02:07:16 PM</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 11:15:36 AM</t>
+          <t>10 Oct 2026 11:04:09 AM</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>5d 20h 56m</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>18h 42m</t>
+          <t>5d 20h 56m</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>TKT1358080</t>
+          <t>TKT1358035</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>Baburaja Maharjan</t>
+          <t>Saurav Lamsal</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
@@ -4826,12 +5129,12 @@
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
@@ -4841,44 +5144,44 @@
       </c>
       <c r="H29" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Chandramani Tharu</t>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I29" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 11:13:31 AM</t>
+          <t>04 Oct 2026 02:07:16 PM</t>
         </is>
       </c>
       <c r="J29" s="5" t="inlineStr">
         <is>
-          <t>04 Oct 2026 02:29:39 PM</t>
+          <t>04 Oct 2026 02:07:16 PM</t>
         </is>
       </c>
       <c r="K29" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 11:13:31 AM</t>
+          <t>10 Oct 2026 11:04:09 AM</t>
         </is>
       </c>
       <c r="L29" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>5d 20h 56m</t>
         </is>
       </c>
       <c r="M29" s="5" t="inlineStr">
         <is>
-          <t>5d 20h 43m</t>
+          <t>5d 20h 56m</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>TKT1359556</t>
+          <t>TKT1364756</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Puspa KC</t>
+          <t>New Assist Traders</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
@@ -4908,22 +5211,22 @@
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>Case : router upgrade  has been updated by Sabin Giri</t>
+          <t>Case : wifi6  has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 11:23:36 AM</t>
+          <t>10 Oct 2026 11:15:36 AM</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>05 Oct 2026 03:34:34 PM</t>
+          <t>09 Oct 2026 04:33:35 PM</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 11:23:36 AM</t>
+          <t>10 Oct 2026 11:15:36 AM</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
@@ -4933,19 +5236,19 @@
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>4d 19h 49m</t>
+          <t>18h 42m</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>TKT1365031</t>
+          <t>TKT1358080</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>Prem Kumar Shrestha</t>
+          <t>Baburaja Maharjan</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
@@ -4975,22 +5278,22 @@
       </c>
       <c r="H31" s="5" t="inlineStr">
         <is>
-          <t>Case : WiFi 6   has been updated by Sanjeev Giri</t>
+          <t>Case : wifi6  has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I31" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 11:41:30 AM</t>
+          <t>10 Oct 2026 11:13:31 AM</t>
         </is>
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>09 Oct 2026 09:56:52 PM</t>
+          <t>04 Oct 2026 02:29:39 PM</t>
         </is>
       </c>
       <c r="K31" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 11:41:30 AM</t>
+          <t>10 Oct 2026 11:13:31 AM</t>
         </is>
       </c>
       <c r="L31" s="5" t="inlineStr">
@@ -5000,19 +5303,19 @@
       </c>
       <c r="M31" s="5" t="inlineStr">
         <is>
-          <t>13h 44m</t>
+          <t>5d 20h 43m</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>TKT1362058</t>
+          <t>TKT1359556</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>Gyan Chiraniya</t>
+          <t>Puspa KC</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
@@ -5027,12 +5330,12 @@
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
@@ -5042,44 +5345,44 @@
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>Case : For upgradation to wifi6   has been updated by Ajit Shrestha</t>
+          <t>Case : router upgrade  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>07 Oct 2026 02:43:23 PM</t>
+          <t>10 Oct 2026 11:23:36 AM</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>07 Oct 2026 02:43:23 PM</t>
+          <t>05 Oct 2026 03:34:34 PM</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 11:36:00 AM</t>
+          <t>10 Oct 2026 11:23:36 AM</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t>2d 20h 52m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>2d 20h 52m</t>
+          <t>4d 19h 49m</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>TKT1362058</t>
+          <t>TKT1365031</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>Gyan Chiraniya</t>
+          <t>Prem Kumar Shrestha</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
@@ -5094,12 +5397,12 @@
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
@@ -5109,44 +5412,44 @@
       </c>
       <c r="H33" s="5" t="inlineStr">
         <is>
-          <t>Case : For upgradation to wifi6   has been updated by Ajit Shrestha</t>
+          <t>Case : WiFi 6   has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I33" s="5" t="inlineStr">
         <is>
-          <t>07 Oct 2026 02:43:23 PM</t>
+          <t>10 Oct 2026 11:41:30 AM</t>
         </is>
       </c>
       <c r="J33" s="5" t="inlineStr">
         <is>
-          <t>07 Oct 2026 02:43:23 PM</t>
+          <t>09 Oct 2026 09:56:52 PM</t>
         </is>
       </c>
       <c r="K33" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 11:36:00 AM</t>
+          <t>10 Oct 2026 11:41:30 AM</t>
         </is>
       </c>
       <c r="L33" s="5" t="inlineStr">
         <is>
-          <t>2d 20h 52m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M33" s="5" t="inlineStr">
         <is>
-          <t>2d 20h 52m</t>
+          <t>13h 44m</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>TKT1362055</t>
+          <t>TKT1362058</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>Ravi Shahi</t>
+          <t>Gyan Chiraniya</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
@@ -5161,114 +5464,382 @@
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>Case : For upgradation to wifi6   has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>Case : For upgradation to wifi6   has been updated by Chandramani Tharu</t>
+          <t>Case : For upgradation to wifi6   has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 11:53:17 AM</t>
+          <t>07 Oct 2026 02:43:23 PM</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>07 Oct 2026 02:42:05 PM</t>
+          <t>07 Oct 2026 02:43:23 PM</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 11:53:17 AM</t>
+          <t>10 Oct 2026 11:36:00 AM</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>2d 20h 52m</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>2d 21h 11m</t>
+          <t>2d 20h 52m</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
+          <t>TKT1362058</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>Gyan Chiraniya</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H35" s="5" t="inlineStr">
+        <is>
+          <t>Case : For upgradation to wifi6   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I35" s="5" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 02:43:23 PM</t>
+        </is>
+      </c>
+      <c r="J35" s="5" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 02:43:23 PM</t>
+        </is>
+      </c>
+      <c r="K35" s="5" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 11:36:00 AM</t>
+        </is>
+      </c>
+      <c r="L35" s="5" t="inlineStr">
+        <is>
+          <t>2d 20h 52m</t>
+        </is>
+      </c>
+      <c r="M35" s="5" t="inlineStr">
+        <is>
+          <t>2d 20h 52m</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>TKT1362055</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>Ravi Shahi</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>Case : For upgradation to wifi6   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 11:53:17 AM</t>
+        </is>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 02:42:05 PM</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 11:53:17 AM</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t>2d 21h 11m</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
           <t>TKT1364261</t>
         </is>
       </c>
-      <c r="B35" s="5" t="inlineStr">
+      <c r="B37" s="5" t="inlineStr">
         <is>
           <t>Niratna manandhar</t>
         </is>
       </c>
-      <c r="C35" s="5" t="inlineStr">
+      <c r="C37" s="5" t="inlineStr">
         <is>
           <t>IPTV Related Issues</t>
         </is>
       </c>
-      <c r="D35" s="5" t="inlineStr">
+      <c r="D37" s="5" t="inlineStr">
         <is>
           <t>NETTV-Welcome Screen Issue</t>
         </is>
       </c>
-      <c r="E35" s="5" t="inlineStr">
+      <c r="E37" s="5" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="F35" s="5" t="inlineStr">
+      <c r="F37" s="5" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="G35" s="5" t="inlineStr">
+      <c r="G37" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H37" s="5" t="inlineStr">
         <is>
           <t>Case : NETTV issue  has been updated by Ajit Shrestha</t>
         </is>
       </c>
-      <c r="H35" s="5" t="inlineStr">
-        <is>
-          <t>Case : NETTV issue  has been updated by Ajit Shrestha</t>
-        </is>
-      </c>
-      <c r="I35" s="5" t="inlineStr">
+      <c r="I37" s="5" t="inlineStr">
         <is>
           <t>10 Oct 2026 12:00:52 PM</t>
         </is>
       </c>
-      <c r="J35" s="5" t="inlineStr">
+      <c r="J37" s="5" t="inlineStr">
         <is>
           <t>09 Oct 2026 10:23:09 AM</t>
         </is>
       </c>
-      <c r="K35" s="5" t="inlineStr">
+      <c r="K37" s="5" t="inlineStr">
         <is>
           <t>10 Oct 2026 12:00:52 PM</t>
         </is>
       </c>
-      <c r="L35" s="5" t="inlineStr">
+      <c r="L37" s="5" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="M35" s="5" t="inlineStr">
+      <c r="M37" s="5" t="inlineStr">
         <is>
           <t>1d 1h 37m</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>TKT1360378</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>Maheshwor Maharjan</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="inlineStr">
+        <is>
+          <t>Case :   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>Case :   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I38" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 12:04:10 PM</t>
+        </is>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 10:49:38 AM</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 12:04:10 PM</t>
+        </is>
+      </c>
+      <c r="L38" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t>4d 1h 14m</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>TKT1365280</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>Atul Ali</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>Wi-Fi Range</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>Low Wi-Fi Range on both band</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F39" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G39" s="5" t="inlineStr">
+        <is>
+          <t>Case : low wifi range issue  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="H39" s="5" t="inlineStr">
+        <is>
+          <t>Case : low wifi range issue  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I39" s="5" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 12:06:57 PM</t>
+        </is>
+      </c>
+      <c r="J39" s="5" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 10:00:04 AM</t>
+        </is>
+      </c>
+      <c r="K39" s="5" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 12:06:57 PM</t>
+        </is>
+      </c>
+      <c r="L39" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M39" s="5" t="inlineStr">
+        <is>
+          <t>2h 6m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_10_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_10_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW19"/>
+  <dimension ref="A1:AW20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -4061,20 +4061,14 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="M18" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="M18" s="3" t="inlineStr"/>
       <c r="N18" s="3" t="inlineStr">
         <is>
           <t>Maheshwor Maharjan</t>
         </is>
       </c>
-      <c r="O18" s="3" t="inlineStr">
-        <is>
-          <t>9841390735</t>
-        </is>
+      <c r="O18" s="3" t="n">
+        <v>9841390735</v>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
@@ -4164,25 +4158,21 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN18" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN18" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO18" s="3" t="inlineStr">
         <is>
           <t>3,4</t>
         </is>
       </c>
-      <c r="AP18" s="3" t="inlineStr">
-        <is>
-          <t>85.308081</t>
-        </is>
+      <c r="AP18" s="3" t="n">
+        <v>85.308081</v>
       </c>
       <c r="AQ18" s="3" t="inlineStr"/>
       <c r="AR18" s="3" t="inlineStr">
         <is>
-          <t>Case :   has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS18" s="3" t="inlineStr">
@@ -4278,10 +4268,8 @@
           <t>Atul Ali</t>
         </is>
       </c>
-      <c r="O19" s="3" t="inlineStr">
-        <is>
-          <t>9841121934</t>
-        </is>
+      <c r="O19" s="3" t="n">
+        <v>9841121934</v>
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
@@ -4371,10 +4359,8 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN19" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN19" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO19" s="3" t="inlineStr">
         <is>
@@ -4385,32 +4371,235 @@
       <c r="AQ19" s="3" t="inlineStr"/>
       <c r="AR19" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS19" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT19" s="3" t="inlineStr">
+        <is>
+          <t>2h 6m</t>
+        </is>
+      </c>
+      <c r="AU19" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV19" s="3" t="inlineStr">
+        <is>
           <t>Case : low wifi range issue  has been updated by Sabin Giri</t>
         </is>
       </c>
-      <c r="AS19" s="3" t="inlineStr">
+      <c r="AW19" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 12:30 PM</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr"/>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>wifi6</t>
+        </is>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>TKT1364910</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>Ayush Duwal</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
+          <t>Ayush Duwal</t>
+        </is>
+      </c>
+      <c r="O20" s="3" t="inlineStr">
+        <is>
+          <t>9869078453</t>
+        </is>
+      </c>
+      <c r="P20" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q20" s="3" t="inlineStr"/>
+      <c r="R20" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 12:30:17 PM</t>
+        </is>
+      </c>
+      <c r="S20" s="3" t="inlineStr"/>
+      <c r="T20" s="3" t="inlineStr"/>
+      <c r="U20" s="3" t="inlineStr">
+        <is>
+          <t>9869078453</t>
+        </is>
+      </c>
+      <c r="V20" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 06:57:31 PM</t>
+        </is>
+      </c>
+      <c r="W20" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 12:30:17 PM</t>
+        </is>
+      </c>
+      <c r="X20" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y20" s="3" t="inlineStr"/>
+      <c r="Z20" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA20" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB20" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC20" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD20" s="3" t="inlineStr"/>
+      <c r="AE20" s="3" t="inlineStr">
+        <is>
+          <t>Surya Binayayak Near khopa engeneering college, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF20" s="3" t="inlineStr">
+        <is>
+          <t>duwalaayush234@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG20" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH20" s="3" t="inlineStr"/>
+      <c r="AI20" s="3" t="inlineStr">
+        <is>
+          <t>03:33 hour</t>
+        </is>
+      </c>
+      <c r="AJ20" s="3" t="inlineStr"/>
+      <c r="AK20" s="3" t="inlineStr"/>
+      <c r="AL20" s="3" t="inlineStr">
+        <is>
+          <t>Indra KC</t>
+        </is>
+      </c>
+      <c r="AM20" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN20" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO20" s="3" t="inlineStr">
+        <is>
+          <t>L3-4</t>
+        </is>
+      </c>
+      <c r="AP20" s="3" t="inlineStr"/>
+      <c r="AQ20" s="3" t="inlineStr"/>
+      <c r="AR20" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS20" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT19" s="3" t="inlineStr">
-        <is>
-          <t>2h 6m</t>
-        </is>
-      </c>
-      <c r="AU19" s="3" t="inlineStr">
+      <c r="AT20" s="3" t="inlineStr">
+        <is>
+          <t>17h 32m</t>
+        </is>
+      </c>
+      <c r="AU20" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV19" s="3" t="inlineStr">
-        <is>
-          <t>Case : low wifi range issue  has been updated by Sabin Giri</t>
-        </is>
-      </c>
-      <c r="AW19" s="3" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
+      <c r="AV20" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW20" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
         </is>
       </c>
     </row>
@@ -4425,7 +4614,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M39"/>
+  <dimension ref="A1:M40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -4462,7 +4651,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3">
@@ -4472,7 +4661,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4">
@@ -4483,7 +4672,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>84.2%</t>
         </is>
       </c>
     </row>
@@ -4495,7 +4684,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>1d 3h 58m</t>
+          <t>1d 2h 13m</t>
         </is>
       </c>
     </row>
@@ -4507,7 +4696,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>3d 54m</t>
+          <t>2d 21h 26m</t>
         </is>
       </c>
     </row>
@@ -4548,14 +4737,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="C10" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="C10" s="3" t="n">
-        <v>13</v>
-      </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>92.9%</t>
+          <t>93.3%</t>
         </is>
       </c>
     </row>
@@ -4660,14 +4849,14 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="D17" s="5" t="n">
         <v>14</v>
       </c>
-      <c r="D17" s="5" t="n">
-        <v>13</v>
-      </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>92.9%</t>
+          <t>93.3%</t>
         </is>
       </c>
     </row>
@@ -5742,7 +5931,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>Case :   has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
@@ -5809,14 +5998,14 @@
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H39" s="5" t="inlineStr">
+        <is>
           <t>Case : low wifi range issue  has been updated by Sabin Giri</t>
         </is>
       </c>
-      <c r="H39" s="5" t="inlineStr">
-        <is>
-          <t>Case : low wifi range issue  has been updated by Sabin Giri</t>
-        </is>
-      </c>
       <c r="I39" s="5" t="inlineStr">
         <is>
           <t>10 Oct 2026 12:06:57 PM</t>
@@ -5840,6 +6029,73 @@
       <c r="M39" s="5" t="inlineStr">
         <is>
           <t>2h 6m</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>TKT1364910</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>Ayush Duwal</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I40" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 12:30:17 PM</t>
+        </is>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 06:57:31 PM</t>
+        </is>
+      </c>
+      <c r="K40" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 12:30:17 PM</t>
+        </is>
+      </c>
+      <c r="L40" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t>17h 32m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_10_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_10_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW20"/>
+  <dimension ref="A1:AW25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -496,12 +496,12 @@
     <col width="40" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="25" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="22" customWidth="1" min="14" max="14"/>
+    <col width="25" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
-    <col width="27" customWidth="1" min="16" max="16"/>
+    <col width="32" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
     <col width="26" customWidth="1" min="18" max="18"/>
     <col width="37" customWidth="1" min="19" max="19"/>
@@ -511,7 +511,7 @@
     <col width="26" customWidth="1" min="23" max="23"/>
     <col width="29" customWidth="1" min="24" max="24"/>
     <col width="12" customWidth="1" min="25" max="25"/>
-    <col width="27" customWidth="1" min="26" max="26"/>
+    <col width="32" customWidth="1" min="26" max="26"/>
     <col width="19" customWidth="1" min="27" max="27"/>
     <col width="17" customWidth="1" min="28" max="28"/>
     <col width="11" customWidth="1" min="29" max="29"/>
@@ -4467,10 +4467,8 @@
           <t>Ayush Duwal</t>
         </is>
       </c>
-      <c r="O20" s="3" t="inlineStr">
-        <is>
-          <t>9869078453</t>
-        </is>
+      <c r="O20" s="3" t="n">
+        <v>9869078453</v>
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
@@ -4560,10 +4558,8 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN20" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN20" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO20" s="3" t="inlineStr">
         <is>
@@ -4574,30 +4570,1069 @@
       <c r="AQ20" s="3" t="inlineStr"/>
       <c r="AR20" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS20" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT20" s="3" t="inlineStr">
+        <is>
+          <t>17h 32m</t>
+        </is>
+      </c>
+      <c r="AU20" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV20" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi6  has been updated by Sabin Giri</t>
         </is>
       </c>
-      <c r="AS20" s="3" t="inlineStr">
+      <c r="AW20" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 12:35 PM</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr"/>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>Case : no light blinking   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>no light blinking</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>TKT1364848</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>Mayanka Kirana Store</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
+          <t>Mayanka Kirana Store</t>
+        </is>
+      </c>
+      <c r="O21" s="3" t="inlineStr">
+        <is>
+          <t>9844294603</t>
+        </is>
+      </c>
+      <c r="P21" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q21" s="3" t="inlineStr"/>
+      <c r="R21" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 12:35:23 PM</t>
+        </is>
+      </c>
+      <c r="S21" s="3" t="inlineStr"/>
+      <c r="T21" s="3" t="inlineStr"/>
+      <c r="U21" s="3" t="inlineStr">
+        <is>
+          <t>9844294603</t>
+        </is>
+      </c>
+      <c r="V21" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 05:45:00 PM</t>
+        </is>
+      </c>
+      <c r="W21" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 12:35:23 PM</t>
+        </is>
+      </c>
+      <c r="X21" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y21" s="3" t="inlineStr">
+        <is>
+          <t>27.666563</t>
+        </is>
+      </c>
+      <c r="Z21" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA21" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB21" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC21" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD21" s="3" t="inlineStr"/>
+      <c r="AE21" s="3" t="inlineStr">
+        <is>
+          <t>Near Preciois school,Bhaktapur Municipality, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF21" s="3" t="inlineStr">
+        <is>
+          <t>9844294603@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG21" s="3" t="inlineStr">
+        <is>
+          <t>Router Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH21" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI21" s="3" t="inlineStr">
+        <is>
+          <t>04:50 hour</t>
+        </is>
+      </c>
+      <c r="AJ21" s="3" t="inlineStr"/>
+      <c r="AK21" s="3" t="inlineStr"/>
+      <c r="AL21" s="3" t="inlineStr">
+        <is>
+          <t>Manisha kunwar</t>
+        </is>
+      </c>
+      <c r="AM21" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN21" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO21" s="3" t="inlineStr">
+        <is>
+          <t>L4-1</t>
+        </is>
+      </c>
+      <c r="AP21" s="3" t="inlineStr">
+        <is>
+          <t>85.374291</t>
+        </is>
+      </c>
+      <c r="AQ21" s="3" t="inlineStr"/>
+      <c r="AR21" s="3" t="inlineStr">
+        <is>
+          <t>Case : no light blinking   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS21" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT20" s="3" t="inlineStr">
-        <is>
-          <t>17h 32m</t>
-        </is>
-      </c>
-      <c r="AU20" s="3" t="inlineStr">
+      <c r="AT21" s="3" t="inlineStr">
+        <is>
+          <t>18h 50m</t>
+        </is>
+      </c>
+      <c r="AU21" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV20" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi6  has been updated by Sabin Giri</t>
-        </is>
-      </c>
-      <c r="AW20" s="3" t="inlineStr">
+      <c r="AV21" s="3" t="inlineStr">
+        <is>
+          <t>Case : no light blinking   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW21" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 12:45 PM</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr"/>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6 upgrade</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>TKT1364245</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>Banking Stack Pvt. Ltd</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
+          <t>Banking Stack Pvt. Ltd</t>
+        </is>
+      </c>
+      <c r="O22" s="3" t="inlineStr">
+        <is>
+          <t>9801098007</t>
+        </is>
+      </c>
+      <c r="P22" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q22" s="3" t="inlineStr"/>
+      <c r="R22" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 12:45:25 PM</t>
+        </is>
+      </c>
+      <c r="S22" s="3" t="inlineStr"/>
+      <c r="T22" s="3" t="inlineStr"/>
+      <c r="U22" s="3" t="inlineStr">
+        <is>
+          <t>9801098007</t>
+        </is>
+      </c>
+      <c r="V22" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 10:12:34 AM</t>
+        </is>
+      </c>
+      <c r="W22" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 12:45:25 PM</t>
+        </is>
+      </c>
+      <c r="X22" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y22" s="3" t="inlineStr">
+        <is>
+          <t>27.740113</t>
+        </is>
+      </c>
+      <c r="Z22" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA22" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB22" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC22" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD22" s="3" t="inlineStr"/>
+      <c r="AE22" s="3" t="inlineStr">
+        <is>
+          <t>Near Trimurti Academy,Maharajgunj, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF22" s="3" t="inlineStr">
+        <is>
+          <t>buddha.thapa@mail.com</t>
+        </is>
+      </c>
+      <c r="AG22" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH22" s="3" t="inlineStr"/>
+      <c r="AI22" s="3" t="inlineStr"/>
+      <c r="AJ22" s="3" t="inlineStr"/>
+      <c r="AK22" s="3" t="inlineStr"/>
+      <c r="AL22" s="3" t="inlineStr">
+        <is>
+          <t>Merika Silwal</t>
+        </is>
+      </c>
+      <c r="AM22" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN22" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO22" s="3" t="inlineStr">
+        <is>
+          <t>L21-3</t>
+        </is>
+      </c>
+      <c r="AP22" s="3" t="inlineStr">
+        <is>
+          <t>85.346797</t>
+        </is>
+      </c>
+      <c r="AQ22" s="3" t="inlineStr"/>
+      <c r="AR22" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS22" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT22" s="3" t="inlineStr">
+        <is>
+          <t>1d 2h 32m</t>
+        </is>
+      </c>
+      <c r="AU22" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV22" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW22" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 12:35 PM</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr"/>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>wifi6</t>
+        </is>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>TKT1358952</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t>Sanjay Dangol</t>
+        </is>
+      </c>
+      <c r="L23" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="inlineStr">
+        <is>
+          <t>Sanjay Dangol</t>
+        </is>
+      </c>
+      <c r="O23" s="3" t="inlineStr">
+        <is>
+          <t>9840877910</t>
+        </is>
+      </c>
+      <c r="P23" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q23" s="3" t="inlineStr"/>
+      <c r="R23" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 12:34:52 PM</t>
+        </is>
+      </c>
+      <c r="S23" s="3" t="inlineStr"/>
+      <c r="T23" s="3" t="inlineStr"/>
+      <c r="U23" s="3" t="inlineStr">
+        <is>
+          <t>9840877910</t>
+        </is>
+      </c>
+      <c r="V23" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 09:20:16 AM</t>
+        </is>
+      </c>
+      <c r="W23" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 12:35:24 PM</t>
+        </is>
+      </c>
+      <c r="X23" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y23" s="3" t="inlineStr"/>
+      <c r="Z23" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA23" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB23" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC23" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD23" s="3" t="inlineStr"/>
+      <c r="AE23" s="3" t="inlineStr">
+        <is>
+          <t>Q856+RH2 Road Tarakeshwar 44600,Q856+RH2 Road Tarakeshwar 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF23" s="3" t="inlineStr">
+        <is>
+          <t>dangolsanjay292@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG23" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH23" s="3" t="inlineStr"/>
+      <c r="AI23" s="3" t="inlineStr">
+        <is>
+          <t>04:35 hour</t>
+        </is>
+      </c>
+      <c r="AJ23" s="3" t="inlineStr"/>
+      <c r="AK23" s="3" t="inlineStr"/>
+      <c r="AL23" s="3" t="inlineStr">
+        <is>
+          <t>Swastima Silwal</t>
+        </is>
+      </c>
+      <c r="AM23" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN23" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO23" s="3" t="inlineStr">
+        <is>
+          <t>2,1</t>
+        </is>
+      </c>
+      <c r="AP23" s="3" t="inlineStr"/>
+      <c r="AQ23" s="3" t="inlineStr"/>
+      <c r="AR23" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS23" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT23" s="3" t="inlineStr">
+        <is>
+          <t>5d 3h 15m</t>
+        </is>
+      </c>
+      <c r="AU23" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV23" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW23" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 12:34 PM</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr"/>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>wifi6</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>TKT1358952</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>Sanjay Dangol</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
+          <t>Sanjay Dangol</t>
+        </is>
+      </c>
+      <c r="O24" s="3" t="inlineStr">
+        <is>
+          <t>9840877910</t>
+        </is>
+      </c>
+      <c r="P24" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q24" s="3" t="inlineStr"/>
+      <c r="R24" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 12:34:52 PM</t>
+        </is>
+      </c>
+      <c r="S24" s="3" t="inlineStr"/>
+      <c r="T24" s="3" t="inlineStr"/>
+      <c r="U24" s="3" t="inlineStr">
+        <is>
+          <t>9840877910</t>
+        </is>
+      </c>
+      <c r="V24" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 09:20:16 AM</t>
+        </is>
+      </c>
+      <c r="W24" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 12:35:24 PM</t>
+        </is>
+      </c>
+      <c r="X24" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y24" s="3" t="inlineStr"/>
+      <c r="Z24" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA24" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB24" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC24" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD24" s="3" t="inlineStr"/>
+      <c r="AE24" s="3" t="inlineStr">
+        <is>
+          <t>Q856+RH2 Road Tarakeshwar 44600,Q856+RH2 Road Tarakeshwar 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF24" s="3" t="inlineStr">
+        <is>
+          <t>dangolsanjay292@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG24" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH24" s="3" t="inlineStr"/>
+      <c r="AI24" s="3" t="inlineStr">
+        <is>
+          <t>04:35 hour</t>
+        </is>
+      </c>
+      <c r="AJ24" s="3" t="inlineStr"/>
+      <c r="AK24" s="3" t="inlineStr"/>
+      <c r="AL24" s="3" t="inlineStr">
+        <is>
+          <t>Swastima Silwal</t>
+        </is>
+      </c>
+      <c r="AM24" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN24" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO24" s="3" t="inlineStr">
+        <is>
+          <t>2,1</t>
+        </is>
+      </c>
+      <c r="AP24" s="3" t="inlineStr"/>
+      <c r="AQ24" s="3" t="inlineStr"/>
+      <c r="AR24" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS24" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT24" s="3" t="inlineStr">
+        <is>
+          <t>5d 3h 15m</t>
+        </is>
+      </c>
+      <c r="AU24" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV24" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW24" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 12:34 PM</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr"/>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>TKT1362114</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>Punam shah</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
+          <t>Punam shah</t>
+        </is>
+      </c>
+      <c r="O25" s="3" t="inlineStr">
+        <is>
+          <t>9840860400</t>
+        </is>
+      </c>
+      <c r="P25" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q25" s="3" t="inlineStr"/>
+      <c r="R25" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 12:34:03 PM</t>
+        </is>
+      </c>
+      <c r="S25" s="3" t="inlineStr"/>
+      <c r="T25" s="3" t="inlineStr"/>
+      <c r="U25" s="3" t="inlineStr">
+        <is>
+          <t>9810388424</t>
+        </is>
+      </c>
+      <c r="V25" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 03:17:23 PM</t>
+        </is>
+      </c>
+      <c r="W25" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 12:34:03 PM</t>
+        </is>
+      </c>
+      <c r="X25" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y25" s="3" t="inlineStr">
+        <is>
+          <t>27.74363</t>
+        </is>
+      </c>
+      <c r="Z25" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA25" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB25" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC25" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD25" s="3" t="inlineStr"/>
+      <c r="AE25" s="3" t="inlineStr">
+        <is>
+          <t>Gongabu Baniyatar, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF25" s="3" t="inlineStr">
+        <is>
+          <t>punam02shah@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG25" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH25" s="3" t="inlineStr"/>
+      <c r="AI25" s="3" t="inlineStr">
+        <is>
+          <t>03:17 hour</t>
+        </is>
+      </c>
+      <c r="AJ25" s="3" t="inlineStr"/>
+      <c r="AK25" s="3" t="inlineStr"/>
+      <c r="AL25" s="3" t="inlineStr">
+        <is>
+          <t>Susmita Thapa</t>
+        </is>
+      </c>
+      <c r="AM25" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN25" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO25" s="3" t="inlineStr">
+        <is>
+          <t>L57-4</t>
+        </is>
+      </c>
+      <c r="AP25" s="3" t="inlineStr">
+        <is>
+          <t>85.3155</t>
+        </is>
+      </c>
+      <c r="AQ25" s="3" t="inlineStr"/>
+      <c r="AR25" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS25" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT25" s="3" t="inlineStr">
+        <is>
+          <t>2d 21h 16m</t>
+        </is>
+      </c>
+      <c r="AU25" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV25" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW25" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
@@ -4614,12 +5649,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M40"/>
+  <dimension ref="A1:M46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
     <col width="39" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="33" customWidth="1" min="3" max="3"/>
     <col width="32" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
@@ -4651,7 +5686,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3">
@@ -4661,7 +5696,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4">
@@ -4672,7 +5707,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>84.2%</t>
+          <t>83.3%</t>
         </is>
       </c>
     </row>
@@ -4684,7 +5719,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>1d 2h 13m</t>
+          <t>20h 59m</t>
         </is>
       </c>
     </row>
@@ -4696,7 +5731,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>2d 21h 26m</t>
+          <t>3d 17m</t>
         </is>
       </c>
     </row>
@@ -4737,161 +5772,156 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>93.3%</t>
+          <t>89.5%</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C11" s="5" t="n">
         <v>1</v>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>Slow Internet Connection</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="B12" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C12" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C12" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>Wi-Fi Range</t>
+          <t>Slow Internet Connection</t>
         </is>
       </c>
       <c r="B13" s="5" t="n">
         <v>1</v>
       </c>
       <c r="C13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Wi-Fi Range</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="C14" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
     </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="A15" s="6" t="inlineStr">
+    <row r="15"/>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>Total Tickets Breakdown by Category &amp; Sub Category</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>Sub Category</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>Total Scraped Tickets</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="inlineStr">
-        <is>
-          <t>Solved / Handled Count</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>Solution Rate %</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="D17" s="5" t="n">
-        <v>14</v>
-      </c>
-      <c r="E17" s="5" t="inlineStr">
-        <is>
-          <t>93.3%</t>
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>Sub Category</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>Total Scraped Tickets</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>Solved / Handled Count</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>Solution Rate %</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>NETTV-No internet connection in STB</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>89.5%</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>NETTV-Welcome Screen Issue</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="C19" s="5" t="n">
@@ -4909,12 +5939,12 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>Slow Internet Connection</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Video content is Buffering</t>
+          <t>NETTV-No internet connection in STB</t>
         </is>
       </c>
       <c r="C20" s="3" t="n">
@@ -4932,12 +5962,12 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>Wi-Fi Range</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>Low Wi-Fi Range on both band</t>
+          <t>NETTV-Welcome Screen Issue</t>
         </is>
       </c>
       <c r="C21" s="5" t="n">
@@ -4952,224 +5982,136 @@
         </is>
       </c>
     </row>
-    <row r="22"/>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
     <row r="23">
-      <c r="A23" s="6" t="inlineStr">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>Wi-Fi Range</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>Low Wi-Fi Range on both band</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="24"/>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t>Ticket Number</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t>Account Name</t>
-        </is>
-      </c>
-      <c r="C24" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D24" s="4" t="inlineStr">
-        <is>
-          <t>Sub Category</t>
-        </is>
-      </c>
-      <c r="E24" s="4" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="F24" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Type</t>
-        </is>
-      </c>
-      <c r="G24" s="4" t="inlineStr">
-        <is>
-          <t>Employee Remark / Solution Note</t>
-        </is>
-      </c>
-      <c r="H24" s="4" t="inlineStr">
-        <is>
-          <t>Action / Transfer Remark</t>
-        </is>
-      </c>
-      <c r="I24" s="4" t="inlineStr">
-        <is>
-          <t>Assigned Date</t>
-        </is>
-      </c>
-      <c r="J24" s="4" t="inlineStr">
-        <is>
-          <t>Created Date</t>
-        </is>
-      </c>
-      <c r="K24" s="4" t="inlineStr">
-        <is>
-          <t>Last Modified Date</t>
-        </is>
-      </c>
-      <c r="L24" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Assigned)</t>
-        </is>
-      </c>
-      <c r="M24" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Created)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>TKT1364446</t>
-        </is>
-      </c>
-      <c r="B25" s="5" t="inlineStr">
-        <is>
-          <t>Jeet Bahadur Basnet</t>
-        </is>
-      </c>
-      <c r="C25" s="5" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E25" s="5" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F25" s="5" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G25" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H25" s="5" t="inlineStr">
-        <is>
-          <t>Case : upgrade wifi 6  has been updated by Sabin Giri</t>
-        </is>
-      </c>
-      <c r="I25" s="5" t="inlineStr">
-        <is>
-          <t>10 Oct 2026 10:40:59 AM</t>
-        </is>
-      </c>
-      <c r="J25" s="5" t="inlineStr">
-        <is>
-          <t>09 Oct 2026 12:30:31 PM</t>
-        </is>
-      </c>
-      <c r="K25" s="5" t="inlineStr">
-        <is>
-          <t>10 Oct 2026 10:40:59 AM</t>
-        </is>
-      </c>
-      <c r="L25" s="5" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M25" s="5" t="inlineStr">
-        <is>
-          <t>22h 10m</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t>TKT1364411</t>
-        </is>
-      </c>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>Bijya Lama</t>
-        </is>
-      </c>
-      <c r="C26" s="3" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D26" s="3" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E26" s="3" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F26" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G26" s="3" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H26" s="3" t="inlineStr">
-        <is>
-          <t>Case : Wifi 6 upgrade   has been updated by Sabin Giri</t>
-        </is>
-      </c>
-      <c r="I26" s="3" t="inlineStr">
-        <is>
-          <t>10 Oct 2026 10:40:30 AM</t>
-        </is>
-      </c>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t>09 Oct 2026 12:06:35 PM</t>
-        </is>
-      </c>
-      <c r="K26" s="3" t="inlineStr">
-        <is>
-          <t>10 Oct 2026 10:40:30 AM</t>
-        </is>
-      </c>
-      <c r="L26" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M26" s="3" t="inlineStr">
-        <is>
-          <t>22h 33m</t>
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>Ticket Number</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>Account Name</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>Sub Category</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Type</t>
+        </is>
+      </c>
+      <c r="G26" s="4" t="inlineStr">
+        <is>
+          <t>Employee Remark / Solution Note</t>
+        </is>
+      </c>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>Action / Transfer Remark</t>
+        </is>
+      </c>
+      <c r="I26" s="4" t="inlineStr">
+        <is>
+          <t>Assigned Date</t>
+        </is>
+      </c>
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t>Created Date</t>
+        </is>
+      </c>
+      <c r="K26" s="4" t="inlineStr">
+        <is>
+          <t>Last Modified Date</t>
+        </is>
+      </c>
+      <c r="L26" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Assigned)</t>
+        </is>
+      </c>
+      <c r="M26" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>TKT1357376</t>
+          <t>TKT1364446</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>Goma Adhikari</t>
+          <t>Jeet Bahadur Basnet</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
@@ -5199,22 +6141,22 @@
       </c>
       <c r="H27" s="5" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 upgrade   has been updated by Sanjeev Giri</t>
+          <t>Case : upgrade wifi 6  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I27" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 10:49:43 AM</t>
+          <t>10 Oct 2026 10:40:59 AM</t>
         </is>
       </c>
       <c r="J27" s="5" t="inlineStr">
         <is>
-          <t>04 Oct 2026 08:51:00 AM</t>
+          <t>09 Oct 2026 12:30:31 PM</t>
         </is>
       </c>
       <c r="K27" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 10:49:43 AM</t>
+          <t>10 Oct 2026 10:40:59 AM</t>
         </is>
       </c>
       <c r="L27" s="5" t="inlineStr">
@@ -5224,19 +6166,19 @@
       </c>
       <c r="M27" s="5" t="inlineStr">
         <is>
-          <t>6d 1h 58m</t>
+          <t>22h 10m</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>TKT1358035</t>
+          <t>TKT1364411</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Saurav Lamsal</t>
+          <t>Bijya Lama</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
@@ -5251,12 +6193,12 @@
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
@@ -5266,44 +6208,44 @@
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+          <t>Case : Wifi 6 upgrade   has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>04 Oct 2026 02:07:16 PM</t>
+          <t>10 Oct 2026 10:40:30 AM</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>04 Oct 2026 02:07:16 PM</t>
+          <t>09 Oct 2026 12:06:35 PM</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 11:04:09 AM</t>
+          <t>10 Oct 2026 10:40:30 AM</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t>5d 20h 56m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>5d 20h 56m</t>
+          <t>22h 33m</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>TKT1358035</t>
+          <t>TKT1357376</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>Saurav Lamsal</t>
+          <t>Goma Adhikari</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
@@ -5318,12 +6260,12 @@
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
@@ -5333,44 +6275,44 @@
       </c>
       <c r="H29" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+          <t>Case : Wifi 6 upgrade   has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I29" s="5" t="inlineStr">
         <is>
-          <t>04 Oct 2026 02:07:16 PM</t>
+          <t>10 Oct 2026 10:49:43 AM</t>
         </is>
       </c>
       <c r="J29" s="5" t="inlineStr">
         <is>
-          <t>04 Oct 2026 02:07:16 PM</t>
+          <t>04 Oct 2026 08:51:00 AM</t>
         </is>
       </c>
       <c r="K29" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 11:04:09 AM</t>
+          <t>10 Oct 2026 10:49:43 AM</t>
         </is>
       </c>
       <c r="L29" s="5" t="inlineStr">
         <is>
-          <t>5d 20h 56m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M29" s="5" t="inlineStr">
         <is>
-          <t>5d 20h 56m</t>
+          <t>6d 1h 58m</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>TKT1364756</t>
+          <t>TKT1358035</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>New Assist Traders</t>
+          <t>Saurav Lamsal</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
@@ -5385,12 +6327,12 @@
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
@@ -5400,44 +6342,44 @@
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Chandramani Tharu</t>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 11:15:36 AM</t>
+          <t>04 Oct 2026 02:07:16 PM</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>09 Oct 2026 04:33:35 PM</t>
+          <t>04 Oct 2026 02:07:16 PM</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 11:15:36 AM</t>
+          <t>10 Oct 2026 11:04:09 AM</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>5d 20h 56m</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>18h 42m</t>
+          <t>5d 20h 56m</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>TKT1358080</t>
+          <t>TKT1358035</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>Baburaja Maharjan</t>
+          <t>Saurav Lamsal</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
@@ -5452,12 +6394,12 @@
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
@@ -5467,44 +6409,44 @@
       </c>
       <c r="H31" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Chandramani Tharu</t>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I31" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 11:13:31 AM</t>
+          <t>04 Oct 2026 02:07:16 PM</t>
         </is>
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>04 Oct 2026 02:29:39 PM</t>
+          <t>04 Oct 2026 02:07:16 PM</t>
         </is>
       </c>
       <c r="K31" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 11:13:31 AM</t>
+          <t>10 Oct 2026 11:04:09 AM</t>
         </is>
       </c>
       <c r="L31" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>5d 20h 56m</t>
         </is>
       </c>
       <c r="M31" s="5" t="inlineStr">
         <is>
-          <t>5d 20h 43m</t>
+          <t>5d 20h 56m</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>TKT1359556</t>
+          <t>TKT1364756</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>Puspa KC</t>
+          <t>New Assist Traders</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
@@ -5534,22 +6476,22 @@
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>Case : router upgrade  has been updated by Sabin Giri</t>
+          <t>Case : wifi6  has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 11:23:36 AM</t>
+          <t>10 Oct 2026 11:15:36 AM</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>05 Oct 2026 03:34:34 PM</t>
+          <t>09 Oct 2026 04:33:35 PM</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 11:23:36 AM</t>
+          <t>10 Oct 2026 11:15:36 AM</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
@@ -5559,19 +6501,19 @@
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>4d 19h 49m</t>
+          <t>18h 42m</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>TKT1365031</t>
+          <t>TKT1358080</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>Prem Kumar Shrestha</t>
+          <t>Baburaja Maharjan</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
@@ -5601,22 +6543,22 @@
       </c>
       <c r="H33" s="5" t="inlineStr">
         <is>
-          <t>Case : WiFi 6   has been updated by Sanjeev Giri</t>
+          <t>Case : wifi6  has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I33" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 11:41:30 AM</t>
+          <t>10 Oct 2026 11:13:31 AM</t>
         </is>
       </c>
       <c r="J33" s="5" t="inlineStr">
         <is>
-          <t>09 Oct 2026 09:56:52 PM</t>
+          <t>04 Oct 2026 02:29:39 PM</t>
         </is>
       </c>
       <c r="K33" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 11:41:30 AM</t>
+          <t>10 Oct 2026 11:13:31 AM</t>
         </is>
       </c>
       <c r="L33" s="5" t="inlineStr">
@@ -5626,19 +6568,19 @@
       </c>
       <c r="M33" s="5" t="inlineStr">
         <is>
-          <t>13h 44m</t>
+          <t>5d 20h 43m</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>TKT1362058</t>
+          <t>TKT1359556</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>Gyan Chiraniya</t>
+          <t>Puspa KC</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
@@ -5653,12 +6595,12 @@
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
@@ -5668,44 +6610,44 @@
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>Case : For upgradation to wifi6   has been updated by Ajit Shrestha</t>
+          <t>Case : router upgrade  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>07 Oct 2026 02:43:23 PM</t>
+          <t>10 Oct 2026 11:23:36 AM</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>07 Oct 2026 02:43:23 PM</t>
+          <t>05 Oct 2026 03:34:34 PM</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 11:36:00 AM</t>
+          <t>10 Oct 2026 11:23:36 AM</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t>2d 20h 52m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>2d 20h 52m</t>
+          <t>4d 19h 49m</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>TKT1362058</t>
+          <t>TKT1365031</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>Gyan Chiraniya</t>
+          <t>Prem Kumar Shrestha</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
@@ -5720,12 +6662,12 @@
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
@@ -5735,44 +6677,44 @@
       </c>
       <c r="H35" s="5" t="inlineStr">
         <is>
-          <t>Case : For upgradation to wifi6   has been updated by Ajit Shrestha</t>
+          <t>Case : WiFi 6   has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I35" s="5" t="inlineStr">
         <is>
-          <t>07 Oct 2026 02:43:23 PM</t>
+          <t>10 Oct 2026 11:41:30 AM</t>
         </is>
       </c>
       <c r="J35" s="5" t="inlineStr">
         <is>
-          <t>07 Oct 2026 02:43:23 PM</t>
+          <t>09 Oct 2026 09:56:52 PM</t>
         </is>
       </c>
       <c r="K35" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 11:36:00 AM</t>
+          <t>10 Oct 2026 11:41:30 AM</t>
         </is>
       </c>
       <c r="L35" s="5" t="inlineStr">
         <is>
-          <t>2d 20h 52m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M35" s="5" t="inlineStr">
         <is>
-          <t>2d 20h 52m</t>
+          <t>13h 44m</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>TKT1362055</t>
+          <t>TKT1362058</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Ravi Shahi</t>
+          <t>Gyan Chiraniya</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
@@ -5787,12 +6729,12 @@
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
@@ -5802,64 +6744,64 @@
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>Case : For upgradation to wifi6   has been updated by Chandramani Tharu</t>
+          <t>Case : For upgradation to wifi6   has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 11:53:17 AM</t>
+          <t>07 Oct 2026 02:43:23 PM</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>07 Oct 2026 02:42:05 PM</t>
+          <t>07 Oct 2026 02:43:23 PM</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 11:53:17 AM</t>
+          <t>10 Oct 2026 11:36:00 AM</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>2d 20h 52m</t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>2d 21h 11m</t>
+          <t>2d 20h 52m</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>TKT1364261</t>
+          <t>TKT1362058</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>Niratna manandhar</t>
+          <t>Gyan Chiraniya</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>NETTV-Welcome Screen Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
@@ -5869,44 +6811,44 @@
       </c>
       <c r="H37" s="5" t="inlineStr">
         <is>
-          <t>Case : NETTV issue  has been updated by Ajit Shrestha</t>
+          <t>Case : For upgradation to wifi6   has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I37" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 12:00:52 PM</t>
+          <t>07 Oct 2026 02:43:23 PM</t>
         </is>
       </c>
       <c r="J37" s="5" t="inlineStr">
         <is>
-          <t>09 Oct 2026 10:23:09 AM</t>
+          <t>07 Oct 2026 02:43:23 PM</t>
         </is>
       </c>
       <c r="K37" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 12:00:52 PM</t>
+          <t>10 Oct 2026 11:36:00 AM</t>
         </is>
       </c>
       <c r="L37" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>2d 20h 52m</t>
         </is>
       </c>
       <c r="M37" s="5" t="inlineStr">
         <is>
-          <t>1d 1h 37m</t>
+          <t>2d 20h 52m</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>TKT1360378</t>
+          <t>TKT1362055</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Maheshwor Maharjan</t>
+          <t>Ravi Shahi</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
@@ -5936,22 +6878,22 @@
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>Case :   has been updated by Sanjeev Giri</t>
+          <t>Case : For upgradation to wifi6   has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 12:04:10 PM</t>
+          <t>10 Oct 2026 11:53:17 AM</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>06 Oct 2026 10:49:38 AM</t>
+          <t>07 Oct 2026 02:42:05 PM</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 12:04:10 PM</t>
+          <t>10 Oct 2026 11:53:17 AM</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
@@ -5961,29 +6903,29 @@
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>4d 1h 14m</t>
+          <t>2d 21h 11m</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>TKT1365280</t>
+          <t>TKT1364261</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>Atul Ali</t>
+          <t>Niratna manandhar</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>Wi-Fi Range</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>Low Wi-Fi Range on both band</t>
+          <t>NETTV-Welcome Screen Issue</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -6003,22 +6945,22 @@
       </c>
       <c r="H39" s="5" t="inlineStr">
         <is>
-          <t>Case : low wifi range issue  has been updated by Sabin Giri</t>
+          <t>Case : NETTV issue  has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I39" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 12:06:57 PM</t>
+          <t>10 Oct 2026 12:00:52 PM</t>
         </is>
       </c>
       <c r="J39" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 10:00:04 AM</t>
+          <t>09 Oct 2026 10:23:09 AM</t>
         </is>
       </c>
       <c r="K39" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 12:06:57 PM</t>
+          <t>10 Oct 2026 12:00:52 PM</t>
         </is>
       </c>
       <c r="L39" s="5" t="inlineStr">
@@ -6028,74 +6970,476 @@
       </c>
       <c r="M39" s="5" t="inlineStr">
         <is>
-          <t>2h 6m</t>
+          <t>1d 1h 37m</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
+          <t>TKT1360378</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>Maheshwor Maharjan</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>Case :   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I40" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 12:04:10 PM</t>
+        </is>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>06 Oct 2026 10:49:38 AM</t>
+        </is>
+      </c>
+      <c r="K40" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 12:04:10 PM</t>
+        </is>
+      </c>
+      <c r="L40" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t>4d 1h 14m</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>TKT1365280</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>Atul Ali</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>Wi-Fi Range</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>Low Wi-Fi Range on both band</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F41" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G41" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H41" s="5" t="inlineStr">
+        <is>
+          <t>Case : low wifi range issue  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I41" s="5" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 12:06:57 PM</t>
+        </is>
+      </c>
+      <c r="J41" s="5" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 10:00:04 AM</t>
+        </is>
+      </c>
+      <c r="K41" s="5" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 12:06:57 PM</t>
+        </is>
+      </c>
+      <c r="L41" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M41" s="5" t="inlineStr">
+        <is>
+          <t>2h 6m</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
           <t>TKT1364910</t>
         </is>
       </c>
-      <c r="B40" s="3" t="inlineStr">
+      <c r="B42" s="3" t="inlineStr">
         <is>
           <t>Ayush Duwal</t>
         </is>
       </c>
-      <c r="C40" s="3" t="inlineStr">
+      <c r="C42" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="D40" s="3" t="inlineStr">
+      <c r="D42" s="3" t="inlineStr">
         <is>
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="E40" s="3" t="inlineStr">
+      <c r="E42" s="3" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="F40" s="3" t="inlineStr">
+      <c r="F42" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="G40" s="3" t="inlineStr">
+      <c r="G42" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H42" s="3" t="inlineStr">
         <is>
           <t>Case : wifi6  has been updated by Sabin Giri</t>
         </is>
       </c>
-      <c r="H40" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi6  has been updated by Sabin Giri</t>
-        </is>
-      </c>
-      <c r="I40" s="3" t="inlineStr">
+      <c r="I42" s="3" t="inlineStr">
         <is>
           <t>10 Oct 2026 12:30:17 PM</t>
         </is>
       </c>
-      <c r="J40" s="3" t="inlineStr">
+      <c r="J42" s="3" t="inlineStr">
         <is>
           <t>09 Oct 2026 06:57:31 PM</t>
         </is>
       </c>
-      <c r="K40" s="3" t="inlineStr">
+      <c r="K42" s="3" t="inlineStr">
         <is>
           <t>10 Oct 2026 12:30:17 PM</t>
         </is>
       </c>
-      <c r="L40" s="3" t="inlineStr">
+      <c r="L42" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="M40" s="3" t="inlineStr">
+      <c r="M42" s="3" t="inlineStr">
         <is>
           <t>17h 32m</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>TKT1364848</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>Mayanka Kirana Store</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>Router Damage Issue</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F43" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G43" s="5" t="inlineStr">
+        <is>
+          <t>Case : no light blinking   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="H43" s="5" t="inlineStr">
+        <is>
+          <t>Case : no light blinking   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I43" s="5" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 12:35:23 PM</t>
+        </is>
+      </c>
+      <c r="J43" s="5" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 05:45:00 PM</t>
+        </is>
+      </c>
+      <c r="K43" s="5" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 12:35:23 PM</t>
+        </is>
+      </c>
+      <c r="L43" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M43" s="5" t="inlineStr">
+        <is>
+          <t>18h 50m</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>TKT1358952</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>Sanjay Dangol</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I44" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 12:34:52 PM</t>
+        </is>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 09:20:16 AM</t>
+        </is>
+      </c>
+      <c r="K44" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 12:35:24 PM</t>
+        </is>
+      </c>
+      <c r="L44" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M44" s="3" t="inlineStr">
+        <is>
+          <t>5d 3h 15m</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>TKT1358952</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>Sanjay Dangol</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F45" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G45" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="H45" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I45" s="5" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 12:34:52 PM</t>
+        </is>
+      </c>
+      <c r="J45" s="5" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 09:20:16 AM</t>
+        </is>
+      </c>
+      <c r="K45" s="5" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 12:35:24 PM</t>
+        </is>
+      </c>
+      <c r="L45" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M45" s="5" t="inlineStr">
+        <is>
+          <t>5d 3h 15m</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>TKT1362114</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>Punam shah</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="H46" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I46" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 12:34:03 PM</t>
+        </is>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 03:17:23 PM</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 12:34:03 PM</t>
+        </is>
+      </c>
+      <c r="L46" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t>2d 21h 16m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_10_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_10_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW25"/>
+  <dimension ref="A1:AW26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -4656,20 +4656,14 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="M21" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="M21" s="3" t="inlineStr"/>
       <c r="N21" s="3" t="inlineStr">
         <is>
           <t>Mayanka Kirana Store</t>
         </is>
       </c>
-      <c r="O21" s="3" t="inlineStr">
-        <is>
-          <t>9844294603</t>
-        </is>
+      <c r="O21" s="3" t="n">
+        <v>9844294603</v>
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
@@ -4745,10 +4739,8 @@
           <t>Router Damage Issue</t>
         </is>
       </c>
-      <c r="AH21" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH21" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI21" s="3" t="inlineStr">
         <is>
@@ -4767,25 +4759,21 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN21" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN21" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO21" s="3" t="inlineStr">
         <is>
           <t>L4-1</t>
         </is>
       </c>
-      <c r="AP21" s="3" t="inlineStr">
-        <is>
-          <t>85.374291</t>
-        </is>
+      <c r="AP21" s="3" t="n">
+        <v>85.374291</v>
       </c>
       <c r="AQ21" s="3" t="inlineStr"/>
       <c r="AR21" s="3" t="inlineStr">
         <is>
-          <t>Case : no light blinking   has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS21" s="3" t="inlineStr">
@@ -4881,10 +4869,8 @@
           <t>Banking Stack Pvt. Ltd</t>
         </is>
       </c>
-      <c r="O22" s="3" t="inlineStr">
-        <is>
-          <t>9801098007</t>
-        </is>
+      <c r="O22" s="3" t="n">
+        <v>9801098007</v>
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
@@ -4974,25 +4960,21 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN22" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN22" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO22" s="3" t="inlineStr">
         <is>
           <t>L21-3</t>
         </is>
       </c>
-      <c r="AP22" s="3" t="inlineStr">
-        <is>
-          <t>85.346797</t>
-        </is>
+      <c r="AP22" s="3" t="n">
+        <v>85.346797</v>
       </c>
       <c r="AQ22" s="3" t="inlineStr"/>
       <c r="AR22" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6 upgrade   has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS22" s="3" t="inlineStr">
@@ -5088,10 +5070,8 @@
           <t>Sanjay Dangol</t>
         </is>
       </c>
-      <c r="O23" s="3" t="inlineStr">
-        <is>
-          <t>9840877910</t>
-        </is>
+      <c r="O23" s="3" t="n">
+        <v>9840877910</v>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
@@ -5181,10 +5161,8 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN23" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN23" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO23" s="3" t="inlineStr">
         <is>
@@ -5195,7 +5173,7 @@
       <c r="AQ23" s="3" t="inlineStr"/>
       <c r="AR23" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS23" s="3" t="inlineStr">
@@ -5291,10 +5269,8 @@
           <t>Sanjay Dangol</t>
         </is>
       </c>
-      <c r="O24" s="3" t="inlineStr">
-        <is>
-          <t>9840877910</t>
-        </is>
+      <c r="O24" s="3" t="n">
+        <v>9840877910</v>
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
@@ -5384,10 +5360,8 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN24" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN24" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO24" s="3" t="inlineStr">
         <is>
@@ -5398,7 +5372,7 @@
       <c r="AQ24" s="3" t="inlineStr"/>
       <c r="AR24" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS24" s="3" t="inlineStr">
@@ -5494,10 +5468,8 @@
           <t>Punam shah</t>
         </is>
       </c>
-      <c r="O25" s="3" t="inlineStr">
-        <is>
-          <t>9840860400</t>
-        </is>
+      <c r="O25" s="3" t="n">
+        <v>9840860400</v>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
@@ -5591,48 +5563,251 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN25" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN25" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO25" s="3" t="inlineStr">
         <is>
           <t>L57-4</t>
         </is>
       </c>
-      <c r="AP25" s="3" t="inlineStr">
-        <is>
-          <t>85.3155</t>
-        </is>
+      <c r="AP25" s="3" t="n">
+        <v>85.3155</v>
       </c>
       <c r="AQ25" s="3" t="inlineStr"/>
       <c r="AR25" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS25" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT25" s="3" t="inlineStr">
+        <is>
+          <t>2d 21h 16m</t>
+        </is>
+      </c>
+      <c r="AU25" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV25" s="3" t="inlineStr">
+        <is>
           <t>Case : Wi-Fi 6  has been updated by Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AS25" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="AT25" s="3" t="inlineStr">
-        <is>
-          <t>2d 21h 16m</t>
-        </is>
-      </c>
-      <c r="AU25" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="AV25" s="3" t="inlineStr">
-        <is>
-          <t>Case : Wi-Fi 6  has been updated by Sanjeev Giri</t>
-        </is>
-      </c>
       <c r="AW25" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 12:50 PM</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr"/>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 router upgrade   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6 router upgrade</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>TKT1364639</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>Anil Pradhan</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
+          <t>Anil Pradhan</t>
+        </is>
+      </c>
+      <c r="O26" s="3" t="inlineStr">
+        <is>
+          <t>9851100323</t>
+        </is>
+      </c>
+      <c r="P26" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q26" s="3" t="inlineStr"/>
+      <c r="R26" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 03:05:33 PM</t>
+        </is>
+      </c>
+      <c r="S26" s="3" t="inlineStr"/>
+      <c r="T26" s="3" t="inlineStr"/>
+      <c r="U26" s="3" t="inlineStr">
+        <is>
+          <t>9851100323</t>
+        </is>
+      </c>
+      <c r="V26" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 03:05:33 PM</t>
+        </is>
+      </c>
+      <c r="W26" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 12:50:22 PM</t>
+        </is>
+      </c>
+      <c r="X26" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y26" s="3" t="inlineStr">
+        <is>
+          <t>27.73338</t>
+        </is>
+      </c>
+      <c r="Z26" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA26" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB26" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC26" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD26" s="3" t="inlineStr"/>
+      <c r="AE26" s="3" t="inlineStr">
+        <is>
+          <t>Ranibari -03, Nearby Takshashila Academy Higher Sec. School, Kathmandu, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF26" s="3" t="inlineStr"/>
+      <c r="AG26" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH26" s="3" t="inlineStr"/>
+      <c r="AI26" s="3" t="inlineStr">
+        <is>
+          <t>07:45 hour</t>
+        </is>
+      </c>
+      <c r="AJ26" s="3" t="inlineStr"/>
+      <c r="AK26" s="3" t="inlineStr"/>
+      <c r="AL26" s="3" t="inlineStr">
+        <is>
+          <t>Anu Bogati</t>
+        </is>
+      </c>
+      <c r="AM26" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN26" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO26" s="3" t="inlineStr">
+        <is>
+          <t>L10-8</t>
+        </is>
+      </c>
+      <c r="AP26" s="3" t="inlineStr">
+        <is>
+          <t>85.31954</t>
+        </is>
+      </c>
+      <c r="AQ26" s="3" t="inlineStr"/>
+      <c r="AR26" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 router upgrade   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS26" s="3" t="inlineStr">
+        <is>
+          <t>21h 44m</t>
+        </is>
+      </c>
+      <c r="AT26" s="3" t="inlineStr">
+        <is>
+          <t>21h 44m</t>
+        </is>
+      </c>
+      <c r="AU26" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV26" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 router upgrade   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW26" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
@@ -5649,7 +5824,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M46"/>
+  <dimension ref="A1:M47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -5686,7 +5861,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3">
@@ -5696,7 +5871,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4">
@@ -5707,7 +5882,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>84.0%</t>
         </is>
       </c>
     </row>
@@ -5719,7 +5894,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>20h 59m</t>
+          <t>21h 1m</t>
         </is>
       </c>
     </row>
@@ -5731,7 +5906,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>3d 17m</t>
+          <t>2d 21h 52m</t>
         </is>
       </c>
     </row>
@@ -5772,14 +5947,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>89.5%</t>
+          <t>90.0%</t>
         </is>
       </c>
     </row>
@@ -5902,14 +6077,14 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>89.5%</t>
+          <t>90.0%</t>
         </is>
       </c>
     </row>
@@ -7208,7 +7383,7 @@
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>Case : no light blinking   has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H43" s="5" t="inlineStr">
@@ -7275,7 +7450,7 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H44" s="3" t="inlineStr">
@@ -7342,7 +7517,7 @@
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H45" s="5" t="inlineStr">
@@ -7409,14 +7584,14 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H46" s="3" t="inlineStr">
+        <is>
           <t>Case : Wi-Fi 6  has been updated by Sanjeev Giri</t>
         </is>
       </c>
-      <c r="H46" s="3" t="inlineStr">
-        <is>
-          <t>Case : Wi-Fi 6  has been updated by Sanjeev Giri</t>
-        </is>
-      </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
           <t>10 Oct 2026 12:34:03 PM</t>
@@ -7440,6 +7615,73 @@
       <c r="M46" s="3" t="inlineStr">
         <is>
           <t>2d 21h 16m</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>TKT1364639</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>Anil Pradhan</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F47" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G47" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 router upgrade   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="H47" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 router upgrade   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I47" s="5" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 03:05:33 PM</t>
+        </is>
+      </c>
+      <c r="J47" s="5" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 03:05:33 PM</t>
+        </is>
+      </c>
+      <c r="K47" s="5" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 12:50:22 PM</t>
+        </is>
+      </c>
+      <c r="L47" s="5" t="inlineStr">
+        <is>
+          <t>21h 44m</t>
+        </is>
+      </c>
+      <c r="M47" s="5" t="inlineStr">
+        <is>
+          <t>21h 44m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_10_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_10_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW26"/>
+  <dimension ref="A1:AW27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -5673,10 +5673,8 @@
           <t>Anil Pradhan</t>
         </is>
       </c>
-      <c r="O26" s="3" t="inlineStr">
-        <is>
-          <t>9851100323</t>
-        </is>
+      <c r="O26" s="3" t="n">
+        <v>9851100323</v>
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
@@ -5766,48 +5764,243 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN26" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN26" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO26" s="3" t="inlineStr">
         <is>
           <t>L10-8</t>
         </is>
       </c>
-      <c r="AP26" s="3" t="inlineStr">
-        <is>
-          <t>85.31954</t>
-        </is>
+      <c r="AP26" s="3" t="n">
+        <v>85.31954</v>
       </c>
       <c r="AQ26" s="3" t="inlineStr"/>
       <c r="AR26" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS26" s="3" t="inlineStr">
+        <is>
+          <t>21h 44m</t>
+        </is>
+      </c>
+      <c r="AT26" s="3" t="inlineStr">
+        <is>
+          <t>21h 44m</t>
+        </is>
+      </c>
+      <c r="AU26" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV26" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6 router upgrade   has been updated by Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AS26" s="3" t="inlineStr">
-        <is>
-          <t>21h 44m</t>
-        </is>
-      </c>
-      <c r="AT26" s="3" t="inlineStr">
-        <is>
-          <t>21h 44m</t>
-        </is>
-      </c>
-      <c r="AU26" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Closed)</t>
-        </is>
-      </c>
-      <c r="AV26" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6 router upgrade   has been updated by Ajit Shrestha</t>
-        </is>
-      </c>
       <c r="AW26" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 1:16 PM</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr"/>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>wifi6</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>TKT1364684</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t>Bhumi Raj Bhandari</t>
+        </is>
+      </c>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
+          <t>Bhumi Raj Bhandari</t>
+        </is>
+      </c>
+      <c r="O27" s="3" t="inlineStr">
+        <is>
+          <t>9865036914</t>
+        </is>
+      </c>
+      <c r="P27" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q27" s="3" t="inlineStr"/>
+      <c r="R27" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 03:42:56 PM</t>
+        </is>
+      </c>
+      <c r="S27" s="3" t="inlineStr"/>
+      <c r="T27" s="3" t="inlineStr"/>
+      <c r="U27" s="3" t="inlineStr">
+        <is>
+          <t>9865036914</t>
+        </is>
+      </c>
+      <c r="V27" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 03:42:56 PM</t>
+        </is>
+      </c>
+      <c r="W27" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 01:16:31 PM</t>
+        </is>
+      </c>
+      <c r="X27" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y27" s="3" t="inlineStr"/>
+      <c r="Z27" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA27" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB27" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC27" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD27" s="3" t="inlineStr"/>
+      <c r="AE27" s="3" t="inlineStr">
+        <is>
+          <t>Near Dhapasi Height Details from Google Maps Q82P+PC8, Dhapasi Marg, Tokha 44600, Bagmati, Central,</t>
+        </is>
+      </c>
+      <c r="AF27" s="3" t="inlineStr">
+        <is>
+          <t>krishibhumi@outlook.com</t>
+        </is>
+      </c>
+      <c r="AG27" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH27" s="3" t="inlineStr"/>
+      <c r="AI27" s="3" t="inlineStr"/>
+      <c r="AJ27" s="3" t="inlineStr"/>
+      <c r="AK27" s="3" t="inlineStr"/>
+      <c r="AL27" s="3" t="inlineStr">
+        <is>
+          <t>Ishlok Shahi</t>
+        </is>
+      </c>
+      <c r="AM27" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN27" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO27" s="3" t="inlineStr">
+        <is>
+          <t>L15-6</t>
+        </is>
+      </c>
+      <c r="AP27" s="3" t="inlineStr"/>
+      <c r="AQ27" s="3" t="inlineStr"/>
+      <c r="AR27" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS27" s="3" t="inlineStr">
+        <is>
+          <t>21h 33m</t>
+        </is>
+      </c>
+      <c r="AT27" s="3" t="inlineStr">
+        <is>
+          <t>21h 33m</t>
+        </is>
+      </c>
+      <c r="AU27" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV27" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW27" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
@@ -5833,7 +6026,7 @@
     <col width="32" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -5861,7 +6054,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3">
@@ -5882,7 +6075,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>84.0%</t>
+          <t>80.8%</t>
         </is>
       </c>
     </row>
@@ -5947,14 +6140,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C10" s="3" t="n">
         <v>18</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>90.0%</t>
+          <t>85.7%</t>
         </is>
       </c>
     </row>
@@ -6077,14 +6270,14 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D18" s="3" t="n">
         <v>18</v>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>90.0%</t>
+          <t>85.7%</t>
         </is>
       </c>
     </row>
@@ -7651,7 +7844,7 @@
       </c>
       <c r="G47" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6 router upgrade   has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H47" s="5" t="inlineStr">

--- a/audit_report_ALL_TEAM_10_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_10_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW27"/>
+  <dimension ref="A1:AW28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -5874,10 +5874,8 @@
           <t>Bhumi Raj Bhandari</t>
         </is>
       </c>
-      <c r="O27" s="3" t="inlineStr">
-        <is>
-          <t>9865036914</t>
-        </is>
+      <c r="O27" s="3" t="n">
+        <v>9865036914</v>
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
@@ -5963,10 +5961,8 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN27" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN27" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO27" s="3" t="inlineStr">
         <is>
@@ -5977,32 +5973,135 @@
       <c r="AQ27" s="3" t="inlineStr"/>
       <c r="AR27" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS27" s="3" t="inlineStr">
+        <is>
+          <t>21h 33m</t>
+        </is>
+      </c>
+      <c r="AT27" s="3" t="inlineStr">
+        <is>
+          <t>21h 33m</t>
+        </is>
+      </c>
+      <c r="AU27" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV27" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi6   has been updated by Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AS27" s="3" t="inlineStr">
-        <is>
-          <t>21h 33m</t>
-        </is>
-      </c>
-      <c r="AT27" s="3" t="inlineStr">
-        <is>
-          <t>21h 33m</t>
-        </is>
-      </c>
-      <c r="AU27" s="3" t="inlineStr">
-        <is>
-          <t>Other / In Progress (On Hold)</t>
-        </is>
-      </c>
-      <c r="AV27" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi6   has been updated by Sanjeev Giri</t>
-        </is>
-      </c>
       <c r="AW27" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 1:24 PM</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr"/>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>Case : remote issue   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr"/>
+      <c r="J28" s="3" t="inlineStr"/>
+      <c r="K28" s="3" t="inlineStr"/>
+      <c r="L28" s="3" t="inlineStr"/>
+      <c r="M28" s="3" t="inlineStr"/>
+      <c r="N28" s="3" t="inlineStr"/>
+      <c r="O28" s="3" t="inlineStr"/>
+      <c r="P28" s="3" t="inlineStr"/>
+      <c r="Q28" s="3" t="inlineStr"/>
+      <c r="R28" s="3" t="inlineStr"/>
+      <c r="S28" s="3" t="inlineStr"/>
+      <c r="T28" s="3" t="inlineStr"/>
+      <c r="U28" s="3" t="inlineStr"/>
+      <c r="V28" s="3" t="inlineStr"/>
+      <c r="W28" s="3" t="inlineStr"/>
+      <c r="X28" s="3" t="inlineStr"/>
+      <c r="Y28" s="3" t="inlineStr"/>
+      <c r="Z28" s="3" t="inlineStr"/>
+      <c r="AA28" s="3" t="inlineStr"/>
+      <c r="AB28" s="3" t="inlineStr"/>
+      <c r="AC28" s="3" t="inlineStr"/>
+      <c r="AD28" s="3" t="inlineStr"/>
+      <c r="AE28" s="3" t="inlineStr"/>
+      <c r="AF28" s="3" t="inlineStr"/>
+      <c r="AG28" s="3" t="inlineStr"/>
+      <c r="AH28" s="3" t="inlineStr"/>
+      <c r="AI28" s="3" t="inlineStr"/>
+      <c r="AJ28" s="3" t="inlineStr"/>
+      <c r="AK28" s="3" t="inlineStr"/>
+      <c r="AL28" s="3" t="inlineStr"/>
+      <c r="AM28" s="3" t="inlineStr"/>
+      <c r="AN28" s="3" t="inlineStr"/>
+      <c r="AO28" s="3" t="inlineStr"/>
+      <c r="AP28" s="3" t="inlineStr"/>
+      <c r="AQ28" s="3" t="inlineStr"/>
+      <c r="AR28" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS28" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT28" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU28" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV28" s="3" t="inlineStr">
+        <is>
+          <t>Case : remote issue   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW28" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
         </is>
       </c>
     </row>
@@ -6017,7 +6116,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M47"/>
+  <dimension ref="A1:M49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -6054,7 +6153,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3">
@@ -6075,7 +6174,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>80.8%</t>
+          <t>77.8%</t>
         </is>
       </c>
     </row>
@@ -6223,107 +6322,98 @@
         </is>
       </c>
     </row>
-    <row r="15"/>
-    <row r="16">
-      <c r="A16" s="6" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr"/>
+      <c r="B15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>nan%</t>
+        </is>
+      </c>
+    </row>
+    <row r="16"/>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
         <is>
           <t>Total Tickets Breakdown by Category &amp; Sub Category</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>Sub Category</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>Total Scraped Tickets</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="inlineStr">
-        <is>
-          <t>Solved / Handled Count</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>Solution Rate %</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="D18" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="E18" s="3" t="inlineStr">
-        <is>
-          <t>85.7%</t>
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>Sub Category</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>Total Scraped Tickets</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>Solved / Handled Count</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>Solution Rate %</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>85.7%</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>NETTV-No internet connection in STB</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="C20" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -6335,285 +6425,189 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>NETTV-Welcome Screen Issue</t>
+          <t>NETTV-No internet connection in STB</t>
         </is>
       </c>
       <c r="C21" s="5" t="n">
         <v>1</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>Slow Internet Connection</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Video content is Buffering</t>
+          <t>NETTV-Welcome Screen Issue</t>
         </is>
       </c>
       <c r="C22" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>Wi-Fi Range</t>
+          <t>Slow Internet Connection</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>Low Wi-Fi Range on both band</t>
+          <t>Video content is Buffering</t>
         </is>
       </c>
       <c r="C23" s="5" t="n">
         <v>1</v>
       </c>
       <c r="D23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>Wi-Fi Range</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>Low Wi-Fi Range on both band</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="E23" s="5" t="inlineStr">
+      <c r="D24" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
     </row>
-    <row r="24"/>
     <row r="25">
-      <c r="A25" s="6" t="inlineStr">
+      <c r="A25" s="5" t="inlineStr"/>
+      <c r="B25" s="5" t="inlineStr"/>
+      <c r="C25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>nan%</t>
+        </is>
+      </c>
+    </row>
+    <row r="26"/>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>Ticket Number</t>
-        </is>
-      </c>
-      <c r="B26" s="4" t="inlineStr">
-        <is>
-          <t>Account Name</t>
-        </is>
-      </c>
-      <c r="C26" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D26" s="4" t="inlineStr">
-        <is>
-          <t>Sub Category</t>
-        </is>
-      </c>
-      <c r="E26" s="4" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="F26" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Type</t>
-        </is>
-      </c>
-      <c r="G26" s="4" t="inlineStr">
-        <is>
-          <t>Employee Remark / Solution Note</t>
-        </is>
-      </c>
-      <c r="H26" s="4" t="inlineStr">
-        <is>
-          <t>Action / Transfer Remark</t>
-        </is>
-      </c>
-      <c r="I26" s="4" t="inlineStr">
-        <is>
-          <t>Assigned Date</t>
-        </is>
-      </c>
-      <c r="J26" s="4" t="inlineStr">
-        <is>
-          <t>Created Date</t>
-        </is>
-      </c>
-      <c r="K26" s="4" t="inlineStr">
-        <is>
-          <t>Last Modified Date</t>
-        </is>
-      </c>
-      <c r="L26" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Assigned)</t>
-        </is>
-      </c>
-      <c r="M26" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Created)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>TKT1364446</t>
-        </is>
-      </c>
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>Jeet Bahadur Basnet</t>
-        </is>
-      </c>
-      <c r="C27" s="5" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D27" s="5" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E27" s="5" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F27" s="5" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G27" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H27" s="5" t="inlineStr">
-        <is>
-          <t>Case : upgrade wifi 6  has been updated by Sabin Giri</t>
-        </is>
-      </c>
-      <c r="I27" s="5" t="inlineStr">
-        <is>
-          <t>10 Oct 2026 10:40:59 AM</t>
-        </is>
-      </c>
-      <c r="J27" s="5" t="inlineStr">
-        <is>
-          <t>09 Oct 2026 12:30:31 PM</t>
-        </is>
-      </c>
-      <c r="K27" s="5" t="inlineStr">
-        <is>
-          <t>10 Oct 2026 10:40:59 AM</t>
-        </is>
-      </c>
-      <c r="L27" s="5" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M27" s="5" t="inlineStr">
-        <is>
-          <t>22h 10m</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>TKT1364411</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>Bijya Lama</t>
-        </is>
-      </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E28" s="3" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F28" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G28" s="3" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H28" s="3" t="inlineStr">
-        <is>
-          <t>Case : Wifi 6 upgrade   has been updated by Sabin Giri</t>
-        </is>
-      </c>
-      <c r="I28" s="3" t="inlineStr">
-        <is>
-          <t>10 Oct 2026 10:40:30 AM</t>
-        </is>
-      </c>
-      <c r="J28" s="3" t="inlineStr">
-        <is>
-          <t>09 Oct 2026 12:06:35 PM</t>
-        </is>
-      </c>
-      <c r="K28" s="3" t="inlineStr">
-        <is>
-          <t>10 Oct 2026 10:40:30 AM</t>
-        </is>
-      </c>
-      <c r="L28" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M28" s="3" t="inlineStr">
-        <is>
-          <t>22h 33m</t>
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>Ticket Number</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>Account Name</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>Sub Category</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Type</t>
+        </is>
+      </c>
+      <c r="G28" s="4" t="inlineStr">
+        <is>
+          <t>Employee Remark / Solution Note</t>
+        </is>
+      </c>
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t>Action / Transfer Remark</t>
+        </is>
+      </c>
+      <c r="I28" s="4" t="inlineStr">
+        <is>
+          <t>Assigned Date</t>
+        </is>
+      </c>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>Created Date</t>
+        </is>
+      </c>
+      <c r="K28" s="4" t="inlineStr">
+        <is>
+          <t>Last Modified Date</t>
+        </is>
+      </c>
+      <c r="L28" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Assigned)</t>
+        </is>
+      </c>
+      <c r="M28" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>TKT1357376</t>
+          <t>TKT1364446</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>Goma Adhikari</t>
+          <t>Jeet Bahadur Basnet</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
@@ -6643,22 +6637,22 @@
       </c>
       <c r="H29" s="5" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 upgrade   has been updated by Sanjeev Giri</t>
+          <t>Case : upgrade wifi 6  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I29" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 10:49:43 AM</t>
+          <t>10 Oct 2026 10:40:59 AM</t>
         </is>
       </c>
       <c r="J29" s="5" t="inlineStr">
         <is>
-          <t>04 Oct 2026 08:51:00 AM</t>
+          <t>09 Oct 2026 12:30:31 PM</t>
         </is>
       </c>
       <c r="K29" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 10:49:43 AM</t>
+          <t>10 Oct 2026 10:40:59 AM</t>
         </is>
       </c>
       <c r="L29" s="5" t="inlineStr">
@@ -6668,19 +6662,19 @@
       </c>
       <c r="M29" s="5" t="inlineStr">
         <is>
-          <t>6d 1h 58m</t>
+          <t>22h 10m</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>TKT1358035</t>
+          <t>TKT1364411</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Saurav Lamsal</t>
+          <t>Bijya Lama</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
@@ -6695,12 +6689,12 @@
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
@@ -6710,44 +6704,44 @@
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+          <t>Case : Wifi 6 upgrade   has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>04 Oct 2026 02:07:16 PM</t>
+          <t>10 Oct 2026 10:40:30 AM</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>04 Oct 2026 02:07:16 PM</t>
+          <t>09 Oct 2026 12:06:35 PM</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 11:04:09 AM</t>
+          <t>10 Oct 2026 10:40:30 AM</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>5d 20h 56m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>5d 20h 56m</t>
+          <t>22h 33m</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>TKT1358035</t>
+          <t>TKT1357376</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>Saurav Lamsal</t>
+          <t>Goma Adhikari</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
@@ -6762,12 +6756,12 @@
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
@@ -6777,44 +6771,44 @@
       </c>
       <c r="H31" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+          <t>Case : Wifi 6 upgrade   has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I31" s="5" t="inlineStr">
         <is>
-          <t>04 Oct 2026 02:07:16 PM</t>
+          <t>10 Oct 2026 10:49:43 AM</t>
         </is>
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>04 Oct 2026 02:07:16 PM</t>
+          <t>04 Oct 2026 08:51:00 AM</t>
         </is>
       </c>
       <c r="K31" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 11:04:09 AM</t>
+          <t>10 Oct 2026 10:49:43 AM</t>
         </is>
       </c>
       <c r="L31" s="5" t="inlineStr">
         <is>
-          <t>5d 20h 56m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M31" s="5" t="inlineStr">
         <is>
-          <t>5d 20h 56m</t>
+          <t>6d 1h 58m</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>TKT1364756</t>
+          <t>TKT1358035</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>New Assist Traders</t>
+          <t>Saurav Lamsal</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
@@ -6829,12 +6823,12 @@
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
@@ -6844,44 +6838,44 @@
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Chandramani Tharu</t>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 11:15:36 AM</t>
+          <t>04 Oct 2026 02:07:16 PM</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>09 Oct 2026 04:33:35 PM</t>
+          <t>04 Oct 2026 02:07:16 PM</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 11:15:36 AM</t>
+          <t>10 Oct 2026 11:04:09 AM</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>5d 20h 56m</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>18h 42m</t>
+          <t>5d 20h 56m</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>TKT1358080</t>
+          <t>TKT1358035</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>Baburaja Maharjan</t>
+          <t>Saurav Lamsal</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
@@ -6896,12 +6890,12 @@
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
@@ -6911,44 +6905,44 @@
       </c>
       <c r="H33" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Chandramani Tharu</t>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I33" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 11:13:31 AM</t>
+          <t>04 Oct 2026 02:07:16 PM</t>
         </is>
       </c>
       <c r="J33" s="5" t="inlineStr">
         <is>
-          <t>04 Oct 2026 02:29:39 PM</t>
+          <t>04 Oct 2026 02:07:16 PM</t>
         </is>
       </c>
       <c r="K33" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 11:13:31 AM</t>
+          <t>10 Oct 2026 11:04:09 AM</t>
         </is>
       </c>
       <c r="L33" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>5d 20h 56m</t>
         </is>
       </c>
       <c r="M33" s="5" t="inlineStr">
         <is>
-          <t>5d 20h 43m</t>
+          <t>5d 20h 56m</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>TKT1359556</t>
+          <t>TKT1364756</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>Puspa KC</t>
+          <t>New Assist Traders</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
@@ -6978,22 +6972,22 @@
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>Case : router upgrade  has been updated by Sabin Giri</t>
+          <t>Case : wifi6  has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 11:23:36 AM</t>
+          <t>10 Oct 2026 11:15:36 AM</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>05 Oct 2026 03:34:34 PM</t>
+          <t>09 Oct 2026 04:33:35 PM</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 11:23:36 AM</t>
+          <t>10 Oct 2026 11:15:36 AM</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
@@ -7003,19 +6997,19 @@
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>4d 19h 49m</t>
+          <t>18h 42m</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>TKT1365031</t>
+          <t>TKT1358080</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>Prem Kumar Shrestha</t>
+          <t>Baburaja Maharjan</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
@@ -7045,22 +7039,22 @@
       </c>
       <c r="H35" s="5" t="inlineStr">
         <is>
-          <t>Case : WiFi 6   has been updated by Sanjeev Giri</t>
+          <t>Case : wifi6  has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I35" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 11:41:30 AM</t>
+          <t>10 Oct 2026 11:13:31 AM</t>
         </is>
       </c>
       <c r="J35" s="5" t="inlineStr">
         <is>
-          <t>09 Oct 2026 09:56:52 PM</t>
+          <t>04 Oct 2026 02:29:39 PM</t>
         </is>
       </c>
       <c r="K35" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 11:41:30 AM</t>
+          <t>10 Oct 2026 11:13:31 AM</t>
         </is>
       </c>
       <c r="L35" s="5" t="inlineStr">
@@ -7070,19 +7064,19 @@
       </c>
       <c r="M35" s="5" t="inlineStr">
         <is>
-          <t>13h 44m</t>
+          <t>5d 20h 43m</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>TKT1362058</t>
+          <t>TKT1359556</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Gyan Chiraniya</t>
+          <t>Puspa KC</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
@@ -7097,12 +7091,12 @@
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
@@ -7112,44 +7106,44 @@
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>Case : For upgradation to wifi6   has been updated by Ajit Shrestha</t>
+          <t>Case : router upgrade  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>07 Oct 2026 02:43:23 PM</t>
+          <t>10 Oct 2026 11:23:36 AM</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>07 Oct 2026 02:43:23 PM</t>
+          <t>05 Oct 2026 03:34:34 PM</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 11:36:00 AM</t>
+          <t>10 Oct 2026 11:23:36 AM</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t>2d 20h 52m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>2d 20h 52m</t>
+          <t>4d 19h 49m</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>TKT1362058</t>
+          <t>TKT1365031</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>Gyan Chiraniya</t>
+          <t>Prem Kumar Shrestha</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
@@ -7164,12 +7158,12 @@
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
@@ -7179,44 +7173,44 @@
       </c>
       <c r="H37" s="5" t="inlineStr">
         <is>
-          <t>Case : For upgradation to wifi6   has been updated by Ajit Shrestha</t>
+          <t>Case : WiFi 6   has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I37" s="5" t="inlineStr">
         <is>
-          <t>07 Oct 2026 02:43:23 PM</t>
+          <t>10 Oct 2026 11:41:30 AM</t>
         </is>
       </c>
       <c r="J37" s="5" t="inlineStr">
         <is>
-          <t>07 Oct 2026 02:43:23 PM</t>
+          <t>09 Oct 2026 09:56:52 PM</t>
         </is>
       </c>
       <c r="K37" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 11:36:00 AM</t>
+          <t>10 Oct 2026 11:41:30 AM</t>
         </is>
       </c>
       <c r="L37" s="5" t="inlineStr">
         <is>
-          <t>2d 20h 52m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M37" s="5" t="inlineStr">
         <is>
-          <t>2d 20h 52m</t>
+          <t>13h 44m</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>TKT1362055</t>
+          <t>TKT1362058</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Ravi Shahi</t>
+          <t>Gyan Chiraniya</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
@@ -7231,12 +7225,12 @@
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
@@ -7246,64 +7240,64 @@
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>Case : For upgradation to wifi6   has been updated by Chandramani Tharu</t>
+          <t>Case : For upgradation to wifi6   has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 11:53:17 AM</t>
+          <t>07 Oct 2026 02:43:23 PM</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>07 Oct 2026 02:42:05 PM</t>
+          <t>07 Oct 2026 02:43:23 PM</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 11:53:17 AM</t>
+          <t>10 Oct 2026 11:36:00 AM</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>2d 20h 52m</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>2d 21h 11m</t>
+          <t>2d 20h 52m</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>TKT1364261</t>
+          <t>TKT1362058</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>Niratna manandhar</t>
+          <t>Gyan Chiraniya</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>NETTV-Welcome Screen Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
@@ -7313,44 +7307,44 @@
       </c>
       <c r="H39" s="5" t="inlineStr">
         <is>
-          <t>Case : NETTV issue  has been updated by Ajit Shrestha</t>
+          <t>Case : For upgradation to wifi6   has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I39" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 12:00:52 PM</t>
+          <t>07 Oct 2026 02:43:23 PM</t>
         </is>
       </c>
       <c r="J39" s="5" t="inlineStr">
         <is>
-          <t>09 Oct 2026 10:23:09 AM</t>
+          <t>07 Oct 2026 02:43:23 PM</t>
         </is>
       </c>
       <c r="K39" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 12:00:52 PM</t>
+          <t>10 Oct 2026 11:36:00 AM</t>
         </is>
       </c>
       <c r="L39" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>2d 20h 52m</t>
         </is>
       </c>
       <c r="M39" s="5" t="inlineStr">
         <is>
-          <t>1d 1h 37m</t>
+          <t>2d 20h 52m</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>TKT1360378</t>
+          <t>TKT1362055</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Maheshwor Maharjan</t>
+          <t>Ravi Shahi</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
@@ -7380,22 +7374,22 @@
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>Case :   has been updated by Sanjeev Giri</t>
+          <t>Case : For upgradation to wifi6   has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 12:04:10 PM</t>
+          <t>10 Oct 2026 11:53:17 AM</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>06 Oct 2026 10:49:38 AM</t>
+          <t>07 Oct 2026 02:42:05 PM</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 12:04:10 PM</t>
+          <t>10 Oct 2026 11:53:17 AM</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
@@ -7405,29 +7399,29 @@
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>4d 1h 14m</t>
+          <t>2d 21h 11m</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>TKT1365280</t>
+          <t>TKT1364261</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>Atul Ali</t>
+          <t>Niratna manandhar</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>Wi-Fi Range</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>Low Wi-Fi Range on both band</t>
+          <t>NETTV-Welcome Screen Issue</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -7447,22 +7441,22 @@
       </c>
       <c r="H41" s="5" t="inlineStr">
         <is>
-          <t>Case : low wifi range issue  has been updated by Sabin Giri</t>
+          <t>Case : NETTV issue  has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I41" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 12:06:57 PM</t>
+          <t>10 Oct 2026 12:00:52 PM</t>
         </is>
       </c>
       <c r="J41" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 10:00:04 AM</t>
+          <t>09 Oct 2026 10:23:09 AM</t>
         </is>
       </c>
       <c r="K41" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 12:06:57 PM</t>
+          <t>10 Oct 2026 12:00:52 PM</t>
         </is>
       </c>
       <c r="L41" s="5" t="inlineStr">
@@ -7472,19 +7466,19 @@
       </c>
       <c r="M41" s="5" t="inlineStr">
         <is>
-          <t>2h 6m</t>
+          <t>1d 1h 37m</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>TKT1364910</t>
+          <t>TKT1360378</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>Ayush Duwal</t>
+          <t>Maheshwor Maharjan</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
@@ -7514,22 +7508,22 @@
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Sabin Giri</t>
+          <t>Case :   has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 12:30:17 PM</t>
+          <t>10 Oct 2026 12:04:10 PM</t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>09 Oct 2026 06:57:31 PM</t>
+          <t>06 Oct 2026 10:49:38 AM</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 12:30:17 PM</t>
+          <t>10 Oct 2026 12:04:10 PM</t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
@@ -7539,29 +7533,29 @@
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t>17h 32m</t>
+          <t>4d 1h 14m</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>TKT1364848</t>
+          <t>TKT1365280</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>Mayanka Kirana Store</t>
+          <t>Atul Ali</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>Wi-Fi Range</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>Low Wi-Fi Range on both band</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -7581,22 +7575,22 @@
       </c>
       <c r="H43" s="5" t="inlineStr">
         <is>
-          <t>Case : no light blinking   has been updated by Sabin Giri</t>
+          <t>Case : low wifi range issue  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I43" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 12:35:23 PM</t>
+          <t>10 Oct 2026 12:06:57 PM</t>
         </is>
       </c>
       <c r="J43" s="5" t="inlineStr">
         <is>
-          <t>09 Oct 2026 05:45:00 PM</t>
+          <t>10 Oct 2026 10:00:04 AM</t>
         </is>
       </c>
       <c r="K43" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 12:35:23 PM</t>
+          <t>10 Oct 2026 12:06:57 PM</t>
         </is>
       </c>
       <c r="L43" s="5" t="inlineStr">
@@ -7606,19 +7600,19 @@
       </c>
       <c r="M43" s="5" t="inlineStr">
         <is>
-          <t>18h 50m</t>
+          <t>2h 6m</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>TKT1358952</t>
+          <t>TKT1364910</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>Sanjay Dangol</t>
+          <t>Ayush Duwal</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
@@ -7648,22 +7642,22 @@
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Sanjeev Giri</t>
+          <t>Case : wifi6  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 12:34:52 PM</t>
+          <t>10 Oct 2026 12:30:17 PM</t>
         </is>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>05 Oct 2026 09:20:16 AM</t>
+          <t>09 Oct 2026 06:57:31 PM</t>
         </is>
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 12:35:24 PM</t>
+          <t>10 Oct 2026 12:30:17 PM</t>
         </is>
       </c>
       <c r="L44" s="3" t="inlineStr">
@@ -7673,29 +7667,29 @@
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t>5d 3h 15m</t>
+          <t>17h 32m</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>TKT1358952</t>
+          <t>TKT1364848</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>Sanjay Dangol</t>
+          <t>Mayanka Kirana Store</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -7715,22 +7709,22 @@
       </c>
       <c r="H45" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Sanjeev Giri</t>
+          <t>Case : no light blinking   has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I45" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 12:34:52 PM</t>
+          <t>10 Oct 2026 12:35:23 PM</t>
         </is>
       </c>
       <c r="J45" s="5" t="inlineStr">
         <is>
-          <t>05 Oct 2026 09:20:16 AM</t>
+          <t>09 Oct 2026 05:45:00 PM</t>
         </is>
       </c>
       <c r="K45" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 12:35:24 PM</t>
+          <t>10 Oct 2026 12:35:23 PM</t>
         </is>
       </c>
       <c r="L45" s="5" t="inlineStr">
@@ -7740,19 +7734,19 @@
       </c>
       <c r="M45" s="5" t="inlineStr">
         <is>
-          <t>5d 3h 15m</t>
+          <t>18h 50m</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>TKT1362114</t>
+          <t>TKT1358952</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>Punam shah</t>
+          <t>Sanjay Dangol</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
@@ -7782,22 +7776,22 @@
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t>Case : Wi-Fi 6  has been updated by Sanjeev Giri</t>
+          <t>Case : wifi6  has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 12:34:03 PM</t>
+          <t>10 Oct 2026 12:34:52 PM</t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>07 Oct 2026 03:17:23 PM</t>
+          <t>05 Oct 2026 09:20:16 AM</t>
         </is>
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 12:34:03 PM</t>
+          <t>10 Oct 2026 12:35:24 PM</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
@@ -7807,72 +7801,206 @@
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t>2d 21h 16m</t>
+          <t>5d 3h 15m</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
+          <t>TKT1358952</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>Sanjay Dangol</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F47" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G47" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H47" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I47" s="5" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 12:34:52 PM</t>
+        </is>
+      </c>
+      <c r="J47" s="5" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 09:20:16 AM</t>
+        </is>
+      </c>
+      <c r="K47" s="5" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 12:35:24 PM</t>
+        </is>
+      </c>
+      <c r="L47" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M47" s="5" t="inlineStr">
+        <is>
+          <t>5d 3h 15m</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>TKT1362114</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>Punam shah</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F48" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G48" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H48" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I48" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 12:34:03 PM</t>
+        </is>
+      </c>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 03:17:23 PM</t>
+        </is>
+      </c>
+      <c r="K48" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 12:34:03 PM</t>
+        </is>
+      </c>
+      <c r="L48" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M48" s="3" t="inlineStr">
+        <is>
+          <t>2d 21h 16m</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
           <t>TKT1364639</t>
         </is>
       </c>
-      <c r="B47" s="5" t="inlineStr">
+      <c r="B49" s="5" t="inlineStr">
         <is>
           <t>Anil Pradhan</t>
         </is>
       </c>
-      <c r="C47" s="5" t="inlineStr">
+      <c r="C49" s="5" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="D47" s="5" t="inlineStr">
+      <c r="D49" s="5" t="inlineStr">
         <is>
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="E47" s="5" t="inlineStr">
+      <c r="E49" s="5" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
       </c>
-      <c r="F47" s="5" t="inlineStr">
+      <c r="F49" s="5" t="inlineStr">
         <is>
           <t>Completed (Closed)</t>
         </is>
       </c>
-      <c r="G47" s="5" t="inlineStr">
+      <c r="G49" s="5" t="inlineStr">
         <is>
           <t>nan</t>
         </is>
       </c>
-      <c r="H47" s="5" t="inlineStr">
+      <c r="H49" s="5" t="inlineStr">
         <is>
           <t>Case : wifi 6 router upgrade   has been updated by Ajit Shrestha</t>
         </is>
       </c>
-      <c r="I47" s="5" t="inlineStr">
+      <c r="I49" s="5" t="inlineStr">
         <is>
           <t>09 Oct 2026 03:05:33 PM</t>
         </is>
       </c>
-      <c r="J47" s="5" t="inlineStr">
+      <c r="J49" s="5" t="inlineStr">
         <is>
           <t>09 Oct 2026 03:05:33 PM</t>
         </is>
       </c>
-      <c r="K47" s="5" t="inlineStr">
+      <c r="K49" s="5" t="inlineStr">
         <is>
           <t>10 Oct 2026 12:50:22 PM</t>
         </is>
       </c>
-      <c r="L47" s="5" t="inlineStr">
+      <c r="L49" s="5" t="inlineStr">
         <is>
           <t>21h 44m</t>
         </is>
       </c>
-      <c r="M47" s="5" t="inlineStr">
+      <c r="M49" s="5" t="inlineStr">
         <is>
           <t>21h 44m</t>
         </is>

--- a/audit_report_ALL_TEAM_10_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_10_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW28"/>
+  <dimension ref="A1:AW30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -6105,6 +6105,416 @@
         </is>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 1:46 PM</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr"/>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>TKT1359613</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t>lok bahadur malla</t>
+        </is>
+      </c>
+      <c r="L29" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N29" s="3" t="inlineStr">
+        <is>
+          <t>lok bahadur malla</t>
+        </is>
+      </c>
+      <c r="O29" s="3" t="inlineStr">
+        <is>
+          <t>9803269701</t>
+        </is>
+      </c>
+      <c r="P29" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q29" s="3" t="inlineStr"/>
+      <c r="R29" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 01:46:58 PM</t>
+        </is>
+      </c>
+      <c r="S29" s="3" t="inlineStr"/>
+      <c r="T29" s="3" t="inlineStr"/>
+      <c r="U29" s="3" t="inlineStr">
+        <is>
+          <t>KLK9803269701</t>
+        </is>
+      </c>
+      <c r="V29" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 04:13:23 PM</t>
+        </is>
+      </c>
+      <c r="W29" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 01:46:58 PM</t>
+        </is>
+      </c>
+      <c r="X29" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y29" s="3" t="inlineStr"/>
+      <c r="Z29" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA29" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB29" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC29" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD29" s="3" t="inlineStr"/>
+      <c r="AE29" s="3" t="inlineStr">
+        <is>
+          <t>Bhadrakali English Medium School - General education school Q85W+7VJ Unnamed Road Budhanilkantha 446</t>
+        </is>
+      </c>
+      <c r="AF29" s="3" t="inlineStr">
+        <is>
+          <t>grgashim20242@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="AG29" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH29" s="3" t="inlineStr"/>
+      <c r="AI29" s="3" t="inlineStr">
+        <is>
+          <t>23:33 hour</t>
+        </is>
+      </c>
+      <c r="AJ29" s="3" t="inlineStr"/>
+      <c r="AK29" s="3" t="inlineStr"/>
+      <c r="AL29" s="3" t="inlineStr">
+        <is>
+          <t>Susmita Thapa</t>
+        </is>
+      </c>
+      <c r="AM29" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN29" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO29" s="3" t="inlineStr">
+        <is>
+          <t>L36-3</t>
+        </is>
+      </c>
+      <c r="AP29" s="3" t="inlineStr"/>
+      <c r="AQ29" s="3" t="inlineStr"/>
+      <c r="AR29" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS29" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT29" s="3" t="inlineStr">
+        <is>
+          <t>4d 21h 33m</t>
+        </is>
+      </c>
+      <c r="AU29" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV29" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW29" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 1:50 PM</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr"/>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>Case : worst internet service   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="inlineStr">
+        <is>
+          <t>worst internet service</t>
+        </is>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>TKT1350654</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t>Roshan Shrestha</t>
+        </is>
+      </c>
+      <c r="L30" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t>Self Care</t>
+        </is>
+      </c>
+      <c r="N30" s="3" t="inlineStr">
+        <is>
+          <t>Roshan Shrestha</t>
+        </is>
+      </c>
+      <c r="O30" s="3" t="inlineStr">
+        <is>
+          <t>9700971170</t>
+        </is>
+      </c>
+      <c r="P30" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="Q30" s="3" t="inlineStr"/>
+      <c r="R30" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 01:50:05 PM</t>
+        </is>
+      </c>
+      <c r="S30" s="3" t="inlineStr"/>
+      <c r="T30" s="3" t="inlineStr"/>
+      <c r="U30" s="3" t="inlineStr">
+        <is>
+          <t>9823190890R</t>
+        </is>
+      </c>
+      <c r="V30" s="3" t="inlineStr">
+        <is>
+          <t>28 Sep 2026 07:40:24 PM</t>
+        </is>
+      </c>
+      <c r="W30" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 01:50:05 PM</t>
+        </is>
+      </c>
+      <c r="X30" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y30" s="3" t="inlineStr">
+        <is>
+          <t>27.66368,</t>
+        </is>
+      </c>
+      <c r="Z30" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="AA30" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB30" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC30" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD30" s="3" t="inlineStr">
+        <is>
+          <t>Box End</t>
+        </is>
+      </c>
+      <c r="AE30" s="3" t="inlineStr">
+        <is>
+          <t>ala Futsal &amp; Recreational Center Details from Google Maps Unnamed Road, M87P+5VQ, ?????????? 44700 +</t>
+        </is>
+      </c>
+      <c r="AF30" s="3" t="inlineStr">
+        <is>
+          <t>rs1460451@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG30" s="3" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="AH30" s="3" t="inlineStr"/>
+      <c r="AI30" s="3" t="inlineStr"/>
+      <c r="AJ30" s="3" t="inlineStr"/>
+      <c r="AK30" s="3" t="inlineStr"/>
+      <c r="AL30" s="3" t="inlineStr"/>
+      <c r="AM30" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN30" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO30" s="3" t="inlineStr">
+        <is>
+          <t>1,15</t>
+        </is>
+      </c>
+      <c r="AP30" s="3" t="inlineStr">
+        <is>
+          <t>85.33794</t>
+        </is>
+      </c>
+      <c r="AQ30" s="3" t="inlineStr"/>
+      <c r="AR30" s="3" t="inlineStr">
+        <is>
+          <t>Case : worst internet service   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS30" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT30" s="3" t="inlineStr">
+        <is>
+          <t>11d 18h 9m</t>
+        </is>
+      </c>
+      <c r="AU30" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV30" s="3" t="inlineStr">
+        <is>
+          <t>Case : worst internet service   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW30" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6116,7 +6526,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M49"/>
+  <dimension ref="A1:M50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -6125,7 +6535,7 @@
     <col width="32" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -6153,7 +6563,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3">
@@ -6163,7 +6573,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4">
@@ -6174,7 +6584,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>77.8%</t>
+          <t>75.9%</t>
         </is>
       </c>
     </row>
@@ -6186,7 +6596,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>21h 1m</t>
+          <t>20h 3m</t>
         </is>
       </c>
     </row>
@@ -6198,7 +6608,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>2d 21h 52m</t>
+          <t>3d 2m</t>
         </is>
       </c>
     </row>
@@ -6239,14 +6649,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>85.7%</t>
+          <t>86.4%</t>
         </is>
       </c>
     </row>
@@ -6293,7 +6703,7 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C13" s="5" t="n">
         <v>0</v>
@@ -6383,14 +6793,14 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>85.7%</t>
+          <t>86.4%</t>
         </is>
       </c>
     </row>
@@ -6475,7 +6885,7 @@
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D23" s="5" t="n">
         <v>0</v>
@@ -8006,6 +8416,73 @@
         </is>
       </c>
     </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>TKT1359613</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>lok bahadur malla</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F50" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G50" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="H50" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I50" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 01:46:58 PM</t>
+        </is>
+      </c>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 04:13:23 PM</t>
+        </is>
+      </c>
+      <c r="K50" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 01:46:58 PM</t>
+        </is>
+      </c>
+      <c r="L50" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M50" s="3" t="inlineStr">
+        <is>
+          <t>4d 21h 33m</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/audit_report_ALL_TEAM_10_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_10_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW30"/>
+  <dimension ref="A1:AW33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -6172,10 +6172,8 @@
           <t>lok bahadur malla</t>
         </is>
       </c>
-      <c r="O29" s="3" t="inlineStr">
-        <is>
-          <t>9803269701</t>
-        </is>
+      <c r="O29" s="3" t="n">
+        <v>9803269701</v>
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
@@ -6265,10 +6263,8 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN29" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN29" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO29" s="3" t="inlineStr">
         <is>
@@ -6279,7 +6275,7 @@
       <c r="AQ29" s="3" t="inlineStr"/>
       <c r="AR29" s="3" t="inlineStr">
         <is>
-          <t>Case : Wi-Fi 6  has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS29" s="3" t="inlineStr">
@@ -6375,10 +6371,8 @@
           <t>Roshan Shrestha</t>
         </is>
       </c>
-      <c r="O30" s="3" t="inlineStr">
-        <is>
-          <t>9700971170</t>
-        </is>
+      <c r="O30" s="3" t="n">
+        <v>9700971170</v>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
@@ -6468,50 +6462,355 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN30" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN30" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO30" s="3" t="inlineStr">
         <is>
           <t>1,15</t>
         </is>
       </c>
-      <c r="AP30" s="3" t="inlineStr">
-        <is>
-          <t>85.33794</t>
-        </is>
+      <c r="AP30" s="3" t="n">
+        <v>85.33794</v>
       </c>
       <c r="AQ30" s="3" t="inlineStr"/>
       <c r="AR30" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS30" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT30" s="3" t="inlineStr">
+        <is>
+          <t>11d 18h 9m</t>
+        </is>
+      </c>
+      <c r="AU30" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV30" s="3" t="inlineStr">
+        <is>
           <t>Case : worst internet service   has been updated by Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AS30" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="AT30" s="3" t="inlineStr">
-        <is>
-          <t>11d 18h 9m</t>
-        </is>
-      </c>
-      <c r="AU30" s="3" t="inlineStr">
-        <is>
-          <t>Other / In Progress (On Hold)</t>
-        </is>
-      </c>
-      <c r="AV30" s="3" t="inlineStr">
-        <is>
-          <t>Case : worst internet service   has been updated by Chandramani Tharu</t>
-        </is>
-      </c>
       <c r="AW30" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 1:52 PM</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr"/>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router upgrade   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I31" s="3" t="inlineStr"/>
+      <c r="J31" s="3" t="inlineStr"/>
+      <c r="K31" s="3" t="inlineStr"/>
+      <c r="L31" s="3" t="inlineStr"/>
+      <c r="M31" s="3" t="inlineStr"/>
+      <c r="N31" s="3" t="inlineStr"/>
+      <c r="O31" s="3" t="inlineStr"/>
+      <c r="P31" s="3" t="inlineStr"/>
+      <c r="Q31" s="3" t="inlineStr"/>
+      <c r="R31" s="3" t="inlineStr"/>
+      <c r="S31" s="3" t="inlineStr"/>
+      <c r="T31" s="3" t="inlineStr"/>
+      <c r="U31" s="3" t="inlineStr"/>
+      <c r="V31" s="3" t="inlineStr"/>
+      <c r="W31" s="3" t="inlineStr"/>
+      <c r="X31" s="3" t="inlineStr"/>
+      <c r="Y31" s="3" t="inlineStr"/>
+      <c r="Z31" s="3" t="inlineStr"/>
+      <c r="AA31" s="3" t="inlineStr"/>
+      <c r="AB31" s="3" t="inlineStr"/>
+      <c r="AC31" s="3" t="inlineStr"/>
+      <c r="AD31" s="3" t="inlineStr"/>
+      <c r="AE31" s="3" t="inlineStr"/>
+      <c r="AF31" s="3" t="inlineStr"/>
+      <c r="AG31" s="3" t="inlineStr"/>
+      <c r="AH31" s="3" t="inlineStr"/>
+      <c r="AI31" s="3" t="inlineStr"/>
+      <c r="AJ31" s="3" t="inlineStr"/>
+      <c r="AK31" s="3" t="inlineStr"/>
+      <c r="AL31" s="3" t="inlineStr"/>
+      <c r="AM31" s="3" t="inlineStr"/>
+      <c r="AN31" s="3" t="inlineStr"/>
+      <c r="AO31" s="3" t="inlineStr"/>
+      <c r="AP31" s="3" t="inlineStr"/>
+      <c r="AQ31" s="3" t="inlineStr"/>
+      <c r="AR31" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS31" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT31" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU31" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV31" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router upgrade   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW31" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 1:53 PM</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr"/>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="inlineStr"/>
+      <c r="J32" s="3" t="inlineStr"/>
+      <c r="K32" s="3" t="inlineStr"/>
+      <c r="L32" s="3" t="inlineStr"/>
+      <c r="M32" s="3" t="inlineStr"/>
+      <c r="N32" s="3" t="inlineStr"/>
+      <c r="O32" s="3" t="inlineStr"/>
+      <c r="P32" s="3" t="inlineStr"/>
+      <c r="Q32" s="3" t="inlineStr"/>
+      <c r="R32" s="3" t="inlineStr"/>
+      <c r="S32" s="3" t="inlineStr"/>
+      <c r="T32" s="3" t="inlineStr"/>
+      <c r="U32" s="3" t="inlineStr"/>
+      <c r="V32" s="3" t="inlineStr"/>
+      <c r="W32" s="3" t="inlineStr"/>
+      <c r="X32" s="3" t="inlineStr"/>
+      <c r="Y32" s="3" t="inlineStr"/>
+      <c r="Z32" s="3" t="inlineStr"/>
+      <c r="AA32" s="3" t="inlineStr"/>
+      <c r="AB32" s="3" t="inlineStr"/>
+      <c r="AC32" s="3" t="inlineStr"/>
+      <c r="AD32" s="3" t="inlineStr"/>
+      <c r="AE32" s="3" t="inlineStr"/>
+      <c r="AF32" s="3" t="inlineStr"/>
+      <c r="AG32" s="3" t="inlineStr"/>
+      <c r="AH32" s="3" t="inlineStr"/>
+      <c r="AI32" s="3" t="inlineStr"/>
+      <c r="AJ32" s="3" t="inlineStr"/>
+      <c r="AK32" s="3" t="inlineStr"/>
+      <c r="AL32" s="3" t="inlineStr"/>
+      <c r="AM32" s="3" t="inlineStr"/>
+      <c r="AN32" s="3" t="inlineStr"/>
+      <c r="AO32" s="3" t="inlineStr"/>
+      <c r="AP32" s="3" t="inlineStr"/>
+      <c r="AQ32" s="3" t="inlineStr"/>
+      <c r="AR32" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS32" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT32" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU32" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV32" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW32" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 1:53 PM</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr"/>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I33" s="3" t="inlineStr"/>
+      <c r="J33" s="3" t="inlineStr"/>
+      <c r="K33" s="3" t="inlineStr"/>
+      <c r="L33" s="3" t="inlineStr"/>
+      <c r="M33" s="3" t="inlineStr"/>
+      <c r="N33" s="3" t="inlineStr"/>
+      <c r="O33" s="3" t="inlineStr"/>
+      <c r="P33" s="3" t="inlineStr"/>
+      <c r="Q33" s="3" t="inlineStr"/>
+      <c r="R33" s="3" t="inlineStr"/>
+      <c r="S33" s="3" t="inlineStr"/>
+      <c r="T33" s="3" t="inlineStr"/>
+      <c r="U33" s="3" t="inlineStr"/>
+      <c r="V33" s="3" t="inlineStr"/>
+      <c r="W33" s="3" t="inlineStr"/>
+      <c r="X33" s="3" t="inlineStr"/>
+      <c r="Y33" s="3" t="inlineStr"/>
+      <c r="Z33" s="3" t="inlineStr"/>
+      <c r="AA33" s="3" t="inlineStr"/>
+      <c r="AB33" s="3" t="inlineStr"/>
+      <c r="AC33" s="3" t="inlineStr"/>
+      <c r="AD33" s="3" t="inlineStr"/>
+      <c r="AE33" s="3" t="inlineStr"/>
+      <c r="AF33" s="3" t="inlineStr"/>
+      <c r="AG33" s="3" t="inlineStr"/>
+      <c r="AH33" s="3" t="inlineStr"/>
+      <c r="AI33" s="3" t="inlineStr"/>
+      <c r="AJ33" s="3" t="inlineStr"/>
+      <c r="AK33" s="3" t="inlineStr"/>
+      <c r="AL33" s="3" t="inlineStr"/>
+      <c r="AM33" s="3" t="inlineStr"/>
+      <c r="AN33" s="3" t="inlineStr"/>
+      <c r="AO33" s="3" t="inlineStr"/>
+      <c r="AP33" s="3" t="inlineStr"/>
+      <c r="AQ33" s="3" t="inlineStr"/>
+      <c r="AR33" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS33" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT33" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU33" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV33" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW33" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
         </is>
       </c>
     </row>
@@ -6535,7 +6834,7 @@
     <col width="32" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -6563,7 +6862,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3">
@@ -6584,7 +6883,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>75.9%</t>
+          <t>68.8%</t>
         </is>
       </c>
     </row>
@@ -8449,7 +8748,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>Case : Wi-Fi 6  has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H50" s="3" t="inlineStr">

--- a/audit_report_ALL_TEAM_10_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_10_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW33"/>
+  <dimension ref="A1:AW35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -6814,6 +6814,428 @@
         </is>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 2:14 PM</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr"/>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t>wifi6</t>
+        </is>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>TKT1363352</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>Rajan Dawadi</t>
+        </is>
+      </c>
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
+          <t>Rajan Dawadi</t>
+        </is>
+      </c>
+      <c r="O34" s="3" t="inlineStr">
+        <is>
+          <t>9851026168</t>
+        </is>
+      </c>
+      <c r="P34" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q34" s="3" t="inlineStr"/>
+      <c r="R34" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 01:21:13 PM</t>
+        </is>
+      </c>
+      <c r="S34" s="3" t="inlineStr"/>
+      <c r="T34" s="3" t="inlineStr"/>
+      <c r="U34" s="3" t="inlineStr">
+        <is>
+          <t>9851026168</t>
+        </is>
+      </c>
+      <c r="V34" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 01:21:13 PM</t>
+        </is>
+      </c>
+      <c r="W34" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 02:14:45 PM</t>
+        </is>
+      </c>
+      <c r="X34" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y34" s="3" t="inlineStr">
+        <is>
+          <t>P7MP+QF3</t>
+        </is>
+      </c>
+      <c r="Z34" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA34" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB34" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC34" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD34" s="3" t="inlineStr"/>
+      <c r="AE34" s="3" t="inlineStr">
+        <is>
+          <t>near Your Choice Minimart , Nagarjun, Raniban Rd 1, ???????? 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF34" s="3" t="inlineStr">
+        <is>
+          <t>mail.dawadi@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG34" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH34" s="3" t="inlineStr"/>
+      <c r="AI34" s="3" t="inlineStr">
+        <is>
+          <t>20:53 hour</t>
+        </is>
+      </c>
+      <c r="AJ34" s="3" t="inlineStr"/>
+      <c r="AK34" s="3" t="inlineStr"/>
+      <c r="AL34" s="3" t="inlineStr">
+        <is>
+          <t>Swastima Silwal</t>
+        </is>
+      </c>
+      <c r="AM34" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN34" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO34" s="3" t="inlineStr">
+        <is>
+          <t>CDB614</t>
+        </is>
+      </c>
+      <c r="AP34" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ34" s="3" t="inlineStr"/>
+      <c r="AR34" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS34" s="3" t="inlineStr">
+        <is>
+          <t>2d 53m</t>
+        </is>
+      </c>
+      <c r="AT34" s="3" t="inlineStr">
+        <is>
+          <t>2d 53m</t>
+        </is>
+      </c>
+      <c r="AU34" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV34" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW34" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 2:06 PM</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="inlineStr"/>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I35" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>TKT1365302</t>
+        </is>
+      </c>
+      <c r="K35" s="3" t="inlineStr">
+        <is>
+          <t>Kritika Sah</t>
+        </is>
+      </c>
+      <c r="L35" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N35" s="3" t="inlineStr">
+        <is>
+          <t>Kritika Sah</t>
+        </is>
+      </c>
+      <c r="O35" s="3" t="inlineStr">
+        <is>
+          <t>9742917951</t>
+        </is>
+      </c>
+      <c r="P35" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q35" s="3" t="inlineStr"/>
+      <c r="R35" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 02:06:16 PM</t>
+        </is>
+      </c>
+      <c r="S35" s="3" t="inlineStr"/>
+      <c r="T35" s="3" t="inlineStr"/>
+      <c r="U35" s="3" t="inlineStr">
+        <is>
+          <t>9829489302</t>
+        </is>
+      </c>
+      <c r="V35" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 10:19:45 AM</t>
+        </is>
+      </c>
+      <c r="W35" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 02:06:16 PM</t>
+        </is>
+      </c>
+      <c r="X35" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y35" s="3" t="inlineStr">
+        <is>
+          <t>27.694486</t>
+        </is>
+      </c>
+      <c r="Z35" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA35" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB35" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC35" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD35" s="3" t="inlineStr"/>
+      <c r="AE35" s="3" t="inlineStr">
+        <is>
+          <t>Near to Pathshala Foundation,Kathmandu , Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF35" s="3" t="inlineStr">
+        <is>
+          <t>kritikasah2331@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG35" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH35" s="3" t="inlineStr"/>
+      <c r="AI35" s="3" t="inlineStr">
+        <is>
+          <t>03:47 hour</t>
+        </is>
+      </c>
+      <c r="AJ35" s="3" t="inlineStr"/>
+      <c r="AK35" s="3" t="inlineStr"/>
+      <c r="AL35" s="3" t="inlineStr">
+        <is>
+          <t>Bipana Neupane</t>
+        </is>
+      </c>
+      <c r="AM35" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN35" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO35" s="3" t="inlineStr">
+        <is>
+          <t>L51-6</t>
+        </is>
+      </c>
+      <c r="AP35" s="3" t="inlineStr">
+        <is>
+          <t>85.332862</t>
+        </is>
+      </c>
+      <c r="AQ35" s="3" t="inlineStr"/>
+      <c r="AR35" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS35" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT35" s="3" t="inlineStr">
+        <is>
+          <t>3h 46m</t>
+        </is>
+      </c>
+      <c r="AU35" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV35" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW35" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6825,7 +7247,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M50"/>
+  <dimension ref="A1:M52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -6834,7 +7256,7 @@
     <col width="32" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -6862,7 +7284,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3">
@@ -6872,7 +7294,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4">
@@ -6883,7 +7305,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>68.8%</t>
+          <t>70.6%</t>
         </is>
       </c>
     </row>
@@ -6895,7 +7317,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>20h 3m</t>
+          <t>20h 25m</t>
         </is>
       </c>
     </row>
@@ -6907,7 +7329,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>3d 2m</t>
+          <t>2d 20h 14m</t>
         </is>
       </c>
     </row>
@@ -6948,14 +7370,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>86.4%</t>
+          <t>87.5%</t>
         </is>
       </c>
     </row>
@@ -7092,14 +7514,14 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>86.4%</t>
+          <t>87.5%</t>
         </is>
       </c>
     </row>
@@ -8782,6 +9204,140 @@
         </is>
       </c>
     </row>
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>TKT1363352</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>Rajan Dawadi</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E51" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F51" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G51" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="H51" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I51" s="5" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 01:21:13 PM</t>
+        </is>
+      </c>
+      <c r="J51" s="5" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 01:21:13 PM</t>
+        </is>
+      </c>
+      <c r="K51" s="5" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 02:14:45 PM</t>
+        </is>
+      </c>
+      <c r="L51" s="5" t="inlineStr">
+        <is>
+          <t>2d 53m</t>
+        </is>
+      </c>
+      <c r="M51" s="5" t="inlineStr">
+        <is>
+          <t>2d 53m</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>TKT1365302</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>Kritika Sah</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F52" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G52" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="H52" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I52" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 02:06:16 PM</t>
+        </is>
+      </c>
+      <c r="J52" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 10:19:45 AM</t>
+        </is>
+      </c>
+      <c r="K52" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 02:06:16 PM</t>
+        </is>
+      </c>
+      <c r="L52" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M52" s="3" t="inlineStr">
+        <is>
+          <t>3h 46m</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/audit_report_ALL_TEAM_10_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_10_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW35"/>
+  <dimension ref="A1:AW36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -496,10 +496,10 @@
     <col width="40" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="25" customWidth="1" min="11" max="11"/>
+    <col width="40" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="25" customWidth="1" min="14" max="14"/>
+    <col width="40" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="32" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
@@ -6881,10 +6881,8 @@
           <t>Rajan Dawadi</t>
         </is>
       </c>
-      <c r="O34" s="3" t="inlineStr">
-        <is>
-          <t>9851026168</t>
-        </is>
+      <c r="O34" s="3" t="n">
+        <v>9851026168</v>
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
@@ -6978,25 +6976,21 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN34" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN34" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO34" s="3" t="inlineStr">
         <is>
           <t>CDB614</t>
         </is>
       </c>
-      <c r="AP34" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AP34" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="AQ34" s="3" t="inlineStr"/>
       <c r="AR34" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS34" s="3" t="inlineStr">
@@ -7092,10 +7086,8 @@
           <t>Kritika Sah</t>
         </is>
       </c>
-      <c r="O35" s="3" t="inlineStr">
-        <is>
-          <t>9742917951</t>
-        </is>
+      <c r="O35" s="3" t="n">
+        <v>9742917951</v>
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
@@ -7189,50 +7181,249 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN35" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN35" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO35" s="3" t="inlineStr">
         <is>
           <t>L51-6</t>
         </is>
       </c>
-      <c r="AP35" s="3" t="inlineStr">
-        <is>
-          <t>85.332862</t>
-        </is>
+      <c r="AP35" s="3" t="n">
+        <v>85.33286200000001</v>
       </c>
       <c r="AQ35" s="3" t="inlineStr"/>
       <c r="AR35" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS35" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT35" s="3" t="inlineStr">
+        <is>
+          <t>3h 46m</t>
+        </is>
+      </c>
+      <c r="AU35" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV35" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6  has been updated by Sabin Giri</t>
         </is>
       </c>
-      <c r="AS35" s="3" t="inlineStr">
+      <c r="AW35" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 2:40 PM</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr"/>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router faulty   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="inlineStr">
+        <is>
+          <t>Router faulty</t>
+        </is>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>TKT1365176</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>Aafnai Deal Online Shopping Center Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
+          <t>Aafnai Deal Online Shopping Center Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="O36" s="3" t="inlineStr">
+        <is>
+          <t>9851412379</t>
+        </is>
+      </c>
+      <c r="P36" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q36" s="3" t="inlineStr"/>
+      <c r="R36" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 02:40:00 PM</t>
+        </is>
+      </c>
+      <c r="S36" s="3" t="inlineStr"/>
+      <c r="T36" s="3" t="inlineStr"/>
+      <c r="U36" s="3" t="inlineStr">
+        <is>
+          <t>KLK9851412379</t>
+        </is>
+      </c>
+      <c r="V36" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 08:51:05 AM</t>
+        </is>
+      </c>
+      <c r="W36" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 02:40:00 PM</t>
+        </is>
+      </c>
+      <c r="X36" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y36" s="3" t="inlineStr"/>
+      <c r="Z36" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA36" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB36" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC36" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD36" s="3" t="inlineStr"/>
+      <c r="AE36" s="3" t="inlineStr">
+        <is>
+          <t>Gai bachha chowk Gai bachha chowk - Hindu temple P72Q+Q59 Kathmandu 44600, Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF36" s="3" t="inlineStr">
+        <is>
+          <t>9851412379@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG36" s="3" t="inlineStr">
+        <is>
+          <t>Router Adaptor damage Issue</t>
+        </is>
+      </c>
+      <c r="AH36" s="3" t="inlineStr"/>
+      <c r="AI36" s="3" t="inlineStr">
+        <is>
+          <t>04:40 hour</t>
+        </is>
+      </c>
+      <c r="AJ36" s="3" t="inlineStr"/>
+      <c r="AK36" s="3" t="inlineStr"/>
+      <c r="AL36" s="3" t="inlineStr">
+        <is>
+          <t>Bhawana Bista</t>
+        </is>
+      </c>
+      <c r="AM36" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN36" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO36" s="3" t="inlineStr">
+        <is>
+          <t>2,3</t>
+        </is>
+      </c>
+      <c r="AP36" s="3" t="inlineStr"/>
+      <c r="AQ36" s="3" t="inlineStr"/>
+      <c r="AR36" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router faulty   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS36" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT35" s="3" t="inlineStr">
-        <is>
-          <t>3h 46m</t>
-        </is>
-      </c>
-      <c r="AU35" s="3" t="inlineStr">
+      <c r="AT36" s="3" t="inlineStr">
+        <is>
+          <t>5h 48m</t>
+        </is>
+      </c>
+      <c r="AU36" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV35" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
-        </is>
-      </c>
-      <c r="AW35" s="3" t="inlineStr">
-        <is>
-          <t>WiFi 6 Upgrade</t>
+      <c r="AV36" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router faulty   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW36" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
         </is>
       </c>
     </row>
@@ -7247,11 +7438,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M52"/>
+  <dimension ref="A1:M54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
-    <col width="39" customWidth="1" min="2" max="2"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
     <col width="33" customWidth="1" min="3" max="3"/>
     <col width="32" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
@@ -7284,7 +7475,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3">
@@ -7294,7 +7485,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4">
@@ -7305,7 +7496,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>70.6%</t>
+          <t>71.4%</t>
         </is>
       </c>
     </row>
@@ -7317,7 +7508,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>20h 25m</t>
+          <t>19h 36m</t>
         </is>
       </c>
     </row>
@@ -7329,7 +7520,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>2d 20h 14m</t>
+          <t>2d 17h 44m</t>
         </is>
       </c>
     </row>
@@ -7388,10 +7579,10 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
@@ -7533,7 +7724,7 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>Router Adaptor damage Issue</t>
         </is>
       </c>
       <c r="C20" s="3" t="n">
@@ -7551,23 +7742,23 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>NETTV-No internet connection in STB</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="C21" s="5" t="n">
         <v>1</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -7579,233 +7770,189 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>NETTV-Welcome Screen Issue</t>
+          <t>NETTV-No internet connection in STB</t>
         </is>
       </c>
       <c r="C22" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>Slow Internet Connection</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>Video content is Buffering</t>
+          <t>NETTV-Welcome Screen Issue</t>
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>Wi-Fi Range</t>
+          <t>Slow Internet Connection</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Low Wi-Fi Range on both band</t>
+          <t>Video content is Buffering</t>
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="inlineStr"/>
-      <c r="B25" s="5" t="inlineStr"/>
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>Wi-Fi Range</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>Low Wi-Fi Range on both band</t>
+        </is>
+      </c>
       <c r="C25" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr"/>
+      <c r="B26" s="3" t="inlineStr"/>
+      <c r="C26" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D25" s="5" t="n">
+      <c r="D26" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E25" s="5" t="inlineStr">
+      <c r="E26" s="3" t="inlineStr">
         <is>
           <t>nan%</t>
         </is>
       </c>
     </row>
-    <row r="26"/>
-    <row r="27">
-      <c r="A27" s="6" t="inlineStr">
+    <row r="27"/>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="4" t="inlineStr">
-        <is>
-          <t>Ticket Number</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="inlineStr">
-        <is>
-          <t>Account Name</t>
-        </is>
-      </c>
-      <c r="C28" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D28" s="4" t="inlineStr">
-        <is>
-          <t>Sub Category</t>
-        </is>
-      </c>
-      <c r="E28" s="4" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="F28" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Type</t>
-        </is>
-      </c>
-      <c r="G28" s="4" t="inlineStr">
-        <is>
-          <t>Employee Remark / Solution Note</t>
-        </is>
-      </c>
-      <c r="H28" s="4" t="inlineStr">
-        <is>
-          <t>Action / Transfer Remark</t>
-        </is>
-      </c>
-      <c r="I28" s="4" t="inlineStr">
-        <is>
-          <t>Assigned Date</t>
-        </is>
-      </c>
-      <c r="J28" s="4" t="inlineStr">
-        <is>
-          <t>Created Date</t>
-        </is>
-      </c>
-      <c r="K28" s="4" t="inlineStr">
-        <is>
-          <t>Last Modified Date</t>
-        </is>
-      </c>
-      <c r="L28" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Assigned)</t>
-        </is>
-      </c>
-      <c r="M28" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="inlineStr">
-        <is>
-          <t>TKT1364446</t>
-        </is>
-      </c>
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>Jeet Bahadur Basnet</t>
-        </is>
-      </c>
-      <c r="C29" s="5" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D29" s="5" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E29" s="5" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F29" s="5" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G29" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H29" s="5" t="inlineStr">
-        <is>
-          <t>Case : upgrade wifi 6  has been updated by Sabin Giri</t>
-        </is>
-      </c>
-      <c r="I29" s="5" t="inlineStr">
-        <is>
-          <t>10 Oct 2026 10:40:59 AM</t>
-        </is>
-      </c>
-      <c r="J29" s="5" t="inlineStr">
-        <is>
-          <t>09 Oct 2026 12:30:31 PM</t>
-        </is>
-      </c>
-      <c r="K29" s="5" t="inlineStr">
-        <is>
-          <t>10 Oct 2026 10:40:59 AM</t>
-        </is>
-      </c>
-      <c r="L29" s="5" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M29" s="5" t="inlineStr">
-        <is>
-          <t>22h 10m</t>
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>Ticket Number</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>Account Name</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>Sub Category</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Type</t>
+        </is>
+      </c>
+      <c r="G29" s="4" t="inlineStr">
+        <is>
+          <t>Employee Remark / Solution Note</t>
+        </is>
+      </c>
+      <c r="H29" s="4" t="inlineStr">
+        <is>
+          <t>Action / Transfer Remark</t>
+        </is>
+      </c>
+      <c r="I29" s="4" t="inlineStr">
+        <is>
+          <t>Assigned Date</t>
+        </is>
+      </c>
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>Created Date</t>
+        </is>
+      </c>
+      <c r="K29" s="4" t="inlineStr">
+        <is>
+          <t>Last Modified Date</t>
+        </is>
+      </c>
+      <c r="L29" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Assigned)</t>
+        </is>
+      </c>
+      <c r="M29" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>TKT1364411</t>
+          <t>TKT1364446</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Bijya Lama</t>
+          <t>Jeet Bahadur Basnet</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
@@ -7835,22 +7982,22 @@
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 upgrade   has been updated by Sabin Giri</t>
+          <t>Case : upgrade wifi 6  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 10:40:30 AM</t>
+          <t>10 Oct 2026 10:40:59 AM</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>09 Oct 2026 12:06:35 PM</t>
+          <t>09 Oct 2026 12:30:31 PM</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 10:40:30 AM</t>
+          <t>10 Oct 2026 10:40:59 AM</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
@@ -7860,19 +8007,19 @@
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>22h 33m</t>
+          <t>22h 10m</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>TKT1357376</t>
+          <t>TKT1364411</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>Goma Adhikari</t>
+          <t>Bijya Lama</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
@@ -7902,22 +8049,22 @@
       </c>
       <c r="H31" s="5" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 upgrade   has been updated by Sanjeev Giri</t>
+          <t>Case : Wifi 6 upgrade   has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I31" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 10:49:43 AM</t>
+          <t>10 Oct 2026 10:40:30 AM</t>
         </is>
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>04 Oct 2026 08:51:00 AM</t>
+          <t>09 Oct 2026 12:06:35 PM</t>
         </is>
       </c>
       <c r="K31" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 10:49:43 AM</t>
+          <t>10 Oct 2026 10:40:30 AM</t>
         </is>
       </c>
       <c r="L31" s="5" t="inlineStr">
@@ -7927,19 +8074,19 @@
       </c>
       <c r="M31" s="5" t="inlineStr">
         <is>
-          <t>6d 1h 58m</t>
+          <t>22h 33m</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>TKT1358035</t>
+          <t>TKT1357376</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>Saurav Lamsal</t>
+          <t>Goma Adhikari</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
@@ -7954,12 +8101,12 @@
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
@@ -7969,32 +8116,32 @@
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+          <t>Case : Wifi 6 upgrade   has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>04 Oct 2026 02:07:16 PM</t>
+          <t>10 Oct 2026 10:49:43 AM</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>04 Oct 2026 02:07:16 PM</t>
+          <t>04 Oct 2026 08:51:00 AM</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 11:04:09 AM</t>
+          <t>10 Oct 2026 10:49:43 AM</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t>5d 20h 56m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>5d 20h 56m</t>
+          <t>6d 1h 58m</t>
         </is>
       </c>
     </row>
@@ -8068,12 +8215,12 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>TKT1364756</t>
+          <t>TKT1358035</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>New Assist Traders</t>
+          <t>Saurav Lamsal</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
@@ -8088,12 +8235,12 @@
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
@@ -8103,44 +8250,44 @@
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Chandramani Tharu</t>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 11:15:36 AM</t>
+          <t>04 Oct 2026 02:07:16 PM</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>09 Oct 2026 04:33:35 PM</t>
+          <t>04 Oct 2026 02:07:16 PM</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 11:15:36 AM</t>
+          <t>10 Oct 2026 11:04:09 AM</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>5d 20h 56m</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>18h 42m</t>
+          <t>5d 20h 56m</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>TKT1358080</t>
+          <t>TKT1364756</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>Baburaja Maharjan</t>
+          <t>New Assist Traders</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
@@ -8175,17 +8322,17 @@
       </c>
       <c r="I35" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 11:13:31 AM</t>
+          <t>10 Oct 2026 11:15:36 AM</t>
         </is>
       </c>
       <c r="J35" s="5" t="inlineStr">
         <is>
-          <t>04 Oct 2026 02:29:39 PM</t>
+          <t>09 Oct 2026 04:33:35 PM</t>
         </is>
       </c>
       <c r="K35" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 11:13:31 AM</t>
+          <t>10 Oct 2026 11:15:36 AM</t>
         </is>
       </c>
       <c r="L35" s="5" t="inlineStr">
@@ -8195,19 +8342,19 @@
       </c>
       <c r="M35" s="5" t="inlineStr">
         <is>
-          <t>5d 20h 43m</t>
+          <t>18h 42m</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>TKT1359556</t>
+          <t>TKT1358080</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Puspa KC</t>
+          <t>Baburaja Maharjan</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
@@ -8237,22 +8384,22 @@
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>Case : router upgrade  has been updated by Sabin Giri</t>
+          <t>Case : wifi6  has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 11:23:36 AM</t>
+          <t>10 Oct 2026 11:13:31 AM</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>05 Oct 2026 03:34:34 PM</t>
+          <t>04 Oct 2026 02:29:39 PM</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 11:23:36 AM</t>
+          <t>10 Oct 2026 11:13:31 AM</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
@@ -8262,19 +8409,19 @@
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>4d 19h 49m</t>
+          <t>5d 20h 43m</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>TKT1365031</t>
+          <t>TKT1359556</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>Prem Kumar Shrestha</t>
+          <t>Puspa KC</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
@@ -8304,22 +8451,22 @@
       </c>
       <c r="H37" s="5" t="inlineStr">
         <is>
-          <t>Case : WiFi 6   has been updated by Sanjeev Giri</t>
+          <t>Case : router upgrade  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I37" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 11:41:30 AM</t>
+          <t>10 Oct 2026 11:23:36 AM</t>
         </is>
       </c>
       <c r="J37" s="5" t="inlineStr">
         <is>
-          <t>09 Oct 2026 09:56:52 PM</t>
+          <t>05 Oct 2026 03:34:34 PM</t>
         </is>
       </c>
       <c r="K37" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 11:41:30 AM</t>
+          <t>10 Oct 2026 11:23:36 AM</t>
         </is>
       </c>
       <c r="L37" s="5" t="inlineStr">
@@ -8329,19 +8476,19 @@
       </c>
       <c r="M37" s="5" t="inlineStr">
         <is>
-          <t>13h 44m</t>
+          <t>4d 19h 49m</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>TKT1362058</t>
+          <t>TKT1365031</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Gyan Chiraniya</t>
+          <t>Prem Kumar Shrestha</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
@@ -8356,12 +8503,12 @@
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
@@ -8371,32 +8518,32 @@
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>Case : For upgradation to wifi6   has been updated by Ajit Shrestha</t>
+          <t>Case : WiFi 6   has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>07 Oct 2026 02:43:23 PM</t>
+          <t>10 Oct 2026 11:41:30 AM</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>07 Oct 2026 02:43:23 PM</t>
+          <t>09 Oct 2026 09:56:52 PM</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 11:36:00 AM</t>
+          <t>10 Oct 2026 11:41:30 AM</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t>2d 20h 52m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>2d 20h 52m</t>
+          <t>13h 44m</t>
         </is>
       </c>
     </row>
@@ -8470,12 +8617,12 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>TKT1362055</t>
+          <t>TKT1362058</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Ravi Shahi</t>
+          <t>Gyan Chiraniya</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
@@ -8490,12 +8637,12 @@
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
@@ -8505,54 +8652,54 @@
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>Case : For upgradation to wifi6   has been updated by Chandramani Tharu</t>
+          <t>Case : For upgradation to wifi6   has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 11:53:17 AM</t>
+          <t>07 Oct 2026 02:43:23 PM</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>07 Oct 2026 02:42:05 PM</t>
+          <t>07 Oct 2026 02:43:23 PM</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 11:53:17 AM</t>
+          <t>10 Oct 2026 11:36:00 AM</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>2d 20h 52m</t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>2d 21h 11m</t>
+          <t>2d 20h 52m</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>TKT1364261</t>
+          <t>TKT1362055</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>Niratna manandhar</t>
+          <t>Ravi Shahi</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>NETTV-Welcome Screen Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -8572,22 +8719,22 @@
       </c>
       <c r="H41" s="5" t="inlineStr">
         <is>
-          <t>Case : NETTV issue  has been updated by Ajit Shrestha</t>
+          <t>Case : For upgradation to wifi6   has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I41" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 12:00:52 PM</t>
+          <t>10 Oct 2026 11:53:17 AM</t>
         </is>
       </c>
       <c r="J41" s="5" t="inlineStr">
         <is>
-          <t>09 Oct 2026 10:23:09 AM</t>
+          <t>07 Oct 2026 02:42:05 PM</t>
         </is>
       </c>
       <c r="K41" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 12:00:52 PM</t>
+          <t>10 Oct 2026 11:53:17 AM</t>
         </is>
       </c>
       <c r="L41" s="5" t="inlineStr">
@@ -8597,29 +8744,29 @@
       </c>
       <c r="M41" s="5" t="inlineStr">
         <is>
-          <t>1d 1h 37m</t>
+          <t>2d 21h 11m</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>TKT1360378</t>
+          <t>TKT1364261</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>Maheshwor Maharjan</t>
+          <t>Niratna manandhar</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>NETTV-Welcome Screen Issue</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
@@ -8639,22 +8786,22 @@
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t>Case :   has been updated by Sanjeev Giri</t>
+          <t>Case : NETTV issue  has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 12:04:10 PM</t>
+          <t>10 Oct 2026 12:00:52 PM</t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>06 Oct 2026 10:49:38 AM</t>
+          <t>09 Oct 2026 10:23:09 AM</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 12:04:10 PM</t>
+          <t>10 Oct 2026 12:00:52 PM</t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
@@ -8664,29 +8811,29 @@
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t>4d 1h 14m</t>
+          <t>1d 1h 37m</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>TKT1365280</t>
+          <t>TKT1360378</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>Atul Ali</t>
+          <t>Maheshwor Maharjan</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>Wi-Fi Range</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>Low Wi-Fi Range on both band</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -8706,22 +8853,22 @@
       </c>
       <c r="H43" s="5" t="inlineStr">
         <is>
-          <t>Case : low wifi range issue  has been updated by Sabin Giri</t>
+          <t>Case :   has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I43" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 12:06:57 PM</t>
+          <t>10 Oct 2026 12:04:10 PM</t>
         </is>
       </c>
       <c r="J43" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 10:00:04 AM</t>
+          <t>06 Oct 2026 10:49:38 AM</t>
         </is>
       </c>
       <c r="K43" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 12:06:57 PM</t>
+          <t>10 Oct 2026 12:04:10 PM</t>
         </is>
       </c>
       <c r="L43" s="5" t="inlineStr">
@@ -8731,29 +8878,29 @@
       </c>
       <c r="M43" s="5" t="inlineStr">
         <is>
-          <t>2h 6m</t>
+          <t>4d 1h 14m</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>TKT1364910</t>
+          <t>TKT1365280</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>Ayush Duwal</t>
+          <t>Atul Ali</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Wi-Fi Range</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Low Wi-Fi Range on both band</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
@@ -8773,22 +8920,22 @@
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Sabin Giri</t>
+          <t>Case : low wifi range issue  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 12:30:17 PM</t>
+          <t>10 Oct 2026 12:06:57 PM</t>
         </is>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>09 Oct 2026 06:57:31 PM</t>
+          <t>10 Oct 2026 10:00:04 AM</t>
         </is>
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 12:30:17 PM</t>
+          <t>10 Oct 2026 12:06:57 PM</t>
         </is>
       </c>
       <c r="L44" s="3" t="inlineStr">
@@ -8798,29 +8945,29 @@
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t>17h 32m</t>
+          <t>2h 6m</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>TKT1364848</t>
+          <t>TKT1364910</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>Mayanka Kirana Store</t>
+          <t>Ayush Duwal</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -8840,22 +8987,22 @@
       </c>
       <c r="H45" s="5" t="inlineStr">
         <is>
-          <t>Case : no light blinking   has been updated by Sabin Giri</t>
+          <t>Case : wifi6  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I45" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 12:35:23 PM</t>
+          <t>10 Oct 2026 12:30:17 PM</t>
         </is>
       </c>
       <c r="J45" s="5" t="inlineStr">
         <is>
-          <t>09 Oct 2026 05:45:00 PM</t>
+          <t>09 Oct 2026 06:57:31 PM</t>
         </is>
       </c>
       <c r="K45" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 12:35:23 PM</t>
+          <t>10 Oct 2026 12:30:17 PM</t>
         </is>
       </c>
       <c r="L45" s="5" t="inlineStr">
@@ -8865,29 +9012,29 @@
       </c>
       <c r="M45" s="5" t="inlineStr">
         <is>
-          <t>18h 50m</t>
+          <t>17h 32m</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>TKT1358952</t>
+          <t>TKT1364848</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>Sanjay Dangol</t>
+          <t>Mayanka Kirana Store</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
@@ -8907,22 +9054,22 @@
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Sanjeev Giri</t>
+          <t>Case : no light blinking   has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 12:34:52 PM</t>
+          <t>10 Oct 2026 12:35:23 PM</t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>05 Oct 2026 09:20:16 AM</t>
+          <t>09 Oct 2026 05:45:00 PM</t>
         </is>
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 12:35:24 PM</t>
+          <t>10 Oct 2026 12:35:23 PM</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
@@ -8932,7 +9079,7 @@
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t>5d 3h 15m</t>
+          <t>18h 50m</t>
         </is>
       </c>
     </row>
@@ -9006,12 +9153,12 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>TKT1362114</t>
+          <t>TKT1358952</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>Punam shah</t>
+          <t>Sanjay Dangol</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
@@ -9041,22 +9188,22 @@
       </c>
       <c r="H48" s="3" t="inlineStr">
         <is>
-          <t>Case : Wi-Fi 6  has been updated by Sanjeev Giri</t>
+          <t>Case : wifi6  has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I48" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 12:34:03 PM</t>
+          <t>10 Oct 2026 12:34:52 PM</t>
         </is>
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>07 Oct 2026 03:17:23 PM</t>
+          <t>05 Oct 2026 09:20:16 AM</t>
         </is>
       </c>
       <c r="K48" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 12:34:03 PM</t>
+          <t>10 Oct 2026 12:35:24 PM</t>
         </is>
       </c>
       <c r="L48" s="3" t="inlineStr">
@@ -9066,19 +9213,19 @@
       </c>
       <c r="M48" s="3" t="inlineStr">
         <is>
-          <t>2d 21h 16m</t>
+          <t>5d 3h 15m</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>TKT1364639</t>
+          <t>TKT1362114</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>Anil Pradhan</t>
+          <t>Punam shah</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
@@ -9093,12 +9240,12 @@
       </c>
       <c r="E49" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F49" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G49" s="5" t="inlineStr">
@@ -9108,44 +9255,44 @@
       </c>
       <c r="H49" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6 router upgrade   has been updated by Ajit Shrestha</t>
+          <t>Case : Wi-Fi 6  has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I49" s="5" t="inlineStr">
         <is>
-          <t>09 Oct 2026 03:05:33 PM</t>
+          <t>10 Oct 2026 12:34:03 PM</t>
         </is>
       </c>
       <c r="J49" s="5" t="inlineStr">
         <is>
-          <t>09 Oct 2026 03:05:33 PM</t>
+          <t>07 Oct 2026 03:17:23 PM</t>
         </is>
       </c>
       <c r="K49" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 12:50:22 PM</t>
+          <t>10 Oct 2026 12:34:03 PM</t>
         </is>
       </c>
       <c r="L49" s="5" t="inlineStr">
         <is>
-          <t>21h 44m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M49" s="5" t="inlineStr">
         <is>
-          <t>21h 44m</t>
+          <t>2d 21h 16m</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>TKT1359613</t>
+          <t>TKT1364639</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>lok bahadur malla</t>
+          <t>Anil Pradhan</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
@@ -9160,12 +9307,12 @@
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G50" s="3" t="inlineStr">
@@ -9175,44 +9322,44 @@
       </c>
       <c r="H50" s="3" t="inlineStr">
         <is>
-          <t>Case : Wi-Fi 6  has been updated by Sanjeev Giri</t>
+          <t>Case : wifi 6 router upgrade   has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I50" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 01:46:58 PM</t>
+          <t>09 Oct 2026 03:05:33 PM</t>
         </is>
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
-          <t>05 Oct 2026 04:13:23 PM</t>
+          <t>09 Oct 2026 03:05:33 PM</t>
         </is>
       </c>
       <c r="K50" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 01:46:58 PM</t>
+          <t>10 Oct 2026 12:50:22 PM</t>
         </is>
       </c>
       <c r="L50" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>21h 44m</t>
         </is>
       </c>
       <c r="M50" s="3" t="inlineStr">
         <is>
-          <t>4d 21h 33m</t>
+          <t>21h 44m</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>TKT1363352</t>
+          <t>TKT1359613</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>Rajan Dawadi</t>
+          <t>lok bahadur malla</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
@@ -9227,114 +9374,248 @@
       </c>
       <c r="E51" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F51" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G51" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H51" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Ajit Shrestha</t>
+          <t>Case : Wi-Fi 6  has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I51" s="5" t="inlineStr">
         <is>
-          <t>08 Oct 2026 01:21:13 PM</t>
+          <t>10 Oct 2026 01:46:58 PM</t>
         </is>
       </c>
       <c r="J51" s="5" t="inlineStr">
         <is>
-          <t>08 Oct 2026 01:21:13 PM</t>
+          <t>05 Oct 2026 04:13:23 PM</t>
         </is>
       </c>
       <c r="K51" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 02:14:45 PM</t>
+          <t>10 Oct 2026 01:46:58 PM</t>
         </is>
       </c>
       <c r="L51" s="5" t="inlineStr">
         <is>
-          <t>2d 53m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M51" s="5" t="inlineStr">
         <is>
-          <t>2d 53m</t>
+          <t>4d 21h 33m</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
+          <t>TKT1363352</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>Rajan Dawadi</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F52" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G52" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H52" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I52" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 01:21:13 PM</t>
+        </is>
+      </c>
+      <c r="J52" s="3" t="inlineStr">
+        <is>
+          <t>08 Oct 2026 01:21:13 PM</t>
+        </is>
+      </c>
+      <c r="K52" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 02:14:45 PM</t>
+        </is>
+      </c>
+      <c r="L52" s="3" t="inlineStr">
+        <is>
+          <t>2d 53m</t>
+        </is>
+      </c>
+      <c r="M52" s="3" t="inlineStr">
+        <is>
+          <t>2d 53m</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
           <t>TKT1365302</t>
         </is>
       </c>
-      <c r="B52" s="3" t="inlineStr">
+      <c r="B53" s="5" t="inlineStr">
         <is>
           <t>Kritika Sah</t>
         </is>
       </c>
-      <c r="C52" s="3" t="inlineStr">
+      <c r="C53" s="5" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="D52" s="3" t="inlineStr">
+      <c r="D53" s="5" t="inlineStr">
         <is>
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="E52" s="3" t="inlineStr">
+      <c r="E53" s="5" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="F52" s="3" t="inlineStr">
+      <c r="F53" s="5" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="G52" s="3" t="inlineStr">
+      <c r="G53" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H53" s="5" t="inlineStr">
         <is>
           <t>Case : wifi 6  has been updated by Sabin Giri</t>
         </is>
       </c>
-      <c r="H52" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
-        </is>
-      </c>
-      <c r="I52" s="3" t="inlineStr">
+      <c r="I53" s="5" t="inlineStr">
         <is>
           <t>10 Oct 2026 02:06:16 PM</t>
         </is>
       </c>
-      <c r="J52" s="3" t="inlineStr">
+      <c r="J53" s="5" t="inlineStr">
         <is>
           <t>10 Oct 2026 10:19:45 AM</t>
         </is>
       </c>
-      <c r="K52" s="3" t="inlineStr">
+      <c r="K53" s="5" t="inlineStr">
         <is>
           <t>10 Oct 2026 02:06:16 PM</t>
         </is>
       </c>
-      <c r="L52" s="3" t="inlineStr">
+      <c r="L53" s="5" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="M52" s="3" t="inlineStr">
+      <c r="M53" s="5" t="inlineStr">
         <is>
           <t>3h 46m</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>TKT1365176</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>Aafnai Deal Online Shopping Center Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>Router Adaptor damage Issue</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F54" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G54" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router faulty   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="H54" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router faulty   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I54" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 02:40:00 PM</t>
+        </is>
+      </c>
+      <c r="J54" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 08:51:05 AM</t>
+        </is>
+      </c>
+      <c r="K54" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 02:40:00 PM</t>
+        </is>
+      </c>
+      <c r="L54" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M54" s="3" t="inlineStr">
+        <is>
+          <t>5h 48m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_10_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_10_Oct_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -7291,10 +7291,8 @@
           <t>Aafnai Deal Online Shopping Center Pvt Ltd</t>
         </is>
       </c>
-      <c r="O36" s="3" t="inlineStr">
-        <is>
-          <t>9851412379</t>
-        </is>
+      <c r="O36" s="3" t="n">
+        <v>9851412379</v>
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
@@ -7384,10 +7382,8 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN36" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN36" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO36" s="3" t="inlineStr">
         <is>
@@ -7398,7 +7394,7 @@
       <c r="AQ36" s="3" t="inlineStr"/>
       <c r="AR36" s="3" t="inlineStr">
         <is>
-          <t>Case : Router faulty   has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS36" s="3" t="inlineStr">
@@ -7447,7 +7443,7 @@
     <col width="32" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -9585,7 +9581,7 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>Case : Router faulty   has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H54" s="3" t="inlineStr">

--- a/audit_report_ALL_TEAM_10_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_10_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW36"/>
+  <dimension ref="A1:AW40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -517,19 +517,19 @@
     <col width="11" customWidth="1" min="29" max="29"/>
     <col width="10" customWidth="1" min="30" max="30"/>
     <col width="40" customWidth="1" min="31" max="31"/>
-    <col width="30" customWidth="1" min="32" max="32"/>
+    <col width="35" customWidth="1" min="32" max="32"/>
     <col width="38" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
     <col width="17" customWidth="1" min="37" max="37"/>
-    <col width="18" customWidth="1" min="38" max="38"/>
+    <col width="19" customWidth="1" min="38" max="38"/>
     <col width="20" customWidth="1" min="39" max="39"/>
     <col width="28" customWidth="1" min="40" max="40"/>
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -7423,6 +7423,826 @@
         </is>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 3:12 PM</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="inlineStr"/>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I37" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6</t>
+        </is>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>TKT1362110</t>
+        </is>
+      </c>
+      <c r="K37" s="3" t="inlineStr">
+        <is>
+          <t>Prem Bahadur Karki</t>
+        </is>
+      </c>
+      <c r="L37" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N37" s="3" t="inlineStr">
+        <is>
+          <t>Prem Bahadur Karki</t>
+        </is>
+      </c>
+      <c r="O37" s="3" t="inlineStr">
+        <is>
+          <t>9866494523</t>
+        </is>
+      </c>
+      <c r="P37" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q37" s="3" t="inlineStr"/>
+      <c r="R37" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 03:16:15 PM</t>
+        </is>
+      </c>
+      <c r="S37" s="3" t="inlineStr"/>
+      <c r="T37" s="3" t="inlineStr"/>
+      <c r="U37" s="3" t="inlineStr">
+        <is>
+          <t>9869365032R</t>
+        </is>
+      </c>
+      <c r="V37" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 03:16:15 PM</t>
+        </is>
+      </c>
+      <c r="W37" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 03:12:56 PM</t>
+        </is>
+      </c>
+      <c r="X37" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y37" s="3" t="inlineStr"/>
+      <c r="Z37" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA37" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB37" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC37" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD37" s="3" t="inlineStr"/>
+      <c r="AE37" s="3" t="inlineStr">
+        <is>
+          <t>Eresha cafe and restaurant - Family restaurant Kharibot Chowk Kharibot, , ,</t>
+        </is>
+      </c>
+      <c r="AF37" s="3" t="inlineStr">
+        <is>
+          <t>Premkarki440@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG37" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH37" s="3" t="inlineStr"/>
+      <c r="AI37" s="3" t="inlineStr">
+        <is>
+          <t>05:56 hour</t>
+        </is>
+      </c>
+      <c r="AJ37" s="3" t="inlineStr"/>
+      <c r="AK37" s="3" t="inlineStr"/>
+      <c r="AL37" s="3" t="inlineStr">
+        <is>
+          <t>Nirajan Dhamala</t>
+        </is>
+      </c>
+      <c r="AM37" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN37" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO37" s="3" t="inlineStr">
+        <is>
+          <t>CDB348</t>
+        </is>
+      </c>
+      <c r="AP37" s="3" t="inlineStr"/>
+      <c r="AQ37" s="3" t="inlineStr"/>
+      <c r="AR37" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS37" s="3" t="inlineStr">
+        <is>
+          <t>2d 23h 56m</t>
+        </is>
+      </c>
+      <c r="AT37" s="3" t="inlineStr">
+        <is>
+          <t>2d 23h 56m</t>
+        </is>
+      </c>
+      <c r="AU37" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV37" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW37" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 3:41 PM</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="inlineStr"/>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I38" s="3" t="inlineStr">
+        <is>
+          <t>iptv issue</t>
+        </is>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>TKT1364906</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t>Pasang sherpa</t>
+        </is>
+      </c>
+      <c r="L38" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N38" s="3" t="inlineStr">
+        <is>
+          <t>Pasang sherpa</t>
+        </is>
+      </c>
+      <c r="O38" s="3" t="inlineStr">
+        <is>
+          <t>9842868756</t>
+        </is>
+      </c>
+      <c r="P38" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q38" s="3" t="inlineStr"/>
+      <c r="R38" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 03:41:05 PM</t>
+        </is>
+      </c>
+      <c r="S38" s="3" t="inlineStr"/>
+      <c r="T38" s="3" t="inlineStr"/>
+      <c r="U38" s="3" t="inlineStr">
+        <is>
+          <t>CHB9842868756</t>
+        </is>
+      </c>
+      <c r="V38" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 06:55:03 PM</t>
+        </is>
+      </c>
+      <c r="W38" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 03:41:05 PM</t>
+        </is>
+      </c>
+      <c r="X38" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y38" s="3" t="inlineStr"/>
+      <c r="Z38" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA38" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB38" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC38" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD38" s="3" t="inlineStr"/>
+      <c r="AE38" s="3" t="inlineStr">
+        <is>
+          <t>near by Sherpa Chowk - Shopping mall Sherpa Chowk Kapan 11 Budhanilkantha 44600, Kathmandu, Nepal, N</t>
+        </is>
+      </c>
+      <c r="AF38" s="3" t="inlineStr">
+        <is>
+          <t>9842868756@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG38" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH38" s="3" t="inlineStr"/>
+      <c r="AI38" s="3" t="inlineStr">
+        <is>
+          <t>06:46 hour</t>
+        </is>
+      </c>
+      <c r="AJ38" s="3" t="inlineStr"/>
+      <c r="AK38" s="3" t="inlineStr"/>
+      <c r="AL38" s="3" t="inlineStr">
+        <is>
+          <t>Aakash Shah</t>
+        </is>
+      </c>
+      <c r="AM38" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN38" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO38" s="3" t="inlineStr">
+        <is>
+          <t>L28-6</t>
+        </is>
+      </c>
+      <c r="AP38" s="3" t="inlineStr"/>
+      <c r="AQ38" s="3" t="inlineStr"/>
+      <c r="AR38" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS38" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT38" s="3" t="inlineStr">
+        <is>
+          <t>20h 46m</t>
+        </is>
+      </c>
+      <c r="AU38" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV38" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW38" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 3:38 PM</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="inlineStr"/>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 Router   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I39" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6 Router</t>
+        </is>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>TKT1365415</t>
+        </is>
+      </c>
+      <c r="K39" s="3" t="inlineStr">
+        <is>
+          <t>Sarmila Sangasarar</t>
+        </is>
+      </c>
+      <c r="L39" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M39" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N39" s="3" t="inlineStr">
+        <is>
+          <t>Sarmila Sangasarar</t>
+        </is>
+      </c>
+      <c r="O39" s="3" t="inlineStr">
+        <is>
+          <t>9810289618</t>
+        </is>
+      </c>
+      <c r="P39" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q39" s="3" t="inlineStr"/>
+      <c r="R39" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 03:38:34 PM</t>
+        </is>
+      </c>
+      <c r="S39" s="3" t="inlineStr"/>
+      <c r="T39" s="3" t="inlineStr"/>
+      <c r="U39" s="3" t="inlineStr">
+        <is>
+          <t>CHB9810289618</t>
+        </is>
+      </c>
+      <c r="V39" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 11:51:02 AM</t>
+        </is>
+      </c>
+      <c r="W39" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 03:38:34 PM</t>
+        </is>
+      </c>
+      <c r="X39" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y39" s="3" t="inlineStr"/>
+      <c r="Z39" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA39" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB39" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC39" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD39" s="3" t="inlineStr"/>
+      <c r="AE39" s="3" t="inlineStr">
+        <is>
+          <t>baudha ram hiti, Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF39" s="3" t="inlineStr">
+        <is>
+          <t>sarmila74@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG39" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH39" s="3" t="inlineStr"/>
+      <c r="AI39" s="3" t="inlineStr">
+        <is>
+          <t>03:47 hour</t>
+        </is>
+      </c>
+      <c r="AJ39" s="3" t="inlineStr"/>
+      <c r="AK39" s="3" t="inlineStr"/>
+      <c r="AL39" s="3" t="inlineStr">
+        <is>
+          <t>Sabina Baskota</t>
+        </is>
+      </c>
+      <c r="AM39" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN39" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO39" s="3" t="inlineStr">
+        <is>
+          <t>3,11</t>
+        </is>
+      </c>
+      <c r="AP39" s="3" t="inlineStr"/>
+      <c r="AQ39" s="3" t="inlineStr"/>
+      <c r="AR39" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 Router   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS39" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT39" s="3" t="inlineStr">
+        <is>
+          <t>3h 47m</t>
+        </is>
+      </c>
+      <c r="AU39" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV39" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 Router   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW39" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 3:04 PM</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="inlineStr"/>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I40" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>TKT1365328</t>
+        </is>
+      </c>
+      <c r="K40" s="3" t="inlineStr">
+        <is>
+          <t>Bishal Shrestha</t>
+        </is>
+      </c>
+      <c r="L40" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N40" s="3" t="inlineStr">
+        <is>
+          <t>Bishal Shrestha</t>
+        </is>
+      </c>
+      <c r="O40" s="3" t="inlineStr">
+        <is>
+          <t>9765565085</t>
+        </is>
+      </c>
+      <c r="P40" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q40" s="3" t="inlineStr"/>
+      <c r="R40" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 03:04:54 PM</t>
+        </is>
+      </c>
+      <c r="S40" s="3" t="inlineStr"/>
+      <c r="T40" s="3" t="inlineStr"/>
+      <c r="U40" s="3" t="inlineStr">
+        <is>
+          <t>9765565085</t>
+        </is>
+      </c>
+      <c r="V40" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 10:37:42 AM</t>
+        </is>
+      </c>
+      <c r="W40" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 03:04:54 PM</t>
+        </is>
+      </c>
+      <c r="X40" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y40" s="3" t="inlineStr">
+        <is>
+          <t>27.74183</t>
+        </is>
+      </c>
+      <c r="Z40" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA40" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB40" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC40" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD40" s="3" t="inlineStr"/>
+      <c r="AE40" s="3" t="inlineStr">
+        <is>
+          <t>CARPRO Basundhara Kathmandu 44600, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF40" s="3" t="inlineStr">
+        <is>
+          <t>bishalshrestha98180073@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG40" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH40" s="3" t="inlineStr"/>
+      <c r="AI40" s="3" t="inlineStr">
+        <is>
+          <t>04:27 hour</t>
+        </is>
+      </c>
+      <c r="AJ40" s="3" t="inlineStr"/>
+      <c r="AK40" s="3" t="inlineStr"/>
+      <c r="AL40" s="3" t="inlineStr">
+        <is>
+          <t>Monika Chaudhary</t>
+        </is>
+      </c>
+      <c r="AM40" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN40" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO40" s="3" t="inlineStr">
+        <is>
+          <t>L3-8</t>
+        </is>
+      </c>
+      <c r="AP40" s="3" t="inlineStr">
+        <is>
+          <t>85.32801</t>
+        </is>
+      </c>
+      <c r="AQ40" s="3" t="inlineStr"/>
+      <c r="AR40" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS40" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT40" s="3" t="inlineStr">
+        <is>
+          <t>4h 27m</t>
+        </is>
+      </c>
+      <c r="AU40" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV40" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW40" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7434,7 +8254,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M54"/>
+  <dimension ref="A1:M59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -7443,7 +8263,7 @@
     <col width="32" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -7471,7 +8291,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3">
@@ -7481,7 +8301,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4">
@@ -7492,7 +8312,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>74.4%</t>
         </is>
       </c>
     </row>
@@ -7504,7 +8324,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>19h 36m</t>
+          <t>19h 23m</t>
         </is>
       </c>
     </row>
@@ -7516,7 +8336,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>2d 17h 44m</t>
+          <t>2d 12h 9m</t>
         </is>
       </c>
     </row>
@@ -7557,14 +8377,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="C10" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="C10" s="3" t="n">
-        <v>21</v>
-      </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>87.5%</t>
+          <t>88.9%</t>
         </is>
       </c>
     </row>
@@ -7575,10 +8395,10 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
@@ -7701,14 +8521,14 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
+        <v>27</v>
+      </c>
+      <c r="D19" s="5" t="n">
         <v>24</v>
       </c>
-      <c r="D19" s="5" t="n">
-        <v>21</v>
-      </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>87.5%</t>
+          <t>88.9%</t>
         </is>
       </c>
     </row>
@@ -7720,7 +8540,7 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Router Adaptor damage Issue</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="C20" s="3" t="n">
@@ -7743,7 +8563,7 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>Router Adaptor damage Issue</t>
         </is>
       </c>
       <c r="C21" s="5" t="n">
@@ -7761,23 +8581,23 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>NETTV-No internet connection in STB</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="C22" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -7789,233 +8609,189 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>NETTV-Welcome Screen Issue</t>
+          <t>NETTV-No internet connection in STB</t>
         </is>
       </c>
       <c r="C23" s="5" t="n">
         <v>1</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>Slow Internet Connection</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Video content is Buffering</t>
+          <t>NETTV-Welcome Screen Issue</t>
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>Wi-Fi Range</t>
+          <t>Slow Internet Connection</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>Low Wi-Fi Range on both band</t>
+          <t>Video content is Buffering</t>
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D25" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="inlineStr"/>
-      <c r="B26" s="3" t="inlineStr"/>
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>Wi-Fi Range</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>Low Wi-Fi Range on both band</t>
+        </is>
+      </c>
       <c r="C26" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr"/>
+      <c r="B27" s="5" t="inlineStr"/>
+      <c r="C27" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="D26" s="3" t="n">
+      <c r="D27" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="E26" s="3" t="inlineStr">
+      <c r="E27" s="5" t="inlineStr">
         <is>
           <t>nan%</t>
         </is>
       </c>
     </row>
-    <row r="27"/>
-    <row r="28">
-      <c r="A28" s="6" t="inlineStr">
+    <row r="28"/>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="4" t="inlineStr">
-        <is>
-          <t>Ticket Number</t>
-        </is>
-      </c>
-      <c r="B29" s="4" t="inlineStr">
-        <is>
-          <t>Account Name</t>
-        </is>
-      </c>
-      <c r="C29" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D29" s="4" t="inlineStr">
-        <is>
-          <t>Sub Category</t>
-        </is>
-      </c>
-      <c r="E29" s="4" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="F29" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Type</t>
-        </is>
-      </c>
-      <c r="G29" s="4" t="inlineStr">
-        <is>
-          <t>Employee Remark / Solution Note</t>
-        </is>
-      </c>
-      <c r="H29" s="4" t="inlineStr">
-        <is>
-          <t>Action / Transfer Remark</t>
-        </is>
-      </c>
-      <c r="I29" s="4" t="inlineStr">
-        <is>
-          <t>Assigned Date</t>
-        </is>
-      </c>
-      <c r="J29" s="4" t="inlineStr">
-        <is>
-          <t>Created Date</t>
-        </is>
-      </c>
-      <c r="K29" s="4" t="inlineStr">
-        <is>
-          <t>Last Modified Date</t>
-        </is>
-      </c>
-      <c r="L29" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Assigned)</t>
-        </is>
-      </c>
-      <c r="M29" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="inlineStr">
-        <is>
-          <t>TKT1364446</t>
-        </is>
-      </c>
-      <c r="B30" s="3" t="inlineStr">
-        <is>
-          <t>Jeet Bahadur Basnet</t>
-        </is>
-      </c>
-      <c r="C30" s="3" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D30" s="3" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E30" s="3" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F30" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G30" s="3" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H30" s="3" t="inlineStr">
-        <is>
-          <t>Case : upgrade wifi 6  has been updated by Sabin Giri</t>
-        </is>
-      </c>
-      <c r="I30" s="3" t="inlineStr">
-        <is>
-          <t>10 Oct 2026 10:40:59 AM</t>
-        </is>
-      </c>
-      <c r="J30" s="3" t="inlineStr">
-        <is>
-          <t>09 Oct 2026 12:30:31 PM</t>
-        </is>
-      </c>
-      <c r="K30" s="3" t="inlineStr">
-        <is>
-          <t>10 Oct 2026 10:40:59 AM</t>
-        </is>
-      </c>
-      <c r="L30" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M30" s="3" t="inlineStr">
-        <is>
-          <t>22h 10m</t>
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>Ticket Number</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>Account Name</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>Sub Category</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Type</t>
+        </is>
+      </c>
+      <c r="G30" s="4" t="inlineStr">
+        <is>
+          <t>Employee Remark / Solution Note</t>
+        </is>
+      </c>
+      <c r="H30" s="4" t="inlineStr">
+        <is>
+          <t>Action / Transfer Remark</t>
+        </is>
+      </c>
+      <c r="I30" s="4" t="inlineStr">
+        <is>
+          <t>Assigned Date</t>
+        </is>
+      </c>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>Created Date</t>
+        </is>
+      </c>
+      <c r="K30" s="4" t="inlineStr">
+        <is>
+          <t>Last Modified Date</t>
+        </is>
+      </c>
+      <c r="L30" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Assigned)</t>
+        </is>
+      </c>
+      <c r="M30" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>TKT1364411</t>
+          <t>TKT1364446</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>Bijya Lama</t>
+          <t>Jeet Bahadur Basnet</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
@@ -8045,22 +8821,22 @@
       </c>
       <c r="H31" s="5" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 upgrade   has been updated by Sabin Giri</t>
+          <t>Case : upgrade wifi 6  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I31" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 10:40:30 AM</t>
+          <t>10 Oct 2026 10:40:59 AM</t>
         </is>
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>09 Oct 2026 12:06:35 PM</t>
+          <t>09 Oct 2026 12:30:31 PM</t>
         </is>
       </c>
       <c r="K31" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 10:40:30 AM</t>
+          <t>10 Oct 2026 10:40:59 AM</t>
         </is>
       </c>
       <c r="L31" s="5" t="inlineStr">
@@ -8070,19 +8846,19 @@
       </c>
       <c r="M31" s="5" t="inlineStr">
         <is>
-          <t>22h 33m</t>
+          <t>22h 10m</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>TKT1357376</t>
+          <t>TKT1364411</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>Goma Adhikari</t>
+          <t>Bijya Lama</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
@@ -8112,22 +8888,22 @@
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 upgrade   has been updated by Sanjeev Giri</t>
+          <t>Case : Wifi 6 upgrade   has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 10:49:43 AM</t>
+          <t>10 Oct 2026 10:40:30 AM</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>04 Oct 2026 08:51:00 AM</t>
+          <t>09 Oct 2026 12:06:35 PM</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 10:49:43 AM</t>
+          <t>10 Oct 2026 10:40:30 AM</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
@@ -8137,19 +8913,19 @@
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>6d 1h 58m</t>
+          <t>22h 33m</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>TKT1358035</t>
+          <t>TKT1357376</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>Saurav Lamsal</t>
+          <t>Goma Adhikari</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
@@ -8164,12 +8940,12 @@
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
@@ -8179,32 +8955,32 @@
       </c>
       <c r="H33" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+          <t>Case : Wifi 6 upgrade   has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I33" s="5" t="inlineStr">
         <is>
-          <t>04 Oct 2026 02:07:16 PM</t>
+          <t>10 Oct 2026 10:49:43 AM</t>
         </is>
       </c>
       <c r="J33" s="5" t="inlineStr">
         <is>
-          <t>04 Oct 2026 02:07:16 PM</t>
+          <t>04 Oct 2026 08:51:00 AM</t>
         </is>
       </c>
       <c r="K33" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 11:04:09 AM</t>
+          <t>10 Oct 2026 10:49:43 AM</t>
         </is>
       </c>
       <c r="L33" s="5" t="inlineStr">
         <is>
-          <t>5d 20h 56m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M33" s="5" t="inlineStr">
         <is>
-          <t>5d 20h 56m</t>
+          <t>6d 1h 58m</t>
         </is>
       </c>
     </row>
@@ -8278,12 +9054,12 @@
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>TKT1364756</t>
+          <t>TKT1358035</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>New Assist Traders</t>
+          <t>Saurav Lamsal</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
@@ -8298,12 +9074,12 @@
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
@@ -8313,44 +9089,44 @@
       </c>
       <c r="H35" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Chandramani Tharu</t>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I35" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 11:15:36 AM</t>
+          <t>04 Oct 2026 02:07:16 PM</t>
         </is>
       </c>
       <c r="J35" s="5" t="inlineStr">
         <is>
-          <t>09 Oct 2026 04:33:35 PM</t>
+          <t>04 Oct 2026 02:07:16 PM</t>
         </is>
       </c>
       <c r="K35" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 11:15:36 AM</t>
+          <t>10 Oct 2026 11:04:09 AM</t>
         </is>
       </c>
       <c r="L35" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>5d 20h 56m</t>
         </is>
       </c>
       <c r="M35" s="5" t="inlineStr">
         <is>
-          <t>18h 42m</t>
+          <t>5d 20h 56m</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>TKT1358080</t>
+          <t>TKT1364756</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Baburaja Maharjan</t>
+          <t>New Assist Traders</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
@@ -8385,17 +9161,17 @@
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 11:13:31 AM</t>
+          <t>10 Oct 2026 11:15:36 AM</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>04 Oct 2026 02:29:39 PM</t>
+          <t>09 Oct 2026 04:33:35 PM</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 11:13:31 AM</t>
+          <t>10 Oct 2026 11:15:36 AM</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
@@ -8405,19 +9181,19 @@
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>5d 20h 43m</t>
+          <t>18h 42m</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>TKT1359556</t>
+          <t>TKT1358080</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>Puspa KC</t>
+          <t>Baburaja Maharjan</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
@@ -8447,22 +9223,22 @@
       </c>
       <c r="H37" s="5" t="inlineStr">
         <is>
-          <t>Case : router upgrade  has been updated by Sabin Giri</t>
+          <t>Case : wifi6  has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I37" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 11:23:36 AM</t>
+          <t>10 Oct 2026 11:13:31 AM</t>
         </is>
       </c>
       <c r="J37" s="5" t="inlineStr">
         <is>
-          <t>05 Oct 2026 03:34:34 PM</t>
+          <t>04 Oct 2026 02:29:39 PM</t>
         </is>
       </c>
       <c r="K37" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 11:23:36 AM</t>
+          <t>10 Oct 2026 11:13:31 AM</t>
         </is>
       </c>
       <c r="L37" s="5" t="inlineStr">
@@ -8472,19 +9248,19 @@
       </c>
       <c r="M37" s="5" t="inlineStr">
         <is>
-          <t>4d 19h 49m</t>
+          <t>5d 20h 43m</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>TKT1365031</t>
+          <t>TKT1359556</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Prem Kumar Shrestha</t>
+          <t>Puspa KC</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
@@ -8514,22 +9290,22 @@
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>Case : WiFi 6   has been updated by Sanjeev Giri</t>
+          <t>Case : router upgrade  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 11:41:30 AM</t>
+          <t>10 Oct 2026 11:23:36 AM</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>09 Oct 2026 09:56:52 PM</t>
+          <t>05 Oct 2026 03:34:34 PM</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 11:41:30 AM</t>
+          <t>10 Oct 2026 11:23:36 AM</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
@@ -8539,19 +9315,19 @@
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>13h 44m</t>
+          <t>4d 19h 49m</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>TKT1362058</t>
+          <t>TKT1365031</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>Gyan Chiraniya</t>
+          <t>Prem Kumar Shrestha</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
@@ -8566,12 +9342,12 @@
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
@@ -8581,32 +9357,32 @@
       </c>
       <c r="H39" s="5" t="inlineStr">
         <is>
-          <t>Case : For upgradation to wifi6   has been updated by Ajit Shrestha</t>
+          <t>Case : WiFi 6   has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I39" s="5" t="inlineStr">
         <is>
-          <t>07 Oct 2026 02:43:23 PM</t>
+          <t>10 Oct 2026 11:41:30 AM</t>
         </is>
       </c>
       <c r="J39" s="5" t="inlineStr">
         <is>
-          <t>07 Oct 2026 02:43:23 PM</t>
+          <t>09 Oct 2026 09:56:52 PM</t>
         </is>
       </c>
       <c r="K39" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 11:36:00 AM</t>
+          <t>10 Oct 2026 11:41:30 AM</t>
         </is>
       </c>
       <c r="L39" s="5" t="inlineStr">
         <is>
-          <t>2d 20h 52m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M39" s="5" t="inlineStr">
         <is>
-          <t>2d 20h 52m</t>
+          <t>13h 44m</t>
         </is>
       </c>
     </row>
@@ -8680,12 +9456,12 @@
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>TKT1362055</t>
+          <t>TKT1362058</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>Ravi Shahi</t>
+          <t>Gyan Chiraniya</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
@@ -8700,12 +9476,12 @@
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr">
@@ -8715,54 +9491,54 @@
       </c>
       <c r="H41" s="5" t="inlineStr">
         <is>
-          <t>Case : For upgradation to wifi6   has been updated by Chandramani Tharu</t>
+          <t>Case : For upgradation to wifi6   has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I41" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 11:53:17 AM</t>
+          <t>07 Oct 2026 02:43:23 PM</t>
         </is>
       </c>
       <c r="J41" s="5" t="inlineStr">
         <is>
-          <t>07 Oct 2026 02:42:05 PM</t>
+          <t>07 Oct 2026 02:43:23 PM</t>
         </is>
       </c>
       <c r="K41" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 11:53:17 AM</t>
+          <t>10 Oct 2026 11:36:00 AM</t>
         </is>
       </c>
       <c r="L41" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>2d 20h 52m</t>
         </is>
       </c>
       <c r="M41" s="5" t="inlineStr">
         <is>
-          <t>2d 21h 11m</t>
+          <t>2d 20h 52m</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>TKT1364261</t>
+          <t>TKT1362055</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>Niratna manandhar</t>
+          <t>Ravi Shahi</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>NETTV-Welcome Screen Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
@@ -8782,22 +9558,22 @@
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t>Case : NETTV issue  has been updated by Ajit Shrestha</t>
+          <t>Case : For upgradation to wifi6   has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 12:00:52 PM</t>
+          <t>10 Oct 2026 11:53:17 AM</t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>09 Oct 2026 10:23:09 AM</t>
+          <t>07 Oct 2026 02:42:05 PM</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 12:00:52 PM</t>
+          <t>10 Oct 2026 11:53:17 AM</t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
@@ -8807,29 +9583,29 @@
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t>1d 1h 37m</t>
+          <t>2d 21h 11m</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>TKT1360378</t>
+          <t>TKT1364261</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>Maheshwor Maharjan</t>
+          <t>Niratna manandhar</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>NETTV-Welcome Screen Issue</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -8849,22 +9625,22 @@
       </c>
       <c r="H43" s="5" t="inlineStr">
         <is>
-          <t>Case :   has been updated by Sanjeev Giri</t>
+          <t>Case : NETTV issue  has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I43" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 12:04:10 PM</t>
+          <t>10 Oct 2026 12:00:52 PM</t>
         </is>
       </c>
       <c r="J43" s="5" t="inlineStr">
         <is>
-          <t>06 Oct 2026 10:49:38 AM</t>
+          <t>09 Oct 2026 10:23:09 AM</t>
         </is>
       </c>
       <c r="K43" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 12:04:10 PM</t>
+          <t>10 Oct 2026 12:00:52 PM</t>
         </is>
       </c>
       <c r="L43" s="5" t="inlineStr">
@@ -8874,29 +9650,29 @@
       </c>
       <c r="M43" s="5" t="inlineStr">
         <is>
-          <t>4d 1h 14m</t>
+          <t>1d 1h 37m</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>TKT1365280</t>
+          <t>TKT1360378</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>Atul Ali</t>
+          <t>Maheshwor Maharjan</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>Wi-Fi Range</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>Low Wi-Fi Range on both band</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
@@ -8916,22 +9692,22 @@
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t>Case : low wifi range issue  has been updated by Sabin Giri</t>
+          <t>Case :   has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 12:06:57 PM</t>
+          <t>10 Oct 2026 12:04:10 PM</t>
         </is>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 10:00:04 AM</t>
+          <t>06 Oct 2026 10:49:38 AM</t>
         </is>
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 12:06:57 PM</t>
+          <t>10 Oct 2026 12:04:10 PM</t>
         </is>
       </c>
       <c r="L44" s="3" t="inlineStr">
@@ -8941,29 +9717,29 @@
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t>2h 6m</t>
+          <t>4d 1h 14m</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>TKT1364910</t>
+          <t>TKT1365280</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>Ayush Duwal</t>
+          <t>Atul Ali</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Wi-Fi Range</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Low Wi-Fi Range on both band</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -8983,22 +9759,22 @@
       </c>
       <c r="H45" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Sabin Giri</t>
+          <t>Case : low wifi range issue  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I45" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 12:30:17 PM</t>
+          <t>10 Oct 2026 12:06:57 PM</t>
         </is>
       </c>
       <c r="J45" s="5" t="inlineStr">
         <is>
-          <t>09 Oct 2026 06:57:31 PM</t>
+          <t>10 Oct 2026 10:00:04 AM</t>
         </is>
       </c>
       <c r="K45" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 12:30:17 PM</t>
+          <t>10 Oct 2026 12:06:57 PM</t>
         </is>
       </c>
       <c r="L45" s="5" t="inlineStr">
@@ -9008,29 +9784,29 @@
       </c>
       <c r="M45" s="5" t="inlineStr">
         <is>
-          <t>17h 32m</t>
+          <t>2h 6m</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>TKT1364848</t>
+          <t>TKT1364910</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>Mayanka Kirana Store</t>
+          <t>Ayush Duwal</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
@@ -9050,22 +9826,22 @@
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t>Case : no light blinking   has been updated by Sabin Giri</t>
+          <t>Case : wifi6  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 12:35:23 PM</t>
+          <t>10 Oct 2026 12:30:17 PM</t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>09 Oct 2026 05:45:00 PM</t>
+          <t>09 Oct 2026 06:57:31 PM</t>
         </is>
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 12:35:23 PM</t>
+          <t>10 Oct 2026 12:30:17 PM</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
@@ -9075,29 +9851,29 @@
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t>18h 50m</t>
+          <t>17h 32m</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>TKT1358952</t>
+          <t>TKT1364848</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>Sanjay Dangol</t>
+          <t>Mayanka Kirana Store</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -9117,22 +9893,22 @@
       </c>
       <c r="H47" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Sanjeev Giri</t>
+          <t>Case : no light blinking   has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I47" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 12:34:52 PM</t>
+          <t>10 Oct 2026 12:35:23 PM</t>
         </is>
       </c>
       <c r="J47" s="5" t="inlineStr">
         <is>
-          <t>05 Oct 2026 09:20:16 AM</t>
+          <t>09 Oct 2026 05:45:00 PM</t>
         </is>
       </c>
       <c r="K47" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 12:35:24 PM</t>
+          <t>10 Oct 2026 12:35:23 PM</t>
         </is>
       </c>
       <c r="L47" s="5" t="inlineStr">
@@ -9142,7 +9918,7 @@
       </c>
       <c r="M47" s="5" t="inlineStr">
         <is>
-          <t>5d 3h 15m</t>
+          <t>18h 50m</t>
         </is>
       </c>
     </row>
@@ -9216,12 +9992,12 @@
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>TKT1362114</t>
+          <t>TKT1358952</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>Punam shah</t>
+          <t>Sanjay Dangol</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
@@ -9251,22 +10027,22 @@
       </c>
       <c r="H49" s="5" t="inlineStr">
         <is>
-          <t>Case : Wi-Fi 6  has been updated by Sanjeev Giri</t>
+          <t>Case : wifi6  has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I49" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 12:34:03 PM</t>
+          <t>10 Oct 2026 12:34:52 PM</t>
         </is>
       </c>
       <c r="J49" s="5" t="inlineStr">
         <is>
-          <t>07 Oct 2026 03:17:23 PM</t>
+          <t>05 Oct 2026 09:20:16 AM</t>
         </is>
       </c>
       <c r="K49" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 12:34:03 PM</t>
+          <t>10 Oct 2026 12:35:24 PM</t>
         </is>
       </c>
       <c r="L49" s="5" t="inlineStr">
@@ -9276,19 +10052,19 @@
       </c>
       <c r="M49" s="5" t="inlineStr">
         <is>
-          <t>2d 21h 16m</t>
+          <t>5d 3h 15m</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>TKT1364639</t>
+          <t>TKT1362114</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>Anil Pradhan</t>
+          <t>Punam shah</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
@@ -9303,12 +10079,12 @@
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G50" s="3" t="inlineStr">
@@ -9318,44 +10094,44 @@
       </c>
       <c r="H50" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6 router upgrade   has been updated by Ajit Shrestha</t>
+          <t>Case : Wi-Fi 6  has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I50" s="3" t="inlineStr">
         <is>
-          <t>09 Oct 2026 03:05:33 PM</t>
+          <t>10 Oct 2026 12:34:03 PM</t>
         </is>
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
-          <t>09 Oct 2026 03:05:33 PM</t>
+          <t>07 Oct 2026 03:17:23 PM</t>
         </is>
       </c>
       <c r="K50" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 12:50:22 PM</t>
+          <t>10 Oct 2026 12:34:03 PM</t>
         </is>
       </c>
       <c r="L50" s="3" t="inlineStr">
         <is>
-          <t>21h 44m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M50" s="3" t="inlineStr">
         <is>
-          <t>21h 44m</t>
+          <t>2d 21h 16m</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>TKT1359613</t>
+          <t>TKT1364639</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>lok bahadur malla</t>
+          <t>Anil Pradhan</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
@@ -9370,12 +10146,12 @@
       </c>
       <c r="E51" s="5" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F51" s="5" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G51" s="5" t="inlineStr">
@@ -9385,44 +10161,44 @@
       </c>
       <c r="H51" s="5" t="inlineStr">
         <is>
-          <t>Case : Wi-Fi 6  has been updated by Sanjeev Giri</t>
+          <t>Case : wifi 6 router upgrade   has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I51" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 01:46:58 PM</t>
+          <t>09 Oct 2026 03:05:33 PM</t>
         </is>
       </c>
       <c r="J51" s="5" t="inlineStr">
         <is>
-          <t>05 Oct 2026 04:13:23 PM</t>
+          <t>09 Oct 2026 03:05:33 PM</t>
         </is>
       </c>
       <c r="K51" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 01:46:58 PM</t>
+          <t>10 Oct 2026 12:50:22 PM</t>
         </is>
       </c>
       <c r="L51" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>21h 44m</t>
         </is>
       </c>
       <c r="M51" s="5" t="inlineStr">
         <is>
-          <t>4d 21h 33m</t>
+          <t>21h 44m</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>TKT1363352</t>
+          <t>TKT1359613</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>Rajan Dawadi</t>
+          <t>lok bahadur malla</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
@@ -9437,12 +10213,12 @@
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G52" s="3" t="inlineStr">
@@ -9452,44 +10228,44 @@
       </c>
       <c r="H52" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Ajit Shrestha</t>
+          <t>Case : Wi-Fi 6  has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I52" s="3" t="inlineStr">
         <is>
-          <t>08 Oct 2026 01:21:13 PM</t>
+          <t>10 Oct 2026 01:46:58 PM</t>
         </is>
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
-          <t>08 Oct 2026 01:21:13 PM</t>
+          <t>05 Oct 2026 04:13:23 PM</t>
         </is>
       </c>
       <c r="K52" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 02:14:45 PM</t>
+          <t>10 Oct 2026 01:46:58 PM</t>
         </is>
       </c>
       <c r="L52" s="3" t="inlineStr">
         <is>
-          <t>2d 53m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M52" s="3" t="inlineStr">
         <is>
-          <t>2d 53m</t>
+          <t>4d 21h 33m</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>TKT1365302</t>
+          <t>TKT1363352</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>Kritika Sah</t>
+          <t>Rajan Dawadi</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
@@ -9504,12 +10280,12 @@
       </c>
       <c r="E53" s="5" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F53" s="5" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G53" s="5" t="inlineStr">
@@ -9519,99 +10295,434 @@
       </c>
       <c r="H53" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+          <t>Case : wifi6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I53" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 02:06:16 PM</t>
+          <t>08 Oct 2026 01:21:13 PM</t>
         </is>
       </c>
       <c r="J53" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 10:19:45 AM</t>
+          <t>08 Oct 2026 01:21:13 PM</t>
         </is>
       </c>
       <c r="K53" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 02:06:16 PM</t>
+          <t>10 Oct 2026 02:14:45 PM</t>
         </is>
       </c>
       <c r="L53" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>2d 53m</t>
         </is>
       </c>
       <c r="M53" s="5" t="inlineStr">
         <is>
-          <t>3h 46m</t>
+          <t>2d 53m</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
+          <t>TKT1365302</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>Kritika Sah</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F54" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G54" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H54" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I54" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 02:06:16 PM</t>
+        </is>
+      </c>
+      <c r="J54" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 10:19:45 AM</t>
+        </is>
+      </c>
+      <c r="K54" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 02:06:16 PM</t>
+        </is>
+      </c>
+      <c r="L54" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M54" s="3" t="inlineStr">
+        <is>
+          <t>3h 46m</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
           <t>TKT1365176</t>
         </is>
       </c>
-      <c r="B54" s="3" t="inlineStr">
+      <c r="B55" s="5" t="inlineStr">
         <is>
           <t>Aafnai Deal Online Shopping Center Pvt Ltd</t>
         </is>
       </c>
-      <c r="C54" s="3" t="inlineStr">
+      <c r="C55" s="5" t="inlineStr">
         <is>
           <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
-      <c r="D54" s="3" t="inlineStr">
+      <c r="D55" s="5" t="inlineStr">
         <is>
           <t>Router Adaptor damage Issue</t>
         </is>
       </c>
-      <c r="E54" s="3" t="inlineStr">
+      <c r="E55" s="5" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="F54" s="3" t="inlineStr">
+      <c r="F55" s="5" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="G54" s="3" t="inlineStr">
+      <c r="G55" s="5" t="inlineStr">
         <is>
           <t>nan</t>
         </is>
       </c>
-      <c r="H54" s="3" t="inlineStr">
+      <c r="H55" s="5" t="inlineStr">
         <is>
           <t>Case : Router faulty   has been updated by Ajit Shrestha</t>
         </is>
       </c>
-      <c r="I54" s="3" t="inlineStr">
+      <c r="I55" s="5" t="inlineStr">
         <is>
           <t>10 Oct 2026 02:40:00 PM</t>
         </is>
       </c>
-      <c r="J54" s="3" t="inlineStr">
+      <c r="J55" s="5" t="inlineStr">
         <is>
           <t>10 Oct 2026 08:51:05 AM</t>
         </is>
       </c>
-      <c r="K54" s="3" t="inlineStr">
+      <c r="K55" s="5" t="inlineStr">
         <is>
           <t>10 Oct 2026 02:40:00 PM</t>
         </is>
       </c>
-      <c r="L54" s="3" t="inlineStr">
+      <c r="L55" s="5" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="M54" s="3" t="inlineStr">
+      <c r="M55" s="5" t="inlineStr">
         <is>
           <t>5h 48m</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>TKT1362110</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>Prem Bahadur Karki</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F56" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G56" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="H56" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I56" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 03:16:15 PM</t>
+        </is>
+      </c>
+      <c r="J56" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 03:16:15 PM</t>
+        </is>
+      </c>
+      <c r="K56" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 03:12:56 PM</t>
+        </is>
+      </c>
+      <c r="L56" s="3" t="inlineStr">
+        <is>
+          <t>2d 23h 56m</t>
+        </is>
+      </c>
+      <c r="M56" s="3" t="inlineStr">
+        <is>
+          <t>2d 23h 56m</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="5" t="inlineStr">
+        <is>
+          <t>TKT1364906</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="inlineStr">
+        <is>
+          <t>Pasang sherpa</t>
+        </is>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="D57" s="5" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="E57" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F57" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G57" s="5" t="inlineStr">
+        <is>
+          <t>Case : iptv issue  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="H57" s="5" t="inlineStr">
+        <is>
+          <t>Case : iptv issue  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I57" s="5" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 03:41:05 PM</t>
+        </is>
+      </c>
+      <c r="J57" s="5" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 06:55:03 PM</t>
+        </is>
+      </c>
+      <c r="K57" s="5" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 03:41:05 PM</t>
+        </is>
+      </c>
+      <c r="L57" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M57" s="5" t="inlineStr">
+        <is>
+          <t>20h 46m</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>TKT1365415</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>Sarmila Sangasarar</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E58" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F58" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G58" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 Router   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="H58" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 Router   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I58" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 03:38:34 PM</t>
+        </is>
+      </c>
+      <c r="J58" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 11:51:02 AM</t>
+        </is>
+      </c>
+      <c r="K58" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 03:38:34 PM</t>
+        </is>
+      </c>
+      <c r="L58" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M58" s="3" t="inlineStr">
+        <is>
+          <t>3h 47m</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="5" t="inlineStr">
+        <is>
+          <t>TKT1365328</t>
+        </is>
+      </c>
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>Bishal Shrestha</t>
+        </is>
+      </c>
+      <c r="C59" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D59" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E59" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F59" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G59" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="H59" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I59" s="5" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 03:04:54 PM</t>
+        </is>
+      </c>
+      <c r="J59" s="5" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 10:37:42 AM</t>
+        </is>
+      </c>
+      <c r="K59" s="5" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 03:04:54 PM</t>
+        </is>
+      </c>
+      <c r="L59" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M59" s="5" t="inlineStr">
+        <is>
+          <t>4h 27m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_10_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_10_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW40"/>
+  <dimension ref="A1:AW44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -7490,10 +7490,8 @@
           <t>Prem Bahadur Karki</t>
         </is>
       </c>
-      <c r="O37" s="3" t="inlineStr">
-        <is>
-          <t>9866494523</t>
-        </is>
+      <c r="O37" s="3" t="n">
+        <v>9866494523</v>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
@@ -7583,10 +7581,8 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN37" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN37" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO37" s="3" t="inlineStr">
         <is>
@@ -7597,7 +7593,7 @@
       <c r="AQ37" s="3" t="inlineStr"/>
       <c r="AR37" s="3" t="inlineStr">
         <is>
-          <t>Case : WiFi 6  has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS37" s="3" t="inlineStr">
@@ -7693,10 +7689,8 @@
           <t>Pasang sherpa</t>
         </is>
       </c>
-      <c r="O38" s="3" t="inlineStr">
-        <is>
-          <t>9842868756</t>
-        </is>
+      <c r="O38" s="3" t="n">
+        <v>9842868756</v>
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
@@ -7786,10 +7780,8 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN38" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN38" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO38" s="3" t="inlineStr">
         <is>
@@ -7800,7 +7792,7 @@
       <c r="AQ38" s="3" t="inlineStr"/>
       <c r="AR38" s="3" t="inlineStr">
         <is>
-          <t>Case : iptv issue  has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS38" s="3" t="inlineStr">
@@ -7896,10 +7888,8 @@
           <t>Sarmila Sangasarar</t>
         </is>
       </c>
-      <c r="O39" s="3" t="inlineStr">
-        <is>
-          <t>9810289618</t>
-        </is>
+      <c r="O39" s="3" t="n">
+        <v>9810289618</v>
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
@@ -7989,10 +7979,8 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN39" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN39" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO39" s="3" t="inlineStr">
         <is>
@@ -8003,7 +7991,7 @@
       <c r="AQ39" s="3" t="inlineStr"/>
       <c r="AR39" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6 Router   has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS39" s="3" t="inlineStr">
@@ -8099,10 +8087,8 @@
           <t>Bishal Shrestha</t>
         </is>
       </c>
-      <c r="O40" s="3" t="inlineStr">
-        <is>
-          <t>9765565085</t>
-        </is>
+      <c r="O40" s="3" t="n">
+        <v>9765565085</v>
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
@@ -8196,48 +8182,876 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN40" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN40" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO40" s="3" t="inlineStr">
         <is>
           <t>L3-8</t>
         </is>
       </c>
-      <c r="AP40" s="3" t="inlineStr">
-        <is>
-          <t>85.32801</t>
-        </is>
+      <c r="AP40" s="3" t="n">
+        <v>85.32801000000001</v>
       </c>
       <c r="AQ40" s="3" t="inlineStr"/>
       <c r="AR40" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS40" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT40" s="3" t="inlineStr">
+        <is>
+          <t>4h 27m</t>
+        </is>
+      </c>
+      <c r="AU40" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV40" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AS40" s="3" t="inlineStr">
+      <c r="AW40" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 3:41 PM</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="inlineStr"/>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV issue  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I41" s="3" t="inlineStr">
+        <is>
+          <t>IPTV issue</t>
+        </is>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>TKT1364260</t>
+        </is>
+      </c>
+      <c r="K41" s="3" t="inlineStr">
+        <is>
+          <t>Suresh Raut</t>
+        </is>
+      </c>
+      <c r="L41" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M41" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N41" s="3" t="inlineStr">
+        <is>
+          <t>Suresh Raut</t>
+        </is>
+      </c>
+      <c r="O41" s="3" t="inlineStr">
+        <is>
+          <t>9747744379</t>
+        </is>
+      </c>
+      <c r="P41" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="Q41" s="3" t="inlineStr"/>
+      <c r="R41" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 03:41:47 PM</t>
+        </is>
+      </c>
+      <c r="S41" s="3" t="inlineStr"/>
+      <c r="T41" s="3" t="inlineStr"/>
+      <c r="U41" s="3" t="inlineStr">
+        <is>
+          <t>LTP9747744379</t>
+        </is>
+      </c>
+      <c r="V41" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 10:21:21 AM</t>
+        </is>
+      </c>
+      <c r="W41" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 03:41:47 PM</t>
+        </is>
+      </c>
+      <c r="X41" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y41" s="3" t="inlineStr">
+        <is>
+          <t>27.680963</t>
+        </is>
+      </c>
+      <c r="Z41" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="AA41" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB41" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC41" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD41" s="3" t="inlineStr"/>
+      <c r="AE41" s="3" t="inlineStr">
+        <is>
+          <t>Opposite of Star Hospital, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF41" s="3" t="inlineStr">
+        <is>
+          <t>test@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG41" s="3" t="inlineStr">
+        <is>
+          <t>SKYCOM-Welcome Screen Issue</t>
+        </is>
+      </c>
+      <c r="AH41" s="3" t="inlineStr"/>
+      <c r="AI41" s="3" t="inlineStr">
+        <is>
+          <t>15:20 hour</t>
+        </is>
+      </c>
+      <c r="AJ41" s="3" t="inlineStr"/>
+      <c r="AK41" s="3" t="inlineStr"/>
+      <c r="AL41" s="3" t="inlineStr">
+        <is>
+          <t>Naman Mallik</t>
+        </is>
+      </c>
+      <c r="AM41" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN41" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO41" s="3" t="inlineStr">
+        <is>
+          <t>CDB423</t>
+        </is>
+      </c>
+      <c r="AP41" s="3" t="inlineStr">
+        <is>
+          <t>85.301988</t>
+        </is>
+      </c>
+      <c r="AQ41" s="3" t="inlineStr"/>
+      <c r="AR41" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV issue  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS41" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT40" s="3" t="inlineStr">
-        <is>
-          <t>4h 27m</t>
-        </is>
-      </c>
-      <c r="AU40" s="3" t="inlineStr">
+      <c r="AT41" s="3" t="inlineStr">
+        <is>
+          <t>1d 5h 20m</t>
+        </is>
+      </c>
+      <c r="AU41" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV40" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
-        </is>
-      </c>
-      <c r="AW40" s="3" t="inlineStr">
+      <c r="AV41" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV issue  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW41" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 3:41 PM</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G42" s="3" t="inlineStr"/>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t>Case : frequent disconnection issue   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I42" s="3" t="inlineStr">
+        <is>
+          <t>IPTV issue</t>
+        </is>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>TKT1364260</t>
+        </is>
+      </c>
+      <c r="K42" s="3" t="inlineStr">
+        <is>
+          <t>Suresh Raut</t>
+        </is>
+      </c>
+      <c r="L42" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N42" s="3" t="inlineStr">
+        <is>
+          <t>Suresh Raut</t>
+        </is>
+      </c>
+      <c r="O42" s="3" t="inlineStr">
+        <is>
+          <t>9747744379</t>
+        </is>
+      </c>
+      <c r="P42" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="Q42" s="3" t="inlineStr"/>
+      <c r="R42" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 03:41:47 PM</t>
+        </is>
+      </c>
+      <c r="S42" s="3" t="inlineStr"/>
+      <c r="T42" s="3" t="inlineStr"/>
+      <c r="U42" s="3" t="inlineStr">
+        <is>
+          <t>LTP9747744379</t>
+        </is>
+      </c>
+      <c r="V42" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 10:21:21 AM</t>
+        </is>
+      </c>
+      <c r="W42" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 03:41:47 PM</t>
+        </is>
+      </c>
+      <c r="X42" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y42" s="3" t="inlineStr">
+        <is>
+          <t>27.680963</t>
+        </is>
+      </c>
+      <c r="Z42" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="AA42" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB42" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC42" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD42" s="3" t="inlineStr"/>
+      <c r="AE42" s="3" t="inlineStr">
+        <is>
+          <t>Opposite of Star Hospital, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF42" s="3" t="inlineStr">
+        <is>
+          <t>test@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG42" s="3" t="inlineStr">
+        <is>
+          <t>SKYCOM-Welcome Screen Issue</t>
+        </is>
+      </c>
+      <c r="AH42" s="3" t="inlineStr"/>
+      <c r="AI42" s="3" t="inlineStr">
+        <is>
+          <t>15:20 hour</t>
+        </is>
+      </c>
+      <c r="AJ42" s="3" t="inlineStr"/>
+      <c r="AK42" s="3" t="inlineStr"/>
+      <c r="AL42" s="3" t="inlineStr">
+        <is>
+          <t>Naman Mallik</t>
+        </is>
+      </c>
+      <c r="AM42" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN42" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO42" s="3" t="inlineStr">
+        <is>
+          <t>CDB423</t>
+        </is>
+      </c>
+      <c r="AP42" s="3" t="inlineStr">
+        <is>
+          <t>85.301988</t>
+        </is>
+      </c>
+      <c r="AQ42" s="3" t="inlineStr"/>
+      <c r="AR42" s="3" t="inlineStr">
+        <is>
+          <t>Case : frequent disconnection issue   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS42" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT42" s="3" t="inlineStr">
+        <is>
+          <t>1d 5h 20m</t>
+        </is>
+      </c>
+      <c r="AU42" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV42" s="3" t="inlineStr">
+        <is>
+          <t>Case : frequent disconnection issue   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW42" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 3:27 PM</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G43" s="3" t="inlineStr"/>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t>Case : router change   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I43" s="3" t="inlineStr">
+        <is>
+          <t>router change</t>
+        </is>
+      </c>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t>TKT1359002</t>
+        </is>
+      </c>
+      <c r="K43" s="3" t="inlineStr">
+        <is>
+          <t>Dinesh Thakur</t>
+        </is>
+      </c>
+      <c r="L43" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N43" s="3" t="inlineStr">
+        <is>
+          <t>Pankaj kumar jha</t>
+        </is>
+      </c>
+      <c r="O43" s="3" t="inlineStr">
+        <is>
+          <t>9849680028</t>
+        </is>
+      </c>
+      <c r="P43" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q43" s="3" t="inlineStr"/>
+      <c r="R43" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 03:27:45 PM</t>
+        </is>
+      </c>
+      <c r="S43" s="3" t="inlineStr"/>
+      <c r="T43" s="3" t="inlineStr"/>
+      <c r="U43" s="3" t="inlineStr">
+        <is>
+          <t>LTP9849680028</t>
+        </is>
+      </c>
+      <c r="V43" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 10:04:47 AM</t>
+        </is>
+      </c>
+      <c r="W43" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 03:34:04 PM</t>
+        </is>
+      </c>
+      <c r="X43" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y43" s="3" t="inlineStr"/>
+      <c r="Z43" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA43" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB43" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC43" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD43" s="3" t="inlineStr"/>
+      <c r="AE43" s="3" t="inlineStr">
+        <is>
+          <t>.., , Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF43" s="3" t="inlineStr">
+        <is>
+          <t>1@g.com</t>
+        </is>
+      </c>
+      <c r="AG43" s="3" t="inlineStr">
+        <is>
+          <t>Router placement CR</t>
+        </is>
+      </c>
+      <c r="AH43" s="3" t="inlineStr"/>
+      <c r="AI43" s="3" t="inlineStr">
+        <is>
+          <t>07:29 hour</t>
+        </is>
+      </c>
+      <c r="AJ43" s="3" t="inlineStr"/>
+      <c r="AK43" s="3" t="inlineStr"/>
+      <c r="AL43" s="3" t="inlineStr">
+        <is>
+          <t>Praktisha Subedi</t>
+        </is>
+      </c>
+      <c r="AM43" s="3" t="inlineStr">
+        <is>
+          <t>Rikesh Shrestha</t>
+        </is>
+      </c>
+      <c r="AN43" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO43" s="3" t="inlineStr">
+        <is>
+          <t>CDB521</t>
+        </is>
+      </c>
+      <c r="AP43" s="3" t="inlineStr"/>
+      <c r="AQ43" s="3" t="inlineStr"/>
+      <c r="AR43" s="3" t="inlineStr">
+        <is>
+          <t>Case : router change   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS43" s="3" t="inlineStr">
+        <is>
+          <t>6m</t>
+        </is>
+      </c>
+      <c r="AT43" s="3" t="inlineStr">
+        <is>
+          <t>5d 5h 29m</t>
+        </is>
+      </c>
+      <c r="AU43" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV43" s="3" t="inlineStr">
+        <is>
+          <t>Case : router change   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW43" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 3:21 PM</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="inlineStr"/>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I44" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6</t>
+        </is>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>TKT1359809</t>
+        </is>
+      </c>
+      <c r="K44" s="3" t="inlineStr">
+        <is>
+          <t>Ashutosh Regmi</t>
+        </is>
+      </c>
+      <c r="L44" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M44" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N44" s="3" t="inlineStr">
+        <is>
+          <t>Ashutosh Regmi</t>
+        </is>
+      </c>
+      <c r="O44" s="3" t="inlineStr">
+        <is>
+          <t>9867171444</t>
+        </is>
+      </c>
+      <c r="P44" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q44" s="3" t="inlineStr"/>
+      <c r="R44" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 04:55:59 PM</t>
+        </is>
+      </c>
+      <c r="S44" s="3" t="inlineStr"/>
+      <c r="T44" s="3" t="inlineStr"/>
+      <c r="U44" s="3" t="inlineStr">
+        <is>
+          <t>9867171444</t>
+        </is>
+      </c>
+      <c r="V44" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 06:58:32 PM</t>
+        </is>
+      </c>
+      <c r="W44" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 03:21:37 PM</t>
+        </is>
+      </c>
+      <c r="X44" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y44" s="3" t="inlineStr">
+        <is>
+          <t>27.70175</t>
+        </is>
+      </c>
+      <c r="Z44" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA44" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB44" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC44" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD44" s="3" t="inlineStr"/>
+      <c r="AE44" s="3" t="inlineStr">
+        <is>
+          <t>27.655793801439316, 85.34194749764016, Lalitpur, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF44" s="3" t="inlineStr">
+        <is>
+          <t>regmiashutosh3@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG44" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH44" s="3" t="inlineStr"/>
+      <c r="AI44" s="3" t="inlineStr"/>
+      <c r="AJ44" s="3" t="inlineStr"/>
+      <c r="AK44" s="3" t="inlineStr"/>
+      <c r="AL44" s="3" t="inlineStr">
+        <is>
+          <t>Nirajan Dhamala</t>
+        </is>
+      </c>
+      <c r="AM44" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN44" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO44" s="3" t="inlineStr">
+        <is>
+          <t>CDB091A</t>
+        </is>
+      </c>
+      <c r="AP44" s="3" t="inlineStr">
+        <is>
+          <t>85.3341</t>
+        </is>
+      </c>
+      <c r="AQ44" s="3" t="inlineStr"/>
+      <c r="AR44" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS44" s="3" t="inlineStr">
+        <is>
+          <t>22h 25m</t>
+        </is>
+      </c>
+      <c r="AT44" s="3" t="inlineStr">
+        <is>
+          <t>4d 20h 23m</t>
+        </is>
+      </c>
+      <c r="AU44" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV44" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW44" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
@@ -8254,7 +9068,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M59"/>
+  <dimension ref="A1:M64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -8291,7 +9105,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3">
@@ -8301,7 +9115,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4">
@@ -8324,7 +9138,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>19h 23m</t>
+          <t>17h 34m</t>
         </is>
       </c>
     </row>
@@ -8336,7 +9150,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>2d 12h 9m</t>
+          <t>2d 12h 16m</t>
         </is>
       </c>
     </row>
@@ -8377,14 +9191,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>88.9%</t>
+          <t>86.2%</t>
         </is>
       </c>
     </row>
@@ -8413,14 +9227,14 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -8521,26 +9335,26 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D19" s="5" t="n">
         <v>24</v>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>88.9%</t>
+          <t>85.7%</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>Router placement CR</t>
         </is>
       </c>
       <c r="C20" s="3" t="n">
@@ -8563,7 +9377,7 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>Router Adaptor damage Issue</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="C21" s="5" t="n">
@@ -8586,7 +9400,7 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>Router Adaptor damage Issue</t>
         </is>
       </c>
       <c r="C22" s="3" t="n">
@@ -8604,23 +9418,23 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>NETTV-No internet connection in STB</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="C23" s="5" t="n">
         <v>1</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -8632,60 +9446,60 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>NETTV-Welcome Screen Issue</t>
+          <t>NETTV-No internet connection in STB</t>
         </is>
       </c>
       <c r="C24" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>Slow Internet Connection</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>Video content is Buffering</t>
+          <t>NETTV-Welcome Screen Issue</t>
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D25" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>Wi-Fi Range</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Low Wi-Fi Range on both band</t>
+          <t>SKYCOM-Welcome Screen Issue</t>
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
@@ -8694,238 +9508,150 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="inlineStr"/>
-      <c r="B27" s="5" t="inlineStr"/>
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
       <c r="C27" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D27" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>Wi-Fi Range</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>Low Wi-Fi Range on both band</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr"/>
+      <c r="B29" s="5" t="inlineStr"/>
+      <c r="C29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
           <t>nan%</t>
         </is>
       </c>
     </row>
-    <row r="28"/>
-    <row r="29">
-      <c r="A29" s="6" t="inlineStr">
+    <row r="30"/>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="4" t="inlineStr">
-        <is>
-          <t>Ticket Number</t>
-        </is>
-      </c>
-      <c r="B30" s="4" t="inlineStr">
-        <is>
-          <t>Account Name</t>
-        </is>
-      </c>
-      <c r="C30" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D30" s="4" t="inlineStr">
-        <is>
-          <t>Sub Category</t>
-        </is>
-      </c>
-      <c r="E30" s="4" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="F30" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Type</t>
-        </is>
-      </c>
-      <c r="G30" s="4" t="inlineStr">
-        <is>
-          <t>Employee Remark / Solution Note</t>
-        </is>
-      </c>
-      <c r="H30" s="4" t="inlineStr">
-        <is>
-          <t>Action / Transfer Remark</t>
-        </is>
-      </c>
-      <c r="I30" s="4" t="inlineStr">
-        <is>
-          <t>Assigned Date</t>
-        </is>
-      </c>
-      <c r="J30" s="4" t="inlineStr">
-        <is>
-          <t>Created Date</t>
-        </is>
-      </c>
-      <c r="K30" s="4" t="inlineStr">
-        <is>
-          <t>Last Modified Date</t>
-        </is>
-      </c>
-      <c r="L30" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Assigned)</t>
-        </is>
-      </c>
-      <c r="M30" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Created)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>TKT1364446</t>
-        </is>
-      </c>
-      <c r="B31" s="5" t="inlineStr">
-        <is>
-          <t>Jeet Bahadur Basnet</t>
-        </is>
-      </c>
-      <c r="C31" s="5" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D31" s="5" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E31" s="5" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F31" s="5" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G31" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H31" s="5" t="inlineStr">
-        <is>
-          <t>Case : upgrade wifi 6  has been updated by Sabin Giri</t>
-        </is>
-      </c>
-      <c r="I31" s="5" t="inlineStr">
-        <is>
-          <t>10 Oct 2026 10:40:59 AM</t>
-        </is>
-      </c>
-      <c r="J31" s="5" t="inlineStr">
-        <is>
-          <t>09 Oct 2026 12:30:31 PM</t>
-        </is>
-      </c>
-      <c r="K31" s="5" t="inlineStr">
-        <is>
-          <t>10 Oct 2026 10:40:59 AM</t>
-        </is>
-      </c>
-      <c r="L31" s="5" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M31" s="5" t="inlineStr">
-        <is>
-          <t>22h 10m</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="inlineStr">
-        <is>
-          <t>TKT1364411</t>
-        </is>
-      </c>
-      <c r="B32" s="3" t="inlineStr">
-        <is>
-          <t>Bijya Lama</t>
-        </is>
-      </c>
-      <c r="C32" s="3" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D32" s="3" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E32" s="3" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F32" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G32" s="3" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H32" s="3" t="inlineStr">
-        <is>
-          <t>Case : Wifi 6 upgrade   has been updated by Sabin Giri</t>
-        </is>
-      </c>
-      <c r="I32" s="3" t="inlineStr">
-        <is>
-          <t>10 Oct 2026 10:40:30 AM</t>
-        </is>
-      </c>
-      <c r="J32" s="3" t="inlineStr">
-        <is>
-          <t>09 Oct 2026 12:06:35 PM</t>
-        </is>
-      </c>
-      <c r="K32" s="3" t="inlineStr">
-        <is>
-          <t>10 Oct 2026 10:40:30 AM</t>
-        </is>
-      </c>
-      <c r="L32" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M32" s="3" t="inlineStr">
-        <is>
-          <t>22h 33m</t>
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>Ticket Number</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>Account Name</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>Sub Category</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Type</t>
+        </is>
+      </c>
+      <c r="G32" s="4" t="inlineStr">
+        <is>
+          <t>Employee Remark / Solution Note</t>
+        </is>
+      </c>
+      <c r="H32" s="4" t="inlineStr">
+        <is>
+          <t>Action / Transfer Remark</t>
+        </is>
+      </c>
+      <c r="I32" s="4" t="inlineStr">
+        <is>
+          <t>Assigned Date</t>
+        </is>
+      </c>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>Created Date</t>
+        </is>
+      </c>
+      <c r="K32" s="4" t="inlineStr">
+        <is>
+          <t>Last Modified Date</t>
+        </is>
+      </c>
+      <c r="L32" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Assigned)</t>
+        </is>
+      </c>
+      <c r="M32" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>TKT1357376</t>
+          <t>TKT1364446</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>Goma Adhikari</t>
+          <t>Jeet Bahadur Basnet</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
@@ -8955,22 +9681,22 @@
       </c>
       <c r="H33" s="5" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 upgrade   has been updated by Sanjeev Giri</t>
+          <t>Case : upgrade wifi 6  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I33" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 10:49:43 AM</t>
+          <t>10 Oct 2026 10:40:59 AM</t>
         </is>
       </c>
       <c r="J33" s="5" t="inlineStr">
         <is>
-          <t>04 Oct 2026 08:51:00 AM</t>
+          <t>09 Oct 2026 12:30:31 PM</t>
         </is>
       </c>
       <c r="K33" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 10:49:43 AM</t>
+          <t>10 Oct 2026 10:40:59 AM</t>
         </is>
       </c>
       <c r="L33" s="5" t="inlineStr">
@@ -8980,19 +9706,19 @@
       </c>
       <c r="M33" s="5" t="inlineStr">
         <is>
-          <t>6d 1h 58m</t>
+          <t>22h 10m</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>TKT1358035</t>
+          <t>TKT1364411</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>Saurav Lamsal</t>
+          <t>Bijya Lama</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
@@ -9007,12 +9733,12 @@
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
@@ -9022,44 +9748,44 @@
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+          <t>Case : Wifi 6 upgrade   has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>04 Oct 2026 02:07:16 PM</t>
+          <t>10 Oct 2026 10:40:30 AM</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>04 Oct 2026 02:07:16 PM</t>
+          <t>09 Oct 2026 12:06:35 PM</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 11:04:09 AM</t>
+          <t>10 Oct 2026 10:40:30 AM</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t>5d 20h 56m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>5d 20h 56m</t>
+          <t>22h 33m</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>TKT1358035</t>
+          <t>TKT1357376</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>Saurav Lamsal</t>
+          <t>Goma Adhikari</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
@@ -9074,12 +9800,12 @@
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
@@ -9089,44 +9815,44 @@
       </c>
       <c r="H35" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+          <t>Case : Wifi 6 upgrade   has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I35" s="5" t="inlineStr">
         <is>
-          <t>04 Oct 2026 02:07:16 PM</t>
+          <t>10 Oct 2026 10:49:43 AM</t>
         </is>
       </c>
       <c r="J35" s="5" t="inlineStr">
         <is>
-          <t>04 Oct 2026 02:07:16 PM</t>
+          <t>04 Oct 2026 08:51:00 AM</t>
         </is>
       </c>
       <c r="K35" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 11:04:09 AM</t>
+          <t>10 Oct 2026 10:49:43 AM</t>
         </is>
       </c>
       <c r="L35" s="5" t="inlineStr">
         <is>
-          <t>5d 20h 56m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M35" s="5" t="inlineStr">
         <is>
-          <t>5d 20h 56m</t>
+          <t>6d 1h 58m</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>TKT1364756</t>
+          <t>TKT1358035</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>New Assist Traders</t>
+          <t>Saurav Lamsal</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
@@ -9141,12 +9867,12 @@
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
@@ -9156,44 +9882,44 @@
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Chandramani Tharu</t>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 11:15:36 AM</t>
+          <t>04 Oct 2026 02:07:16 PM</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>09 Oct 2026 04:33:35 PM</t>
+          <t>04 Oct 2026 02:07:16 PM</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 11:15:36 AM</t>
+          <t>10 Oct 2026 11:04:09 AM</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>5d 20h 56m</t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>18h 42m</t>
+          <t>5d 20h 56m</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>TKT1358080</t>
+          <t>TKT1358035</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>Baburaja Maharjan</t>
+          <t>Saurav Lamsal</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
@@ -9208,12 +9934,12 @@
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
@@ -9223,44 +9949,44 @@
       </c>
       <c r="H37" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Chandramani Tharu</t>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I37" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 11:13:31 AM</t>
+          <t>04 Oct 2026 02:07:16 PM</t>
         </is>
       </c>
       <c r="J37" s="5" t="inlineStr">
         <is>
-          <t>04 Oct 2026 02:29:39 PM</t>
+          <t>04 Oct 2026 02:07:16 PM</t>
         </is>
       </c>
       <c r="K37" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 11:13:31 AM</t>
+          <t>10 Oct 2026 11:04:09 AM</t>
         </is>
       </c>
       <c r="L37" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>5d 20h 56m</t>
         </is>
       </c>
       <c r="M37" s="5" t="inlineStr">
         <is>
-          <t>5d 20h 43m</t>
+          <t>5d 20h 56m</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>TKT1359556</t>
+          <t>TKT1364756</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Puspa KC</t>
+          <t>New Assist Traders</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
@@ -9290,22 +10016,22 @@
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>Case : router upgrade  has been updated by Sabin Giri</t>
+          <t>Case : wifi6  has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 11:23:36 AM</t>
+          <t>10 Oct 2026 11:15:36 AM</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>05 Oct 2026 03:34:34 PM</t>
+          <t>09 Oct 2026 04:33:35 PM</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 11:23:36 AM</t>
+          <t>10 Oct 2026 11:15:36 AM</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
@@ -9315,19 +10041,19 @@
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>4d 19h 49m</t>
+          <t>18h 42m</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>TKT1365031</t>
+          <t>TKT1358080</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>Prem Kumar Shrestha</t>
+          <t>Baburaja Maharjan</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
@@ -9357,22 +10083,22 @@
       </c>
       <c r="H39" s="5" t="inlineStr">
         <is>
-          <t>Case : WiFi 6   has been updated by Sanjeev Giri</t>
+          <t>Case : wifi6  has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I39" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 11:41:30 AM</t>
+          <t>10 Oct 2026 11:13:31 AM</t>
         </is>
       </c>
       <c r="J39" s="5" t="inlineStr">
         <is>
-          <t>09 Oct 2026 09:56:52 PM</t>
+          <t>04 Oct 2026 02:29:39 PM</t>
         </is>
       </c>
       <c r="K39" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 11:41:30 AM</t>
+          <t>10 Oct 2026 11:13:31 AM</t>
         </is>
       </c>
       <c r="L39" s="5" t="inlineStr">
@@ -9382,19 +10108,19 @@
       </c>
       <c r="M39" s="5" t="inlineStr">
         <is>
-          <t>13h 44m</t>
+          <t>5d 20h 43m</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>TKT1362058</t>
+          <t>TKT1359556</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Gyan Chiraniya</t>
+          <t>Puspa KC</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
@@ -9409,12 +10135,12 @@
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
@@ -9424,44 +10150,44 @@
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>Case : For upgradation to wifi6   has been updated by Ajit Shrestha</t>
+          <t>Case : router upgrade  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t>07 Oct 2026 02:43:23 PM</t>
+          <t>10 Oct 2026 11:23:36 AM</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>07 Oct 2026 02:43:23 PM</t>
+          <t>05 Oct 2026 03:34:34 PM</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 11:36:00 AM</t>
+          <t>10 Oct 2026 11:23:36 AM</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t>2d 20h 52m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>2d 20h 52m</t>
+          <t>4d 19h 49m</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>TKT1362058</t>
+          <t>TKT1365031</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>Gyan Chiraniya</t>
+          <t>Prem Kumar Shrestha</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
@@ -9476,12 +10202,12 @@
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr">
@@ -9491,44 +10217,44 @@
       </c>
       <c r="H41" s="5" t="inlineStr">
         <is>
-          <t>Case : For upgradation to wifi6   has been updated by Ajit Shrestha</t>
+          <t>Case : WiFi 6   has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I41" s="5" t="inlineStr">
         <is>
-          <t>07 Oct 2026 02:43:23 PM</t>
+          <t>10 Oct 2026 11:41:30 AM</t>
         </is>
       </c>
       <c r="J41" s="5" t="inlineStr">
         <is>
-          <t>07 Oct 2026 02:43:23 PM</t>
+          <t>09 Oct 2026 09:56:52 PM</t>
         </is>
       </c>
       <c r="K41" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 11:36:00 AM</t>
+          <t>10 Oct 2026 11:41:30 AM</t>
         </is>
       </c>
       <c r="L41" s="5" t="inlineStr">
         <is>
-          <t>2d 20h 52m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M41" s="5" t="inlineStr">
         <is>
-          <t>2d 20h 52m</t>
+          <t>13h 44m</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>TKT1362055</t>
+          <t>TKT1362058</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>Ravi Shahi</t>
+          <t>Gyan Chiraniya</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
@@ -9543,12 +10269,12 @@
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
@@ -9558,64 +10284,64 @@
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t>Case : For upgradation to wifi6   has been updated by Chandramani Tharu</t>
+          <t>Case : For upgradation to wifi6   has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 11:53:17 AM</t>
+          <t>07 Oct 2026 02:43:23 PM</t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>07 Oct 2026 02:42:05 PM</t>
+          <t>07 Oct 2026 02:43:23 PM</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 11:53:17 AM</t>
+          <t>10 Oct 2026 11:36:00 AM</t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>2d 20h 52m</t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t>2d 21h 11m</t>
+          <t>2d 20h 52m</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>TKT1364261</t>
+          <t>TKT1362058</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>Niratna manandhar</t>
+          <t>Gyan Chiraniya</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>NETTV-Welcome Screen Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr">
@@ -9625,44 +10351,44 @@
       </c>
       <c r="H43" s="5" t="inlineStr">
         <is>
-          <t>Case : NETTV issue  has been updated by Ajit Shrestha</t>
+          <t>Case : For upgradation to wifi6   has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I43" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 12:00:52 PM</t>
+          <t>07 Oct 2026 02:43:23 PM</t>
         </is>
       </c>
       <c r="J43" s="5" t="inlineStr">
         <is>
-          <t>09 Oct 2026 10:23:09 AM</t>
+          <t>07 Oct 2026 02:43:23 PM</t>
         </is>
       </c>
       <c r="K43" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 12:00:52 PM</t>
+          <t>10 Oct 2026 11:36:00 AM</t>
         </is>
       </c>
       <c r="L43" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>2d 20h 52m</t>
         </is>
       </c>
       <c r="M43" s="5" t="inlineStr">
         <is>
-          <t>1d 1h 37m</t>
+          <t>2d 20h 52m</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>TKT1360378</t>
+          <t>TKT1362055</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>Maheshwor Maharjan</t>
+          <t>Ravi Shahi</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
@@ -9692,22 +10418,22 @@
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t>Case :   has been updated by Sanjeev Giri</t>
+          <t>Case : For upgradation to wifi6   has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 12:04:10 PM</t>
+          <t>10 Oct 2026 11:53:17 AM</t>
         </is>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>06 Oct 2026 10:49:38 AM</t>
+          <t>07 Oct 2026 02:42:05 PM</t>
         </is>
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 12:04:10 PM</t>
+          <t>10 Oct 2026 11:53:17 AM</t>
         </is>
       </c>
       <c r="L44" s="3" t="inlineStr">
@@ -9717,29 +10443,29 @@
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t>4d 1h 14m</t>
+          <t>2d 21h 11m</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>TKT1365280</t>
+          <t>TKT1364261</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>Atul Ali</t>
+          <t>Niratna manandhar</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>Wi-Fi Range</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>Low Wi-Fi Range on both band</t>
+          <t>NETTV-Welcome Screen Issue</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -9759,22 +10485,22 @@
       </c>
       <c r="H45" s="5" t="inlineStr">
         <is>
-          <t>Case : low wifi range issue  has been updated by Sabin Giri</t>
+          <t>Case : NETTV issue  has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I45" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 12:06:57 PM</t>
+          <t>10 Oct 2026 12:00:52 PM</t>
         </is>
       </c>
       <c r="J45" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 10:00:04 AM</t>
+          <t>09 Oct 2026 10:23:09 AM</t>
         </is>
       </c>
       <c r="K45" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 12:06:57 PM</t>
+          <t>10 Oct 2026 12:00:52 PM</t>
         </is>
       </c>
       <c r="L45" s="5" t="inlineStr">
@@ -9784,19 +10510,19 @@
       </c>
       <c r="M45" s="5" t="inlineStr">
         <is>
-          <t>2h 6m</t>
+          <t>1d 1h 37m</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>TKT1364910</t>
+          <t>TKT1360378</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>Ayush Duwal</t>
+          <t>Maheshwor Maharjan</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
@@ -9826,22 +10552,22 @@
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Sabin Giri</t>
+          <t>Case :   has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 12:30:17 PM</t>
+          <t>10 Oct 2026 12:04:10 PM</t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>09 Oct 2026 06:57:31 PM</t>
+          <t>06 Oct 2026 10:49:38 AM</t>
         </is>
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 12:30:17 PM</t>
+          <t>10 Oct 2026 12:04:10 PM</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
@@ -9851,29 +10577,29 @@
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t>17h 32m</t>
+          <t>4d 1h 14m</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>TKT1364848</t>
+          <t>TKT1365280</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>Mayanka Kirana Store</t>
+          <t>Atul Ali</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>Wi-Fi Range</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>Low Wi-Fi Range on both band</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -9893,22 +10619,22 @@
       </c>
       <c r="H47" s="5" t="inlineStr">
         <is>
-          <t>Case : no light blinking   has been updated by Sabin Giri</t>
+          <t>Case : low wifi range issue  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I47" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 12:35:23 PM</t>
+          <t>10 Oct 2026 12:06:57 PM</t>
         </is>
       </c>
       <c r="J47" s="5" t="inlineStr">
         <is>
-          <t>09 Oct 2026 05:45:00 PM</t>
+          <t>10 Oct 2026 10:00:04 AM</t>
         </is>
       </c>
       <c r="K47" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 12:35:23 PM</t>
+          <t>10 Oct 2026 12:06:57 PM</t>
         </is>
       </c>
       <c r="L47" s="5" t="inlineStr">
@@ -9918,19 +10644,19 @@
       </c>
       <c r="M47" s="5" t="inlineStr">
         <is>
-          <t>18h 50m</t>
+          <t>2h 6m</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>TKT1358952</t>
+          <t>TKT1364910</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>Sanjay Dangol</t>
+          <t>Ayush Duwal</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
@@ -9960,22 +10686,22 @@
       </c>
       <c r="H48" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Sanjeev Giri</t>
+          <t>Case : wifi6  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I48" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 12:34:52 PM</t>
+          <t>10 Oct 2026 12:30:17 PM</t>
         </is>
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>05 Oct 2026 09:20:16 AM</t>
+          <t>09 Oct 2026 06:57:31 PM</t>
         </is>
       </c>
       <c r="K48" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 12:35:24 PM</t>
+          <t>10 Oct 2026 12:30:17 PM</t>
         </is>
       </c>
       <c r="L48" s="3" t="inlineStr">
@@ -9985,29 +10711,29 @@
       </c>
       <c r="M48" s="3" t="inlineStr">
         <is>
-          <t>5d 3h 15m</t>
+          <t>17h 32m</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>TKT1358952</t>
+          <t>TKT1364848</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>Sanjay Dangol</t>
+          <t>Mayanka Kirana Store</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
@@ -10027,22 +10753,22 @@
       </c>
       <c r="H49" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Sanjeev Giri</t>
+          <t>Case : no light blinking   has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I49" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 12:34:52 PM</t>
+          <t>10 Oct 2026 12:35:23 PM</t>
         </is>
       </c>
       <c r="J49" s="5" t="inlineStr">
         <is>
-          <t>05 Oct 2026 09:20:16 AM</t>
+          <t>09 Oct 2026 05:45:00 PM</t>
         </is>
       </c>
       <c r="K49" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 12:35:24 PM</t>
+          <t>10 Oct 2026 12:35:23 PM</t>
         </is>
       </c>
       <c r="L49" s="5" t="inlineStr">
@@ -10052,19 +10778,19 @@
       </c>
       <c r="M49" s="5" t="inlineStr">
         <is>
-          <t>5d 3h 15m</t>
+          <t>18h 50m</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>TKT1362114</t>
+          <t>TKT1358952</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>Punam shah</t>
+          <t>Sanjay Dangol</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
@@ -10094,22 +10820,22 @@
       </c>
       <c r="H50" s="3" t="inlineStr">
         <is>
-          <t>Case : Wi-Fi 6  has been updated by Sanjeev Giri</t>
+          <t>Case : wifi6  has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I50" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 12:34:03 PM</t>
+          <t>10 Oct 2026 12:34:52 PM</t>
         </is>
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
-          <t>07 Oct 2026 03:17:23 PM</t>
+          <t>05 Oct 2026 09:20:16 AM</t>
         </is>
       </c>
       <c r="K50" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 12:34:03 PM</t>
+          <t>10 Oct 2026 12:35:24 PM</t>
         </is>
       </c>
       <c r="L50" s="3" t="inlineStr">
@@ -10119,19 +10845,19 @@
       </c>
       <c r="M50" s="3" t="inlineStr">
         <is>
-          <t>2d 21h 16m</t>
+          <t>5d 3h 15m</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>TKT1364639</t>
+          <t>TKT1358952</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>Anil Pradhan</t>
+          <t>Sanjay Dangol</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
@@ -10146,12 +10872,12 @@
       </c>
       <c r="E51" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F51" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G51" s="5" t="inlineStr">
@@ -10161,44 +10887,44 @@
       </c>
       <c r="H51" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6 router upgrade   has been updated by Ajit Shrestha</t>
+          <t>Case : wifi6  has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I51" s="5" t="inlineStr">
         <is>
-          <t>09 Oct 2026 03:05:33 PM</t>
+          <t>10 Oct 2026 12:34:52 PM</t>
         </is>
       </c>
       <c r="J51" s="5" t="inlineStr">
         <is>
-          <t>09 Oct 2026 03:05:33 PM</t>
+          <t>05 Oct 2026 09:20:16 AM</t>
         </is>
       </c>
       <c r="K51" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 12:50:22 PM</t>
+          <t>10 Oct 2026 12:35:24 PM</t>
         </is>
       </c>
       <c r="L51" s="5" t="inlineStr">
         <is>
-          <t>21h 44m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M51" s="5" t="inlineStr">
         <is>
-          <t>21h 44m</t>
+          <t>5d 3h 15m</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>TKT1359613</t>
+          <t>TKT1362114</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>lok bahadur malla</t>
+          <t>Punam shah</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
@@ -10233,17 +10959,17 @@
       </c>
       <c r="I52" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 01:46:58 PM</t>
+          <t>10 Oct 2026 12:34:03 PM</t>
         </is>
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
-          <t>05 Oct 2026 04:13:23 PM</t>
+          <t>07 Oct 2026 03:17:23 PM</t>
         </is>
       </c>
       <c r="K52" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 01:46:58 PM</t>
+          <t>10 Oct 2026 12:34:03 PM</t>
         </is>
       </c>
       <c r="L52" s="3" t="inlineStr">
@@ -10253,19 +10979,19 @@
       </c>
       <c r="M52" s="3" t="inlineStr">
         <is>
-          <t>4d 21h 33m</t>
+          <t>2d 21h 16m</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>TKT1363352</t>
+          <t>TKT1364639</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>Rajan Dawadi</t>
+          <t>Anil Pradhan</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
@@ -10295,44 +11021,44 @@
       </c>
       <c r="H53" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Ajit Shrestha</t>
+          <t>Case : wifi 6 router upgrade   has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I53" s="5" t="inlineStr">
         <is>
-          <t>08 Oct 2026 01:21:13 PM</t>
+          <t>09 Oct 2026 03:05:33 PM</t>
         </is>
       </c>
       <c r="J53" s="5" t="inlineStr">
         <is>
-          <t>08 Oct 2026 01:21:13 PM</t>
+          <t>09 Oct 2026 03:05:33 PM</t>
         </is>
       </c>
       <c r="K53" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 02:14:45 PM</t>
+          <t>10 Oct 2026 12:50:22 PM</t>
         </is>
       </c>
       <c r="L53" s="5" t="inlineStr">
         <is>
-          <t>2d 53m</t>
+          <t>21h 44m</t>
         </is>
       </c>
       <c r="M53" s="5" t="inlineStr">
         <is>
-          <t>2d 53m</t>
+          <t>21h 44m</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>TKT1365302</t>
+          <t>TKT1359613</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>Kritika Sah</t>
+          <t>lok bahadur malla</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
@@ -10362,22 +11088,22 @@
       </c>
       <c r="H54" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+          <t>Case : Wi-Fi 6  has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I54" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 02:06:16 PM</t>
+          <t>10 Oct 2026 01:46:58 PM</t>
         </is>
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 10:19:45 AM</t>
+          <t>05 Oct 2026 04:13:23 PM</t>
         </is>
       </c>
       <c r="K54" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 02:06:16 PM</t>
+          <t>10 Oct 2026 01:46:58 PM</t>
         </is>
       </c>
       <c r="L54" s="3" t="inlineStr">
@@ -10387,39 +11113,39 @@
       </c>
       <c r="M54" s="3" t="inlineStr">
         <is>
-          <t>3h 46m</t>
+          <t>4d 21h 33m</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>TKT1365176</t>
+          <t>TKT1363352</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>Aafnai Deal Online Shopping Center Pvt Ltd</t>
+          <t>Rajan Dawadi</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>Router Adaptor damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F55" s="5" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G55" s="5" t="inlineStr">
@@ -10429,44 +11155,44 @@
       </c>
       <c r="H55" s="5" t="inlineStr">
         <is>
-          <t>Case : Router faulty   has been updated by Ajit Shrestha</t>
+          <t>Case : wifi6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I55" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 02:40:00 PM</t>
+          <t>08 Oct 2026 01:21:13 PM</t>
         </is>
       </c>
       <c r="J55" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 08:51:05 AM</t>
+          <t>08 Oct 2026 01:21:13 PM</t>
         </is>
       </c>
       <c r="K55" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 02:40:00 PM</t>
+          <t>10 Oct 2026 02:14:45 PM</t>
         </is>
       </c>
       <c r="L55" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>2d 53m</t>
         </is>
       </c>
       <c r="M55" s="5" t="inlineStr">
         <is>
-          <t>5h 48m</t>
+          <t>2d 53m</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>TKT1362110</t>
+          <t>TKT1365302</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>Prem Bahadur Karki</t>
+          <t>Kritika Sah</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
@@ -10481,59 +11207,59 @@
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F56" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>Case : WiFi 6  has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H56" s="3" t="inlineStr">
         <is>
-          <t>Case : WiFi 6  has been updated by Ajit Shrestha</t>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I56" s="3" t="inlineStr">
         <is>
-          <t>07 Oct 2026 03:16:15 PM</t>
+          <t>10 Oct 2026 02:06:16 PM</t>
         </is>
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
-          <t>07 Oct 2026 03:16:15 PM</t>
+          <t>10 Oct 2026 10:19:45 AM</t>
         </is>
       </c>
       <c r="K56" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 03:12:56 PM</t>
+          <t>10 Oct 2026 02:06:16 PM</t>
         </is>
       </c>
       <c r="L56" s="3" t="inlineStr">
         <is>
-          <t>2d 23h 56m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M56" s="3" t="inlineStr">
         <is>
-          <t>2d 23h 56m</t>
+          <t>3h 46m</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>TKT1364906</t>
+          <t>TKT1365176</t>
         </is>
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>Pasang sherpa</t>
+          <t>Aafnai Deal Online Shopping Center Pvt Ltd</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
@@ -10543,7 +11269,7 @@
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>Router Adaptor damage Issue</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
@@ -10558,27 +11284,27 @@
       </c>
       <c r="G57" s="5" t="inlineStr">
         <is>
-          <t>Case : iptv issue  has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H57" s="5" t="inlineStr">
         <is>
-          <t>Case : iptv issue  has been updated by Sanjeev Giri</t>
+          <t>Case : Router faulty   has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I57" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 03:41:05 PM</t>
+          <t>10 Oct 2026 02:40:00 PM</t>
         </is>
       </c>
       <c r="J57" s="5" t="inlineStr">
         <is>
-          <t>09 Oct 2026 06:55:03 PM</t>
+          <t>10 Oct 2026 08:51:05 AM</t>
         </is>
       </c>
       <c r="K57" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 03:41:05 PM</t>
+          <t>10 Oct 2026 02:40:00 PM</t>
         </is>
       </c>
       <c r="L57" s="5" t="inlineStr">
@@ -10588,19 +11314,19 @@
       </c>
       <c r="M57" s="5" t="inlineStr">
         <is>
-          <t>20h 46m</t>
+          <t>5h 48m</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>TKT1365415</t>
+          <t>TKT1362110</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>Sarmila Sangasarar</t>
+          <t>Prem Bahadur Karki</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
@@ -10615,114 +11341,449 @@
       </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6 Router   has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H58" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6 Router   has been updated by Sanjeev Giri</t>
+          <t>Case : WiFi 6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I58" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 03:38:34 PM</t>
+          <t>07 Oct 2026 03:16:15 PM</t>
         </is>
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 11:51:02 AM</t>
+          <t>07 Oct 2026 03:16:15 PM</t>
         </is>
       </c>
       <c r="K58" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 03:38:34 PM</t>
+          <t>10 Oct 2026 03:12:56 PM</t>
         </is>
       </c>
       <c r="L58" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>2d 23h 56m</t>
         </is>
       </c>
       <c r="M58" s="3" t="inlineStr">
         <is>
-          <t>3h 47m</t>
+          <t>2d 23h 56m</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
+          <t>TKT1364906</t>
+        </is>
+      </c>
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>Pasang sherpa</t>
+        </is>
+      </c>
+      <c r="C59" s="5" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="D59" s="5" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="E59" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F59" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G59" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H59" s="5" t="inlineStr">
+        <is>
+          <t>Case : iptv issue  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I59" s="5" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 03:41:05 PM</t>
+        </is>
+      </c>
+      <c r="J59" s="5" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 06:55:03 PM</t>
+        </is>
+      </c>
+      <c r="K59" s="5" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 03:41:05 PM</t>
+        </is>
+      </c>
+      <c r="L59" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M59" s="5" t="inlineStr">
+        <is>
+          <t>20h 46m</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>TKT1365415</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>Sarmila Sangasarar</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E60" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F60" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G60" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H60" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 Router   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I60" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 03:38:34 PM</t>
+        </is>
+      </c>
+      <c r="J60" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 11:51:02 AM</t>
+        </is>
+      </c>
+      <c r="K60" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 03:38:34 PM</t>
+        </is>
+      </c>
+      <c r="L60" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M60" s="3" t="inlineStr">
+        <is>
+          <t>3h 47m</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
           <t>TKT1365328</t>
         </is>
       </c>
-      <c r="B59" s="5" t="inlineStr">
+      <c r="B61" s="5" t="inlineStr">
         <is>
           <t>Bishal Shrestha</t>
         </is>
       </c>
-      <c r="C59" s="5" t="inlineStr">
+      <c r="C61" s="5" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="D59" s="5" t="inlineStr">
+      <c r="D61" s="5" t="inlineStr">
         <is>
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="E59" s="5" t="inlineStr">
+      <c r="E61" s="5" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="F59" s="5" t="inlineStr">
+      <c r="F61" s="5" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="G59" s="5" t="inlineStr">
+      <c r="G61" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H61" s="5" t="inlineStr">
         <is>
           <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
         </is>
       </c>
-      <c r="H59" s="5" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
-        </is>
-      </c>
-      <c r="I59" s="5" t="inlineStr">
+      <c r="I61" s="5" t="inlineStr">
         <is>
           <t>10 Oct 2026 03:04:54 PM</t>
         </is>
       </c>
-      <c r="J59" s="5" t="inlineStr">
+      <c r="J61" s="5" t="inlineStr">
         <is>
           <t>10 Oct 2026 10:37:42 AM</t>
         </is>
       </c>
-      <c r="K59" s="5" t="inlineStr">
+      <c r="K61" s="5" t="inlineStr">
         <is>
           <t>10 Oct 2026 03:04:54 PM</t>
         </is>
       </c>
-      <c r="L59" s="5" t="inlineStr">
+      <c r="L61" s="5" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="M59" s="5" t="inlineStr">
+      <c r="M61" s="5" t="inlineStr">
         <is>
           <t>4h 27m</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>TKT1364260</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>Suresh Raut</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="D62" s="3" t="inlineStr">
+        <is>
+          <t>SKYCOM-Welcome Screen Issue</t>
+        </is>
+      </c>
+      <c r="E62" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F62" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G62" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV issue  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="H62" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV issue  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I62" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 03:41:47 PM</t>
+        </is>
+      </c>
+      <c r="J62" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 10:21:21 AM</t>
+        </is>
+      </c>
+      <c r="K62" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 03:41:47 PM</t>
+        </is>
+      </c>
+      <c r="L62" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M62" s="3" t="inlineStr">
+        <is>
+          <t>1d 5h 20m</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="5" t="inlineStr">
+        <is>
+          <t>TKT1364260</t>
+        </is>
+      </c>
+      <c r="B63" s="5" t="inlineStr">
+        <is>
+          <t>Suresh Raut</t>
+        </is>
+      </c>
+      <c r="C63" s="5" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="D63" s="5" t="inlineStr">
+        <is>
+          <t>SKYCOM-Welcome Screen Issue</t>
+        </is>
+      </c>
+      <c r="E63" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F63" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G63" s="5" t="inlineStr">
+        <is>
+          <t>Case : frequent disconnection issue   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="H63" s="5" t="inlineStr">
+        <is>
+          <t>Case : frequent disconnection issue   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I63" s="5" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 03:41:47 PM</t>
+        </is>
+      </c>
+      <c r="J63" s="5" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 10:21:21 AM</t>
+        </is>
+      </c>
+      <c r="K63" s="5" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 03:41:47 PM</t>
+        </is>
+      </c>
+      <c r="L63" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M63" s="5" t="inlineStr">
+        <is>
+          <t>1d 5h 20m</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t>TKT1359002</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>Dinesh Thakur</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D64" s="3" t="inlineStr">
+        <is>
+          <t>Router placement CR</t>
+        </is>
+      </c>
+      <c r="E64" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F64" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G64" s="3" t="inlineStr">
+        <is>
+          <t>Case : router change   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="H64" s="3" t="inlineStr">
+        <is>
+          <t>Case : router change   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I64" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 03:27:45 PM</t>
+        </is>
+      </c>
+      <c r="J64" s="3" t="inlineStr">
+        <is>
+          <t>05 Oct 2026 10:04:47 AM</t>
+        </is>
+      </c>
+      <c r="K64" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 03:34:04 PM</t>
+        </is>
+      </c>
+      <c r="L64" s="3" t="inlineStr">
+        <is>
+          <t>6m</t>
+        </is>
+      </c>
+      <c r="M64" s="3" t="inlineStr">
+        <is>
+          <t>5d 5h 29m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_10_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_10_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW44"/>
+  <dimension ref="A1:AW45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -501,7 +501,7 @@
     <col width="14" customWidth="1" min="13" max="13"/>
     <col width="40" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
-    <col width="32" customWidth="1" min="16" max="16"/>
+    <col width="34" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
     <col width="26" customWidth="1" min="18" max="18"/>
     <col width="37" customWidth="1" min="19" max="19"/>
@@ -511,7 +511,7 @@
     <col width="26" customWidth="1" min="23" max="23"/>
     <col width="29" customWidth="1" min="24" max="24"/>
     <col width="12" customWidth="1" min="25" max="25"/>
-    <col width="32" customWidth="1" min="26" max="26"/>
+    <col width="34" customWidth="1" min="26" max="26"/>
     <col width="19" customWidth="1" min="27" max="27"/>
     <col width="17" customWidth="1" min="28" max="28"/>
     <col width="11" customWidth="1" min="29" max="29"/>
@@ -8282,20 +8282,14 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="M41" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="M41" s="3" t="inlineStr"/>
       <c r="N41" s="3" t="inlineStr">
         <is>
           <t>Suresh Raut</t>
         </is>
       </c>
-      <c r="O41" s="3" t="inlineStr">
-        <is>
-          <t>9747744379</t>
-        </is>
+      <c r="O41" s="3" t="n">
+        <v>9747744379</v>
       </c>
       <c r="P41" s="3" t="inlineStr">
         <is>
@@ -8389,25 +8383,21 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN41" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN41" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO41" s="3" t="inlineStr">
         <is>
           <t>CDB423</t>
         </is>
       </c>
-      <c r="AP41" s="3" t="inlineStr">
-        <is>
-          <t>85.301988</t>
-        </is>
+      <c r="AP41" s="3" t="n">
+        <v>85.30198799999999</v>
       </c>
       <c r="AQ41" s="3" t="inlineStr"/>
       <c r="AR41" s="3" t="inlineStr">
         <is>
-          <t>Case : IPTV issue  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS41" s="3" t="inlineStr">
@@ -8493,20 +8483,14 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="M42" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="M42" s="3" t="inlineStr"/>
       <c r="N42" s="3" t="inlineStr">
         <is>
           <t>Suresh Raut</t>
         </is>
       </c>
-      <c r="O42" s="3" t="inlineStr">
-        <is>
-          <t>9747744379</t>
-        </is>
+      <c r="O42" s="3" t="n">
+        <v>9747744379</v>
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
@@ -8600,25 +8584,21 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN42" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN42" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO42" s="3" t="inlineStr">
         <is>
           <t>CDB423</t>
         </is>
       </c>
-      <c r="AP42" s="3" t="inlineStr">
-        <is>
-          <t>85.301988</t>
-        </is>
+      <c r="AP42" s="3" t="n">
+        <v>85.30198799999999</v>
       </c>
       <c r="AQ42" s="3" t="inlineStr"/>
       <c r="AR42" s="3" t="inlineStr">
         <is>
-          <t>Case : frequent disconnection issue   has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS42" s="3" t="inlineStr">
@@ -8714,10 +8694,8 @@
           <t>Pankaj kumar jha</t>
         </is>
       </c>
-      <c r="O43" s="3" t="inlineStr">
-        <is>
-          <t>9849680028</t>
-        </is>
+      <c r="O43" s="3" t="n">
+        <v>9849680028</v>
       </c>
       <c r="P43" s="3" t="inlineStr">
         <is>
@@ -8807,10 +8785,8 @@
           <t>Rikesh Shrestha</t>
         </is>
       </c>
-      <c r="AN43" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN43" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO43" s="3" t="inlineStr">
         <is>
@@ -8821,7 +8797,7 @@
       <c r="AQ43" s="3" t="inlineStr"/>
       <c r="AR43" s="3" t="inlineStr">
         <is>
-          <t>Case : router change   has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS43" s="3" t="inlineStr">
@@ -8917,10 +8893,8 @@
           <t>Ashutosh Regmi</t>
         </is>
       </c>
-      <c r="O44" s="3" t="inlineStr">
-        <is>
-          <t>9867171444</t>
-        </is>
+      <c r="O44" s="3" t="n">
+        <v>9867171444</v>
       </c>
       <c r="P44" s="3" t="inlineStr">
         <is>
@@ -9010,50 +8984,249 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN44" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN44" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO44" s="3" t="inlineStr">
         <is>
           <t>CDB091A</t>
         </is>
       </c>
-      <c r="AP44" s="3" t="inlineStr">
-        <is>
-          <t>85.3341</t>
-        </is>
+      <c r="AP44" s="3" t="n">
+        <v>85.33410000000001</v>
       </c>
       <c r="AQ44" s="3" t="inlineStr"/>
       <c r="AR44" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS44" s="3" t="inlineStr">
+        <is>
+          <t>22h 25m</t>
+        </is>
+      </c>
+      <c r="AT44" s="3" t="inlineStr">
+        <is>
+          <t>4d 20h 23m</t>
+        </is>
+      </c>
+      <c r="AU44" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV44" s="3" t="inlineStr">
+        <is>
           <t>Case : WiFi 6  has been updated by Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AS44" s="3" t="inlineStr">
-        <is>
-          <t>22h 25m</t>
-        </is>
-      </c>
-      <c r="AT44" s="3" t="inlineStr">
-        <is>
-          <t>4d 20h 23m</t>
-        </is>
-      </c>
-      <c r="AU44" s="3" t="inlineStr">
-        <is>
-          <t>Other / In Progress (On Hold)</t>
-        </is>
-      </c>
-      <c r="AV44" s="3" t="inlineStr">
-        <is>
-          <t>Case : WiFi 6  has been updated by Chandramani Tharu</t>
-        </is>
-      </c>
       <c r="AW44" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 4:03 PM</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G45" s="3" t="inlineStr"/>
+      <c r="H45" s="3" t="inlineStr">
+        <is>
+          <t>Case : Frequent disconnection   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I45" s="3" t="inlineStr">
+        <is>
+          <t>Frequent disconnection</t>
+        </is>
+      </c>
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t>TKT1365547</t>
+        </is>
+      </c>
+      <c r="K45" s="3" t="inlineStr">
+        <is>
+          <t>Prabin Chaudhary</t>
+        </is>
+      </c>
+      <c r="L45" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M45" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N45" s="3" t="inlineStr">
+        <is>
+          <t>Prabin Chaudhary</t>
+        </is>
+      </c>
+      <c r="O45" s="3" t="inlineStr">
+        <is>
+          <t>9746625579</t>
+        </is>
+      </c>
+      <c r="P45" s="3" t="inlineStr">
+        <is>
+          <t>Frequent Internet Disconnection</t>
+        </is>
+      </c>
+      <c r="Q45" s="3" t="inlineStr"/>
+      <c r="R45" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 04:03:46 PM</t>
+        </is>
+      </c>
+      <c r="S45" s="3" t="inlineStr"/>
+      <c r="T45" s="3" t="inlineStr"/>
+      <c r="U45" s="3" t="inlineStr">
+        <is>
+          <t>KLK9746625579</t>
+        </is>
+      </c>
+      <c r="V45" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 01:31:20 PM</t>
+        </is>
+      </c>
+      <c r="W45" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 04:03:46 PM</t>
+        </is>
+      </c>
+      <c r="X45" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y45" s="3" t="inlineStr"/>
+      <c r="Z45" s="3" t="inlineStr">
+        <is>
+          <t>Frequent Internet Disconnection</t>
+        </is>
+      </c>
+      <c r="AA45" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB45" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC45" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD45" s="3" t="inlineStr"/>
+      <c r="AE45" s="3" t="inlineStr">
+        <is>
+          <t>27.72239895777987,85.29581583282115, Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF45" s="3" t="inlineStr">
+        <is>
+          <t>naomidon07@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG45" s="3" t="inlineStr">
+        <is>
+          <t>Due to Optical Power flapping</t>
+        </is>
+      </c>
+      <c r="AH45" s="3" t="inlineStr"/>
+      <c r="AI45" s="3" t="inlineStr">
+        <is>
+          <t>02:32 hour</t>
+        </is>
+      </c>
+      <c r="AJ45" s="3" t="inlineStr"/>
+      <c r="AK45" s="3" t="inlineStr"/>
+      <c r="AL45" s="3" t="inlineStr">
+        <is>
+          <t>Sudip Khadka</t>
+        </is>
+      </c>
+      <c r="AM45" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN45" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO45" s="3" t="inlineStr">
+        <is>
+          <t>CDB165</t>
+        </is>
+      </c>
+      <c r="AP45" s="3" t="inlineStr"/>
+      <c r="AQ45" s="3" t="inlineStr"/>
+      <c r="AR45" s="3" t="inlineStr">
+        <is>
+          <t>Case : Frequent disconnection   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS45" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT45" s="3" t="inlineStr">
+        <is>
+          <t>2h 32m</t>
+        </is>
+      </c>
+      <c r="AU45" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV45" s="3" t="inlineStr">
+        <is>
+          <t>Case : Frequent disconnection   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW45" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
         </is>
       </c>
     </row>
@@ -9068,13 +9241,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M64"/>
+  <dimension ref="A1:M67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
     <col width="45" customWidth="1" min="2" max="2"/>
-    <col width="33" customWidth="1" min="3" max="3"/>
-    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="33" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
     <col width="45" customWidth="1" min="7" max="7"/>
@@ -9105,7 +9278,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3">
@@ -9115,7 +9288,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4">
@@ -9126,7 +9299,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>74.4%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -9138,7 +9311,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>17h 34m</t>
+          <t>17h 2m</t>
         </is>
       </c>
     </row>
@@ -9150,7 +9323,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>2d 12h 16m</t>
+          <t>2d 10h 31m</t>
         </is>
       </c>
     </row>
@@ -9187,174 +9360,169 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Frequent Internet Disconnection</t>
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>86.2%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>86.2%</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C12" s="3" t="n">
         <v>3</v>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>Slow Internet Connection</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>Wi-Fi Range</t>
+          <t>Slow Internet Connection</t>
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr"/>
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Wi-Fi Range</t>
+        </is>
+      </c>
       <c r="B15" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr"/>
+      <c r="B16" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C15" s="5" t="n">
+      <c r="C16" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="D16" s="3" t="inlineStr">
         <is>
           <t>nan%</t>
         </is>
       </c>
     </row>
-    <row r="16"/>
-    <row r="17">
-      <c r="A17" s="6" t="inlineStr">
+    <row r="17"/>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>Total Tickets Breakdown by Category &amp; Sub Category</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>Sub Category</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>Total Scraped Tickets</t>
-        </is>
-      </c>
-      <c r="D18" s="4" t="inlineStr">
-        <is>
-          <t>Solved / Handled Count</t>
-        </is>
-      </c>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>Solution Rate %</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="B19" s="5" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="C19" s="5" t="n">
-        <v>28</v>
-      </c>
-      <c r="D19" s="5" t="n">
-        <v>24</v>
-      </c>
-      <c r="E19" s="5" t="inlineStr">
-        <is>
-          <t>85.7%</t>
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>Sub Category</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>Total Scraped Tickets</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>Solved / Handled Count</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>Solution Rate %</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Frequent Internet Disconnection</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Router placement CR</t>
+          <t>Due to Optical Power flapping</t>
         </is>
       </c>
       <c r="C20" s="3" t="n">
@@ -9372,35 +9540,35 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>85.7%</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Router Adaptor damage Issue</t>
+          <t>Router placement CR</t>
         </is>
       </c>
       <c r="C22" s="3" t="n">
@@ -9423,7 +9591,7 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="C23" s="5" t="n">
@@ -9441,35 +9609,35 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>NETTV-No internet connection in STB</t>
+          <t>Router Adaptor damage Issue</t>
         </is>
       </c>
       <c r="C24" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>NETTV-Welcome Screen Issue</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="C25" s="5" t="n">
@@ -9492,60 +9660,60 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>SKYCOM-Welcome Screen Issue</t>
+          <t>NETTV-No internet connection in STB</t>
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>Slow Internet Connection</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>Video content is Buffering</t>
+          <t>NETTV-Welcome Screen Issue</t>
         </is>
       </c>
       <c r="C27" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D27" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>Wi-Fi Range</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Low Wi-Fi Range on both band</t>
+          <t>SKYCOM-Welcome Screen Issue</t>
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
@@ -9554,238 +9722,150 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="inlineStr"/>
-      <c r="B29" s="5" t="inlineStr"/>
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
       <c r="C29" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D29" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>Wi-Fi Range</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>Low Wi-Fi Range on both band</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr"/>
+      <c r="B31" s="5" t="inlineStr"/>
+      <c r="C31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
           <t>nan%</t>
         </is>
       </c>
     </row>
-    <row r="30"/>
-    <row r="31">
-      <c r="A31" s="6" t="inlineStr">
+    <row r="32"/>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="4" t="inlineStr">
-        <is>
-          <t>Ticket Number</t>
-        </is>
-      </c>
-      <c r="B32" s="4" t="inlineStr">
-        <is>
-          <t>Account Name</t>
-        </is>
-      </c>
-      <c r="C32" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D32" s="4" t="inlineStr">
-        <is>
-          <t>Sub Category</t>
-        </is>
-      </c>
-      <c r="E32" s="4" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="F32" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Type</t>
-        </is>
-      </c>
-      <c r="G32" s="4" t="inlineStr">
-        <is>
-          <t>Employee Remark / Solution Note</t>
-        </is>
-      </c>
-      <c r="H32" s="4" t="inlineStr">
-        <is>
-          <t>Action / Transfer Remark</t>
-        </is>
-      </c>
-      <c r="I32" s="4" t="inlineStr">
-        <is>
-          <t>Assigned Date</t>
-        </is>
-      </c>
-      <c r="J32" s="4" t="inlineStr">
-        <is>
-          <t>Created Date</t>
-        </is>
-      </c>
-      <c r="K32" s="4" t="inlineStr">
-        <is>
-          <t>Last Modified Date</t>
-        </is>
-      </c>
-      <c r="L32" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Assigned)</t>
-        </is>
-      </c>
-      <c r="M32" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Created)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="5" t="inlineStr">
-        <is>
-          <t>TKT1364446</t>
-        </is>
-      </c>
-      <c r="B33" s="5" t="inlineStr">
-        <is>
-          <t>Jeet Bahadur Basnet</t>
-        </is>
-      </c>
-      <c r="C33" s="5" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D33" s="5" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E33" s="5" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F33" s="5" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G33" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H33" s="5" t="inlineStr">
-        <is>
-          <t>Case : upgrade wifi 6  has been updated by Sabin Giri</t>
-        </is>
-      </c>
-      <c r="I33" s="5" t="inlineStr">
-        <is>
-          <t>10 Oct 2026 10:40:59 AM</t>
-        </is>
-      </c>
-      <c r="J33" s="5" t="inlineStr">
-        <is>
-          <t>09 Oct 2026 12:30:31 PM</t>
-        </is>
-      </c>
-      <c r="K33" s="5" t="inlineStr">
-        <is>
-          <t>10 Oct 2026 10:40:59 AM</t>
-        </is>
-      </c>
-      <c r="L33" s="5" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M33" s="5" t="inlineStr">
-        <is>
-          <t>22h 10m</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="inlineStr">
-        <is>
-          <t>TKT1364411</t>
-        </is>
-      </c>
-      <c r="B34" s="3" t="inlineStr">
-        <is>
-          <t>Bijya Lama</t>
-        </is>
-      </c>
-      <c r="C34" s="3" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D34" s="3" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E34" s="3" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F34" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G34" s="3" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H34" s="3" t="inlineStr">
-        <is>
-          <t>Case : Wifi 6 upgrade   has been updated by Sabin Giri</t>
-        </is>
-      </c>
-      <c r="I34" s="3" t="inlineStr">
-        <is>
-          <t>10 Oct 2026 10:40:30 AM</t>
-        </is>
-      </c>
-      <c r="J34" s="3" t="inlineStr">
-        <is>
-          <t>09 Oct 2026 12:06:35 PM</t>
-        </is>
-      </c>
-      <c r="K34" s="3" t="inlineStr">
-        <is>
-          <t>10 Oct 2026 10:40:30 AM</t>
-        </is>
-      </c>
-      <c r="L34" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M34" s="3" t="inlineStr">
-        <is>
-          <t>22h 33m</t>
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>Ticket Number</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>Account Name</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>Sub Category</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Type</t>
+        </is>
+      </c>
+      <c r="G34" s="4" t="inlineStr">
+        <is>
+          <t>Employee Remark / Solution Note</t>
+        </is>
+      </c>
+      <c r="H34" s="4" t="inlineStr">
+        <is>
+          <t>Action / Transfer Remark</t>
+        </is>
+      </c>
+      <c r="I34" s="4" t="inlineStr">
+        <is>
+          <t>Assigned Date</t>
+        </is>
+      </c>
+      <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t>Created Date</t>
+        </is>
+      </c>
+      <c r="K34" s="4" t="inlineStr">
+        <is>
+          <t>Last Modified Date</t>
+        </is>
+      </c>
+      <c r="L34" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Assigned)</t>
+        </is>
+      </c>
+      <c r="M34" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>TKT1357376</t>
+          <t>TKT1364446</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>Goma Adhikari</t>
+          <t>Jeet Bahadur Basnet</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
@@ -9815,22 +9895,22 @@
       </c>
       <c r="H35" s="5" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 upgrade   has been updated by Sanjeev Giri</t>
+          <t>Case : upgrade wifi 6  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I35" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 10:49:43 AM</t>
+          <t>10 Oct 2026 10:40:59 AM</t>
         </is>
       </c>
       <c r="J35" s="5" t="inlineStr">
         <is>
-          <t>04 Oct 2026 08:51:00 AM</t>
+          <t>09 Oct 2026 12:30:31 PM</t>
         </is>
       </c>
       <c r="K35" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 10:49:43 AM</t>
+          <t>10 Oct 2026 10:40:59 AM</t>
         </is>
       </c>
       <c r="L35" s="5" t="inlineStr">
@@ -9840,19 +9920,19 @@
       </c>
       <c r="M35" s="5" t="inlineStr">
         <is>
-          <t>6d 1h 58m</t>
+          <t>22h 10m</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>TKT1358035</t>
+          <t>TKT1364411</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Saurav Lamsal</t>
+          <t>Bijya Lama</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
@@ -9867,12 +9947,12 @@
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
@@ -9882,44 +9962,44 @@
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+          <t>Case : Wifi 6 upgrade   has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>04 Oct 2026 02:07:16 PM</t>
+          <t>10 Oct 2026 10:40:30 AM</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>04 Oct 2026 02:07:16 PM</t>
+          <t>09 Oct 2026 12:06:35 PM</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 11:04:09 AM</t>
+          <t>10 Oct 2026 10:40:30 AM</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t>5d 20h 56m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>5d 20h 56m</t>
+          <t>22h 33m</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>TKT1358035</t>
+          <t>TKT1357376</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>Saurav Lamsal</t>
+          <t>Goma Adhikari</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
@@ -9934,12 +10014,12 @@
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
@@ -9949,44 +10029,44 @@
       </c>
       <c r="H37" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+          <t>Case : Wifi 6 upgrade   has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I37" s="5" t="inlineStr">
         <is>
-          <t>04 Oct 2026 02:07:16 PM</t>
+          <t>10 Oct 2026 10:49:43 AM</t>
         </is>
       </c>
       <c r="J37" s="5" t="inlineStr">
         <is>
-          <t>04 Oct 2026 02:07:16 PM</t>
+          <t>04 Oct 2026 08:51:00 AM</t>
         </is>
       </c>
       <c r="K37" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 11:04:09 AM</t>
+          <t>10 Oct 2026 10:49:43 AM</t>
         </is>
       </c>
       <c r="L37" s="5" t="inlineStr">
         <is>
-          <t>5d 20h 56m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M37" s="5" t="inlineStr">
         <is>
-          <t>5d 20h 56m</t>
+          <t>6d 1h 58m</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>TKT1364756</t>
+          <t>TKT1358035</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>New Assist Traders</t>
+          <t>Saurav Lamsal</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
@@ -10001,12 +10081,12 @@
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
@@ -10016,44 +10096,44 @@
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Chandramani Tharu</t>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 11:15:36 AM</t>
+          <t>04 Oct 2026 02:07:16 PM</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>09 Oct 2026 04:33:35 PM</t>
+          <t>04 Oct 2026 02:07:16 PM</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 11:15:36 AM</t>
+          <t>10 Oct 2026 11:04:09 AM</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>5d 20h 56m</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>18h 42m</t>
+          <t>5d 20h 56m</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>TKT1358080</t>
+          <t>TKT1358035</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>Baburaja Maharjan</t>
+          <t>Saurav Lamsal</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
@@ -10068,12 +10148,12 @@
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
@@ -10083,44 +10163,44 @@
       </c>
       <c r="H39" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Chandramani Tharu</t>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I39" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 11:13:31 AM</t>
+          <t>04 Oct 2026 02:07:16 PM</t>
         </is>
       </c>
       <c r="J39" s="5" t="inlineStr">
         <is>
-          <t>04 Oct 2026 02:29:39 PM</t>
+          <t>04 Oct 2026 02:07:16 PM</t>
         </is>
       </c>
       <c r="K39" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 11:13:31 AM</t>
+          <t>10 Oct 2026 11:04:09 AM</t>
         </is>
       </c>
       <c r="L39" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>5d 20h 56m</t>
         </is>
       </c>
       <c r="M39" s="5" t="inlineStr">
         <is>
-          <t>5d 20h 43m</t>
+          <t>5d 20h 56m</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>TKT1359556</t>
+          <t>TKT1364756</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Puspa KC</t>
+          <t>New Assist Traders</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
@@ -10150,22 +10230,22 @@
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>Case : router upgrade  has been updated by Sabin Giri</t>
+          <t>Case : wifi6  has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 11:23:36 AM</t>
+          <t>10 Oct 2026 11:15:36 AM</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>05 Oct 2026 03:34:34 PM</t>
+          <t>09 Oct 2026 04:33:35 PM</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 11:23:36 AM</t>
+          <t>10 Oct 2026 11:15:36 AM</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
@@ -10175,19 +10255,19 @@
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>4d 19h 49m</t>
+          <t>18h 42m</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>TKT1365031</t>
+          <t>TKT1358080</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>Prem Kumar Shrestha</t>
+          <t>Baburaja Maharjan</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
@@ -10217,22 +10297,22 @@
       </c>
       <c r="H41" s="5" t="inlineStr">
         <is>
-          <t>Case : WiFi 6   has been updated by Sanjeev Giri</t>
+          <t>Case : wifi6  has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I41" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 11:41:30 AM</t>
+          <t>10 Oct 2026 11:13:31 AM</t>
         </is>
       </c>
       <c r="J41" s="5" t="inlineStr">
         <is>
-          <t>09 Oct 2026 09:56:52 PM</t>
+          <t>04 Oct 2026 02:29:39 PM</t>
         </is>
       </c>
       <c r="K41" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 11:41:30 AM</t>
+          <t>10 Oct 2026 11:13:31 AM</t>
         </is>
       </c>
       <c r="L41" s="5" t="inlineStr">
@@ -10242,19 +10322,19 @@
       </c>
       <c r="M41" s="5" t="inlineStr">
         <is>
-          <t>13h 44m</t>
+          <t>5d 20h 43m</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>TKT1362058</t>
+          <t>TKT1359556</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>Gyan Chiraniya</t>
+          <t>Puspa KC</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
@@ -10269,12 +10349,12 @@
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
@@ -10284,44 +10364,44 @@
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t>Case : For upgradation to wifi6   has been updated by Ajit Shrestha</t>
+          <t>Case : router upgrade  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t>07 Oct 2026 02:43:23 PM</t>
+          <t>10 Oct 2026 11:23:36 AM</t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>07 Oct 2026 02:43:23 PM</t>
+          <t>05 Oct 2026 03:34:34 PM</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 11:36:00 AM</t>
+          <t>10 Oct 2026 11:23:36 AM</t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t>2d 20h 52m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t>2d 20h 52m</t>
+          <t>4d 19h 49m</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>TKT1362058</t>
+          <t>TKT1365031</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>Gyan Chiraniya</t>
+          <t>Prem Kumar Shrestha</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
@@ -10336,12 +10416,12 @@
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr">
@@ -10351,44 +10431,44 @@
       </c>
       <c r="H43" s="5" t="inlineStr">
         <is>
-          <t>Case : For upgradation to wifi6   has been updated by Ajit Shrestha</t>
+          <t>Case : WiFi 6   has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I43" s="5" t="inlineStr">
         <is>
-          <t>07 Oct 2026 02:43:23 PM</t>
+          <t>10 Oct 2026 11:41:30 AM</t>
         </is>
       </c>
       <c r="J43" s="5" t="inlineStr">
         <is>
-          <t>07 Oct 2026 02:43:23 PM</t>
+          <t>09 Oct 2026 09:56:52 PM</t>
         </is>
       </c>
       <c r="K43" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 11:36:00 AM</t>
+          <t>10 Oct 2026 11:41:30 AM</t>
         </is>
       </c>
       <c r="L43" s="5" t="inlineStr">
         <is>
-          <t>2d 20h 52m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M43" s="5" t="inlineStr">
         <is>
-          <t>2d 20h 52m</t>
+          <t>13h 44m</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>TKT1362055</t>
+          <t>TKT1362058</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>Ravi Shahi</t>
+          <t>Gyan Chiraniya</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
@@ -10403,12 +10483,12 @@
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
@@ -10418,64 +10498,64 @@
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t>Case : For upgradation to wifi6   has been updated by Chandramani Tharu</t>
+          <t>Case : For upgradation to wifi6   has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 11:53:17 AM</t>
+          <t>07 Oct 2026 02:43:23 PM</t>
         </is>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>07 Oct 2026 02:42:05 PM</t>
+          <t>07 Oct 2026 02:43:23 PM</t>
         </is>
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 11:53:17 AM</t>
+          <t>10 Oct 2026 11:36:00 AM</t>
         </is>
       </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>2d 20h 52m</t>
         </is>
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t>2d 21h 11m</t>
+          <t>2d 20h 52m</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>TKT1364261</t>
+          <t>TKT1362058</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>Niratna manandhar</t>
+          <t>Gyan Chiraniya</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>NETTV-Welcome Screen Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G45" s="5" t="inlineStr">
@@ -10485,44 +10565,44 @@
       </c>
       <c r="H45" s="5" t="inlineStr">
         <is>
-          <t>Case : NETTV issue  has been updated by Ajit Shrestha</t>
+          <t>Case : For upgradation to wifi6   has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I45" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 12:00:52 PM</t>
+          <t>07 Oct 2026 02:43:23 PM</t>
         </is>
       </c>
       <c r="J45" s="5" t="inlineStr">
         <is>
-          <t>09 Oct 2026 10:23:09 AM</t>
+          <t>07 Oct 2026 02:43:23 PM</t>
         </is>
       </c>
       <c r="K45" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 12:00:52 PM</t>
+          <t>10 Oct 2026 11:36:00 AM</t>
         </is>
       </c>
       <c r="L45" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>2d 20h 52m</t>
         </is>
       </c>
       <c r="M45" s="5" t="inlineStr">
         <is>
-          <t>1d 1h 37m</t>
+          <t>2d 20h 52m</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>TKT1360378</t>
+          <t>TKT1362055</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>Maheshwor Maharjan</t>
+          <t>Ravi Shahi</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
@@ -10552,22 +10632,22 @@
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t>Case :   has been updated by Sanjeev Giri</t>
+          <t>Case : For upgradation to wifi6   has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 12:04:10 PM</t>
+          <t>10 Oct 2026 11:53:17 AM</t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>06 Oct 2026 10:49:38 AM</t>
+          <t>07 Oct 2026 02:42:05 PM</t>
         </is>
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 12:04:10 PM</t>
+          <t>10 Oct 2026 11:53:17 AM</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
@@ -10577,29 +10657,29 @@
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t>4d 1h 14m</t>
+          <t>2d 21h 11m</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>TKT1365280</t>
+          <t>TKT1364261</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>Atul Ali</t>
+          <t>Niratna manandhar</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>Wi-Fi Range</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>Low Wi-Fi Range on both band</t>
+          <t>NETTV-Welcome Screen Issue</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -10619,22 +10699,22 @@
       </c>
       <c r="H47" s="5" t="inlineStr">
         <is>
-          <t>Case : low wifi range issue  has been updated by Sabin Giri</t>
+          <t>Case : NETTV issue  has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I47" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 12:06:57 PM</t>
+          <t>10 Oct 2026 12:00:52 PM</t>
         </is>
       </c>
       <c r="J47" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 10:00:04 AM</t>
+          <t>09 Oct 2026 10:23:09 AM</t>
         </is>
       </c>
       <c r="K47" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 12:06:57 PM</t>
+          <t>10 Oct 2026 12:00:52 PM</t>
         </is>
       </c>
       <c r="L47" s="5" t="inlineStr">
@@ -10644,19 +10724,19 @@
       </c>
       <c r="M47" s="5" t="inlineStr">
         <is>
-          <t>2h 6m</t>
+          <t>1d 1h 37m</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>TKT1364910</t>
+          <t>TKT1360378</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>Ayush Duwal</t>
+          <t>Maheshwor Maharjan</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
@@ -10686,22 +10766,22 @@
       </c>
       <c r="H48" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Sabin Giri</t>
+          <t>Case :   has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I48" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 12:30:17 PM</t>
+          <t>10 Oct 2026 12:04:10 PM</t>
         </is>
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>09 Oct 2026 06:57:31 PM</t>
+          <t>06 Oct 2026 10:49:38 AM</t>
         </is>
       </c>
       <c r="K48" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 12:30:17 PM</t>
+          <t>10 Oct 2026 12:04:10 PM</t>
         </is>
       </c>
       <c r="L48" s="3" t="inlineStr">
@@ -10711,29 +10791,29 @@
       </c>
       <c r="M48" s="3" t="inlineStr">
         <is>
-          <t>17h 32m</t>
+          <t>4d 1h 14m</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>TKT1364848</t>
+          <t>TKT1365280</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>Mayanka Kirana Store</t>
+          <t>Atul Ali</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>Wi-Fi Range</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>Low Wi-Fi Range on both band</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
@@ -10753,22 +10833,22 @@
       </c>
       <c r="H49" s="5" t="inlineStr">
         <is>
-          <t>Case : no light blinking   has been updated by Sabin Giri</t>
+          <t>Case : low wifi range issue  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I49" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 12:35:23 PM</t>
+          <t>10 Oct 2026 12:06:57 PM</t>
         </is>
       </c>
       <c r="J49" s="5" t="inlineStr">
         <is>
-          <t>09 Oct 2026 05:45:00 PM</t>
+          <t>10 Oct 2026 10:00:04 AM</t>
         </is>
       </c>
       <c r="K49" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 12:35:23 PM</t>
+          <t>10 Oct 2026 12:06:57 PM</t>
         </is>
       </c>
       <c r="L49" s="5" t="inlineStr">
@@ -10778,19 +10858,19 @@
       </c>
       <c r="M49" s="5" t="inlineStr">
         <is>
-          <t>18h 50m</t>
+          <t>2h 6m</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>TKT1358952</t>
+          <t>TKT1364910</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>Sanjay Dangol</t>
+          <t>Ayush Duwal</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
@@ -10820,22 +10900,22 @@
       </c>
       <c r="H50" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Sanjeev Giri</t>
+          <t>Case : wifi6  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I50" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 12:34:52 PM</t>
+          <t>10 Oct 2026 12:30:17 PM</t>
         </is>
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
-          <t>05 Oct 2026 09:20:16 AM</t>
+          <t>09 Oct 2026 06:57:31 PM</t>
         </is>
       </c>
       <c r="K50" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 12:35:24 PM</t>
+          <t>10 Oct 2026 12:30:17 PM</t>
         </is>
       </c>
       <c r="L50" s="3" t="inlineStr">
@@ -10845,29 +10925,29 @@
       </c>
       <c r="M50" s="3" t="inlineStr">
         <is>
-          <t>5d 3h 15m</t>
+          <t>17h 32m</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>TKT1358952</t>
+          <t>TKT1364848</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>Sanjay Dangol</t>
+          <t>Mayanka Kirana Store</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
@@ -10887,22 +10967,22 @@
       </c>
       <c r="H51" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Sanjeev Giri</t>
+          <t>Case : no light blinking   has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I51" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 12:34:52 PM</t>
+          <t>10 Oct 2026 12:35:23 PM</t>
         </is>
       </c>
       <c r="J51" s="5" t="inlineStr">
         <is>
-          <t>05 Oct 2026 09:20:16 AM</t>
+          <t>09 Oct 2026 05:45:00 PM</t>
         </is>
       </c>
       <c r="K51" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 12:35:24 PM</t>
+          <t>10 Oct 2026 12:35:23 PM</t>
         </is>
       </c>
       <c r="L51" s="5" t="inlineStr">
@@ -10912,19 +10992,19 @@
       </c>
       <c r="M51" s="5" t="inlineStr">
         <is>
-          <t>5d 3h 15m</t>
+          <t>18h 50m</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>TKT1362114</t>
+          <t>TKT1358952</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>Punam shah</t>
+          <t>Sanjay Dangol</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
@@ -10954,22 +11034,22 @@
       </c>
       <c r="H52" s="3" t="inlineStr">
         <is>
-          <t>Case : Wi-Fi 6  has been updated by Sanjeev Giri</t>
+          <t>Case : wifi6  has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I52" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 12:34:03 PM</t>
+          <t>10 Oct 2026 12:34:52 PM</t>
         </is>
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
-          <t>07 Oct 2026 03:17:23 PM</t>
+          <t>05 Oct 2026 09:20:16 AM</t>
         </is>
       </c>
       <c r="K52" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 12:34:03 PM</t>
+          <t>10 Oct 2026 12:35:24 PM</t>
         </is>
       </c>
       <c r="L52" s="3" t="inlineStr">
@@ -10979,19 +11059,19 @@
       </c>
       <c r="M52" s="3" t="inlineStr">
         <is>
-          <t>2d 21h 16m</t>
+          <t>5d 3h 15m</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>TKT1364639</t>
+          <t>TKT1358952</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>Anil Pradhan</t>
+          <t>Sanjay Dangol</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
@@ -11006,12 +11086,12 @@
       </c>
       <c r="E53" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F53" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G53" s="5" t="inlineStr">
@@ -11021,44 +11101,44 @@
       </c>
       <c r="H53" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6 router upgrade   has been updated by Ajit Shrestha</t>
+          <t>Case : wifi6  has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I53" s="5" t="inlineStr">
         <is>
-          <t>09 Oct 2026 03:05:33 PM</t>
+          <t>10 Oct 2026 12:34:52 PM</t>
         </is>
       </c>
       <c r="J53" s="5" t="inlineStr">
         <is>
-          <t>09 Oct 2026 03:05:33 PM</t>
+          <t>05 Oct 2026 09:20:16 AM</t>
         </is>
       </c>
       <c r="K53" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 12:50:22 PM</t>
+          <t>10 Oct 2026 12:35:24 PM</t>
         </is>
       </c>
       <c r="L53" s="5" t="inlineStr">
         <is>
-          <t>21h 44m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M53" s="5" t="inlineStr">
         <is>
-          <t>21h 44m</t>
+          <t>5d 3h 15m</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>TKT1359613</t>
+          <t>TKT1362114</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>lok bahadur malla</t>
+          <t>Punam shah</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
@@ -11093,17 +11173,17 @@
       </c>
       <c r="I54" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 01:46:58 PM</t>
+          <t>10 Oct 2026 12:34:03 PM</t>
         </is>
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
-          <t>05 Oct 2026 04:13:23 PM</t>
+          <t>07 Oct 2026 03:17:23 PM</t>
         </is>
       </c>
       <c r="K54" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 01:46:58 PM</t>
+          <t>10 Oct 2026 12:34:03 PM</t>
         </is>
       </c>
       <c r="L54" s="3" t="inlineStr">
@@ -11113,19 +11193,19 @@
       </c>
       <c r="M54" s="3" t="inlineStr">
         <is>
-          <t>4d 21h 33m</t>
+          <t>2d 21h 16m</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>TKT1363352</t>
+          <t>TKT1364639</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>Rajan Dawadi</t>
+          <t>Anil Pradhan</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
@@ -11155,44 +11235,44 @@
       </c>
       <c r="H55" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Ajit Shrestha</t>
+          <t>Case : wifi 6 router upgrade   has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I55" s="5" t="inlineStr">
         <is>
-          <t>08 Oct 2026 01:21:13 PM</t>
+          <t>09 Oct 2026 03:05:33 PM</t>
         </is>
       </c>
       <c r="J55" s="5" t="inlineStr">
         <is>
-          <t>08 Oct 2026 01:21:13 PM</t>
+          <t>09 Oct 2026 03:05:33 PM</t>
         </is>
       </c>
       <c r="K55" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 02:14:45 PM</t>
+          <t>10 Oct 2026 12:50:22 PM</t>
         </is>
       </c>
       <c r="L55" s="5" t="inlineStr">
         <is>
-          <t>2d 53m</t>
+          <t>21h 44m</t>
         </is>
       </c>
       <c r="M55" s="5" t="inlineStr">
         <is>
-          <t>2d 53m</t>
+          <t>21h 44m</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>TKT1365302</t>
+          <t>TKT1359613</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>Kritika Sah</t>
+          <t>lok bahadur malla</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
@@ -11222,22 +11302,22 @@
       </c>
       <c r="H56" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+          <t>Case : Wi-Fi 6  has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I56" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 02:06:16 PM</t>
+          <t>10 Oct 2026 01:46:58 PM</t>
         </is>
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 10:19:45 AM</t>
+          <t>05 Oct 2026 04:13:23 PM</t>
         </is>
       </c>
       <c r="K56" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 02:06:16 PM</t>
+          <t>10 Oct 2026 01:46:58 PM</t>
         </is>
       </c>
       <c r="L56" s="3" t="inlineStr">
@@ -11247,39 +11327,39 @@
       </c>
       <c r="M56" s="3" t="inlineStr">
         <is>
-          <t>3h 46m</t>
+          <t>4d 21h 33m</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>TKT1365176</t>
+          <t>TKT1363352</t>
         </is>
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>Aafnai Deal Online Shopping Center Pvt Ltd</t>
+          <t>Rajan Dawadi</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>Router Adaptor damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F57" s="5" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G57" s="5" t="inlineStr">
@@ -11289,44 +11369,44 @@
       </c>
       <c r="H57" s="5" t="inlineStr">
         <is>
-          <t>Case : Router faulty   has been updated by Ajit Shrestha</t>
+          <t>Case : wifi6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I57" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 02:40:00 PM</t>
+          <t>08 Oct 2026 01:21:13 PM</t>
         </is>
       </c>
       <c r="J57" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 08:51:05 AM</t>
+          <t>08 Oct 2026 01:21:13 PM</t>
         </is>
       </c>
       <c r="K57" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 02:40:00 PM</t>
+          <t>10 Oct 2026 02:14:45 PM</t>
         </is>
       </c>
       <c r="L57" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>2d 53m</t>
         </is>
       </c>
       <c r="M57" s="5" t="inlineStr">
         <is>
-          <t>5h 48m</t>
+          <t>2d 53m</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>TKT1362110</t>
+          <t>TKT1365302</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>Prem Bahadur Karki</t>
+          <t>Kritika Sah</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
@@ -11341,12 +11421,12 @@
       </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G58" s="3" t="inlineStr">
@@ -11356,44 +11436,44 @@
       </c>
       <c r="H58" s="3" t="inlineStr">
         <is>
-          <t>Case : WiFi 6  has been updated by Ajit Shrestha</t>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I58" s="3" t="inlineStr">
         <is>
-          <t>07 Oct 2026 03:16:15 PM</t>
+          <t>10 Oct 2026 02:06:16 PM</t>
         </is>
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
-          <t>07 Oct 2026 03:16:15 PM</t>
+          <t>10 Oct 2026 10:19:45 AM</t>
         </is>
       </c>
       <c r="K58" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 03:12:56 PM</t>
+          <t>10 Oct 2026 02:06:16 PM</t>
         </is>
       </c>
       <c r="L58" s="3" t="inlineStr">
         <is>
-          <t>2d 23h 56m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M58" s="3" t="inlineStr">
         <is>
-          <t>2d 23h 56m</t>
+          <t>3h 46m</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>TKT1364906</t>
+          <t>TKT1365176</t>
         </is>
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>Pasang sherpa</t>
+          <t>Aafnai Deal Online Shopping Center Pvt Ltd</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
@@ -11403,7 +11483,7 @@
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>Router Adaptor damage Issue</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
@@ -11423,22 +11503,22 @@
       </c>
       <c r="H59" s="5" t="inlineStr">
         <is>
-          <t>Case : iptv issue  has been updated by Sanjeev Giri</t>
+          <t>Case : Router faulty   has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I59" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 03:41:05 PM</t>
+          <t>10 Oct 2026 02:40:00 PM</t>
         </is>
       </c>
       <c r="J59" s="5" t="inlineStr">
         <is>
-          <t>09 Oct 2026 06:55:03 PM</t>
+          <t>10 Oct 2026 08:51:05 AM</t>
         </is>
       </c>
       <c r="K59" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 03:41:05 PM</t>
+          <t>10 Oct 2026 02:40:00 PM</t>
         </is>
       </c>
       <c r="L59" s="5" t="inlineStr">
@@ -11448,19 +11528,19 @@
       </c>
       <c r="M59" s="5" t="inlineStr">
         <is>
-          <t>20h 46m</t>
+          <t>5h 48m</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>TKT1365415</t>
+          <t>TKT1362110</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>Sarmila Sangasarar</t>
+          <t>Prem Bahadur Karki</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
@@ -11475,12 +11555,12 @@
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G60" s="3" t="inlineStr">
@@ -11490,54 +11570,54 @@
       </c>
       <c r="H60" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6 Router   has been updated by Sanjeev Giri</t>
+          <t>Case : WiFi 6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I60" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 03:38:34 PM</t>
+          <t>07 Oct 2026 03:16:15 PM</t>
         </is>
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 11:51:02 AM</t>
+          <t>07 Oct 2026 03:16:15 PM</t>
         </is>
       </c>
       <c r="K60" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 03:38:34 PM</t>
+          <t>10 Oct 2026 03:12:56 PM</t>
         </is>
       </c>
       <c r="L60" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>2d 23h 56m</t>
         </is>
       </c>
       <c r="M60" s="3" t="inlineStr">
         <is>
-          <t>3h 47m</t>
+          <t>2d 23h 56m</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>TKT1365328</t>
+          <t>TKT1364906</t>
         </is>
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>Bishal Shrestha</t>
+          <t>Pasang sherpa</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
@@ -11557,22 +11637,22 @@
       </c>
       <c r="H61" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+          <t>Case : iptv issue  has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I61" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 03:04:54 PM</t>
+          <t>10 Oct 2026 03:41:05 PM</t>
         </is>
       </c>
       <c r="J61" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 10:37:42 AM</t>
+          <t>09 Oct 2026 06:55:03 PM</t>
         </is>
       </c>
       <c r="K61" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 03:04:54 PM</t>
+          <t>10 Oct 2026 03:41:05 PM</t>
         </is>
       </c>
       <c r="L61" s="5" t="inlineStr">
@@ -11582,29 +11662,29 @@
       </c>
       <c r="M61" s="5" t="inlineStr">
         <is>
-          <t>4h 27m</t>
+          <t>20h 46m</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>TKT1364260</t>
+          <t>TKT1365415</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>Suresh Raut</t>
+          <t>Sarmila Sangasarar</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>SKYCOM-Welcome Screen Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E62" s="3" t="inlineStr">
@@ -11619,27 +11699,27 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>Case : IPTV issue  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H62" s="3" t="inlineStr">
         <is>
-          <t>Case : IPTV issue  has been updated by Chandramani Tharu</t>
+          <t>Case : wifi 6 Router   has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I62" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 03:41:47 PM</t>
+          <t>10 Oct 2026 03:38:34 PM</t>
         </is>
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
-          <t>09 Oct 2026 10:21:21 AM</t>
+          <t>10 Oct 2026 11:51:02 AM</t>
         </is>
       </c>
       <c r="K62" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 03:41:47 PM</t>
+          <t>10 Oct 2026 03:38:34 PM</t>
         </is>
       </c>
       <c r="L62" s="3" t="inlineStr">
@@ -11649,29 +11729,29 @@
       </c>
       <c r="M62" s="3" t="inlineStr">
         <is>
-          <t>1d 5h 20m</t>
+          <t>3h 47m</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>TKT1364260</t>
+          <t>TKT1365328</t>
         </is>
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>Suresh Raut</t>
+          <t>Bishal Shrestha</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>SKYCOM-Welcome Screen Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E63" s="5" t="inlineStr">
@@ -11686,27 +11766,27 @@
       </c>
       <c r="G63" s="5" t="inlineStr">
         <is>
-          <t>Case : frequent disconnection issue   has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H63" s="5" t="inlineStr">
         <is>
-          <t>Case : frequent disconnection issue   has been updated by Chandramani Tharu</t>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I63" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 03:41:47 PM</t>
+          <t>10 Oct 2026 03:04:54 PM</t>
         </is>
       </c>
       <c r="J63" s="5" t="inlineStr">
         <is>
-          <t>09 Oct 2026 10:21:21 AM</t>
+          <t>10 Oct 2026 10:37:42 AM</t>
         </is>
       </c>
       <c r="K63" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 03:41:47 PM</t>
+          <t>10 Oct 2026 03:04:54 PM</t>
         </is>
       </c>
       <c r="L63" s="5" t="inlineStr">
@@ -11716,74 +11796,275 @@
       </c>
       <c r="M63" s="5" t="inlineStr">
         <is>
-          <t>1d 5h 20m</t>
+          <t>4h 27m</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
+          <t>TKT1364260</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>Suresh Raut</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="D64" s="3" t="inlineStr">
+        <is>
+          <t>SKYCOM-Welcome Screen Issue</t>
+        </is>
+      </c>
+      <c r="E64" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F64" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G64" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H64" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV issue  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I64" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 03:41:47 PM</t>
+        </is>
+      </c>
+      <c r="J64" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 10:21:21 AM</t>
+        </is>
+      </c>
+      <c r="K64" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 03:41:47 PM</t>
+        </is>
+      </c>
+      <c r="L64" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M64" s="3" t="inlineStr">
+        <is>
+          <t>1d 5h 20m</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="5" t="inlineStr">
+        <is>
+          <t>TKT1364260</t>
+        </is>
+      </c>
+      <c r="B65" s="5" t="inlineStr">
+        <is>
+          <t>Suresh Raut</t>
+        </is>
+      </c>
+      <c r="C65" s="5" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="D65" s="5" t="inlineStr">
+        <is>
+          <t>SKYCOM-Welcome Screen Issue</t>
+        </is>
+      </c>
+      <c r="E65" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F65" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G65" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H65" s="5" t="inlineStr">
+        <is>
+          <t>Case : frequent disconnection issue   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I65" s="5" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 03:41:47 PM</t>
+        </is>
+      </c>
+      <c r="J65" s="5" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 10:21:21 AM</t>
+        </is>
+      </c>
+      <c r="K65" s="5" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 03:41:47 PM</t>
+        </is>
+      </c>
+      <c r="L65" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M65" s="5" t="inlineStr">
+        <is>
+          <t>1d 5h 20m</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="3" t="inlineStr">
+        <is>
           <t>TKT1359002</t>
         </is>
       </c>
-      <c r="B64" s="3" t="inlineStr">
+      <c r="B66" s="3" t="inlineStr">
         <is>
           <t>Dinesh Thakur</t>
         </is>
       </c>
-      <c r="C64" s="3" t="inlineStr">
+      <c r="C66" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="D64" s="3" t="inlineStr">
+      <c r="D66" s="3" t="inlineStr">
         <is>
           <t>Router placement CR</t>
         </is>
       </c>
-      <c r="E64" s="3" t="inlineStr">
+      <c r="E66" s="3" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
       </c>
-      <c r="F64" s="3" t="inlineStr">
+      <c r="F66" s="3" t="inlineStr">
         <is>
           <t>Completed (Closed)</t>
         </is>
       </c>
-      <c r="G64" s="3" t="inlineStr">
+      <c r="G66" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H66" s="3" t="inlineStr">
         <is>
           <t>Case : router change   has been updated by Chandramani Tharu</t>
         </is>
       </c>
-      <c r="H64" s="3" t="inlineStr">
-        <is>
-          <t>Case : router change   has been updated by Chandramani Tharu</t>
-        </is>
-      </c>
-      <c r="I64" s="3" t="inlineStr">
+      <c r="I66" s="3" t="inlineStr">
         <is>
           <t>10 Oct 2026 03:27:45 PM</t>
         </is>
       </c>
-      <c r="J64" s="3" t="inlineStr">
+      <c r="J66" s="3" t="inlineStr">
         <is>
           <t>05 Oct 2026 10:04:47 AM</t>
         </is>
       </c>
-      <c r="K64" s="3" t="inlineStr">
+      <c r="K66" s="3" t="inlineStr">
         <is>
           <t>10 Oct 2026 03:34:04 PM</t>
         </is>
       </c>
-      <c r="L64" s="3" t="inlineStr">
+      <c r="L66" s="3" t="inlineStr">
         <is>
           <t>6m</t>
         </is>
       </c>
-      <c r="M64" s="3" t="inlineStr">
+      <c r="M66" s="3" t="inlineStr">
         <is>
           <t>5d 5h 29m</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t>TKT1365547</t>
+        </is>
+      </c>
+      <c r="B67" s="5" t="inlineStr">
+        <is>
+          <t>Prabin Chaudhary</t>
+        </is>
+      </c>
+      <c r="C67" s="5" t="inlineStr">
+        <is>
+          <t>Frequent Internet Disconnection</t>
+        </is>
+      </c>
+      <c r="D67" s="5" t="inlineStr">
+        <is>
+          <t>Due to Optical Power flapping</t>
+        </is>
+      </c>
+      <c r="E67" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F67" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G67" s="5" t="inlineStr">
+        <is>
+          <t>Case : Frequent disconnection   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="H67" s="5" t="inlineStr">
+        <is>
+          <t>Case : Frequent disconnection   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I67" s="5" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 04:03:46 PM</t>
+        </is>
+      </c>
+      <c r="J67" s="5" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 01:31:20 PM</t>
+        </is>
+      </c>
+      <c r="K67" s="5" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 04:03:46 PM</t>
+        </is>
+      </c>
+      <c r="L67" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M67" s="5" t="inlineStr">
+        <is>
+          <t>2h 32m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_10_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_10_Oct_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -9094,10 +9094,8 @@
           <t>Prabin Chaudhary</t>
         </is>
       </c>
-      <c r="O45" s="3" t="inlineStr">
-        <is>
-          <t>9746625579</t>
-        </is>
+      <c r="O45" s="3" t="n">
+        <v>9746625579</v>
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
@@ -9187,10 +9185,8 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN45" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN45" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO45" s="3" t="inlineStr">
         <is>
@@ -9201,7 +9197,7 @@
       <c r="AQ45" s="3" t="inlineStr"/>
       <c r="AR45" s="3" t="inlineStr">
         <is>
-          <t>Case : Frequent disconnection   has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS45" s="3" t="inlineStr">
@@ -9250,7 +9246,7 @@
     <col width="33" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -12034,7 +12030,7 @@
       </c>
       <c r="G67" s="5" t="inlineStr">
         <is>
-          <t>Case : Frequent disconnection   has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H67" s="5" t="inlineStr">

--- a/audit_report_ALL_TEAM_10_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_10_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW45"/>
+  <dimension ref="A1:AW48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -9226,6 +9226,631 @@
         </is>
       </c>
     </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 4:35 PM</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="inlineStr"/>
+      <c r="H46" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I46" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>TKT1365327</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t>dipa baral ghimire</t>
+        </is>
+      </c>
+      <c r="L46" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N46" s="3" t="inlineStr">
+        <is>
+          <t>dipa baral ghimire</t>
+        </is>
+      </c>
+      <c r="O46" s="3" t="inlineStr">
+        <is>
+          <t>9851325162</t>
+        </is>
+      </c>
+      <c r="P46" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q46" s="3" t="inlineStr"/>
+      <c r="R46" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 04:35:28 PM</t>
+        </is>
+      </c>
+      <c r="S46" s="3" t="inlineStr"/>
+      <c r="T46" s="3" t="inlineStr"/>
+      <c r="U46" s="3" t="inlineStr">
+        <is>
+          <t>CHB9851325162</t>
+        </is>
+      </c>
+      <c r="V46" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 10:35:40 AM</t>
+        </is>
+      </c>
+      <c r="W46" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 04:35:28 PM</t>
+        </is>
+      </c>
+      <c r="X46" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y46" s="3" t="inlineStr"/>
+      <c r="Z46" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA46" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB46" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC46" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD46" s="3" t="inlineStr"/>
+      <c r="AE46" s="3" t="inlineStr">
+        <is>
+          <t>6 Saraswatinagar Rd - Building Kathmandu 44600, Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF46" s="3" t="inlineStr">
+        <is>
+          <t>9851325162@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG46" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH46" s="3" t="inlineStr"/>
+      <c r="AI46" s="3" t="inlineStr">
+        <is>
+          <t>06:00 hour</t>
+        </is>
+      </c>
+      <c r="AJ46" s="3" t="inlineStr"/>
+      <c r="AK46" s="3" t="inlineStr"/>
+      <c r="AL46" s="3" t="inlineStr">
+        <is>
+          <t>Bipana Neupane</t>
+        </is>
+      </c>
+      <c r="AM46" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN46" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO46" s="3" t="inlineStr">
+        <is>
+          <t>4,9</t>
+        </is>
+      </c>
+      <c r="AP46" s="3" t="inlineStr"/>
+      <c r="AQ46" s="3" t="inlineStr"/>
+      <c r="AR46" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS46" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT46" s="3" t="inlineStr">
+        <is>
+          <t>5h 59m</t>
+        </is>
+      </c>
+      <c r="AU46" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV46" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW46" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 4:34 PM</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F47" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G47" s="3" t="inlineStr"/>
+      <c r="H47" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I47" s="3" t="inlineStr">
+        <is>
+          <t>Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="J47" s="3" t="inlineStr">
+        <is>
+          <t>TKT1361715</t>
+        </is>
+      </c>
+      <c r="K47" s="3" t="inlineStr">
+        <is>
+          <t>Sujan Subedi</t>
+        </is>
+      </c>
+      <c r="L47" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M47" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N47" s="3" t="inlineStr">
+        <is>
+          <t>Sujan Subedi</t>
+        </is>
+      </c>
+      <c r="O47" s="3" t="inlineStr">
+        <is>
+          <t>9808592524</t>
+        </is>
+      </c>
+      <c r="P47" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q47" s="3" t="inlineStr"/>
+      <c r="R47" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 04:49:55 PM</t>
+        </is>
+      </c>
+      <c r="S47" s="3" t="inlineStr"/>
+      <c r="T47" s="3" t="inlineStr"/>
+      <c r="U47" s="3" t="inlineStr">
+        <is>
+          <t>9808592524</t>
+        </is>
+      </c>
+      <c r="V47" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 11:35:33 AM</t>
+        </is>
+      </c>
+      <c r="W47" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 04:34:38 PM</t>
+        </is>
+      </c>
+      <c r="X47" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y47" s="3" t="inlineStr">
+        <is>
+          <t>27.69354</t>
+        </is>
+      </c>
+      <c r="Z47" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA47" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB47" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC47" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD47" s="3" t="inlineStr"/>
+      <c r="AE47" s="3" t="inlineStr">
+        <is>
+          <t>Kalanki Near By Learning Realm International School,14, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF47" s="3" t="inlineStr">
+        <is>
+          <t>sujansubedi180@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG47" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH47" s="3" t="inlineStr"/>
+      <c r="AI47" s="3" t="inlineStr">
+        <is>
+          <t>10:58 hour</t>
+        </is>
+      </c>
+      <c r="AJ47" s="3" t="inlineStr"/>
+      <c r="AK47" s="3" t="inlineStr"/>
+      <c r="AL47" s="3" t="inlineStr">
+        <is>
+          <t>Susmita Thapa</t>
+        </is>
+      </c>
+      <c r="AM47" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN47" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO47" s="3" t="inlineStr">
+        <is>
+          <t>2,9</t>
+        </is>
+      </c>
+      <c r="AP47" s="3" t="inlineStr">
+        <is>
+          <t>85.27727</t>
+        </is>
+      </c>
+      <c r="AQ47" s="3" t="inlineStr"/>
+      <c r="AR47" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS47" s="3" t="inlineStr">
+        <is>
+          <t>23h 44m</t>
+        </is>
+      </c>
+      <c r="AT47" s="3" t="inlineStr">
+        <is>
+          <t>3d 4h 59m</t>
+        </is>
+      </c>
+      <c r="AU47" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV47" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW47" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 4:33 PM</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F48" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G48" s="3" t="inlineStr"/>
+      <c r="H48" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I48" s="3" t="inlineStr">
+        <is>
+          <t>Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>TKT1361715</t>
+        </is>
+      </c>
+      <c r="K48" s="3" t="inlineStr">
+        <is>
+          <t>Sujan Subedi</t>
+        </is>
+      </c>
+      <c r="L48" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M48" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N48" s="3" t="inlineStr">
+        <is>
+          <t>Sujan Subedi</t>
+        </is>
+      </c>
+      <c r="O48" s="3" t="inlineStr">
+        <is>
+          <t>9808592524</t>
+        </is>
+      </c>
+      <c r="P48" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q48" s="3" t="inlineStr"/>
+      <c r="R48" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 04:49:55 PM</t>
+        </is>
+      </c>
+      <c r="S48" s="3" t="inlineStr"/>
+      <c r="T48" s="3" t="inlineStr"/>
+      <c r="U48" s="3" t="inlineStr">
+        <is>
+          <t>9808592524</t>
+        </is>
+      </c>
+      <c r="V48" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 11:35:33 AM</t>
+        </is>
+      </c>
+      <c r="W48" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 04:34:38 PM</t>
+        </is>
+      </c>
+      <c r="X48" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y48" s="3" t="inlineStr">
+        <is>
+          <t>27.69354</t>
+        </is>
+      </c>
+      <c r="Z48" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA48" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB48" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC48" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD48" s="3" t="inlineStr"/>
+      <c r="AE48" s="3" t="inlineStr">
+        <is>
+          <t>Kalanki Near By Learning Realm International School,14, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF48" s="3" t="inlineStr">
+        <is>
+          <t>sujansubedi180@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG48" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH48" s="3" t="inlineStr"/>
+      <c r="AI48" s="3" t="inlineStr">
+        <is>
+          <t>10:58 hour</t>
+        </is>
+      </c>
+      <c r="AJ48" s="3" t="inlineStr"/>
+      <c r="AK48" s="3" t="inlineStr"/>
+      <c r="AL48" s="3" t="inlineStr">
+        <is>
+          <t>Susmita Thapa</t>
+        </is>
+      </c>
+      <c r="AM48" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN48" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO48" s="3" t="inlineStr">
+        <is>
+          <t>2,9</t>
+        </is>
+      </c>
+      <c r="AP48" s="3" t="inlineStr">
+        <is>
+          <t>85.27727</t>
+        </is>
+      </c>
+      <c r="AQ48" s="3" t="inlineStr"/>
+      <c r="AR48" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS48" s="3" t="inlineStr">
+        <is>
+          <t>23h 44m</t>
+        </is>
+      </c>
+      <c r="AT48" s="3" t="inlineStr">
+        <is>
+          <t>3d 4h 59m</t>
+        </is>
+      </c>
+      <c r="AU48" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV48" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW48" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9237,7 +9862,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M67"/>
+  <dimension ref="A1:M70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -9246,7 +9871,7 @@
     <col width="33" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -9274,7 +9899,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="3">
@@ -9284,7 +9909,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4">
@@ -9295,7 +9920,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>76.6%</t>
         </is>
       </c>
     </row>
@@ -9307,7 +9932,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>17h 2m</t>
+          <t>16h 56m</t>
         </is>
       </c>
     </row>
@@ -9319,7 +9944,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>2d 10h 31m</t>
+          <t>2d 10h 5m</t>
         </is>
       </c>
     </row>
@@ -9378,14 +10003,14 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>86.2%</t>
+          <t>87.5%</t>
         </is>
       </c>
     </row>
@@ -9545,14 +10170,14 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>85.7%</t>
+          <t>87.1%</t>
         </is>
       </c>
     </row>
@@ -12064,6 +12689,207 @@
         </is>
       </c>
     </row>
+    <row r="68">
+      <c r="A68" s="3" t="inlineStr">
+        <is>
+          <t>TKT1365327</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t>dipa baral ghimire</t>
+        </is>
+      </c>
+      <c r="C68" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D68" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E68" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F68" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G68" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="H68" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I68" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 04:35:28 PM</t>
+        </is>
+      </c>
+      <c r="J68" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 10:35:40 AM</t>
+        </is>
+      </c>
+      <c r="K68" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 04:35:28 PM</t>
+        </is>
+      </c>
+      <c r="L68" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M68" s="3" t="inlineStr">
+        <is>
+          <t>5h 59m</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="5" t="inlineStr">
+        <is>
+          <t>TKT1361715</t>
+        </is>
+      </c>
+      <c r="B69" s="5" t="inlineStr">
+        <is>
+          <t>Sujan Subedi</t>
+        </is>
+      </c>
+      <c r="C69" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D69" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E69" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F69" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G69" s="5" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="H69" s="5" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I69" s="5" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 04:49:55 PM</t>
+        </is>
+      </c>
+      <c r="J69" s="5" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 11:35:33 AM</t>
+        </is>
+      </c>
+      <c r="K69" s="5" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 04:34:38 PM</t>
+        </is>
+      </c>
+      <c r="L69" s="5" t="inlineStr">
+        <is>
+          <t>23h 44m</t>
+        </is>
+      </c>
+      <c r="M69" s="5" t="inlineStr">
+        <is>
+          <t>3d 4h 59m</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="inlineStr">
+        <is>
+          <t>TKT1361715</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="inlineStr">
+        <is>
+          <t>Sujan Subedi</t>
+        </is>
+      </c>
+      <c r="C70" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D70" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E70" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F70" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G70" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="H70" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I70" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 04:49:55 PM</t>
+        </is>
+      </c>
+      <c r="J70" s="3" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 11:35:33 AM</t>
+        </is>
+      </c>
+      <c r="K70" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 04:34:38 PM</t>
+        </is>
+      </c>
+      <c r="L70" s="3" t="inlineStr">
+        <is>
+          <t>23h 44m</t>
+        </is>
+      </c>
+      <c r="M70" s="3" t="inlineStr">
+        <is>
+          <t>3d 4h 59m</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/audit_report_ALL_TEAM_10_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_10_Oct_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -9293,10 +9293,8 @@
           <t>dipa baral ghimire</t>
         </is>
       </c>
-      <c r="O46" s="3" t="inlineStr">
-        <is>
-          <t>9851325162</t>
-        </is>
+      <c r="O46" s="3" t="n">
+        <v>9851325162</v>
       </c>
       <c r="P46" s="3" t="inlineStr">
         <is>
@@ -9386,10 +9384,8 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN46" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN46" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO46" s="3" t="inlineStr">
         <is>
@@ -9400,7 +9396,7 @@
       <c r="AQ46" s="3" t="inlineStr"/>
       <c r="AR46" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS46" s="3" t="inlineStr">
@@ -9496,10 +9492,8 @@
           <t>Sujan Subedi</t>
         </is>
       </c>
-      <c r="O47" s="3" t="inlineStr">
-        <is>
-          <t>9808592524</t>
-        </is>
+      <c r="O47" s="3" t="n">
+        <v>9808592524</v>
       </c>
       <c r="P47" s="3" t="inlineStr">
         <is>
@@ -9593,25 +9587,21 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN47" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN47" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO47" s="3" t="inlineStr">
         <is>
           <t>2,9</t>
         </is>
       </c>
-      <c r="AP47" s="3" t="inlineStr">
-        <is>
-          <t>85.27727</t>
-        </is>
+      <c r="AP47" s="3" t="n">
+        <v>85.27727</v>
       </c>
       <c r="AQ47" s="3" t="inlineStr"/>
       <c r="AR47" s="3" t="inlineStr">
         <is>
-          <t>Case : Wi-Fi 6  has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS47" s="3" t="inlineStr">
@@ -9707,10 +9697,8 @@
           <t>Sujan Subedi</t>
         </is>
       </c>
-      <c r="O48" s="3" t="inlineStr">
-        <is>
-          <t>9808592524</t>
-        </is>
+      <c r="O48" s="3" t="n">
+        <v>9808592524</v>
       </c>
       <c r="P48" s="3" t="inlineStr">
         <is>
@@ -9804,25 +9792,21 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN48" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN48" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO48" s="3" t="inlineStr">
         <is>
           <t>2,9</t>
         </is>
       </c>
-      <c r="AP48" s="3" t="inlineStr">
-        <is>
-          <t>85.27727</t>
-        </is>
+      <c r="AP48" s="3" t="n">
+        <v>85.27727</v>
       </c>
       <c r="AQ48" s="3" t="inlineStr"/>
       <c r="AR48" s="3" t="inlineStr">
         <is>
-          <t>Case : Wi-Fi 6  has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS48" s="3" t="inlineStr">
@@ -9871,7 +9855,7 @@
     <col width="33" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -12722,7 +12706,7 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H68" s="3" t="inlineStr">
@@ -12789,7 +12773,7 @@
       </c>
       <c r="G69" s="5" t="inlineStr">
         <is>
-          <t>Case : Wi-Fi 6  has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H69" s="5" t="inlineStr">
@@ -12856,7 +12840,7 @@
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>Case : Wi-Fi 6  has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H70" s="3" t="inlineStr">

--- a/audit_report_ALL_TEAM_10_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_10_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW48"/>
+  <dimension ref="A1:AW49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -9835,6 +9835,221 @@
         </is>
       </c>
     </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 5:13 PM</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F49" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G49" s="3" t="inlineStr"/>
+      <c r="H49" s="3" t="inlineStr">
+        <is>
+          <t>Case : No signal   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I49" s="3" t="inlineStr">
+        <is>
+          <t>No signal</t>
+        </is>
+      </c>
+      <c r="J49" s="3" t="inlineStr">
+        <is>
+          <t>TKT1364939</t>
+        </is>
+      </c>
+      <c r="K49" s="3" t="inlineStr">
+        <is>
+          <t>Navraj Shrestha</t>
+        </is>
+      </c>
+      <c r="L49" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M49" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N49" s="3" t="inlineStr">
+        <is>
+          <t>Navraj Shrestha</t>
+        </is>
+      </c>
+      <c r="O49" s="3" t="inlineStr">
+        <is>
+          <t>9769760515</t>
+        </is>
+      </c>
+      <c r="P49" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="Q49" s="3" t="inlineStr"/>
+      <c r="R49" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 05:13:24 PM</t>
+        </is>
+      </c>
+      <c r="S49" s="3" t="inlineStr"/>
+      <c r="T49" s="3" t="inlineStr"/>
+      <c r="U49" s="3" t="inlineStr">
+        <is>
+          <t>9851007028</t>
+        </is>
+      </c>
+      <c r="V49" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 07:29:44 PM</t>
+        </is>
+      </c>
+      <c r="W49" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 05:13:24 PM</t>
+        </is>
+      </c>
+      <c r="X49" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y49" s="3" t="inlineStr">
+        <is>
+          <t>27.715288</t>
+        </is>
+      </c>
+      <c r="Z49" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="AA49" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB49" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC49" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD49" s="3" t="inlineStr"/>
+      <c r="AE49" s="3" t="inlineStr">
+        <is>
+          <t>Dallu Swoyambhu bhagwan,Swoyambhu Bhagwan Pau , Swayambhu Cir Rd, Kathmandu, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF49" s="3" t="inlineStr">
+        <is>
+          <t>navraj.shrestha22@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG49" s="3" t="inlineStr">
+        <is>
+          <t>SKYCOM-Blank TV Display</t>
+        </is>
+      </c>
+      <c r="AH49" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI49" s="3" t="inlineStr">
+        <is>
+          <t>07:44 hour</t>
+        </is>
+      </c>
+      <c r="AJ49" s="3" t="inlineStr"/>
+      <c r="AK49" s="3" t="inlineStr"/>
+      <c r="AL49" s="3" t="inlineStr">
+        <is>
+          <t>Sudip Khadka</t>
+        </is>
+      </c>
+      <c r="AM49" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN49" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO49" s="3" t="inlineStr">
+        <is>
+          <t>2,15</t>
+        </is>
+      </c>
+      <c r="AP49" s="3" t="inlineStr">
+        <is>
+          <t>85.293141</t>
+        </is>
+      </c>
+      <c r="AQ49" s="3" t="inlineStr"/>
+      <c r="AR49" s="3" t="inlineStr">
+        <is>
+          <t>Case : No signal   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS49" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT49" s="3" t="inlineStr">
+        <is>
+          <t>21h 43m</t>
+        </is>
+      </c>
+      <c r="AU49" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV49" s="3" t="inlineStr">
+        <is>
+          <t>Case : No signal   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW49" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9846,7 +10061,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M70"/>
+  <dimension ref="A1:M72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -9855,7 +10070,7 @@
     <col width="33" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -9883,7 +10098,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3">
@@ -9893,7 +10108,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4">
@@ -9904,7 +10119,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>76.6%</t>
+          <t>77.1%</t>
         </is>
       </c>
     </row>
@@ -9916,7 +10131,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>16h 56m</t>
+          <t>16h 28m</t>
         </is>
       </c>
     </row>
@@ -9928,7 +10143,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>2d 10h 5m</t>
+          <t>2d 9h 6m</t>
         </is>
       </c>
     </row>
@@ -10023,14 +10238,14 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="C13" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="C13" s="5" t="n">
-        <v>3</v>
-      </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>80.0%</t>
         </is>
       </c>
     </row>
@@ -10311,14 +10526,14 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>SKYCOM-Welcome Screen Issue</t>
+          <t>SKYCOM-Blank TV Display</t>
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
@@ -10329,215 +10544,171 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>Slow Internet Connection</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>Video content is Buffering</t>
+          <t>SKYCOM-Welcome Screen Issue</t>
         </is>
       </c>
       <c r="C29" s="5" t="n">
         <v>2</v>
       </c>
       <c r="D29" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>Wi-Fi Range</t>
+          <t>Slow Internet Connection</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Low Wi-Fi Range on both band</t>
+          <t>Video content is Buffering</t>
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="5" t="inlineStr"/>
-      <c r="B31" s="5" t="inlineStr"/>
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>Wi-Fi Range</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>Low Wi-Fi Range on both band</t>
+        </is>
+      </c>
       <c r="C31" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D31" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr"/>
+      <c r="B32" s="3" t="inlineStr"/>
+      <c r="C32" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D31" s="5" t="n">
+      <c r="D32" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E31" s="5" t="inlineStr">
+      <c r="E32" s="3" t="inlineStr">
         <is>
           <t>nan%</t>
         </is>
       </c>
     </row>
-    <row r="32"/>
-    <row r="33">
-      <c r="A33" s="6" t="inlineStr">
+    <row r="33"/>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="4" t="inlineStr">
-        <is>
-          <t>Ticket Number</t>
-        </is>
-      </c>
-      <c r="B34" s="4" t="inlineStr">
-        <is>
-          <t>Account Name</t>
-        </is>
-      </c>
-      <c r="C34" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D34" s="4" t="inlineStr">
-        <is>
-          <t>Sub Category</t>
-        </is>
-      </c>
-      <c r="E34" s="4" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="F34" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Type</t>
-        </is>
-      </c>
-      <c r="G34" s="4" t="inlineStr">
-        <is>
-          <t>Employee Remark / Solution Note</t>
-        </is>
-      </c>
-      <c r="H34" s="4" t="inlineStr">
-        <is>
-          <t>Action / Transfer Remark</t>
-        </is>
-      </c>
-      <c r="I34" s="4" t="inlineStr">
-        <is>
-          <t>Assigned Date</t>
-        </is>
-      </c>
-      <c r="J34" s="4" t="inlineStr">
-        <is>
-          <t>Created Date</t>
-        </is>
-      </c>
-      <c r="K34" s="4" t="inlineStr">
-        <is>
-          <t>Last Modified Date</t>
-        </is>
-      </c>
-      <c r="L34" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Assigned)</t>
-        </is>
-      </c>
-      <c r="M34" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="5" t="inlineStr">
-        <is>
-          <t>TKT1364446</t>
-        </is>
-      </c>
-      <c r="B35" s="5" t="inlineStr">
-        <is>
-          <t>Jeet Bahadur Basnet</t>
-        </is>
-      </c>
-      <c r="C35" s="5" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D35" s="5" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E35" s="5" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F35" s="5" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G35" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H35" s="5" t="inlineStr">
-        <is>
-          <t>Case : upgrade wifi 6  has been updated by Sabin Giri</t>
-        </is>
-      </c>
-      <c r="I35" s="5" t="inlineStr">
-        <is>
-          <t>10 Oct 2026 10:40:59 AM</t>
-        </is>
-      </c>
-      <c r="J35" s="5" t="inlineStr">
-        <is>
-          <t>09 Oct 2026 12:30:31 PM</t>
-        </is>
-      </c>
-      <c r="K35" s="5" t="inlineStr">
-        <is>
-          <t>10 Oct 2026 10:40:59 AM</t>
-        </is>
-      </c>
-      <c r="L35" s="5" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M35" s="5" t="inlineStr">
-        <is>
-          <t>22h 10m</t>
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>Ticket Number</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>Account Name</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>Sub Category</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Type</t>
+        </is>
+      </c>
+      <c r="G35" s="4" t="inlineStr">
+        <is>
+          <t>Employee Remark / Solution Note</t>
+        </is>
+      </c>
+      <c r="H35" s="4" t="inlineStr">
+        <is>
+          <t>Action / Transfer Remark</t>
+        </is>
+      </c>
+      <c r="I35" s="4" t="inlineStr">
+        <is>
+          <t>Assigned Date</t>
+        </is>
+      </c>
+      <c r="J35" s="4" t="inlineStr">
+        <is>
+          <t>Created Date</t>
+        </is>
+      </c>
+      <c r="K35" s="4" t="inlineStr">
+        <is>
+          <t>Last Modified Date</t>
+        </is>
+      </c>
+      <c r="L35" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Assigned)</t>
+        </is>
+      </c>
+      <c r="M35" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>TKT1364411</t>
+          <t>TKT1364446</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Bijya Lama</t>
+          <t>Jeet Bahadur Basnet</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
@@ -10567,22 +10738,22 @@
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 upgrade   has been updated by Sabin Giri</t>
+          <t>Case : upgrade wifi 6  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 10:40:30 AM</t>
+          <t>10 Oct 2026 10:40:59 AM</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>09 Oct 2026 12:06:35 PM</t>
+          <t>09 Oct 2026 12:30:31 PM</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 10:40:30 AM</t>
+          <t>10 Oct 2026 10:40:59 AM</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
@@ -10592,19 +10763,19 @@
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>22h 33m</t>
+          <t>22h 10m</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>TKT1357376</t>
+          <t>TKT1364411</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>Goma Adhikari</t>
+          <t>Bijya Lama</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
@@ -10634,22 +10805,22 @@
       </c>
       <c r="H37" s="5" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 upgrade   has been updated by Sanjeev Giri</t>
+          <t>Case : Wifi 6 upgrade   has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I37" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 10:49:43 AM</t>
+          <t>10 Oct 2026 10:40:30 AM</t>
         </is>
       </c>
       <c r="J37" s="5" t="inlineStr">
         <is>
-          <t>04 Oct 2026 08:51:00 AM</t>
+          <t>09 Oct 2026 12:06:35 PM</t>
         </is>
       </c>
       <c r="K37" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 10:49:43 AM</t>
+          <t>10 Oct 2026 10:40:30 AM</t>
         </is>
       </c>
       <c r="L37" s="5" t="inlineStr">
@@ -10659,19 +10830,19 @@
       </c>
       <c r="M37" s="5" t="inlineStr">
         <is>
-          <t>6d 1h 58m</t>
+          <t>22h 33m</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>TKT1358035</t>
+          <t>TKT1357376</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Saurav Lamsal</t>
+          <t>Goma Adhikari</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
@@ -10686,12 +10857,12 @@
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
@@ -10701,32 +10872,32 @@
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+          <t>Case : Wifi 6 upgrade   has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>04 Oct 2026 02:07:16 PM</t>
+          <t>10 Oct 2026 10:49:43 AM</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>04 Oct 2026 02:07:16 PM</t>
+          <t>04 Oct 2026 08:51:00 AM</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 11:04:09 AM</t>
+          <t>10 Oct 2026 10:49:43 AM</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t>5d 20h 56m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>5d 20h 56m</t>
+          <t>6d 1h 58m</t>
         </is>
       </c>
     </row>
@@ -10800,12 +10971,12 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>TKT1364756</t>
+          <t>TKT1358035</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>New Assist Traders</t>
+          <t>Saurav Lamsal</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
@@ -10820,12 +10991,12 @@
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
@@ -10835,44 +11006,44 @@
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Chandramani Tharu</t>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 11:15:36 AM</t>
+          <t>04 Oct 2026 02:07:16 PM</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>09 Oct 2026 04:33:35 PM</t>
+          <t>04 Oct 2026 02:07:16 PM</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 11:15:36 AM</t>
+          <t>10 Oct 2026 11:04:09 AM</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>5d 20h 56m</t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>18h 42m</t>
+          <t>5d 20h 56m</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>TKT1358080</t>
+          <t>TKT1364756</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>Baburaja Maharjan</t>
+          <t>New Assist Traders</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
@@ -10907,17 +11078,17 @@
       </c>
       <c r="I41" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 11:13:31 AM</t>
+          <t>10 Oct 2026 11:15:36 AM</t>
         </is>
       </c>
       <c r="J41" s="5" t="inlineStr">
         <is>
-          <t>04 Oct 2026 02:29:39 PM</t>
+          <t>09 Oct 2026 04:33:35 PM</t>
         </is>
       </c>
       <c r="K41" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 11:13:31 AM</t>
+          <t>10 Oct 2026 11:15:36 AM</t>
         </is>
       </c>
       <c r="L41" s="5" t="inlineStr">
@@ -10927,19 +11098,19 @@
       </c>
       <c r="M41" s="5" t="inlineStr">
         <is>
-          <t>5d 20h 43m</t>
+          <t>18h 42m</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>TKT1359556</t>
+          <t>TKT1358080</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>Puspa KC</t>
+          <t>Baburaja Maharjan</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
@@ -10969,22 +11140,22 @@
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t>Case : router upgrade  has been updated by Sabin Giri</t>
+          <t>Case : wifi6  has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 11:23:36 AM</t>
+          <t>10 Oct 2026 11:13:31 AM</t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>05 Oct 2026 03:34:34 PM</t>
+          <t>04 Oct 2026 02:29:39 PM</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 11:23:36 AM</t>
+          <t>10 Oct 2026 11:13:31 AM</t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
@@ -10994,19 +11165,19 @@
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t>4d 19h 49m</t>
+          <t>5d 20h 43m</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>TKT1365031</t>
+          <t>TKT1359556</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>Prem Kumar Shrestha</t>
+          <t>Puspa KC</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
@@ -11036,22 +11207,22 @@
       </c>
       <c r="H43" s="5" t="inlineStr">
         <is>
-          <t>Case : WiFi 6   has been updated by Sanjeev Giri</t>
+          <t>Case : router upgrade  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I43" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 11:41:30 AM</t>
+          <t>10 Oct 2026 11:23:36 AM</t>
         </is>
       </c>
       <c r="J43" s="5" t="inlineStr">
         <is>
-          <t>09 Oct 2026 09:56:52 PM</t>
+          <t>05 Oct 2026 03:34:34 PM</t>
         </is>
       </c>
       <c r="K43" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 11:41:30 AM</t>
+          <t>10 Oct 2026 11:23:36 AM</t>
         </is>
       </c>
       <c r="L43" s="5" t="inlineStr">
@@ -11061,19 +11232,19 @@
       </c>
       <c r="M43" s="5" t="inlineStr">
         <is>
-          <t>13h 44m</t>
+          <t>4d 19h 49m</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>TKT1362058</t>
+          <t>TKT1365031</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>Gyan Chiraniya</t>
+          <t>Prem Kumar Shrestha</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
@@ -11088,12 +11259,12 @@
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
@@ -11103,32 +11274,32 @@
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t>Case : For upgradation to wifi6   has been updated by Ajit Shrestha</t>
+          <t>Case : WiFi 6   has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t>07 Oct 2026 02:43:23 PM</t>
+          <t>10 Oct 2026 11:41:30 AM</t>
         </is>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>07 Oct 2026 02:43:23 PM</t>
+          <t>09 Oct 2026 09:56:52 PM</t>
         </is>
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 11:36:00 AM</t>
+          <t>10 Oct 2026 11:41:30 AM</t>
         </is>
       </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
-          <t>2d 20h 52m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t>2d 20h 52m</t>
+          <t>13h 44m</t>
         </is>
       </c>
     </row>
@@ -11202,12 +11373,12 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>TKT1362055</t>
+          <t>TKT1362058</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>Ravi Shahi</t>
+          <t>Gyan Chiraniya</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
@@ -11222,12 +11393,12 @@
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
@@ -11237,54 +11408,54 @@
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t>Case : For upgradation to wifi6   has been updated by Chandramani Tharu</t>
+          <t>Case : For upgradation to wifi6   has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 11:53:17 AM</t>
+          <t>07 Oct 2026 02:43:23 PM</t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>07 Oct 2026 02:42:05 PM</t>
+          <t>07 Oct 2026 02:43:23 PM</t>
         </is>
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 11:53:17 AM</t>
+          <t>10 Oct 2026 11:36:00 AM</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>2d 20h 52m</t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t>2d 21h 11m</t>
+          <t>2d 20h 52m</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>TKT1364261</t>
+          <t>TKT1362055</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>Niratna manandhar</t>
+          <t>Ravi Shahi</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>NETTV-Welcome Screen Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -11304,22 +11475,22 @@
       </c>
       <c r="H47" s="5" t="inlineStr">
         <is>
-          <t>Case : NETTV issue  has been updated by Ajit Shrestha</t>
+          <t>Case : For upgradation to wifi6   has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I47" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 12:00:52 PM</t>
+          <t>10 Oct 2026 11:53:17 AM</t>
         </is>
       </c>
       <c r="J47" s="5" t="inlineStr">
         <is>
-          <t>09 Oct 2026 10:23:09 AM</t>
+          <t>07 Oct 2026 02:42:05 PM</t>
         </is>
       </c>
       <c r="K47" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 12:00:52 PM</t>
+          <t>10 Oct 2026 11:53:17 AM</t>
         </is>
       </c>
       <c r="L47" s="5" t="inlineStr">
@@ -11329,29 +11500,29 @@
       </c>
       <c r="M47" s="5" t="inlineStr">
         <is>
-          <t>1d 1h 37m</t>
+          <t>2d 21h 11m</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>TKT1360378</t>
+          <t>TKT1364261</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>Maheshwor Maharjan</t>
+          <t>Niratna manandhar</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>NETTV-Welcome Screen Issue</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr">
@@ -11371,22 +11542,22 @@
       </c>
       <c r="H48" s="3" t="inlineStr">
         <is>
-          <t>Case :   has been updated by Sanjeev Giri</t>
+          <t>Case : NETTV issue  has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I48" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 12:04:10 PM</t>
+          <t>10 Oct 2026 12:00:52 PM</t>
         </is>
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>06 Oct 2026 10:49:38 AM</t>
+          <t>09 Oct 2026 10:23:09 AM</t>
         </is>
       </c>
       <c r="K48" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 12:04:10 PM</t>
+          <t>10 Oct 2026 12:00:52 PM</t>
         </is>
       </c>
       <c r="L48" s="3" t="inlineStr">
@@ -11396,29 +11567,29 @@
       </c>
       <c r="M48" s="3" t="inlineStr">
         <is>
-          <t>4d 1h 14m</t>
+          <t>1d 1h 37m</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>TKT1365280</t>
+          <t>TKT1360378</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>Atul Ali</t>
+          <t>Maheshwor Maharjan</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>Wi-Fi Range</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>Low Wi-Fi Range on both band</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
@@ -11438,22 +11609,22 @@
       </c>
       <c r="H49" s="5" t="inlineStr">
         <is>
-          <t>Case : low wifi range issue  has been updated by Sabin Giri</t>
+          <t>Case :   has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I49" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 12:06:57 PM</t>
+          <t>10 Oct 2026 12:04:10 PM</t>
         </is>
       </c>
       <c r="J49" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 10:00:04 AM</t>
+          <t>06 Oct 2026 10:49:38 AM</t>
         </is>
       </c>
       <c r="K49" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 12:06:57 PM</t>
+          <t>10 Oct 2026 12:04:10 PM</t>
         </is>
       </c>
       <c r="L49" s="5" t="inlineStr">
@@ -11463,29 +11634,29 @@
       </c>
       <c r="M49" s="5" t="inlineStr">
         <is>
-          <t>2h 6m</t>
+          <t>4d 1h 14m</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>TKT1364910</t>
+          <t>TKT1365280</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>Ayush Duwal</t>
+          <t>Atul Ali</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Wi-Fi Range</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Low Wi-Fi Range on both band</t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr">
@@ -11505,22 +11676,22 @@
       </c>
       <c r="H50" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Sabin Giri</t>
+          <t>Case : low wifi range issue  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I50" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 12:30:17 PM</t>
+          <t>10 Oct 2026 12:06:57 PM</t>
         </is>
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
-          <t>09 Oct 2026 06:57:31 PM</t>
+          <t>10 Oct 2026 10:00:04 AM</t>
         </is>
       </c>
       <c r="K50" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 12:30:17 PM</t>
+          <t>10 Oct 2026 12:06:57 PM</t>
         </is>
       </c>
       <c r="L50" s="3" t="inlineStr">
@@ -11530,29 +11701,29 @@
       </c>
       <c r="M50" s="3" t="inlineStr">
         <is>
-          <t>17h 32m</t>
+          <t>2h 6m</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>TKT1364848</t>
+          <t>TKT1364910</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>Mayanka Kirana Store</t>
+          <t>Ayush Duwal</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
@@ -11572,22 +11743,22 @@
       </c>
       <c r="H51" s="5" t="inlineStr">
         <is>
-          <t>Case : no light blinking   has been updated by Sabin Giri</t>
+          <t>Case : wifi6  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I51" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 12:35:23 PM</t>
+          <t>10 Oct 2026 12:30:17 PM</t>
         </is>
       </c>
       <c r="J51" s="5" t="inlineStr">
         <is>
-          <t>09 Oct 2026 05:45:00 PM</t>
+          <t>09 Oct 2026 06:57:31 PM</t>
         </is>
       </c>
       <c r="K51" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 12:35:23 PM</t>
+          <t>10 Oct 2026 12:30:17 PM</t>
         </is>
       </c>
       <c r="L51" s="5" t="inlineStr">
@@ -11597,29 +11768,29 @@
       </c>
       <c r="M51" s="5" t="inlineStr">
         <is>
-          <t>18h 50m</t>
+          <t>17h 32m</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>TKT1358952</t>
+          <t>TKT1364848</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>Sanjay Dangol</t>
+          <t>Mayanka Kirana Store</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr">
@@ -11639,22 +11810,22 @@
       </c>
       <c r="H52" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Sanjeev Giri</t>
+          <t>Case : no light blinking   has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I52" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 12:34:52 PM</t>
+          <t>10 Oct 2026 12:35:23 PM</t>
         </is>
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
-          <t>05 Oct 2026 09:20:16 AM</t>
+          <t>09 Oct 2026 05:45:00 PM</t>
         </is>
       </c>
       <c r="K52" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 12:35:24 PM</t>
+          <t>10 Oct 2026 12:35:23 PM</t>
         </is>
       </c>
       <c r="L52" s="3" t="inlineStr">
@@ -11664,7 +11835,7 @@
       </c>
       <c r="M52" s="3" t="inlineStr">
         <is>
-          <t>5d 3h 15m</t>
+          <t>18h 50m</t>
         </is>
       </c>
     </row>
@@ -11738,12 +11909,12 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>TKT1362114</t>
+          <t>TKT1358952</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>Punam shah</t>
+          <t>Sanjay Dangol</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
@@ -11773,22 +11944,22 @@
       </c>
       <c r="H54" s="3" t="inlineStr">
         <is>
-          <t>Case : Wi-Fi 6  has been updated by Sanjeev Giri</t>
+          <t>Case : wifi6  has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I54" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 12:34:03 PM</t>
+          <t>10 Oct 2026 12:34:52 PM</t>
         </is>
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
-          <t>07 Oct 2026 03:17:23 PM</t>
+          <t>05 Oct 2026 09:20:16 AM</t>
         </is>
       </c>
       <c r="K54" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 12:34:03 PM</t>
+          <t>10 Oct 2026 12:35:24 PM</t>
         </is>
       </c>
       <c r="L54" s="3" t="inlineStr">
@@ -11798,19 +11969,19 @@
       </c>
       <c r="M54" s="3" t="inlineStr">
         <is>
-          <t>2d 21h 16m</t>
+          <t>5d 3h 15m</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>TKT1364639</t>
+          <t>TKT1362114</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>Anil Pradhan</t>
+          <t>Punam shah</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
@@ -11825,12 +11996,12 @@
       </c>
       <c r="E55" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F55" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G55" s="5" t="inlineStr">
@@ -11840,44 +12011,44 @@
       </c>
       <c r="H55" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6 router upgrade   has been updated by Ajit Shrestha</t>
+          <t>Case : Wi-Fi 6  has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I55" s="5" t="inlineStr">
         <is>
-          <t>09 Oct 2026 03:05:33 PM</t>
+          <t>10 Oct 2026 12:34:03 PM</t>
         </is>
       </c>
       <c r="J55" s="5" t="inlineStr">
         <is>
-          <t>09 Oct 2026 03:05:33 PM</t>
+          <t>07 Oct 2026 03:17:23 PM</t>
         </is>
       </c>
       <c r="K55" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 12:50:22 PM</t>
+          <t>10 Oct 2026 12:34:03 PM</t>
         </is>
       </c>
       <c r="L55" s="5" t="inlineStr">
         <is>
-          <t>21h 44m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M55" s="5" t="inlineStr">
         <is>
-          <t>21h 44m</t>
+          <t>2d 21h 16m</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>TKT1359613</t>
+          <t>TKT1364639</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>lok bahadur malla</t>
+          <t>Anil Pradhan</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
@@ -11892,12 +12063,12 @@
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F56" s="3" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G56" s="3" t="inlineStr">
@@ -11907,44 +12078,44 @@
       </c>
       <c r="H56" s="3" t="inlineStr">
         <is>
-          <t>Case : Wi-Fi 6  has been updated by Sanjeev Giri</t>
+          <t>Case : wifi 6 router upgrade   has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I56" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 01:46:58 PM</t>
+          <t>09 Oct 2026 03:05:33 PM</t>
         </is>
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
-          <t>05 Oct 2026 04:13:23 PM</t>
+          <t>09 Oct 2026 03:05:33 PM</t>
         </is>
       </c>
       <c r="K56" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 01:46:58 PM</t>
+          <t>10 Oct 2026 12:50:22 PM</t>
         </is>
       </c>
       <c r="L56" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>21h 44m</t>
         </is>
       </c>
       <c r="M56" s="3" t="inlineStr">
         <is>
-          <t>4d 21h 33m</t>
+          <t>21h 44m</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>TKT1363352</t>
+          <t>TKT1359613</t>
         </is>
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>Rajan Dawadi</t>
+          <t>lok bahadur malla</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
@@ -11959,12 +12130,12 @@
       </c>
       <c r="E57" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F57" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G57" s="5" t="inlineStr">
@@ -11974,44 +12145,44 @@
       </c>
       <c r="H57" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Ajit Shrestha</t>
+          <t>Case : Wi-Fi 6  has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I57" s="5" t="inlineStr">
         <is>
-          <t>08 Oct 2026 01:21:13 PM</t>
+          <t>10 Oct 2026 01:46:58 PM</t>
         </is>
       </c>
       <c r="J57" s="5" t="inlineStr">
         <is>
-          <t>08 Oct 2026 01:21:13 PM</t>
+          <t>05 Oct 2026 04:13:23 PM</t>
         </is>
       </c>
       <c r="K57" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 02:14:45 PM</t>
+          <t>10 Oct 2026 01:46:58 PM</t>
         </is>
       </c>
       <c r="L57" s="5" t="inlineStr">
         <is>
-          <t>2d 53m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M57" s="5" t="inlineStr">
         <is>
-          <t>2d 53m</t>
+          <t>4d 21h 33m</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>TKT1365302</t>
+          <t>TKT1363352</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>Kritika Sah</t>
+          <t>Rajan Dawadi</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
@@ -12026,12 +12197,12 @@
       </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G58" s="3" t="inlineStr">
@@ -12041,54 +12212,54 @@
       </c>
       <c r="H58" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+          <t>Case : wifi6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I58" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 02:06:16 PM</t>
+          <t>08 Oct 2026 01:21:13 PM</t>
         </is>
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 10:19:45 AM</t>
+          <t>08 Oct 2026 01:21:13 PM</t>
         </is>
       </c>
       <c r="K58" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 02:06:16 PM</t>
+          <t>10 Oct 2026 02:14:45 PM</t>
         </is>
       </c>
       <c r="L58" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>2d 53m</t>
         </is>
       </c>
       <c r="M58" s="3" t="inlineStr">
         <is>
-          <t>3h 46m</t>
+          <t>2d 53m</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>TKT1365176</t>
+          <t>TKT1365302</t>
         </is>
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>Aafnai Deal Online Shopping Center Pvt Ltd</t>
+          <t>Kritika Sah</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>Router Adaptor damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
@@ -12108,22 +12279,22 @@
       </c>
       <c r="H59" s="5" t="inlineStr">
         <is>
-          <t>Case : Router faulty   has been updated by Ajit Shrestha</t>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I59" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 02:40:00 PM</t>
+          <t>10 Oct 2026 02:06:16 PM</t>
         </is>
       </c>
       <c r="J59" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 08:51:05 AM</t>
+          <t>10 Oct 2026 10:19:45 AM</t>
         </is>
       </c>
       <c r="K59" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 02:40:00 PM</t>
+          <t>10 Oct 2026 02:06:16 PM</t>
         </is>
       </c>
       <c r="L59" s="5" t="inlineStr">
@@ -12133,39 +12304,39 @@
       </c>
       <c r="M59" s="5" t="inlineStr">
         <is>
-          <t>5h 48m</t>
+          <t>3h 46m</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>TKT1362110</t>
+          <t>TKT1365176</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>Prem Bahadur Karki</t>
+          <t>Aafnai Deal Online Shopping Center Pvt Ltd</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Router Adaptor damage Issue</t>
         </is>
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G60" s="3" t="inlineStr">
@@ -12175,64 +12346,64 @@
       </c>
       <c r="H60" s="3" t="inlineStr">
         <is>
-          <t>Case : WiFi 6  has been updated by Ajit Shrestha</t>
+          <t>Case : Router faulty   has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I60" s="3" t="inlineStr">
         <is>
-          <t>07 Oct 2026 03:16:15 PM</t>
+          <t>10 Oct 2026 02:40:00 PM</t>
         </is>
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
-          <t>07 Oct 2026 03:16:15 PM</t>
+          <t>10 Oct 2026 08:51:05 AM</t>
         </is>
       </c>
       <c r="K60" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 03:12:56 PM</t>
+          <t>10 Oct 2026 02:40:00 PM</t>
         </is>
       </c>
       <c r="L60" s="3" t="inlineStr">
         <is>
-          <t>2d 23h 56m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M60" s="3" t="inlineStr">
         <is>
-          <t>2d 23h 56m</t>
+          <t>5h 48m</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>TKT1364906</t>
+          <t>TKT1362110</t>
         </is>
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>Pasang sherpa</t>
+          <t>Prem Bahadur Karki</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F61" s="5" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G61" s="5" t="inlineStr">
@@ -12242,54 +12413,54 @@
       </c>
       <c r="H61" s="5" t="inlineStr">
         <is>
-          <t>Case : iptv issue  has been updated by Sanjeev Giri</t>
+          <t>Case : WiFi 6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I61" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 03:41:05 PM</t>
+          <t>07 Oct 2026 03:16:15 PM</t>
         </is>
       </c>
       <c r="J61" s="5" t="inlineStr">
         <is>
-          <t>09 Oct 2026 06:55:03 PM</t>
+          <t>07 Oct 2026 03:16:15 PM</t>
         </is>
       </c>
       <c r="K61" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 03:41:05 PM</t>
+          <t>10 Oct 2026 03:12:56 PM</t>
         </is>
       </c>
       <c r="L61" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>2d 23h 56m</t>
         </is>
       </c>
       <c r="M61" s="5" t="inlineStr">
         <is>
-          <t>20h 46m</t>
+          <t>2d 23h 56m</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>TKT1365415</t>
+          <t>TKT1364906</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>Sarmila Sangasarar</t>
+          <t>Pasang sherpa</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="E62" s="3" t="inlineStr">
@@ -12309,22 +12480,22 @@
       </c>
       <c r="H62" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6 Router   has been updated by Sanjeev Giri</t>
+          <t>Case : iptv issue  has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I62" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 03:38:34 PM</t>
+          <t>10 Oct 2026 03:41:05 PM</t>
         </is>
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 11:51:02 AM</t>
+          <t>09 Oct 2026 06:55:03 PM</t>
         </is>
       </c>
       <c r="K62" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 03:38:34 PM</t>
+          <t>10 Oct 2026 03:41:05 PM</t>
         </is>
       </c>
       <c r="L62" s="3" t="inlineStr">
@@ -12334,19 +12505,19 @@
       </c>
       <c r="M62" s="3" t="inlineStr">
         <is>
-          <t>3h 47m</t>
+          <t>20h 46m</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>TKT1365328</t>
+          <t>TKT1365415</t>
         </is>
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>Bishal Shrestha</t>
+          <t>Sarmila Sangasarar</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
@@ -12376,22 +12547,22 @@
       </c>
       <c r="H63" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+          <t>Case : wifi 6 Router   has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I63" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 03:04:54 PM</t>
+          <t>10 Oct 2026 03:38:34 PM</t>
         </is>
       </c>
       <c r="J63" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 10:37:42 AM</t>
+          <t>10 Oct 2026 11:51:02 AM</t>
         </is>
       </c>
       <c r="K63" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 03:04:54 PM</t>
+          <t>10 Oct 2026 03:38:34 PM</t>
         </is>
       </c>
       <c r="L63" s="5" t="inlineStr">
@@ -12401,29 +12572,29 @@
       </c>
       <c r="M63" s="5" t="inlineStr">
         <is>
-          <t>4h 27m</t>
+          <t>3h 47m</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>TKT1364260</t>
+          <t>TKT1365328</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>Suresh Raut</t>
+          <t>Bishal Shrestha</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
-          <t>SKYCOM-Welcome Screen Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E64" s="3" t="inlineStr">
@@ -12443,22 +12614,22 @@
       </c>
       <c r="H64" s="3" t="inlineStr">
         <is>
-          <t>Case : IPTV issue  has been updated by Chandramani Tharu</t>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I64" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 03:41:47 PM</t>
+          <t>10 Oct 2026 03:04:54 PM</t>
         </is>
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
-          <t>09 Oct 2026 10:21:21 AM</t>
+          <t>10 Oct 2026 10:37:42 AM</t>
         </is>
       </c>
       <c r="K64" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 03:41:47 PM</t>
+          <t>10 Oct 2026 03:04:54 PM</t>
         </is>
       </c>
       <c r="L64" s="3" t="inlineStr">
@@ -12468,7 +12639,7 @@
       </c>
       <c r="M64" s="3" t="inlineStr">
         <is>
-          <t>1d 5h 20m</t>
+          <t>4h 27m</t>
         </is>
       </c>
     </row>
@@ -12510,7 +12681,7 @@
       </c>
       <c r="H65" s="5" t="inlineStr">
         <is>
-          <t>Case : frequent disconnection issue   has been updated by Chandramani Tharu</t>
+          <t>Case : IPTV issue  has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I65" s="5" t="inlineStr">
@@ -12542,32 +12713,32 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>TKT1359002</t>
+          <t>TKT1364260</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>Dinesh Thakur</t>
+          <t>Suresh Raut</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
-          <t>Router placement CR</t>
+          <t>SKYCOM-Welcome Screen Issue</t>
         </is>
       </c>
       <c r="E66" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F66" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G66" s="3" t="inlineStr">
@@ -12577,64 +12748,64 @@
       </c>
       <c r="H66" s="3" t="inlineStr">
         <is>
-          <t>Case : router change   has been updated by Chandramani Tharu</t>
+          <t>Case : frequent disconnection issue   has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I66" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 03:27:45 PM</t>
+          <t>10 Oct 2026 03:41:47 PM</t>
         </is>
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
-          <t>05 Oct 2026 10:04:47 AM</t>
+          <t>09 Oct 2026 10:21:21 AM</t>
         </is>
       </c>
       <c r="K66" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 03:34:04 PM</t>
+          <t>10 Oct 2026 03:41:47 PM</t>
         </is>
       </c>
       <c r="L66" s="3" t="inlineStr">
         <is>
-          <t>6m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M66" s="3" t="inlineStr">
         <is>
-          <t>5d 5h 29m</t>
+          <t>1d 5h 20m</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>TKT1365547</t>
+          <t>TKT1359002</t>
         </is>
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>Prabin Chaudhary</t>
+          <t>Dinesh Thakur</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>Frequent Internet Disconnection</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>Due to Optical Power flapping</t>
+          <t>Router placement CR</t>
         </is>
       </c>
       <c r="E67" s="5" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F67" s="5" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G67" s="5" t="inlineStr">
@@ -12644,54 +12815,54 @@
       </c>
       <c r="H67" s="5" t="inlineStr">
         <is>
-          <t>Case : Frequent disconnection   has been updated by Ajit Shrestha</t>
+          <t>Case : router change   has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I67" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 04:03:46 PM</t>
+          <t>10 Oct 2026 03:27:45 PM</t>
         </is>
       </c>
       <c r="J67" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 01:31:20 PM</t>
+          <t>05 Oct 2026 10:04:47 AM</t>
         </is>
       </c>
       <c r="K67" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 04:03:46 PM</t>
+          <t>10 Oct 2026 03:34:04 PM</t>
         </is>
       </c>
       <c r="L67" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>6m</t>
         </is>
       </c>
       <c r="M67" s="5" t="inlineStr">
         <is>
-          <t>2h 32m</t>
+          <t>5d 5h 29m</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>TKT1365327</t>
+          <t>TKT1365547</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>dipa baral ghimire</t>
+          <t>Prabin Chaudhary</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Frequent Internet Disconnection</t>
         </is>
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Due to Optical Power flapping</t>
         </is>
       </c>
       <c r="E68" s="3" t="inlineStr">
@@ -12711,22 +12882,22 @@
       </c>
       <c r="H68" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+          <t>Case : Frequent disconnection   has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I68" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 04:35:28 PM</t>
+          <t>10 Oct 2026 04:03:46 PM</t>
         </is>
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 10:35:40 AM</t>
+          <t>10 Oct 2026 01:31:20 PM</t>
         </is>
       </c>
       <c r="K68" s="3" t="inlineStr">
         <is>
-          <t>10 Oct 2026 04:35:28 PM</t>
+          <t>10 Oct 2026 04:03:46 PM</t>
         </is>
       </c>
       <c r="L68" s="3" t="inlineStr">
@@ -12736,19 +12907,19 @@
       </c>
       <c r="M68" s="3" t="inlineStr">
         <is>
-          <t>5h 59m</t>
+          <t>2h 32m</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>TKT1361715</t>
+          <t>TKT1365327</t>
         </is>
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>Sujan Subedi</t>
+          <t>dipa baral ghimire</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
@@ -12763,12 +12934,12 @@
       </c>
       <c r="E69" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F69" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G69" s="5" t="inlineStr">
@@ -12778,32 +12949,32 @@
       </c>
       <c r="H69" s="5" t="inlineStr">
         <is>
-          <t>Case : Wi-Fi 6  has been updated by Ajit Shrestha</t>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I69" s="5" t="inlineStr">
         <is>
-          <t>09 Oct 2026 04:49:55 PM</t>
+          <t>10 Oct 2026 04:35:28 PM</t>
         </is>
       </c>
       <c r="J69" s="5" t="inlineStr">
         <is>
-          <t>07 Oct 2026 11:35:33 AM</t>
+          <t>10 Oct 2026 10:35:40 AM</t>
         </is>
       </c>
       <c r="K69" s="5" t="inlineStr">
         <is>
-          <t>10 Oct 2026 04:34:38 PM</t>
+          <t>10 Oct 2026 04:35:28 PM</t>
         </is>
       </c>
       <c r="L69" s="5" t="inlineStr">
         <is>
-          <t>23h 44m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M69" s="5" t="inlineStr">
         <is>
-          <t>3d 4h 59m</t>
+          <t>5h 59m</t>
         </is>
       </c>
     </row>
@@ -12871,6 +13042,140 @@
       <c r="M70" s="3" t="inlineStr">
         <is>
           <t>3d 4h 59m</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="5" t="inlineStr">
+        <is>
+          <t>TKT1361715</t>
+        </is>
+      </c>
+      <c r="B71" s="5" t="inlineStr">
+        <is>
+          <t>Sujan Subedi</t>
+        </is>
+      </c>
+      <c r="C71" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D71" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E71" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F71" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G71" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H71" s="5" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I71" s="5" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 04:49:55 PM</t>
+        </is>
+      </c>
+      <c r="J71" s="5" t="inlineStr">
+        <is>
+          <t>07 Oct 2026 11:35:33 AM</t>
+        </is>
+      </c>
+      <c r="K71" s="5" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 04:34:38 PM</t>
+        </is>
+      </c>
+      <c r="L71" s="5" t="inlineStr">
+        <is>
+          <t>23h 44m</t>
+        </is>
+      </c>
+      <c r="M71" s="5" t="inlineStr">
+        <is>
+          <t>3d 4h 59m</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>TKT1364939</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr">
+        <is>
+          <t>Navraj Shrestha</t>
+        </is>
+      </c>
+      <c r="C72" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="D72" s="3" t="inlineStr">
+        <is>
+          <t>SKYCOM-Blank TV Display</t>
+        </is>
+      </c>
+      <c r="E72" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F72" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G72" s="3" t="inlineStr">
+        <is>
+          <t>Case : No signal   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="H72" s="3" t="inlineStr">
+        <is>
+          <t>Case : No signal   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I72" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 05:13:24 PM</t>
+        </is>
+      </c>
+      <c r="J72" s="3" t="inlineStr">
+        <is>
+          <t>09 Oct 2026 07:29:44 PM</t>
+        </is>
+      </c>
+      <c r="K72" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 05:13:24 PM</t>
+        </is>
+      </c>
+      <c r="L72" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M72" s="3" t="inlineStr">
+        <is>
+          <t>21h 43m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_10_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_10_Oct_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -9902,10 +9902,8 @@
           <t>Navraj Shrestha</t>
         </is>
       </c>
-      <c r="O49" s="3" t="inlineStr">
-        <is>
-          <t>9769760515</t>
-        </is>
+      <c r="O49" s="3" t="n">
+        <v>9769760515</v>
       </c>
       <c r="P49" s="3" t="inlineStr">
         <is>
@@ -9981,10 +9979,8 @@
           <t>SKYCOM-Blank TV Display</t>
         </is>
       </c>
-      <c r="AH49" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH49" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI49" s="3" t="inlineStr">
         <is>
@@ -10003,25 +9999,21 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN49" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN49" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO49" s="3" t="inlineStr">
         <is>
           <t>2,15</t>
         </is>
       </c>
-      <c r="AP49" s="3" t="inlineStr">
-        <is>
-          <t>85.293141</t>
-        </is>
+      <c r="AP49" s="3" t="n">
+        <v>85.29314100000001</v>
       </c>
       <c r="AQ49" s="3" t="inlineStr"/>
       <c r="AR49" s="3" t="inlineStr">
         <is>
-          <t>Case : No signal   has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS49" s="3" t="inlineStr">
@@ -10070,7 +10062,7 @@
     <col width="33" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -13145,7 +13137,7 @@
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>Case : No signal   has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H72" s="3" t="inlineStr">

--- a/audit_report_ALL_TEAM_10_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_10_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW49"/>
+  <dimension ref="A1:AW50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -497,7 +497,7 @@
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="40" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
     <col width="40" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
@@ -529,10 +529,10 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
-    <col width="32" customWidth="1" min="47" max="47"/>
+    <col width="36" customWidth="1" min="47" max="47"/>
     <col width="40" customWidth="1" min="48" max="48"/>
     <col width="25" customWidth="1" min="49" max="49"/>
   </cols>
@@ -10042,6 +10042,217 @@
         </is>
       </c>
     </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 6:38 PM</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F50" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G50" s="3" t="inlineStr"/>
+      <c r="H50" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router upgrade   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I50" s="3" t="inlineStr">
+        <is>
+          <t>Router upgrade</t>
+        </is>
+      </c>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>TKT1355718</t>
+        </is>
+      </c>
+      <c r="K50" s="3" t="inlineStr">
+        <is>
+          <t>Nilam Karki Basnet</t>
+        </is>
+      </c>
+      <c r="L50" s="3" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="M50" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N50" s="3" t="inlineStr">
+        <is>
+          <t>Nilam Karki Basnet</t>
+        </is>
+      </c>
+      <c r="O50" s="3" t="inlineStr">
+        <is>
+          <t>9841258917</t>
+        </is>
+      </c>
+      <c r="P50" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q50" s="3" t="inlineStr"/>
+      <c r="R50" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 06:38:07 PM</t>
+        </is>
+      </c>
+      <c r="S50" s="3" t="inlineStr"/>
+      <c r="T50" s="3" t="inlineStr"/>
+      <c r="U50" s="3" t="inlineStr">
+        <is>
+          <t>nilambasnet</t>
+        </is>
+      </c>
+      <c r="V50" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 05:34:53 PM</t>
+        </is>
+      </c>
+      <c r="W50" s="3" t="inlineStr">
+        <is>
+          <t>10 Oct 2026 06:38:07 PM</t>
+        </is>
+      </c>
+      <c r="X50" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y50" s="3" t="inlineStr">
+        <is>
+          <t>27.67657</t>
+        </is>
+      </c>
+      <c r="Z50" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA50" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB50" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC50" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD50" s="3" t="inlineStr"/>
+      <c r="AE50" s="3" t="inlineStr">
+        <is>
+          <t>Lalitpur, Dhobighat, near by  Progress Boys Hostel, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF50" s="3" t="inlineStr">
+        <is>
+          <t>javanbansent71@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG50" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH50" s="3" t="inlineStr"/>
+      <c r="AI50" s="3" t="inlineStr">
+        <is>
+          <t>18:18 hour</t>
+        </is>
+      </c>
+      <c r="AJ50" s="3" t="inlineStr"/>
+      <c r="AK50" s="3" t="inlineStr"/>
+      <c r="AL50" s="3" t="inlineStr">
+        <is>
+          <t>Susmita Thapa</t>
+        </is>
+      </c>
+      <c r="AM50" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN50" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO50" s="3" t="inlineStr">
+        <is>
+          <t>1,2</t>
+        </is>
+      </c>
+      <c r="AP50" s="3" t="inlineStr">
+        <is>
+          <t>85.30774</t>
+        </is>
+      </c>
+      <c r="AQ50" s="3" t="inlineStr"/>
+      <c r="AR50" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router upgrade   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS50" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT50" s="3" t="inlineStr">
+        <is>
+          <t>8d 1h 3m</t>
+        </is>
+      </c>
+      <c r="AU50" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (In Progress)</t>
+        </is>
+      </c>
+      <c r="AV50" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router upgrade   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW50" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10090,7 +10301,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3">
@@ -10111,7 +10322,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>77.1%</t>
+          <t>75.5%</t>
         </is>
       </c>
     </row>
@@ -10194,14 +10405,14 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C11" s="5" t="n">
         <v>28</v>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>87.5%</t>
+          <t>84.8%</t>
         </is>
       </c>
     </row>
@@ -10361,14 +10572,14 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D21" s="5" t="n">
         <v>27</v>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>87.1%</t>
+          <t>84.4%</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_10_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_10_Oct_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -10109,10 +10109,8 @@
           <t>Nilam Karki Basnet</t>
         </is>
       </c>
-      <c r="O50" s="3" t="inlineStr">
-        <is>
-          <t>9841258917</t>
-        </is>
+      <c r="O50" s="3" t="n">
+        <v>9841258917</v>
       </c>
       <c r="P50" s="3" t="inlineStr">
         <is>
@@ -10206,25 +10204,21 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN50" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN50" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO50" s="3" t="inlineStr">
         <is>
           <t>1,2</t>
         </is>
       </c>
-      <c r="AP50" s="3" t="inlineStr">
-        <is>
-          <t>85.30774</t>
-        </is>
+      <c r="AP50" s="3" t="n">
+        <v>85.30774</v>
       </c>
       <c r="AQ50" s="3" t="inlineStr"/>
       <c r="AR50" s="3" t="inlineStr">
         <is>
-          <t>Case : Router upgrade   has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS50" s="3" t="inlineStr">
